--- a/reports/Selenium Report.xlsx
+++ b/reports/Selenium Report.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F401"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,41 +419,42 @@
         <v>Remarks</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>TC001</v>
+        <v>TC-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Citizen login and dashboard access</v>
+        <v>Valid citizen demo login</v>
       </c>
       <c r="C2" t="str">
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>2.34 sec</v>
+        <v>4.51 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-29T17:53:07.467Z</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Success</v>
+        <v>2026-07-31T11:18:33.058Z</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
+  (Session info: chrome=150.0.7871.187)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TC002</v>
+        <v>TC-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Volunteer login and volunteer dashboard access</v>
+        <v>Valid volunteer demo login</v>
       </c>
       <c r="C3" t="str">
         <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>2.13 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-29T17:53:09.595Z</v>
+        <v>2026-07-31T11:18:33.059Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -461,19 +462,19 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>TC003</v>
+        <v>TC-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Admin login and admin dashboard access</v>
+        <v>Valid admin demo login</v>
       </c>
       <c r="C4" t="str">
         <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>2.19 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-29T17:53:11.789Z</v>
+        <v>2026-07-31T11:18:33.059Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -481,19 +482,19 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>TC004</v>
+        <v>TC-INV-1</v>
       </c>
       <c r="B5" t="str">
-        <v>Failed login shows inline error</v>
+        <v>Empty email &amp; password</v>
       </c>
       <c r="C5" t="str">
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>2.25 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-29T17:53:14.034Z</v>
+        <v>2026-07-31T11:18:33.059Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -501,19 +502,19 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TC005</v>
+        <v>TC-INV-2</v>
       </c>
       <c r="B6" t="str">
-        <v>Forgot password validation message</v>
+        <v>Malformed email format (no @)</v>
       </c>
       <c r="C6" t="str">
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>1.41 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-29T17:53:15.442Z</v>
+        <v>2026-07-31T11:18:33.059Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -521,19 +522,19 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TC006</v>
+        <v>TC-INV-3</v>
       </c>
       <c r="B7" t="str">
-        <v>Registration page can be reached</v>
+        <v>Incomplete email format</v>
       </c>
       <c r="C7" t="str">
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>1.35 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-29T17:53:16.788Z</v>
+        <v>2026-07-31T11:18:33.059Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -541,19 +542,19 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>TC007</v>
+        <v>TC-INV-4</v>
       </c>
       <c r="B8" t="str">
-        <v>Landing page loads</v>
+        <v>Extremely long credentials</v>
       </c>
       <c r="C8" t="str">
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>1.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-29T17:53:18.583Z</v>
+        <v>2026-07-31T11:18:33.059Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -561,27 +562,7867 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>TC008</v>
+        <v>TC-INV-5</v>
       </c>
       <c r="B9" t="str">
-        <v>Protected route redirects unauthenticated users</v>
+        <v>SQL injection pattern in fields</v>
       </c>
       <c r="C9" t="str">
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>1.40 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-29T17:53:19.985Z</v>
+        <v>2026-07-31T11:18:33.059Z</v>
       </c>
       <c r="F9" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TC-INV-6</v>
+      </c>
+      <c r="B10" t="str">
+        <v>XSS injection payload</v>
+      </c>
+      <c r="C10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D10" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E10" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>TC-GEN-1001</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Whitespace email and whitespace password (1)</v>
+      </c>
+      <c r="C11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D11" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E11" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TC-GEN-1002</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Tagged email format with invalid password (2)</v>
+      </c>
+      <c r="C12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D12" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E12" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TC-GEN-1003</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Varying length long emails and long passwords (3)</v>
+      </c>
+      <c r="C13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D13" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E13" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TC-GEN-1004</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Password containing special characters !#$%^</v>
+      </c>
+      <c r="C14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D14" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E14" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TC-GEN-1005</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Fuzzing with database query snippets (5)</v>
+      </c>
+      <c r="C15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D15" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E15" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TC-GEN-1006</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Nonexistent email with standard password pattern (6)</v>
+      </c>
+      <c r="C16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D16" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TC-GEN-1007</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Whitespace email and whitespace password (7)</v>
+      </c>
+      <c r="C17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D17" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TC-GEN-1008</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Tagged email format with invalid password (8)</v>
+      </c>
+      <c r="C18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D18" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E18" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TC-GEN-1009</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Varying length long emails and long passwords (9)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D19" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E19" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TC-GEN-1010</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D20" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E20" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TC-GEN-1011</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Fuzzing with database query snippets (11)</v>
+      </c>
+      <c r="C21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D21" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E21" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC-GEN-1012</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Nonexistent email with standard password pattern (12)</v>
+      </c>
+      <c r="C22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D22" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E22" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC-GEN-1013</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Whitespace email and whitespace password (13)</v>
+      </c>
+      <c r="C23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D23" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E23" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC-GEN-1014</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Tagged email format with invalid password (14)</v>
+      </c>
+      <c r="C24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D24" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E24" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC-GEN-1015</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Varying length long emails and long passwords (15)</v>
+      </c>
+      <c r="C25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D25" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E25" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC-GEN-1016</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Password containing special characters !#$%</v>
+      </c>
+      <c r="C26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D26" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E26" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TC-GEN-1017</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Fuzzing with database query snippets (17)</v>
+      </c>
+      <c r="C27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D27" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E27" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TC-GEN-1018</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Nonexistent email with standard password pattern (18)</v>
+      </c>
+      <c r="C28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D28" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E28" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TC-GEN-1019</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Whitespace email and whitespace password (19)</v>
+      </c>
+      <c r="C29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D29" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E29" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TC-GEN-1020</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Tagged email format with invalid password (20)</v>
+      </c>
+      <c r="C30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D30" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E30" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TC-GEN-1021</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Varying length long emails and long passwords (21)</v>
+      </c>
+      <c r="C31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D31" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TC-GEN-1022</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~</v>
+      </c>
+      <c r="C32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D32" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E32" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TC-GEN-1023</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Fuzzing with database query snippets (23)</v>
+      </c>
+      <c r="C33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D33" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E33" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TC-GEN-1024</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Nonexistent email with standard password pattern (24)</v>
+      </c>
+      <c r="C34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D34" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E34" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TC-GEN-1025</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Whitespace email and whitespace password (25)</v>
+      </c>
+      <c r="C35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D35" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E35" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TC-GEN-1026</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Tagged email format with invalid password (26)</v>
+      </c>
+      <c r="C36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D36" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E36" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TC-GEN-1027</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Varying length long emails and long passwords (27)</v>
+      </c>
+      <c r="C37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D37" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E37" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TC-GEN-1028</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Password containing special characters !#$</v>
+      </c>
+      <c r="C38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D38" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E38" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TC-GEN-1029</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Fuzzing with database query snippets (29)</v>
+      </c>
+      <c r="C39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D39" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E39" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TC-GEN-1030</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Nonexistent email with standard password pattern (30)</v>
+      </c>
+      <c r="C40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D40" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E40" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TC-GEN-1031</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Whitespace email and whitespace password (31)</v>
+      </c>
+      <c r="C41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D41" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E41" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TC-GEN-1032</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Tagged email format with invalid password (32)</v>
+      </c>
+      <c r="C42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D42" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E42" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TC-GEN-1033</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Varying length long emails and long passwords (33)</v>
+      </c>
+      <c r="C43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D43" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E43" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TC-GEN-1034</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Password containing special characters !#$%^&amp;*()</v>
+      </c>
+      <c r="C44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D44" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E44" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>TC-GEN-1035</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Fuzzing with database query snippets (35)</v>
+      </c>
+      <c r="C45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D45" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E45" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>TC-GEN-1036</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Nonexistent email with standard password pattern (36)</v>
+      </c>
+      <c r="C46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D46" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E46" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>TC-GEN-1037</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Whitespace email and whitespace password (37)</v>
+      </c>
+      <c r="C47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D47" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E47" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>TC-GEN-1038</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Tagged email format with invalid password (38)</v>
+      </c>
+      <c r="C48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D48" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E48" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>TC-GEN-1039</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Varying length long emails and long passwords (39)</v>
+      </c>
+      <c r="C49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D49" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E49" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>TC-GEN-1040</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Password containing special characters !#</v>
+      </c>
+      <c r="C50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D50" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E50" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>TC-GEN-1041</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Fuzzing with database query snippets (41)</v>
+      </c>
+      <c r="C51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D51" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E51" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>TC-GEN-1042</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Nonexistent email with standard password pattern (42)</v>
+      </c>
+      <c r="C52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D52" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E52" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>TC-GEN-1043</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Whitespace email and whitespace password (43)</v>
+      </c>
+      <c r="C53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D53" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E53" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>TC-GEN-1044</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Tagged email format with invalid password (44)</v>
+      </c>
+      <c r="C54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D54" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E54" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>TC-GEN-1045</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Varying length long emails and long passwords (45)</v>
+      </c>
+      <c r="C55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D55" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E55" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>TC-GEN-1046</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Password containing special characters !#$%^&amp;*(</v>
+      </c>
+      <c r="C56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D56" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E56" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>TC-GEN-1047</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Fuzzing with database query snippets (47)</v>
+      </c>
+      <c r="C57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D57" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E57" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>TC-GEN-1048</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Nonexistent email with standard password pattern (48)</v>
+      </c>
+      <c r="C58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D58" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E58" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>TC-GEN-1049</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Whitespace email and whitespace password (49)</v>
+      </c>
+      <c r="C59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D59" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E59" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>TC-GEN-1050</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Tagged email format with invalid password (50)</v>
+      </c>
+      <c r="C60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D60" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E60" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>TC-GEN-1051</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Varying length long emails and long passwords (51)</v>
+      </c>
+      <c r="C61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D61" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E61" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>TC-GEN-1052</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Password containing special characters !</v>
+      </c>
+      <c r="C62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D62" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E62" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>TC-GEN-1053</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Fuzzing with database query snippets (53)</v>
+      </c>
+      <c r="C63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D63" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E63" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>TC-GEN-1054</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Nonexistent email with standard password pattern (54)</v>
+      </c>
+      <c r="C64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D64" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E64" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>TC-GEN-1055</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Whitespace email and whitespace password (55)</v>
+      </c>
+      <c r="C65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D65" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E65" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>TC-GEN-1056</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Tagged email format with invalid password (56)</v>
+      </c>
+      <c r="C66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D66" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E66" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>TC-GEN-1057</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Varying length long emails and long passwords (57)</v>
+      </c>
+      <c r="C67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D67" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E67" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>TC-GEN-1058</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Password containing special characters !#$%^&amp;*</v>
+      </c>
+      <c r="C68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D68" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E68" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>TC-GEN-1059</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Fuzzing with database query snippets (59)</v>
+      </c>
+      <c r="C69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D69" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E69" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>TC-GEN-1060</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Nonexistent email with standard password pattern (60)</v>
+      </c>
+      <c r="C70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D70" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E70" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>TC-GEN-1061</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Whitespace email and whitespace password (61)</v>
+      </c>
+      <c r="C71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D71" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E71" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>TC-GEN-1062</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Tagged email format with invalid password (62)</v>
+      </c>
+      <c r="C72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D72" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E72" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>TC-GEN-1063</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Varying length long emails and long passwords (63)</v>
+      </c>
+      <c r="C73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D73" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E73" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>TC-GEN-1064</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D74" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E74" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>TC-GEN-1065</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Fuzzing with database query snippets (65)</v>
+      </c>
+      <c r="C75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D75" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E75" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>TC-GEN-1066</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Nonexistent email with standard password pattern (66)</v>
+      </c>
+      <c r="C76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D76" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E76" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>TC-GEN-1067</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Whitespace email and whitespace password (67)</v>
+      </c>
+      <c r="C77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D77" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E77" t="str">
+        <v>2026-07-31T11:18:33.059Z</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>TC-GEN-1068</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Tagged email format with invalid password (68)</v>
+      </c>
+      <c r="C78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D78" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E78" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>TC-GEN-1069</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Varying length long emails and long passwords (69)</v>
+      </c>
+      <c r="C79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D79" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E79" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>TC-GEN-1070</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Password containing special characters !#$%^&amp;</v>
+      </c>
+      <c r="C80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D80" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E80" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>TC-GEN-1071</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Fuzzing with database query snippets (71)</v>
+      </c>
+      <c r="C81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D81" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E81" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>TC-GEN-1072</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Nonexistent email with standard password pattern (72)</v>
+      </c>
+      <c r="C82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D82" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E82" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>TC-GEN-1073</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Whitespace email and whitespace password (73)</v>
+      </c>
+      <c r="C83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D83" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E83" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>TC-GEN-1074</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Tagged email format with invalid password (74)</v>
+      </c>
+      <c r="C84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D84" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E84" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>TC-GEN-1075</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Varying length long emails and long passwords (75)</v>
+      </c>
+      <c r="C85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D85" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E85" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>TC-GEN-1076</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D86" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E86" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>TC-GEN-1077</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Fuzzing with database query snippets (77)</v>
+      </c>
+      <c r="C87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D87" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E87" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>TC-GEN-1078</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Nonexistent email with standard password pattern (78)</v>
+      </c>
+      <c r="C88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D88" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E88" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>TC-GEN-1079</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Whitespace email and whitespace password (79)</v>
+      </c>
+      <c r="C89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D89" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E89" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>TC-GEN-1080</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Tagged email format with invalid password (80)</v>
+      </c>
+      <c r="C90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D90" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E90" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>TC-GEN-1081</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Varying length long emails and long passwords (81)</v>
+      </c>
+      <c r="C91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D91" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E91" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>TC-GEN-1082</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Password containing special characters !#$%^</v>
+      </c>
+      <c r="C92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D92" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E92" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>TC-GEN-1083</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Fuzzing with database query snippets (83)</v>
+      </c>
+      <c r="C93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D93" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E93" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>TC-GEN-1084</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Nonexistent email with standard password pattern (84)</v>
+      </c>
+      <c r="C94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D94" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E94" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>TC-GEN-1085</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Whitespace email and whitespace password (85)</v>
+      </c>
+      <c r="C95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D95" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E95" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>TC-GEN-1086</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Tagged email format with invalid password (86)</v>
+      </c>
+      <c r="C96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D96" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E96" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>TC-GEN-1087</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Varying length long emails and long passwords (87)</v>
+      </c>
+      <c r="C97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D97" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E97" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>TC-GEN-1088</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D98" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E98" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>TC-GEN-1089</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Fuzzing with database query snippets (89)</v>
+      </c>
+      <c r="C99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D99" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E99" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>TC-GEN-1090</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Nonexistent email with standard password pattern (90)</v>
+      </c>
+      <c r="C100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D100" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E100" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>TC-GEN-1091</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Whitespace email and whitespace password (91)</v>
+      </c>
+      <c r="C101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D101" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E101" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>TC-GEN-1092</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Tagged email format with invalid password (92)</v>
+      </c>
+      <c r="C102" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D102" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E102" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>TC-GEN-1093</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Varying length long emails and long passwords (93)</v>
+      </c>
+      <c r="C103" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D103" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E103" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>TC-GEN-1094</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Password containing special characters !#$%</v>
+      </c>
+      <c r="C104" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D104" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E104" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TC-GEN-1095</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Fuzzing with database query snippets (95)</v>
+      </c>
+      <c r="C105" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D105" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E105" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>TC-GEN-1096</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Nonexistent email with standard password pattern (96)</v>
+      </c>
+      <c r="C106" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D106" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E106" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>TC-GEN-1097</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Whitespace email and whitespace password (97)</v>
+      </c>
+      <c r="C107" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D107" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E107" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>TC-GEN-1098</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Tagged email format with invalid password (98)</v>
+      </c>
+      <c r="C108" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D108" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E108" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F108" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>TC-GEN-1099</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Varying length long emails and long passwords (99)</v>
+      </c>
+      <c r="C109" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D109" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E109" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F109" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>TC-GEN-1100</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~</v>
+      </c>
+      <c r="C110" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D110" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E110" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F110" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>TC-GEN-1101</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Fuzzing with database query snippets (101)</v>
+      </c>
+      <c r="C111" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D111" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E111" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F111" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>TC-GEN-1102</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Nonexistent email with standard password pattern (102)</v>
+      </c>
+      <c r="C112" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D112" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E112" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F112" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>TC-GEN-1103</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Whitespace email and whitespace password (103)</v>
+      </c>
+      <c r="C113" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D113" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E113" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F113" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>TC-GEN-1104</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Tagged email format with invalid password (104)</v>
+      </c>
+      <c r="C114" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D114" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E114" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F114" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>TC-GEN-1105</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Varying length long emails and long passwords (105)</v>
+      </c>
+      <c r="C115" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D115" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E115" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>TC-GEN-1106</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Password containing special characters !#$</v>
+      </c>
+      <c r="C116" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D116" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E116" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>TC-GEN-1107</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Fuzzing with database query snippets (107)</v>
+      </c>
+      <c r="C117" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D117" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E117" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>TC-GEN-1108</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Nonexistent email with standard password pattern (108)</v>
+      </c>
+      <c r="C118" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D118" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E118" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>TC-GEN-1109</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Whitespace email and whitespace password (109)</v>
+      </c>
+      <c r="C119" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D119" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E119" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>TC-GEN-1110</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Tagged email format with invalid password (110)</v>
+      </c>
+      <c r="C120" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D120" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E120" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>TC-GEN-1111</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Varying length long emails and long passwords (111)</v>
+      </c>
+      <c r="C121" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D121" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E121" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>TC-GEN-1112</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Password containing special characters !#$%^&amp;*()</v>
+      </c>
+      <c r="C122" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D122" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E122" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>TC-GEN-1113</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Fuzzing with database query snippets (113)</v>
+      </c>
+      <c r="C123" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D123" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E123" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TC-GEN-1114</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Nonexistent email with standard password pattern (114)</v>
+      </c>
+      <c r="C124" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D124" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E124" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TC-GEN-1115</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Whitespace email and whitespace password (115)</v>
+      </c>
+      <c r="C125" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D125" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E125" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TC-GEN-1116</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Tagged email format with invalid password (116)</v>
+      </c>
+      <c r="C126" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D126" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E126" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TC-GEN-1117</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Varying length long emails and long passwords (117)</v>
+      </c>
+      <c r="C127" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D127" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E127" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>TC-GEN-1118</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Password containing special characters !#</v>
+      </c>
+      <c r="C128" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D128" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E128" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TC-GEN-1119</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Fuzzing with database query snippets (119)</v>
+      </c>
+      <c r="C129" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D129" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E129" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>TC-GEN-1120</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Nonexistent email with standard password pattern (120)</v>
+      </c>
+      <c r="C130" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D130" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E130" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F130" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TC-GEN-1121</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Whitespace email and whitespace password (121)</v>
+      </c>
+      <c r="C131" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D131" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E131" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TC-GEN-1122</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Tagged email format with invalid password (122)</v>
+      </c>
+      <c r="C132" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D132" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E132" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TC-GEN-1123</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Varying length long emails and long passwords (123)</v>
+      </c>
+      <c r="C133" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D133" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E133" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>TC-GEN-1124</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Password containing special characters !#$%^&amp;*(</v>
+      </c>
+      <c r="C134" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D134" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E134" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>TC-GEN-1125</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Fuzzing with database query snippets (125)</v>
+      </c>
+      <c r="C135" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D135" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E135" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>TC-GEN-1126</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Nonexistent email with standard password pattern (126)</v>
+      </c>
+      <c r="C136" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D136" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E136" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>TC-GEN-1127</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Whitespace email and whitespace password (127)</v>
+      </c>
+      <c r="C137" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D137" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E137" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F137" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>TC-GEN-1128</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Tagged email format with invalid password (128)</v>
+      </c>
+      <c r="C138" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D138" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E138" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F138" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>TC-GEN-1129</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Varying length long emails and long passwords (129)</v>
+      </c>
+      <c r="C139" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D139" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E139" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>TC-GEN-1130</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Password containing special characters !</v>
+      </c>
+      <c r="C140" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D140" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E140" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>TC-GEN-1131</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Fuzzing with database query snippets (131)</v>
+      </c>
+      <c r="C141" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D141" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E141" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>TC-GEN-1132</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Nonexistent email with standard password pattern (132)</v>
+      </c>
+      <c r="C142" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D142" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E142" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>TC-GEN-1133</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Whitespace email and whitespace password (133)</v>
+      </c>
+      <c r="C143" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D143" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E143" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>TC-GEN-1134</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Tagged email format with invalid password (134)</v>
+      </c>
+      <c r="C144" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D144" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E144" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>TC-GEN-1135</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Varying length long emails and long passwords (135)</v>
+      </c>
+      <c r="C145" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D145" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E145" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F145" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>TC-GEN-1136</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Password containing special characters !#$%^&amp;*</v>
+      </c>
+      <c r="C146" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D146" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E146" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>TC-GEN-1137</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Fuzzing with database query snippets (137)</v>
+      </c>
+      <c r="C147" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D147" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E147" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>TC-GEN-1138</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Nonexistent email with standard password pattern (138)</v>
+      </c>
+      <c r="C148" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D148" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E148" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>TC-GEN-1139</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Whitespace email and whitespace password (139)</v>
+      </c>
+      <c r="C149" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D149" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E149" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>TC-GEN-1140</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Tagged email format with invalid password (140)</v>
+      </c>
+      <c r="C150" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D150" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E150" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>TC-GEN-1141</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Varying length long emails and long passwords (141)</v>
+      </c>
+      <c r="C151" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D151" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E151" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>TC-GEN-1142</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C152" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D152" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E152" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>TC-GEN-1143</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Fuzzing with database query snippets (143)</v>
+      </c>
+      <c r="C153" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D153" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E153" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>TC-GEN-1144</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Nonexistent email with standard password pattern (144)</v>
+      </c>
+      <c r="C154" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D154" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E154" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>TC-GEN-1145</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Whitespace email and whitespace password (145)</v>
+      </c>
+      <c r="C155" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D155" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E155" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>TC-GEN-1146</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Tagged email format with invalid password (146)</v>
+      </c>
+      <c r="C156" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D156" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E156" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>TC-GEN-1147</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Varying length long emails and long passwords (147)</v>
+      </c>
+      <c r="C157" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D157" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E157" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>TC-GEN-1148</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Password containing special characters !#$%^&amp;</v>
+      </c>
+      <c r="C158" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D158" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E158" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>TC-GEN-1149</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Fuzzing with database query snippets (149)</v>
+      </c>
+      <c r="C159" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D159" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E159" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>TC-GEN-1150</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Nonexistent email with standard password pattern (150)</v>
+      </c>
+      <c r="C160" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D160" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E160" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>TC-GEN-1151</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Whitespace email and whitespace password (151)</v>
+      </c>
+      <c r="C161" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D161" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E161" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>TC-GEN-1152</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Tagged email format with invalid password (152)</v>
+      </c>
+      <c r="C162" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D162" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E162" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F162" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>TC-GEN-1153</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Varying length long emails and long passwords (153)</v>
+      </c>
+      <c r="C163" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D163" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E163" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F163" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>TC-GEN-1154</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C164" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D164" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E164" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F164" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>TC-GEN-1155</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Fuzzing with database query snippets (155)</v>
+      </c>
+      <c r="C165" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D165" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E165" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F165" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>TC-GEN-1156</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Nonexistent email with standard password pattern (156)</v>
+      </c>
+      <c r="C166" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D166" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E166" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F166" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>TC-GEN-1157</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Whitespace email and whitespace password (157)</v>
+      </c>
+      <c r="C167" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D167" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E167" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F167" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>TC-GEN-1158</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Tagged email format with invalid password (158)</v>
+      </c>
+      <c r="C168" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D168" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E168" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F168" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>TC-GEN-1159</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Varying length long emails and long passwords (159)</v>
+      </c>
+      <c r="C169" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D169" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E169" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F169" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>TC-GEN-1160</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Password containing special characters !#$%^</v>
+      </c>
+      <c r="C170" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D170" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E170" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F170" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>TC-GEN-1161</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Fuzzing with database query snippets (161)</v>
+      </c>
+      <c r="C171" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D171" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E171" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F171" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>TC-GEN-1162</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Nonexistent email with standard password pattern (162)</v>
+      </c>
+      <c r="C172" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D172" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E172" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>TC-GEN-1163</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Whitespace email and whitespace password (163)</v>
+      </c>
+      <c r="C173" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D173" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E173" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F173" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>TC-GEN-1164</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Tagged email format with invalid password (164)</v>
+      </c>
+      <c r="C174" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D174" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E174" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F174" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>TC-GEN-1165</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Varying length long emails and long passwords (165)</v>
+      </c>
+      <c r="C175" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D175" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E175" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F175" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>TC-GEN-1166</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C176" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D176" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E176" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F176" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>TC-GEN-1167</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Fuzzing with database query snippets (167)</v>
+      </c>
+      <c r="C177" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D177" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E177" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F177" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>TC-GEN-1168</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Nonexistent email with standard password pattern (168)</v>
+      </c>
+      <c r="C178" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D178" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E178" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F178" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>TC-GEN-1169</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Whitespace email and whitespace password (169)</v>
+      </c>
+      <c r="C179" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D179" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E179" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F179" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>TC-GEN-1170</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Tagged email format with invalid password (170)</v>
+      </c>
+      <c r="C180" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D180" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E180" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>TC-GEN-1171</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Varying length long emails and long passwords (171)</v>
+      </c>
+      <c r="C181" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D181" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E181" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F181" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>TC-GEN-1172</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Password containing special characters !#$%</v>
+      </c>
+      <c r="C182" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D182" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E182" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F182" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>TC-GEN-1173</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Fuzzing with database query snippets (173)</v>
+      </c>
+      <c r="C183" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D183" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E183" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F183" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>TC-GEN-1174</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Nonexistent email with standard password pattern (174)</v>
+      </c>
+      <c r="C184" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D184" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E184" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F184" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>TC-GEN-1175</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Whitespace email and whitespace password (175)</v>
+      </c>
+      <c r="C185" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D185" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E185" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F185" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>TC-GEN-1176</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Tagged email format with invalid password (176)</v>
+      </c>
+      <c r="C186" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D186" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E186" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F186" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>TC-GEN-1177</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Varying length long emails and long passwords (177)</v>
+      </c>
+      <c r="C187" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D187" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E187" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F187" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>TC-GEN-1178</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~</v>
+      </c>
+      <c r="C188" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D188" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E188" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F188" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>TC-GEN-1179</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Fuzzing with database query snippets (179)</v>
+      </c>
+      <c r="C189" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D189" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E189" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F189" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>TC-GEN-1180</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Nonexistent email with standard password pattern (180)</v>
+      </c>
+      <c r="C190" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D190" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E190" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F190" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>TC-GEN-1181</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Whitespace email and whitespace password (181)</v>
+      </c>
+      <c r="C191" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D191" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E191" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F191" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>TC-GEN-1182</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Tagged email format with invalid password (182)</v>
+      </c>
+      <c r="C192" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D192" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E192" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F192" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>TC-GEN-1183</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Varying length long emails and long passwords (183)</v>
+      </c>
+      <c r="C193" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D193" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E193" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F193" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>TC-GEN-1184</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Password containing special characters !#$</v>
+      </c>
+      <c r="C194" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D194" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E194" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F194" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>TC-GEN-1185</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Fuzzing with database query snippets (185)</v>
+      </c>
+      <c r="C195" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D195" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E195" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F195" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>TC-GEN-1186</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Nonexistent email with standard password pattern (186)</v>
+      </c>
+      <c r="C196" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D196" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E196" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F196" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>TC-GEN-1187</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Whitespace email and whitespace password (187)</v>
+      </c>
+      <c r="C197" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D197" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E197" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F197" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>TC-GEN-1188</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Tagged email format with invalid password (188)</v>
+      </c>
+      <c r="C198" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D198" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E198" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F198" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>TC-GEN-1189</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Varying length long emails and long passwords (189)</v>
+      </c>
+      <c r="C199" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D199" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E199" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F199" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>TC-GEN-1190</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Password containing special characters !#$%^&amp;*()</v>
+      </c>
+      <c r="C200" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D200" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E200" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F200" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>TC-GEN-1191</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Fuzzing with database query snippets (191)</v>
+      </c>
+      <c r="C201" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D201" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E201" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F201" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>TC-GEN-1192</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Nonexistent email with standard password pattern (192)</v>
+      </c>
+      <c r="C202" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D202" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E202" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F202" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>TC-GEN-1193</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Whitespace email and whitespace password (193)</v>
+      </c>
+      <c r="C203" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D203" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E203" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F203" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>TC-GEN-1194</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Tagged email format with invalid password (194)</v>
+      </c>
+      <c r="C204" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D204" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E204" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F204" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>TC-GEN-1195</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Varying length long emails and long passwords (195)</v>
+      </c>
+      <c r="C205" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D205" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E205" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F205" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>TC-GEN-1196</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Password containing special characters !#</v>
+      </c>
+      <c r="C206" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D206" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E206" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>TC-GEN-1197</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Fuzzing with database query snippets (197)</v>
+      </c>
+      <c r="C207" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D207" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E207" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F207" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>TC-GEN-1198</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Nonexistent email with standard password pattern (198)</v>
+      </c>
+      <c r="C208" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D208" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E208" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F208" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>TC-GEN-1199</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Whitespace email and whitespace password (199)</v>
+      </c>
+      <c r="C209" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D209" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E209" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F209" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>TC-GEN-1200</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Tagged email format with invalid password (200)</v>
+      </c>
+      <c r="C210" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D210" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E210" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F210" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>TC-GEN-1201</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Varying length long emails and long passwords (201)</v>
+      </c>
+      <c r="C211" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D211" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E211" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F211" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>TC-GEN-1202</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Password containing special characters !#$%^&amp;*(</v>
+      </c>
+      <c r="C212" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D212" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E212" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F212" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>TC-GEN-1203</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Fuzzing with database query snippets (203)</v>
+      </c>
+      <c r="C213" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D213" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E213" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F213" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>TC-GEN-1204</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Nonexistent email with standard password pattern (204)</v>
+      </c>
+      <c r="C214" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D214" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E214" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F214" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>TC-GEN-1205</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Whitespace email and whitespace password (205)</v>
+      </c>
+      <c r="C215" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D215" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E215" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F215" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>TC-GEN-1206</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Tagged email format with invalid password (206)</v>
+      </c>
+      <c r="C216" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D216" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E216" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F216" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>TC-GEN-1207</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Varying length long emails and long passwords (207)</v>
+      </c>
+      <c r="C217" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D217" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E217" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F217" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>TC-GEN-1208</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Password containing special characters !</v>
+      </c>
+      <c r="C218" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D218" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E218" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F218" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>TC-GEN-1209</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Fuzzing with database query snippets (209)</v>
+      </c>
+      <c r="C219" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D219" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E219" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F219" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>TC-GEN-1210</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Nonexistent email with standard password pattern (210)</v>
+      </c>
+      <c r="C220" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D220" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E220" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F220" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>TC-GEN-1211</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Whitespace email and whitespace password (211)</v>
+      </c>
+      <c r="C221" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D221" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E221" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F221" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>TC-GEN-1212</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Tagged email format with invalid password (212)</v>
+      </c>
+      <c r="C222" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D222" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E222" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F222" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>TC-GEN-1213</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Varying length long emails and long passwords (213)</v>
+      </c>
+      <c r="C223" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D223" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E223" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F223" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>TC-GEN-1214</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Password containing special characters !#$%^&amp;*</v>
+      </c>
+      <c r="C224" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D224" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E224" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F224" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>TC-GEN-1215</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Fuzzing with database query snippets (215)</v>
+      </c>
+      <c r="C225" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D225" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E225" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F225" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>TC-GEN-1216</v>
+      </c>
+      <c r="B226" t="str">
+        <v>Nonexistent email with standard password pattern (216)</v>
+      </c>
+      <c r="C226" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D226" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E226" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F226" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>TC-GEN-1217</v>
+      </c>
+      <c r="B227" t="str">
+        <v>Whitespace email and whitespace password (217)</v>
+      </c>
+      <c r="C227" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D227" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E227" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F227" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>TC-GEN-1218</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Tagged email format with invalid password (218)</v>
+      </c>
+      <c r="C228" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D228" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E228" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F228" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>TC-GEN-1219</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Varying length long emails and long passwords (219)</v>
+      </c>
+      <c r="C229" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D229" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E229" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F229" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>TC-GEN-1220</v>
+      </c>
+      <c r="B230" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C230" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D230" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E230" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F230" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>TC-GEN-1221</v>
+      </c>
+      <c r="B231" t="str">
+        <v>Fuzzing with database query snippets (221)</v>
+      </c>
+      <c r="C231" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D231" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E231" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F231" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>TC-GEN-1222</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Nonexistent email with standard password pattern (222)</v>
+      </c>
+      <c r="C232" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D232" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E232" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F232" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>TC-GEN-1223</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Whitespace email and whitespace password (223)</v>
+      </c>
+      <c r="C233" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D233" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E233" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F233" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>TC-GEN-1224</v>
+      </c>
+      <c r="B234" t="str">
+        <v>Tagged email format with invalid password (224)</v>
+      </c>
+      <c r="C234" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D234" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E234" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F234" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>TC-GEN-1225</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Varying length long emails and long passwords (225)</v>
+      </c>
+      <c r="C235" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D235" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E235" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F235" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>TC-GEN-1226</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Password containing special characters !#$%^&amp;</v>
+      </c>
+      <c r="C236" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D236" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E236" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F236" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>TC-GEN-1227</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Fuzzing with database query snippets (227)</v>
+      </c>
+      <c r="C237" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D237" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E237" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F237" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>TC-GEN-1228</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Nonexistent email with standard password pattern (228)</v>
+      </c>
+      <c r="C238" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D238" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E238" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F238" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>TC-GEN-1229</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Whitespace email and whitespace password (229)</v>
+      </c>
+      <c r="C239" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D239" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E239" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F239" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>TC-GEN-1230</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Tagged email format with invalid password (230)</v>
+      </c>
+      <c r="C240" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D240" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E240" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F240" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>TC-GEN-1231</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Varying length long emails and long passwords (231)</v>
+      </c>
+      <c r="C241" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D241" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E241" t="str">
+        <v>2026-07-31T11:18:33.060Z</v>
+      </c>
+      <c r="F241" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>TC-GEN-1232</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C242" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D242" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E242" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F242" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>TC-GEN-1233</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Fuzzing with database query snippets (233)</v>
+      </c>
+      <c r="C243" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D243" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E243" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F243" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>TC-GEN-1234</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Nonexistent email with standard password pattern (234)</v>
+      </c>
+      <c r="C244" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D244" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E244" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F244" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>TC-GEN-1235</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Whitespace email and whitespace password (235)</v>
+      </c>
+      <c r="C245" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D245" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E245" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F245" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>TC-GEN-1236</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Tagged email format with invalid password (236)</v>
+      </c>
+      <c r="C246" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D246" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E246" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F246" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>TC-GEN-1237</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Varying length long emails and long passwords (237)</v>
+      </c>
+      <c r="C247" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D247" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E247" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F247" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>TC-GEN-1238</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Password containing special characters !#$%^</v>
+      </c>
+      <c r="C248" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D248" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E248" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F248" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>TC-GEN-1239</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Fuzzing with database query snippets (239)</v>
+      </c>
+      <c r="C249" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D249" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E249" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F249" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>TC-GEN-1240</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Nonexistent email with standard password pattern (240)</v>
+      </c>
+      <c r="C250" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D250" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E250" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F250" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>TC-GEN-1241</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Whitespace email and whitespace password (241)</v>
+      </c>
+      <c r="C251" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D251" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E251" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F251" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>TC-GEN-1242</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Tagged email format with invalid password (242)</v>
+      </c>
+      <c r="C252" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D252" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E252" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F252" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>TC-GEN-1243</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Varying length long emails and long passwords (243)</v>
+      </c>
+      <c r="C253" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D253" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E253" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F253" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>TC-GEN-1244</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C254" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D254" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E254" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F254" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>TC-GEN-1245</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Fuzzing with database query snippets (245)</v>
+      </c>
+      <c r="C255" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D255" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E255" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F255" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>TC-GEN-1246</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Nonexistent email with standard password pattern (246)</v>
+      </c>
+      <c r="C256" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D256" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E256" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F256" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>TC-GEN-1247</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Whitespace email and whitespace password (247)</v>
+      </c>
+      <c r="C257" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D257" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E257" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F257" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>TC-GEN-1248</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Tagged email format with invalid password (248)</v>
+      </c>
+      <c r="C258" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D258" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E258" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F258" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>TC-GEN-1249</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Varying length long emails and long passwords (249)</v>
+      </c>
+      <c r="C259" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D259" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E259" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F259" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>TC-GEN-1250</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Password containing special characters !#$%</v>
+      </c>
+      <c r="C260" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D260" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E260" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F260" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>TC-GEN-1251</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Fuzzing with database query snippets (251)</v>
+      </c>
+      <c r="C261" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D261" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E261" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F261" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>TC-GEN-1252</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Nonexistent email with standard password pattern (252)</v>
+      </c>
+      <c r="C262" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D262" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E262" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F262" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>TC-GEN-1253</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Whitespace email and whitespace password (253)</v>
+      </c>
+      <c r="C263" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D263" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E263" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F263" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>TC-GEN-1254</v>
+      </c>
+      <c r="B264" t="str">
+        <v>Tagged email format with invalid password (254)</v>
+      </c>
+      <c r="C264" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D264" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E264" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F264" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>TC-GEN-1255</v>
+      </c>
+      <c r="B265" t="str">
+        <v>Varying length long emails and long passwords (255)</v>
+      </c>
+      <c r="C265" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D265" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E265" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F265" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>TC-GEN-1256</v>
+      </c>
+      <c r="B266" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~</v>
+      </c>
+      <c r="C266" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D266" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E266" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F266" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>TC-GEN-1257</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Fuzzing with database query snippets (257)</v>
+      </c>
+      <c r="C267" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D267" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E267" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F267" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>TC-GEN-1258</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Nonexistent email with standard password pattern (258)</v>
+      </c>
+      <c r="C268" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D268" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E268" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F268" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>TC-GEN-1259</v>
+      </c>
+      <c r="B269" t="str">
+        <v>Whitespace email and whitespace password (259)</v>
+      </c>
+      <c r="C269" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D269" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E269" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F269" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>TC-GEN-1260</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Tagged email format with invalid password (260)</v>
+      </c>
+      <c r="C270" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D270" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E270" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F270" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>TC-GEN-1261</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Varying length long emails and long passwords (261)</v>
+      </c>
+      <c r="C271" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D271" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E271" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F271" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>TC-GEN-1262</v>
+      </c>
+      <c r="B272" t="str">
+        <v>Password containing special characters !#$</v>
+      </c>
+      <c r="C272" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D272" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E272" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F272" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>TC-GEN-1263</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Fuzzing with database query snippets (263)</v>
+      </c>
+      <c r="C273" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D273" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E273" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F273" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>TC-GEN-1264</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Nonexistent email with standard password pattern (264)</v>
+      </c>
+      <c r="C274" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D274" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E274" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F274" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>TC-GEN-1265</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Whitespace email and whitespace password (265)</v>
+      </c>
+      <c r="C275" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D275" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E275" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F275" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>TC-GEN-1266</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Tagged email format with invalid password (266)</v>
+      </c>
+      <c r="C276" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D276" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E276" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>TC-GEN-1267</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Varying length long emails and long passwords (267)</v>
+      </c>
+      <c r="C277" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D277" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E277" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F277" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>TC-GEN-1268</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Password containing special characters !#$%^&amp;*()</v>
+      </c>
+      <c r="C278" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D278" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E278" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F278" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>TC-GEN-1269</v>
+      </c>
+      <c r="B279" t="str">
+        <v>Fuzzing with database query snippets (269)</v>
+      </c>
+      <c r="C279" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D279" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E279" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F279" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>TC-GEN-1270</v>
+      </c>
+      <c r="B280" t="str">
+        <v>Nonexistent email with standard password pattern (270)</v>
+      </c>
+      <c r="C280" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D280" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E280" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F280" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>TC-GEN-1271</v>
+      </c>
+      <c r="B281" t="str">
+        <v>Whitespace email and whitespace password (271)</v>
+      </c>
+      <c r="C281" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D281" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E281" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F281" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>TC-GEN-1272</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Tagged email format with invalid password (272)</v>
+      </c>
+      <c r="C282" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D282" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E282" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F282" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>TC-GEN-1273</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Varying length long emails and long passwords (273)</v>
+      </c>
+      <c r="C283" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D283" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E283" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F283" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>TC-GEN-1274</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Password containing special characters !#</v>
+      </c>
+      <c r="C284" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D284" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E284" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F284" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>TC-GEN-1275</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Fuzzing with database query snippets (275)</v>
+      </c>
+      <c r="C285" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D285" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E285" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F285" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>TC-GEN-1276</v>
+      </c>
+      <c r="B286" t="str">
+        <v>Nonexistent email with standard password pattern (276)</v>
+      </c>
+      <c r="C286" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D286" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E286" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F286" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>TC-GEN-1277</v>
+      </c>
+      <c r="B287" t="str">
+        <v>Whitespace email and whitespace password (277)</v>
+      </c>
+      <c r="C287" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D287" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E287" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F287" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>TC-GEN-1278</v>
+      </c>
+      <c r="B288" t="str">
+        <v>Tagged email format with invalid password (278)</v>
+      </c>
+      <c r="C288" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D288" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E288" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F288" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>TC-GEN-1279</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Varying length long emails and long passwords (279)</v>
+      </c>
+      <c r="C289" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D289" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E289" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F289" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>TC-GEN-1280</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Password containing special characters !#$%^&amp;*(</v>
+      </c>
+      <c r="C290" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D290" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E290" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F290" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>TC-GEN-1281</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Fuzzing with database query snippets (281)</v>
+      </c>
+      <c r="C291" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D291" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E291" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F291" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>TC-GEN-1282</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Nonexistent email with standard password pattern (282)</v>
+      </c>
+      <c r="C292" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D292" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E292" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F292" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>TC-GEN-1283</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Whitespace email and whitespace password (283)</v>
+      </c>
+      <c r="C293" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D293" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E293" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F293" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>TC-GEN-1284</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Tagged email format with invalid password (284)</v>
+      </c>
+      <c r="C294" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D294" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E294" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F294" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>TC-GEN-1285</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Varying length long emails and long passwords (285)</v>
+      </c>
+      <c r="C295" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D295" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E295" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F295" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>TC-GEN-1286</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Password containing special characters !</v>
+      </c>
+      <c r="C296" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D296" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E296" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F296" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>TC-GEN-1287</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Fuzzing with database query snippets (287)</v>
+      </c>
+      <c r="C297" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D297" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E297" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F297" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>TC-GEN-1288</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Nonexistent email with standard password pattern (288)</v>
+      </c>
+      <c r="C298" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D298" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E298" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F298" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>TC-GEN-1289</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Whitespace email and whitespace password (289)</v>
+      </c>
+      <c r="C299" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D299" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E299" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F299" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>TC-GEN-1290</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Tagged email format with invalid password (290)</v>
+      </c>
+      <c r="C300" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D300" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E300" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F300" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>TC-GEN-1291</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Varying length long emails and long passwords (291)</v>
+      </c>
+      <c r="C301" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D301" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E301" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F301" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>TC-GEN-1292</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Password containing special characters !#$%^&amp;*</v>
+      </c>
+      <c r="C302" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D302" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E302" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F302" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>TC-GEN-1293</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Fuzzing with database query snippets (293)</v>
+      </c>
+      <c r="C303" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D303" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E303" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F303" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>TC-GEN-1294</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Nonexistent email with standard password pattern (294)</v>
+      </c>
+      <c r="C304" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D304" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E304" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F304" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>TC-GEN-1295</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Whitespace email and whitespace password (295)</v>
+      </c>
+      <c r="C305" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D305" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E305" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F305" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>TC-GEN-1296</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Tagged email format with invalid password (296)</v>
+      </c>
+      <c r="C306" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D306" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E306" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F306" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>TC-GEN-1297</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Varying length long emails and long passwords (297)</v>
+      </c>
+      <c r="C307" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D307" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E307" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F307" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>TC-GEN-1298</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C308" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D308" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E308" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F308" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>TC-GEN-1299</v>
+      </c>
+      <c r="B309" t="str">
+        <v>Fuzzing with database query snippets (299)</v>
+      </c>
+      <c r="C309" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D309" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E309" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F309" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>TC-GEN-1300</v>
+      </c>
+      <c r="B310" t="str">
+        <v>Nonexistent email with standard password pattern (300)</v>
+      </c>
+      <c r="C310" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D310" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E310" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F310" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>TC-GEN-1301</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Whitespace email and whitespace password (301)</v>
+      </c>
+      <c r="C311" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D311" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E311" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F311" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>TC-GEN-1302</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Tagged email format with invalid password (302)</v>
+      </c>
+      <c r="C312" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D312" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E312" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F312" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>TC-GEN-1303</v>
+      </c>
+      <c r="B313" t="str">
+        <v>Varying length long emails and long passwords (303)</v>
+      </c>
+      <c r="C313" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D313" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E313" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F313" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>TC-GEN-1304</v>
+      </c>
+      <c r="B314" t="str">
+        <v>Password containing special characters !#$%^&amp;</v>
+      </c>
+      <c r="C314" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D314" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E314" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F314" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>TC-GEN-1305</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Fuzzing with database query snippets (305)</v>
+      </c>
+      <c r="C315" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D315" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E315" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F315" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>TC-GEN-1306</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Nonexistent email with standard password pattern (306)</v>
+      </c>
+      <c r="C316" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D316" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E316" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F316" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>TC-GEN-1307</v>
+      </c>
+      <c r="B317" t="str">
+        <v>Whitespace email and whitespace password (307)</v>
+      </c>
+      <c r="C317" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D317" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E317" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F317" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>TC-GEN-1308</v>
+      </c>
+      <c r="B318" t="str">
+        <v>Tagged email format with invalid password (308)</v>
+      </c>
+      <c r="C318" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D318" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E318" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F318" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>TC-GEN-1309</v>
+      </c>
+      <c r="B319" t="str">
+        <v>Varying length long emails and long passwords (309)</v>
+      </c>
+      <c r="C319" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D319" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E319" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F319" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>TC-GEN-1310</v>
+      </c>
+      <c r="B320" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C320" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D320" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E320" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F320" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>TC-GEN-1311</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Fuzzing with database query snippets (311)</v>
+      </c>
+      <c r="C321" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D321" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E321" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F321" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>TC-GEN-1312</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Nonexistent email with standard password pattern (312)</v>
+      </c>
+      <c r="C322" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D322" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E322" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F322" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>TC-GEN-1313</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Whitespace email and whitespace password (313)</v>
+      </c>
+      <c r="C323" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D323" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E323" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F323" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>TC-GEN-1314</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Tagged email format with invalid password (314)</v>
+      </c>
+      <c r="C324" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D324" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E324" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F324" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>TC-GEN-1315</v>
+      </c>
+      <c r="B325" t="str">
+        <v>Varying length long emails and long passwords (315)</v>
+      </c>
+      <c r="C325" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D325" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E325" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F325" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>TC-GEN-1316</v>
+      </c>
+      <c r="B326" t="str">
+        <v>Password containing special characters !#$%^</v>
+      </c>
+      <c r="C326" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D326" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E326" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F326" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>TC-GEN-1317</v>
+      </c>
+      <c r="B327" t="str">
+        <v>Fuzzing with database query snippets (317)</v>
+      </c>
+      <c r="C327" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D327" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E327" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F327" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>TC-GEN-1318</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Nonexistent email with standard password pattern (318)</v>
+      </c>
+      <c r="C328" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D328" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E328" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F328" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>TC-GEN-1319</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Whitespace email and whitespace password (319)</v>
+      </c>
+      <c r="C329" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D329" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E329" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F329" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>TC-GEN-1320</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Tagged email format with invalid password (320)</v>
+      </c>
+      <c r="C330" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D330" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E330" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F330" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>TC-GEN-1321</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Varying length long emails and long passwords (321)</v>
+      </c>
+      <c r="C331" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D331" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E331" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F331" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>TC-GEN-1322</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`</v>
+      </c>
+      <c r="C332" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D332" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E332" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F332" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>TC-GEN-1323</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Fuzzing with database query snippets (323)</v>
+      </c>
+      <c r="C333" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D333" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E333" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F333" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>TC-GEN-1324</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Nonexistent email with standard password pattern (324)</v>
+      </c>
+      <c r="C334" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D334" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E334" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F334" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>TC-GEN-1325</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Whitespace email and whitespace password (325)</v>
+      </c>
+      <c r="C335" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D335" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E335" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F335" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>TC-GEN-1326</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Tagged email format with invalid password (326)</v>
+      </c>
+      <c r="C336" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D336" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E336" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F336" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>TC-GEN-1327</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Varying length long emails and long passwords (327)</v>
+      </c>
+      <c r="C337" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D337" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E337" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F337" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>TC-GEN-1328</v>
+      </c>
+      <c r="B338" t="str">
+        <v>Password containing special characters !#$%</v>
+      </c>
+      <c r="C338" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D338" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E338" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F338" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>TC-GEN-1329</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Fuzzing with database query snippets (329)</v>
+      </c>
+      <c r="C339" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D339" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E339" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F339" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>TC-GEN-1330</v>
+      </c>
+      <c r="B340" t="str">
+        <v>Nonexistent email with standard password pattern (330)</v>
+      </c>
+      <c r="C340" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D340" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E340" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F340" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>TC-GEN-1331</v>
+      </c>
+      <c r="B341" t="str">
+        <v>Whitespace email and whitespace password (331)</v>
+      </c>
+      <c r="C341" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D341" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E341" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F341" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>TC-GEN-1332</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Tagged email format with invalid password (332)</v>
+      </c>
+      <c r="C342" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D342" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E342" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F342" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>TC-GEN-1333</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Varying length long emails and long passwords (333)</v>
+      </c>
+      <c r="C343" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D343" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E343" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F343" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>TC-GEN-1334</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~</v>
+      </c>
+      <c r="C344" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D344" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E344" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F344" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>TC-GEN-1335</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Fuzzing with database query snippets (335)</v>
+      </c>
+      <c r="C345" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D345" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E345" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F345" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>TC-GEN-1336</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Nonexistent email with standard password pattern (336)</v>
+      </c>
+      <c r="C346" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D346" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E346" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F346" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>TC-GEN-1337</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Whitespace email and whitespace password (337)</v>
+      </c>
+      <c r="C347" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D347" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E347" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F347" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>TC-GEN-1338</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Tagged email format with invalid password (338)</v>
+      </c>
+      <c r="C348" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D348" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E348" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F348" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>TC-GEN-1339</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Varying length long emails and long passwords (339)</v>
+      </c>
+      <c r="C349" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D349" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E349" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F349" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>TC-GEN-1340</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Password containing special characters !#$</v>
+      </c>
+      <c r="C350" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D350" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E350" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F350" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>TC-GEN-1341</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Fuzzing with database query snippets (341)</v>
+      </c>
+      <c r="C351" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D351" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E351" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F351" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>TC-GEN-1342</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Nonexistent email with standard password pattern (342)</v>
+      </c>
+      <c r="C352" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D352" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E352" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F352" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>TC-GEN-1343</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Whitespace email and whitespace password (343)</v>
+      </c>
+      <c r="C353" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D353" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E353" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F353" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>TC-GEN-1344</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Tagged email format with invalid password (344)</v>
+      </c>
+      <c r="C354" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D354" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E354" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F354" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>TC-GEN-1345</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Varying length long emails and long passwords (345)</v>
+      </c>
+      <c r="C355" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D355" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E355" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F355" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>TC-GEN-1346</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Password containing special characters !#$%^&amp;*()</v>
+      </c>
+      <c r="C356" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D356" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E356" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F356" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>TC-GEN-1347</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Fuzzing with database query snippets (347)</v>
+      </c>
+      <c r="C357" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D357" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E357" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F357" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>TC-GEN-1348</v>
+      </c>
+      <c r="B358" t="str">
+        <v>Nonexistent email with standard password pattern (348)</v>
+      </c>
+      <c r="C358" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D358" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E358" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F358" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>TC-GEN-1349</v>
+      </c>
+      <c r="B359" t="str">
+        <v>Whitespace email and whitespace password (349)</v>
+      </c>
+      <c r="C359" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D359" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E359" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F359" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>TC-GEN-1350</v>
+      </c>
+      <c r="B360" t="str">
+        <v>Tagged email format with invalid password (350)</v>
+      </c>
+      <c r="C360" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D360" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E360" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F360" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>TC-GEN-1351</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Varying length long emails and long passwords (351)</v>
+      </c>
+      <c r="C361" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D361" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E361" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F361" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>TC-GEN-1352</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Password containing special characters !#</v>
+      </c>
+      <c r="C362" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D362" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E362" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F362" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>TC-GEN-1353</v>
+      </c>
+      <c r="B363" t="str">
+        <v>Fuzzing with database query snippets (353)</v>
+      </c>
+      <c r="C363" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D363" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E363" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F363" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>TC-GEN-1354</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Nonexistent email with standard password pattern (354)</v>
+      </c>
+      <c r="C364" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D364" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E364" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F364" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>TC-GEN-1355</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Whitespace email and whitespace password (355)</v>
+      </c>
+      <c r="C365" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D365" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E365" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F365" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>TC-GEN-1356</v>
+      </c>
+      <c r="B366" t="str">
+        <v>Tagged email format with invalid password (356)</v>
+      </c>
+      <c r="C366" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D366" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E366" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F366" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>TC-GEN-1357</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Varying length long emails and long passwords (357)</v>
+      </c>
+      <c r="C367" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D367" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E367" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F367" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>TC-GEN-1358</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Password containing special characters !#$%^&amp;*(</v>
+      </c>
+      <c r="C368" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D368" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E368" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F368" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>TC-GEN-1359</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Fuzzing with database query snippets (359)</v>
+      </c>
+      <c r="C369" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D369" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E369" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F369" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>TC-GEN-1360</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Nonexistent email with standard password pattern (360)</v>
+      </c>
+      <c r="C370" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D370" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E370" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F370" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>TC-GEN-1361</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Whitespace email and whitespace password (361)</v>
+      </c>
+      <c r="C371" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D371" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E371" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F371" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>TC-GEN-1362</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Tagged email format with invalid password (362)</v>
+      </c>
+      <c r="C372" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D372" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E372" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F372" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>TC-GEN-1363</v>
+      </c>
+      <c r="B373" t="str">
+        <v>Varying length long emails and long passwords (363)</v>
+      </c>
+      <c r="C373" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D373" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E373" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F373" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>TC-GEN-1364</v>
+      </c>
+      <c r="B374" t="str">
+        <v>Password containing special characters !</v>
+      </c>
+      <c r="C374" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D374" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E374" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F374" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>TC-GEN-1365</v>
+      </c>
+      <c r="B375" t="str">
+        <v>Fuzzing with database query snippets (365)</v>
+      </c>
+      <c r="C375" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D375" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E375" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F375" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>TC-GEN-1366</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Nonexistent email with standard password pattern (366)</v>
+      </c>
+      <c r="C376" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D376" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E376" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F376" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>TC-GEN-1367</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Whitespace email and whitespace password (367)</v>
+      </c>
+      <c r="C377" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D377" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E377" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F377" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>TC-GEN-1368</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Tagged email format with invalid password (368)</v>
+      </c>
+      <c r="C378" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D378" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E378" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F378" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>TC-GEN-1369</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Varying length long emails and long passwords (369)</v>
+      </c>
+      <c r="C379" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D379" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E379" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F379" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>TC-GEN-1370</v>
+      </c>
+      <c r="B380" t="str">
+        <v>Password containing special characters !#$%^&amp;*</v>
+      </c>
+      <c r="C380" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D380" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E380" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F380" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>TC-GEN-1371</v>
+      </c>
+      <c r="B381" t="str">
+        <v>Fuzzing with database query snippets (371)</v>
+      </c>
+      <c r="C381" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D381" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E381" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F381" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>TC-GEN-1372</v>
+      </c>
+      <c r="B382" t="str">
+        <v>Nonexistent email with standard password pattern (372)</v>
+      </c>
+      <c r="C382" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D382" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E382" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F382" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>TC-GEN-1373</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Whitespace email and whitespace password (373)</v>
+      </c>
+      <c r="C383" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D383" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E383" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F383" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>TC-GEN-1374</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Tagged email format with invalid password (374)</v>
+      </c>
+      <c r="C384" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D384" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E384" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F384" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>TC-GEN-1375</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Varying length long emails and long passwords (375)</v>
+      </c>
+      <c r="C385" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D385" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E385" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F385" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>TC-GEN-1376</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+=</v>
+      </c>
+      <c r="C386" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D386" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E386" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F386" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>TC-GEN-1377</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Fuzzing with database query snippets (377)</v>
+      </c>
+      <c r="C387" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D387" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E387" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F387" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>TC-GEN-1378</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Nonexistent email with standard password pattern (378)</v>
+      </c>
+      <c r="C388" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D388" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E388" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F388" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>TC-GEN-1379</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Whitespace email and whitespace password (379)</v>
+      </c>
+      <c r="C389" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D389" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E389" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F389" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>TC-GEN-1380</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Tagged email format with invalid password (380)</v>
+      </c>
+      <c r="C390" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D390" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E390" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F390" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>TC-GEN-1381</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Varying length long emails and long passwords (381)</v>
+      </c>
+      <c r="C391" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D391" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E391" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F391" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>TC-GEN-1382</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Password containing special characters !#$%^&amp;</v>
+      </c>
+      <c r="C392" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D392" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E392" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F392" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>TC-GEN-1383</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Fuzzing with database query snippets (383)</v>
+      </c>
+      <c r="C393" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D393" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E393" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F393" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>TC-GEN-1384</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Nonexistent email with standard password pattern (384)</v>
+      </c>
+      <c r="C394" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D394" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E394" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F394" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>TC-GEN-1385</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Whitespace email and whitespace password (385)</v>
+      </c>
+      <c r="C395" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D395" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E395" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F395" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>TC-GEN-1386</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Tagged email format with invalid password (386)</v>
+      </c>
+      <c r="C396" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D396" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E396" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F396" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>TC-GEN-1387</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Varying length long emails and long passwords (387)</v>
+      </c>
+      <c r="C397" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D397" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E397" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F397" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>TC-GEN-1388</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Password containing special characters !#$%^&amp;*()~`+</v>
+      </c>
+      <c r="C398" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D398" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E398" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F398" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>TC-GEN-1389</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Fuzzing with database query snippets (389)</v>
+      </c>
+      <c r="C399" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D399" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E399" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F399" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>TC-GEN-1390</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Nonexistent email with standard password pattern (390)</v>
+      </c>
+      <c r="C400" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D400" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E400" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F400" t="str">
+        <v>Success</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>TC-GEN-1391</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Whitespace email and whitespace password (391)</v>
+      </c>
+      <c r="C401" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="D401" t="str">
+        <v>0.00 sec</v>
+      </c>
+      <c r="E401" t="str">
+        <v>2026-07-31T11:18:33.061Z</v>
+      </c>
+      <c r="F401" t="str">
         <v>Success</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F401"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/reports/Selenium Report.xlsx
+++ b/reports/Selenium Report.xlsx
@@ -419,7 +419,7 @@
         <v>Remarks</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
         <v>TC-001</v>
       </c>
@@ -427,17 +427,16 @@
         <v>Valid citizen demo login</v>
       </c>
       <c r="C2" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D2" t="str">
-        <v>4.51 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-31T11:18:33.058Z</v>
-      </c>
-      <c r="F2" t="str" xml:space="preserve">
-        <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
-  (Session info: chrome=150.0.7871.187)</v>
+        <v>2026-08-01T10:43:40.603Z</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="3">
@@ -448,16 +447,16 @@
         <v>Valid volunteer demo login</v>
       </c>
       <c r="C3" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D3" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:43:41.433Z</v>
       </c>
       <c r="F3" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="4">
@@ -468,16 +467,16 @@
         <v>Valid admin demo login</v>
       </c>
       <c r="C4" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D4" t="str">
-        <v>0.00 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:43:42.183Z</v>
       </c>
       <c r="F4" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>0.00 sec</v>
+        <v>3.71 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:43:45.889Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -511,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>0.00 sec</v>
+        <v>3.56 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:43:49.444Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -531,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>0.00 sec</v>
+        <v>3.52 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:43:52.968Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -551,13 +550,13 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>0.00 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:43:54.400Z</v>
       </c>
       <c r="F8" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="9">
@@ -571,10 +570,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>0.00 sec</v>
+        <v>3.52 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:43:57.922Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -591,10 +590,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>0.00 sec</v>
+        <v>3.85 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:01.774Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -611,13 +610,13 @@
         <v>PASS</v>
       </c>
       <c r="D11" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:02.558Z</v>
       </c>
       <c r="F11" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="12">
@@ -631,13 +630,13 @@
         <v>PASS</v>
       </c>
       <c r="D12" t="str">
-        <v>0.00 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:03.312Z</v>
       </c>
       <c r="F12" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="13">
@@ -651,13 +650,13 @@
         <v>PASS</v>
       </c>
       <c r="D13" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:04.127Z</v>
       </c>
       <c r="F13" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="14">
@@ -671,13 +670,13 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>0.00 sec</v>
+        <v>0.55 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:04.679Z</v>
       </c>
       <c r="F14" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="15">
@@ -691,13 +690,13 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:05.601Z</v>
       </c>
       <c r="F15" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="16">
@@ -711,13 +710,13 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:06.595Z</v>
       </c>
       <c r="F16" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="17">
@@ -731,13 +730,13 @@
         <v>PASS</v>
       </c>
       <c r="D17" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:07.373Z</v>
       </c>
       <c r="F17" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="18">
@@ -751,13 +750,13 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>0.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:08.095Z</v>
       </c>
       <c r="F18" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="19">
@@ -771,13 +770,13 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:08.876Z</v>
       </c>
       <c r="F19" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="20">
@@ -791,13 +790,13 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:09.452Z</v>
       </c>
       <c r="F20" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="21">
@@ -811,13 +810,13 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:10.349Z</v>
       </c>
       <c r="F21" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="22">
@@ -831,13 +830,13 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:11.321Z</v>
       </c>
       <c r="F22" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="23">
@@ -851,13 +850,13 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>0.00 sec</v>
+        <v>0.51 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:11.829Z</v>
       </c>
       <c r="F23" t="str">
-        <v>Success</v>
+        <v>Email address does not exist.</v>
       </c>
     </row>
     <row r="24">
@@ -871,13 +870,13 @@
         <v>PASS</v>
       </c>
       <c r="D24" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:12.655Z</v>
       </c>
       <c r="F24" t="str">
-        <v>Success</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="25">
@@ -891,13 +890,13 @@
         <v>PASS</v>
       </c>
       <c r="D25" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:13.569Z</v>
       </c>
       <c r="F25" t="str">
-        <v>Success</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="26">
@@ -911,13 +910,13 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:14.382Z</v>
       </c>
       <c r="F26" t="str">
-        <v>Success</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="27">
@@ -931,13 +930,13 @@
         <v>PASS</v>
       </c>
       <c r="D27" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:15.284Z</v>
       </c>
       <c r="F27" t="str">
-        <v>Success</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="28">
@@ -951,13 +950,13 @@
         <v>PASS</v>
       </c>
       <c r="D28" t="str">
-        <v>0.00 sec</v>
+        <v>0.56 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:15.845Z</v>
       </c>
       <c r="F28" t="str">
-        <v>Success</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="29">
@@ -971,13 +970,13 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:16.627Z</v>
       </c>
       <c r="F29" t="str">
-        <v>Success</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="30">
@@ -991,13 +990,13 @@
         <v>PASS</v>
       </c>
       <c r="D30" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:17.438Z</v>
       </c>
       <c r="F30" t="str">
-        <v>Success</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="31">
@@ -1011,13 +1010,13 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:18.328Z</v>
       </c>
       <c r="F31" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="32">
@@ -1031,13 +1030,13 @@
         <v>PASS</v>
       </c>
       <c r="D32" t="str">
-        <v>0.00 sec</v>
+        <v>0.61 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:18.943Z</v>
       </c>
       <c r="F32" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="33">
@@ -1051,13 +1050,13 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:19.884Z</v>
       </c>
       <c r="F33" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="34">
@@ -1071,13 +1070,13 @@
         <v>PASS</v>
       </c>
       <c r="D34" t="str">
-        <v>0.00 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:20.868Z</v>
       </c>
       <c r="F34" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="35">
@@ -1091,13 +1090,13 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:21.649Z</v>
       </c>
       <c r="F35" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="36">
@@ -1111,13 +1110,13 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:22.415Z</v>
       </c>
       <c r="F36" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="37">
@@ -1131,13 +1130,13 @@
         <v>PASS</v>
       </c>
       <c r="D37" t="str">
-        <v>0.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:23.134Z</v>
       </c>
       <c r="F37" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="38">
@@ -1151,13 +1150,13 @@
         <v>PASS</v>
       </c>
       <c r="D38" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:23.910Z</v>
       </c>
       <c r="F38" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="39">
@@ -1171,13 +1170,13 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:24.846Z</v>
       </c>
       <c r="F39" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="40">
@@ -1191,13 +1190,13 @@
         <v>PASS</v>
       </c>
       <c r="D40" t="str">
-        <v>0.00 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:25.602Z</v>
       </c>
       <c r="F40" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="41">
@@ -1211,13 +1210,13 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.00 sec</v>
+        <v>0.56 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:26.165Z</v>
       </c>
       <c r="F41" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="42">
@@ -1231,13 +1230,13 @@
         <v>PASS</v>
       </c>
       <c r="D42" t="str">
-        <v>0.00 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:26.915Z</v>
       </c>
       <c r="F42" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="43">
@@ -1251,13 +1250,13 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.00 sec</v>
+        <v>0.65 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:27.567Z</v>
       </c>
       <c r="F43" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="44">
@@ -1271,13 +1270,13 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:28.145Z</v>
       </c>
       <c r="F44" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="45">
@@ -1291,13 +1290,13 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:29.089Z</v>
       </c>
       <c r="F45" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="46">
@@ -1311,13 +1310,13 @@
         <v>PASS</v>
       </c>
       <c r="D46" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:29.880Z</v>
       </c>
       <c r="F46" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="47">
@@ -1331,13 +1330,13 @@
         <v>PASS</v>
       </c>
       <c r="D47" t="str">
-        <v>0.00 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:30.912Z</v>
       </c>
       <c r="F47" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="48">
@@ -1351,13 +1350,13 @@
         <v>PASS</v>
       </c>
       <c r="D48" t="str">
-        <v>0.00 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:31.666Z</v>
       </c>
       <c r="F48" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="49">
@@ -1371,13 +1370,13 @@
         <v>PASS</v>
       </c>
       <c r="D49" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:32.612Z</v>
       </c>
       <c r="F49" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="50">
@@ -1391,13 +1390,13 @@
         <v>PASS</v>
       </c>
       <c r="D50" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:33.409Z</v>
       </c>
       <c r="F50" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="51">
@@ -1411,13 +1410,13 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>0.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:34.127Z</v>
       </c>
       <c r="F51" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="52">
@@ -1431,13 +1430,13 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:34.931Z</v>
       </c>
       <c r="F52" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="53">
@@ -1451,13 +1450,13 @@
         <v>PASS</v>
       </c>
       <c r="D53" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:35.746Z</v>
       </c>
       <c r="F53" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="54">
@@ -1471,13 +1470,13 @@
         <v>PASS</v>
       </c>
       <c r="D54" t="str">
-        <v>0.00 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:36.483Z</v>
       </c>
       <c r="F54" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="55">
@@ -1491,13 +1490,13 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:37.322Z</v>
       </c>
       <c r="F55" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="56">
@@ -1511,13 +1510,13 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:38.129Z</v>
       </c>
       <c r="F56" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="57">
@@ -1531,13 +1530,13 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>0.00 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:39.144Z</v>
       </c>
       <c r="F57" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="58">
@@ -1551,13 +1550,13 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:39.968Z</v>
       </c>
       <c r="F58" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="59">
@@ -1571,13 +1570,13 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:40.916Z</v>
       </c>
       <c r="F59" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="60">
@@ -1591,13 +1590,13 @@
         <v>PASS</v>
       </c>
       <c r="D60" t="str">
-        <v>0.00 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:41.925Z</v>
       </c>
       <c r="F60" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="61">
@@ -1611,13 +1610,13 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:42.831Z</v>
       </c>
       <c r="F61" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="62">
@@ -1631,13 +1630,13 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>0.00 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:43.594Z</v>
       </c>
       <c r="F62" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="63">
@@ -1651,13 +1650,13 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>0.00 sec</v>
+        <v>0.68 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:44.278Z</v>
       </c>
       <c r="F63" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="64">
@@ -1671,13 +1670,13 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:45.100Z</v>
       </c>
       <c r="F64" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="65">
@@ -1691,13 +1690,13 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:46.073Z</v>
       </c>
       <c r="F65" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="66">
@@ -1711,13 +1710,13 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>0.00 sec</v>
+        <v>0.50 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:46.570Z</v>
       </c>
       <c r="F66" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="67">
@@ -1731,13 +1730,13 @@
         <v>PASS</v>
       </c>
       <c r="D67" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:47.467Z</v>
       </c>
       <c r="F67" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="68">
@@ -1751,13 +1750,13 @@
         <v>PASS</v>
       </c>
       <c r="D68" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:48.045Z</v>
       </c>
       <c r="F68" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="69">
@@ -1771,13 +1770,13 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:49.033Z</v>
       </c>
       <c r="F69" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="70">
@@ -1791,13 +1790,13 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>0.00 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:49.742Z</v>
       </c>
       <c r="F70" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="71">
@@ -1811,13 +1810,13 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:50.561Z</v>
       </c>
       <c r="F71" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="72">
@@ -1831,13 +1830,13 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>0.00 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:51.228Z</v>
       </c>
       <c r="F72" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="73">
@@ -1851,13 +1850,13 @@
         <v>PASS</v>
       </c>
       <c r="D73" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:52.198Z</v>
       </c>
       <c r="F73" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="74">
@@ -1871,13 +1870,13 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:53.106Z</v>
       </c>
       <c r="F74" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="75">
@@ -1891,13 +1890,13 @@
         <v>PASS</v>
       </c>
       <c r="D75" t="str">
-        <v>0.00 sec</v>
+        <v>0.70 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:53.811Z</v>
       </c>
       <c r="F75" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="76">
@@ -1911,13 +1910,13 @@
         <v>PASS</v>
       </c>
       <c r="D76" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:54.644Z</v>
       </c>
       <c r="F76" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="77">
@@ -1931,13 +1930,13 @@
         <v>PASS</v>
       </c>
       <c r="D77" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-31T11:18:33.059Z</v>
+        <v>2026-08-01T10:44:55.457Z</v>
       </c>
       <c r="F77" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="78">
@@ -1951,13 +1950,13 @@
         <v>PASS</v>
       </c>
       <c r="D78" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:44:56.258Z</v>
       </c>
       <c r="F78" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="79">
@@ -1971,13 +1970,13 @@
         <v>PASS</v>
       </c>
       <c r="D79" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:44:57.218Z</v>
       </c>
       <c r="F79" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="80">
@@ -1991,13 +1990,13 @@
         <v>PASS</v>
       </c>
       <c r="D80" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:44:58.135Z</v>
       </c>
       <c r="F80" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="81">
@@ -2011,13 +2010,13 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:44:58.914Z</v>
       </c>
       <c r="F81" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="82">
@@ -2031,13 +2030,13 @@
         <v>PASS</v>
       </c>
       <c r="D82" t="str">
-        <v>0.00 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:44:59.941Z</v>
       </c>
       <c r="F82" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="83">
@@ -2051,13 +2050,13 @@
         <v>PASS</v>
       </c>
       <c r="D83" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:00.767Z</v>
       </c>
       <c r="F83" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="84">
@@ -2071,13 +2070,13 @@
         <v>PASS</v>
       </c>
       <c r="D84" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:01.572Z</v>
       </c>
       <c r="F84" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="85">
@@ -2091,13 +2090,13 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>0.00 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:02.611Z</v>
       </c>
       <c r="F85" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="86">
@@ -2111,13 +2110,13 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:03.466Z</v>
       </c>
       <c r="F86" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="87">
@@ -2131,13 +2130,13 @@
         <v>PASS</v>
       </c>
       <c r="D87" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:04.364Z</v>
       </c>
       <c r="F87" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="88">
@@ -2151,13 +2150,13 @@
         <v>PASS</v>
       </c>
       <c r="D88" t="str">
-        <v>0.00 sec</v>
+        <v>0.60 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:04.962Z</v>
       </c>
       <c r="F88" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="89">
@@ -2171,13 +2170,13 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:05.767Z</v>
       </c>
       <c r="F89" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="90">
@@ -2191,13 +2190,13 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.00 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:06.511Z</v>
       </c>
       <c r="F90" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="91">
@@ -2211,13 +2210,13 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:07.416Z</v>
       </c>
       <c r="F91" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="92">
@@ -2231,13 +2230,13 @@
         <v>PASS</v>
       </c>
       <c r="D92" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:08.195Z</v>
       </c>
       <c r="F92" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="93">
@@ -2251,13 +2250,13 @@
         <v>PASS</v>
       </c>
       <c r="D93" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:09.182Z</v>
       </c>
       <c r="F93" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="94">
@@ -2271,13 +2270,13 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>0.00 sec</v>
+        <v>0.60 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:09.781Z</v>
       </c>
       <c r="F94" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="95">
@@ -2291,13 +2290,13 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.00 sec</v>
+        <v>0.55 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:10.332Z</v>
       </c>
       <c r="F95" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="96">
@@ -2311,13 +2310,13 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:11.146Z</v>
       </c>
       <c r="F96" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="97">
@@ -2331,13 +2330,13 @@
         <v>PASS</v>
       </c>
       <c r="D97" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:12.109Z</v>
       </c>
       <c r="F97" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="98">
@@ -2351,13 +2350,13 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:12.895Z</v>
       </c>
       <c r="F98" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="99">
@@ -2371,13 +2370,13 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>0.00 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:14.001Z</v>
       </c>
       <c r="F99" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="100">
@@ -2391,13 +2390,13 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:14.859Z</v>
       </c>
       <c r="F100" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="101">
@@ -2411,13 +2410,13 @@
         <v>PASS</v>
       </c>
       <c r="D101" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:15.679Z</v>
       </c>
       <c r="F101" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="102">
@@ -2431,13 +2430,13 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>0.00 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:16.748Z</v>
       </c>
       <c r="F102" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="103">
@@ -2451,13 +2450,13 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>0.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:17.472Z</v>
       </c>
       <c r="F103" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="104">
@@ -2471,13 +2470,13 @@
         <v>PASS</v>
       </c>
       <c r="D104" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:18.310Z</v>
       </c>
       <c r="F104" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="105">
@@ -2491,13 +2490,13 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>0.00 sec</v>
+        <v>0.69 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:18.999Z</v>
       </c>
       <c r="F105" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="106">
@@ -2511,13 +2510,13 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.00 sec</v>
+        <v>0.61 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:19.610Z</v>
       </c>
       <c r="F106" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="107">
@@ -2531,13 +2530,13 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:20.194Z</v>
       </c>
       <c r="F107" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="108">
@@ -2551,13 +2550,13 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:20.972Z</v>
       </c>
       <c r="F108" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="109">
@@ -2571,13 +2570,13 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>0.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:21.697Z</v>
       </c>
       <c r="F109" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="110">
@@ -2591,13 +2590,13 @@
         <v>PASS</v>
       </c>
       <c r="D110" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:22.543Z</v>
       </c>
       <c r="F110" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="111">
@@ -2611,13 +2610,13 @@
         <v>PASS</v>
       </c>
       <c r="D111" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:23.479Z</v>
       </c>
       <c r="F111" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="112">
@@ -2631,13 +2630,13 @@
         <v>PASS</v>
       </c>
       <c r="D112" t="str">
-        <v>0.00 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:24.147Z</v>
       </c>
       <c r="F112" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="113">
@@ -2651,13 +2650,13 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:24.945Z</v>
       </c>
       <c r="F113" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="114">
@@ -2671,13 +2670,13 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:25.732Z</v>
       </c>
       <c r="F114" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="115">
@@ -2691,13 +2690,13 @@
         <v>PASS</v>
       </c>
       <c r="D115" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:26.670Z</v>
       </c>
       <c r="F115" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="116">
@@ -2711,13 +2710,13 @@
         <v>PASS</v>
       </c>
       <c r="D116" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:27.511Z</v>
       </c>
       <c r="F116" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="117">
@@ -2731,13 +2730,13 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>0.00 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:28.495Z</v>
       </c>
       <c r="F117" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="118">
@@ -2751,13 +2750,13 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:29.357Z</v>
       </c>
       <c r="F118" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="119">
@@ -2771,13 +2770,13 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:30.225Z</v>
       </c>
       <c r="F119" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="120">
@@ -2791,13 +2790,13 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:31.216Z</v>
       </c>
       <c r="F120" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="121">
@@ -2811,13 +2810,13 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:32.179Z</v>
       </c>
       <c r="F121" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="122">
@@ -2831,13 +2830,13 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:32.761Z</v>
       </c>
       <c r="F122" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="123">
@@ -2851,13 +2850,13 @@
         <v>PASS</v>
       </c>
       <c r="D123" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:33.705Z</v>
       </c>
       <c r="F123" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="124">
@@ -2871,13 +2870,13 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.00 sec</v>
+        <v>0.65 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:34.353Z</v>
       </c>
       <c r="F124" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="125">
@@ -2891,13 +2890,13 @@
         <v>PASS</v>
       </c>
       <c r="D125" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:35.194Z</v>
       </c>
       <c r="F125" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="126">
@@ -2911,13 +2910,13 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:36.019Z</v>
       </c>
       <c r="F126" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="127">
@@ -2931,13 +2930,13 @@
         <v>PASS</v>
       </c>
       <c r="D127" t="str">
-        <v>0.00 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:37.090Z</v>
       </c>
       <c r="F127" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="128">
@@ -2951,13 +2950,13 @@
         <v>PASS</v>
       </c>
       <c r="D128" t="str">
-        <v>0.00 sec</v>
+        <v>0.60 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:37.687Z</v>
       </c>
       <c r="F128" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="129">
@@ -2971,13 +2970,13 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:38.640Z</v>
       </c>
       <c r="F129" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="130">
@@ -2991,13 +2990,13 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:39.505Z</v>
       </c>
       <c r="F130" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="131">
@@ -3011,13 +3010,13 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:40.090Z</v>
       </c>
       <c r="F131" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="132">
@@ -3031,13 +3030,13 @@
         <v>PASS</v>
       </c>
       <c r="D132" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:40.893Z</v>
       </c>
       <c r="F132" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="133">
@@ -3051,13 +3050,13 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:41.783Z</v>
       </c>
       <c r="F133" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="134">
@@ -3071,13 +3070,13 @@
         <v>PASS</v>
       </c>
       <c r="D134" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:42.669Z</v>
       </c>
       <c r="F134" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="135">
@@ -3091,13 +3090,13 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>0.00 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:43.837Z</v>
       </c>
       <c r="F135" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="136">
@@ -3111,13 +3110,13 @@
         <v>PASS</v>
       </c>
       <c r="D136" t="str">
-        <v>0.00 sec</v>
+        <v>0.61 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:44.443Z</v>
       </c>
       <c r="F136" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="137">
@@ -3131,13 +3130,13 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:45.278Z</v>
       </c>
       <c r="F137" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="138">
@@ -3151,13 +3150,13 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>0.00 sec</v>
+        <v>0.56 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:45.842Z</v>
       </c>
       <c r="F138" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="139">
@@ -3171,13 +3170,13 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:46.760Z</v>
       </c>
       <c r="F139" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="140">
@@ -3191,13 +3190,13 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>0.00 sec</v>
+        <v>0.57 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:47.328Z</v>
       </c>
       <c r="F140" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="141">
@@ -3211,13 +3210,13 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:48.123Z</v>
       </c>
       <c r="F141" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="142">
@@ -3231,13 +3230,13 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:49.000Z</v>
       </c>
       <c r="F142" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="143">
@@ -3251,13 +3250,13 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:49.811Z</v>
       </c>
       <c r="F143" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="144">
@@ -3271,13 +3270,13 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:50.660Z</v>
       </c>
       <c r="F144" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="145">
@@ -3291,13 +3290,13 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:51.630Z</v>
       </c>
       <c r="F145" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="146">
@@ -3311,13 +3310,13 @@
         <v>PASS</v>
       </c>
       <c r="D146" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:52.429Z</v>
       </c>
       <c r="F146" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="147">
@@ -3331,13 +3330,13 @@
         <v>PASS</v>
       </c>
       <c r="D147" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:53.421Z</v>
       </c>
       <c r="F147" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="148">
@@ -3351,13 +3350,13 @@
         <v>PASS</v>
       </c>
       <c r="D148" t="str">
-        <v>0.00 sec</v>
+        <v>0.66 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:54.080Z</v>
       </c>
       <c r="F148" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="149">
@@ -3371,13 +3370,13 @@
         <v>PASS</v>
       </c>
       <c r="D149" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:54.661Z</v>
       </c>
       <c r="F149" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="150">
@@ -3391,13 +3390,13 @@
         <v>PASS</v>
       </c>
       <c r="D150" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:55.452Z</v>
       </c>
       <c r="F150" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="151">
@@ -3411,13 +3410,13 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:56.360Z</v>
       </c>
       <c r="F151" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="152">
@@ -3431,13 +3430,13 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.00 sec</v>
+        <v>0.62 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:56.977Z</v>
       </c>
       <c r="F152" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="153">
@@ -3451,13 +3450,13 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.00 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:57.730Z</v>
       </c>
       <c r="F153" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="154">
@@ -3471,13 +3470,13 @@
         <v>PASS</v>
       </c>
       <c r="D154" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:58.564Z</v>
       </c>
       <c r="F154" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="155">
@@ -3491,13 +3490,13 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:59.380Z</v>
       </c>
       <c r="F155" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="156">
@@ -3511,13 +3510,13 @@
         <v>PASS</v>
       </c>
       <c r="D156" t="str">
-        <v>0.00 sec</v>
+        <v>0.54 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:45:59.918Z</v>
       </c>
       <c r="F156" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="157">
@@ -3531,13 +3530,13 @@
         <v>PASS</v>
       </c>
       <c r="D157" t="str">
-        <v>0.00 sec</v>
+        <v>0.73 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:00.649Z</v>
       </c>
       <c r="F157" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="158">
@@ -3551,13 +3550,13 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:01.479Z</v>
       </c>
       <c r="F158" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="159">
@@ -3571,13 +3570,13 @@
         <v>PASS</v>
       </c>
       <c r="D159" t="str">
-        <v>0.00 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:02.194Z</v>
       </c>
       <c r="F159" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="160">
@@ -3591,13 +3590,13 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:03.092Z</v>
       </c>
       <c r="F160" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="161">
@@ -3611,13 +3610,13 @@
         <v>PASS</v>
       </c>
       <c r="D161" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:03.969Z</v>
       </c>
       <c r="F161" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="162">
@@ -3631,13 +3630,13 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:04.852Z</v>
       </c>
       <c r="F162" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="163">
@@ -3651,13 +3650,13 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.00 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:05.852Z</v>
       </c>
       <c r="F163" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="164">
@@ -3671,13 +3670,13 @@
         <v>PASS</v>
       </c>
       <c r="D164" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:06.682Z</v>
       </c>
       <c r="F164" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="165">
@@ -3691,13 +3690,13 @@
         <v>PASS</v>
       </c>
       <c r="D165" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:07.592Z</v>
       </c>
       <c r="F165" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="166">
@@ -3711,13 +3710,13 @@
         <v>PASS</v>
       </c>
       <c r="D166" t="str">
-        <v>0.00 sec</v>
+        <v>0.62 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:08.210Z</v>
       </c>
       <c r="F166" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="167">
@@ -3731,13 +3730,13 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:09.059Z</v>
       </c>
       <c r="F167" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="168">
@@ -3751,13 +3750,13 @@
         <v>PASS</v>
       </c>
       <c r="D168" t="str">
-        <v>0.00 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:09.810Z</v>
       </c>
       <c r="F168" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="169">
@@ -3771,13 +3770,13 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:10.746Z</v>
       </c>
       <c r="F169" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="170">
@@ -3791,13 +3790,13 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:11.610Z</v>
       </c>
       <c r="F170" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="171">
@@ -3811,13 +3810,13 @@
         <v>PASS</v>
       </c>
       <c r="D171" t="str">
-        <v>0.00 sec</v>
+        <v>0.68 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:12.292Z</v>
       </c>
       <c r="F171" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="172">
@@ -3831,13 +3830,13 @@
         <v>PASS</v>
       </c>
       <c r="D172" t="str">
-        <v>0.00 sec</v>
+        <v>0.62 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:12.908Z</v>
       </c>
       <c r="F172" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="173">
@@ -3851,13 +3850,13 @@
         <v>PASS</v>
       </c>
       <c r="D173" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:13.736Z</v>
       </c>
       <c r="F173" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="174">
@@ -3871,13 +3870,13 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.00 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:14.480Z</v>
       </c>
       <c r="F174" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="175">
@@ -3891,13 +3890,13 @@
         <v>PASS</v>
       </c>
       <c r="D175" t="str">
-        <v>0.00 sec</v>
+        <v>2.89 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:17.374Z</v>
       </c>
       <c r="F175" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="176">
@@ -3911,13 +3910,13 @@
         <v>PASS</v>
       </c>
       <c r="D176" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:18.226Z</v>
       </c>
       <c r="F176" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="177">
@@ -3931,13 +3930,13 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:19.221Z</v>
       </c>
       <c r="F177" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="178">
@@ -3951,13 +3950,13 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:20.078Z</v>
       </c>
       <c r="F178" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="179">
@@ -3971,13 +3970,13 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:20.662Z</v>
       </c>
       <c r="F179" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="180">
@@ -3991,13 +3990,13 @@
         <v>PASS</v>
       </c>
       <c r="D180" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:21.453Z</v>
       </c>
       <c r="F180" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="181">
@@ -4011,13 +4010,13 @@
         <v>PASS</v>
       </c>
       <c r="D181" t="str">
-        <v>0.00 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:22.212Z</v>
       </c>
       <c r="F181" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="182">
@@ -4031,13 +4030,13 @@
         <v>PASS</v>
       </c>
       <c r="D182" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:23.060Z</v>
       </c>
       <c r="F182" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="183">
@@ -4051,13 +4050,13 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:23.881Z</v>
       </c>
       <c r="F183" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="184">
@@ -4071,13 +4070,13 @@
         <v>PASS</v>
       </c>
       <c r="D184" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:24.775Z</v>
       </c>
       <c r="F184" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="185">
@@ -4091,13 +4090,13 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:25.593Z</v>
       </c>
       <c r="F185" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="186">
@@ -4111,13 +4110,13 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>0.00 sec</v>
+        <v>0.62 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:26.217Z</v>
       </c>
       <c r="F186" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="187">
@@ -4131,13 +4130,13 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>0.00 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:27.258Z</v>
       </c>
       <c r="F187" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="188">
@@ -4151,13 +4150,13 @@
         <v>PASS</v>
       </c>
       <c r="D188" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:28.201Z</v>
       </c>
       <c r="F188" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="189">
@@ -4171,13 +4170,13 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:29.164Z</v>
       </c>
       <c r="F189" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="190">
@@ -4191,13 +4190,13 @@
         <v>PASS</v>
       </c>
       <c r="D190" t="str">
-        <v>0.00 sec</v>
+        <v>0.63 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:29.797Z</v>
       </c>
       <c r="F190" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="191">
@@ -4211,13 +4210,13 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:30.609Z</v>
       </c>
       <c r="F191" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="192">
@@ -4231,13 +4230,13 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:31.452Z</v>
       </c>
       <c r="F192" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="193">
@@ -4251,13 +4250,13 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:32.363Z</v>
       </c>
       <c r="F193" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="194">
@@ -4271,13 +4270,13 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:33.200Z</v>
       </c>
       <c r="F194" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="195">
@@ -4291,13 +4290,13 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>0.00 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:34.231Z</v>
       </c>
       <c r="F195" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="196">
@@ -4311,13 +4310,13 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:35.092Z</v>
       </c>
       <c r="F196" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="197">
@@ -4331,13 +4330,13 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:35.917Z</v>
       </c>
       <c r="F197" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="198">
@@ -4351,13 +4350,13 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:36.772Z</v>
       </c>
       <c r="F198" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="199">
@@ -4371,13 +4370,13 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>0.00 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:37.756Z</v>
       </c>
       <c r="F199" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="200">
@@ -4391,13 +4390,13 @@
         <v>PASS</v>
       </c>
       <c r="D200" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:38.667Z</v>
       </c>
       <c r="F200" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="201">
@@ -4411,13 +4410,13 @@
         <v>PASS</v>
       </c>
       <c r="D201" t="str">
-        <v>0.00 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:39.747Z</v>
       </c>
       <c r="F201" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="202">
@@ -4431,13 +4430,13 @@
         <v>PASS</v>
       </c>
       <c r="D202" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:40.691Z</v>
       </c>
       <c r="F202" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="203">
@@ -4451,13 +4450,13 @@
         <v>PASS</v>
       </c>
       <c r="D203" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:41.570Z</v>
       </c>
       <c r="F203" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="204">
@@ -4471,13 +4470,13 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>0.00 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:42.720Z</v>
       </c>
       <c r="F204" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="205">
@@ -4491,13 +4490,13 @@
         <v>PASS</v>
       </c>
       <c r="D205" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:43.692Z</v>
       </c>
       <c r="F205" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="206">
@@ -4511,13 +4510,13 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>0.00 sec</v>
+        <v>0.62 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:44.308Z</v>
       </c>
       <c r="F206" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="207">
@@ -4531,13 +4530,13 @@
         <v>PASS</v>
       </c>
       <c r="D207" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:45.294Z</v>
       </c>
       <c r="F207" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="208">
@@ -4551,13 +4550,13 @@
         <v>PASS</v>
       </c>
       <c r="D208" t="str">
-        <v>0.00 sec</v>
+        <v>0.65 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:45.944Z</v>
       </c>
       <c r="F208" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="209">
@@ -4571,13 +4570,13 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:46.785Z</v>
       </c>
       <c r="F209" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="210">
@@ -4591,13 +4590,13 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:47.617Z</v>
       </c>
       <c r="F210" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="211">
@@ -4611,13 +4610,13 @@
         <v>PASS</v>
       </c>
       <c r="D211" t="str">
-        <v>0.00 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:48.331Z</v>
       </c>
       <c r="F211" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="212">
@@ -4631,13 +4630,13 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:49.176Z</v>
       </c>
       <c r="F212" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="213">
@@ -4651,13 +4650,13 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:50.146Z</v>
       </c>
       <c r="F213" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="214">
@@ -4671,13 +4670,13 @@
         <v>PASS</v>
       </c>
       <c r="D214" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:51.019Z</v>
       </c>
       <c r="F214" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="215">
@@ -4691,13 +4690,13 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:51.884Z</v>
       </c>
       <c r="F215" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="216">
@@ -4711,13 +4710,13 @@
         <v>PASS</v>
       </c>
       <c r="D216" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:52.735Z</v>
       </c>
       <c r="F216" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="217">
@@ -4731,13 +4730,13 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.00 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:53.740Z</v>
       </c>
       <c r="F217" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="218">
@@ -4751,13 +4750,13 @@
         <v>PASS</v>
       </c>
       <c r="D218" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:54.668Z</v>
       </c>
       <c r="F218" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="219">
@@ -4771,13 +4770,13 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:55.632Z</v>
       </c>
       <c r="F219" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="220">
@@ -4791,13 +4790,13 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:56.506Z</v>
       </c>
       <c r="F220" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="221">
@@ -4811,13 +4810,13 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:57.345Z</v>
       </c>
       <c r="F221" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="222">
@@ -4831,13 +4830,13 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:58.188Z</v>
       </c>
       <c r="F222" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="223">
@@ -4851,13 +4850,13 @@
         <v>PASS</v>
       </c>
       <c r="D223" t="str">
-        <v>0.00 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:46:59.169Z</v>
       </c>
       <c r="F223" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="224">
@@ -4871,13 +4870,13 @@
         <v>PASS</v>
       </c>
       <c r="D224" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:00.059Z</v>
       </c>
       <c r="F224" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="225">
@@ -4891,13 +4890,13 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:01.018Z</v>
       </c>
       <c r="F225" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="226">
@@ -4911,13 +4910,13 @@
         <v>PASS</v>
       </c>
       <c r="D226" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:01.914Z</v>
       </c>
       <c r="F226" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="227">
@@ -4931,13 +4930,13 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>0.00 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:02.974Z</v>
       </c>
       <c r="F227" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="228">
@@ -4951,13 +4950,13 @@
         <v>PASS</v>
       </c>
       <c r="D228" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:03.862Z</v>
       </c>
       <c r="F228" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="229">
@@ -4971,13 +4970,13 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:04.817Z</v>
       </c>
       <c r="F229" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="230">
@@ -4991,13 +4990,13 @@
         <v>PASS</v>
       </c>
       <c r="D230" t="str">
-        <v>0.00 sec</v>
+        <v>0.60 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:05.419Z</v>
       </c>
       <c r="F230" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="231">
@@ -5011,13 +5010,13 @@
         <v>PASS</v>
       </c>
       <c r="D231" t="str">
-        <v>0.00 sec</v>
+        <v>0.73 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:06.146Z</v>
       </c>
       <c r="F231" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="232">
@@ -5031,13 +5030,13 @@
         <v>PASS</v>
       </c>
       <c r="D232" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:07.085Z</v>
       </c>
       <c r="F232" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="233">
@@ -5051,13 +5050,13 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:07.926Z</v>
       </c>
       <c r="F233" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="234">
@@ -5071,13 +5070,13 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:08.706Z</v>
       </c>
       <c r="F234" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="235">
@@ -5091,13 +5090,13 @@
         <v>PASS</v>
       </c>
       <c r="D235" t="str">
-        <v>0.00 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:09.445Z</v>
       </c>
       <c r="F235" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="236">
@@ -5111,13 +5110,13 @@
         <v>PASS</v>
       </c>
       <c r="D236" t="str">
-        <v>0.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:10.168Z</v>
       </c>
       <c r="F236" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="237">
@@ -5131,13 +5130,13 @@
         <v>PASS</v>
       </c>
       <c r="D237" t="str">
-        <v>0.00 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:11.229Z</v>
       </c>
       <c r="F237" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="238">
@@ -5151,13 +5150,13 @@
         <v>PASS</v>
       </c>
       <c r="D238" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:12.174Z</v>
       </c>
       <c r="F238" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="239">
@@ -5171,13 +5170,13 @@
         <v>PASS</v>
       </c>
       <c r="D239" t="str">
-        <v>0.00 sec</v>
+        <v>0.62 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:12.794Z</v>
       </c>
       <c r="F239" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="240">
@@ -5191,13 +5190,13 @@
         <v>PASS</v>
       </c>
       <c r="D240" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:13.727Z</v>
       </c>
       <c r="F240" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="241">
@@ -5211,13 +5210,13 @@
         <v>PASS</v>
       </c>
       <c r="D241" t="str">
-        <v>0.00 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-31T11:18:33.060Z</v>
+        <v>2026-08-01T10:47:14.470Z</v>
       </c>
       <c r="F241" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="242">
@@ -5231,13 +5230,13 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.00 sec</v>
+        <v>0.61 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:15.079Z</v>
       </c>
       <c r="F242" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="243">
@@ -5251,13 +5250,13 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:16.023Z</v>
       </c>
       <c r="F243" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="244">
@@ -5271,13 +5270,13 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>0.00 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:16.695Z</v>
       </c>
       <c r="F244" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="245">
@@ -5291,13 +5290,13 @@
         <v>PASS</v>
       </c>
       <c r="D245" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:17.529Z</v>
       </c>
       <c r="F245" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="246">
@@ -5311,13 +5310,13 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:18.475Z</v>
       </c>
       <c r="F246" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="247">
@@ -5331,13 +5330,13 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:19.276Z</v>
       </c>
       <c r="F247" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="248">
@@ -5351,13 +5350,13 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:20.111Z</v>
       </c>
       <c r="F248" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="249">
@@ -5371,13 +5370,13 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:21.039Z</v>
       </c>
       <c r="F249" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="250">
@@ -5391,13 +5390,13 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:21.922Z</v>
       </c>
       <c r="F250" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="251">
@@ -5411,13 +5410,13 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:22.717Z</v>
       </c>
       <c r="F251" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="252">
@@ -5431,13 +5430,13 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:23.531Z</v>
       </c>
       <c r="F252" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="253">
@@ -5451,13 +5450,13 @@
         <v>PASS</v>
       </c>
       <c r="D253" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:24.422Z</v>
       </c>
       <c r="F253" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="254">
@@ -5471,13 +5470,13 @@
         <v>PASS</v>
       </c>
       <c r="D254" t="str">
-        <v>0.00 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:25.091Z</v>
       </c>
       <c r="F254" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="255">
@@ -5491,13 +5490,13 @@
         <v>PASS</v>
       </c>
       <c r="D255" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:26.059Z</v>
       </c>
       <c r="F255" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="256">
@@ -5511,13 +5510,13 @@
         <v>PASS</v>
       </c>
       <c r="D256" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:26.909Z</v>
       </c>
       <c r="F256" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="257">
@@ -5531,13 +5530,13 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:27.493Z</v>
       </c>
       <c r="F257" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="258">
@@ -5551,13 +5550,13 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>0.00 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:28.558Z</v>
       </c>
       <c r="F258" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="259">
@@ -5571,13 +5570,13 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>0.00 sec</v>
+        <v>1.09 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:29.648Z</v>
       </c>
       <c r="F259" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="260">
@@ -5591,13 +5590,13 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>0.00 sec</v>
+        <v>0.56 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:30.206Z</v>
       </c>
       <c r="F260" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="261">
@@ -5611,13 +5610,13 @@
         <v>PASS</v>
       </c>
       <c r="D261" t="str">
-        <v>0.00 sec</v>
+        <v>0.70 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:30.909Z</v>
       </c>
       <c r="F261" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="262">
@@ -5631,13 +5630,13 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:31.788Z</v>
       </c>
       <c r="F262" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="263">
@@ -5651,13 +5650,13 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:32.576Z</v>
       </c>
       <c r="F263" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="264">
@@ -5671,13 +5670,13 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>0.00 sec</v>
+        <v>0.66 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:33.234Z</v>
       </c>
       <c r="F264" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="265">
@@ -5691,13 +5690,13 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>0.00 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:34.203Z</v>
       </c>
       <c r="F265" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="266">
@@ -5711,13 +5710,13 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:35.109Z</v>
       </c>
       <c r="F266" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="267">
@@ -5731,13 +5730,13 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:36.095Z</v>
       </c>
       <c r="F267" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="268">
@@ -5751,13 +5750,13 @@
         <v>PASS</v>
       </c>
       <c r="D268" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:36.999Z</v>
       </c>
       <c r="F268" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="269">
@@ -5771,13 +5770,13 @@
         <v>PASS</v>
       </c>
       <c r="D269" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:37.772Z</v>
       </c>
       <c r="F269" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="270">
@@ -5791,13 +5790,13 @@
         <v>PASS</v>
       </c>
       <c r="D270" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:38.595Z</v>
       </c>
       <c r="F270" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="271">
@@ -5811,13 +5810,13 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:39.537Z</v>
       </c>
       <c r="F271" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="272">
@@ -5831,13 +5830,13 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:40.348Z</v>
       </c>
       <c r="F272" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="273">
@@ -5851,13 +5850,13 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.00 sec</v>
+        <v>0.66 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:41.011Z</v>
       </c>
       <c r="F273" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="274">
@@ -5871,13 +5870,13 @@
         <v>PASS</v>
       </c>
       <c r="D274" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:41.852Z</v>
       </c>
       <c r="F274" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="275">
@@ -5891,13 +5890,13 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:42.637Z</v>
       </c>
       <c r="F275" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="276">
@@ -5911,13 +5910,13 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:43.421Z</v>
       </c>
       <c r="F276" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="277">
@@ -5931,13 +5930,13 @@
         <v>PASS</v>
       </c>
       <c r="D277" t="str">
-        <v>0.00 sec</v>
+        <v>1.09 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:44.510Z</v>
       </c>
       <c r="F277" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="278">
@@ -5951,13 +5950,13 @@
         <v>PASS</v>
       </c>
       <c r="D278" t="str">
-        <v>0.00 sec</v>
+        <v>0.63 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:45.141Z</v>
       </c>
       <c r="F278" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="279">
@@ -5971,13 +5970,13 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:46.072Z</v>
       </c>
       <c r="F279" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="280">
@@ -5991,13 +5990,13 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>0.00 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:47.157Z</v>
       </c>
       <c r="F280" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="281">
@@ -6011,13 +6010,13 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>0.00 sec</v>
+        <v>0.64 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:47.799Z</v>
       </c>
       <c r="F281" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="282">
@@ -6031,13 +6030,13 @@
         <v>PASS</v>
       </c>
       <c r="D282" t="str">
-        <v>0.00 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:48.707Z</v>
       </c>
       <c r="F282" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="283">
@@ -6051,13 +6050,13 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:49.598Z</v>
       </c>
       <c r="F283" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="284">
@@ -6071,13 +6070,13 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>0.00 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:50.306Z</v>
       </c>
       <c r="F284" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="285">
@@ -6091,13 +6090,13 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.00 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:51.298Z</v>
       </c>
       <c r="F285" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="286">
@@ -6111,13 +6110,13 @@
         <v>PASS</v>
       </c>
       <c r="D286" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:52.169Z</v>
       </c>
       <c r="F286" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="287">
@@ -6131,13 +6130,13 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:53.021Z</v>
       </c>
       <c r="F287" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="288">
@@ -6151,13 +6150,13 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:53.842Z</v>
       </c>
       <c r="F288" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="289">
@@ -6171,13 +6170,13 @@
         <v>PASS</v>
       </c>
       <c r="D289" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:54.788Z</v>
       </c>
       <c r="F289" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="290">
@@ -6191,13 +6190,13 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>0.00 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:55.371Z</v>
       </c>
       <c r="F290" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="291">
@@ -6211,13 +6210,13 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:56.304Z</v>
       </c>
       <c r="F291" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="292">
@@ -6231,13 +6230,13 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:57.202Z</v>
       </c>
       <c r="F292" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="293">
@@ -6251,13 +6250,13 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:58.003Z</v>
       </c>
       <c r="F293" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="294">
@@ -6271,13 +6270,13 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:58.774Z</v>
       </c>
       <c r="F294" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="295">
@@ -6291,13 +6290,13 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:47:59.656Z</v>
       </c>
       <c r="F295" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="296">
@@ -6311,13 +6310,13 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:00.438Z</v>
       </c>
       <c r="F296" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="297">
@@ -6331,13 +6330,13 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:01.370Z</v>
       </c>
       <c r="F297" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="298">
@@ -6351,13 +6350,13 @@
         <v>PASS</v>
       </c>
       <c r="D298" t="str">
-        <v>0.00 sec</v>
+        <v>0.69 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:02.055Z</v>
       </c>
       <c r="F298" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="299">
@@ -6371,13 +6370,13 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>0.00 sec</v>
+        <v>0.62 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:02.674Z</v>
       </c>
       <c r="F299" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="300">
@@ -6391,13 +6390,13 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:03.472Z</v>
       </c>
       <c r="F300" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="301">
@@ -6411,13 +6410,13 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:04.410Z</v>
       </c>
       <c r="F301" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="302">
@@ -6431,13 +6430,13 @@
         <v>PASS</v>
       </c>
       <c r="D302" t="str">
-        <v>0.00 sec</v>
+        <v>0.65 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:05.058Z</v>
       </c>
       <c r="F302" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="303">
@@ -6451,13 +6450,13 @@
         <v>PASS</v>
       </c>
       <c r="D303" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:05.975Z</v>
       </c>
       <c r="F303" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="304">
@@ -6471,13 +6470,13 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:06.834Z</v>
       </c>
       <c r="F304" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="305">
@@ -6491,13 +6490,13 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:07.622Z</v>
       </c>
       <c r="F305" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="306">
@@ -6511,13 +6510,13 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:08.452Z</v>
       </c>
       <c r="F306" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="307">
@@ -6531,13 +6530,13 @@
         <v>PASS</v>
       </c>
       <c r="D307" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:09.223Z</v>
       </c>
       <c r="F307" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="308">
@@ -6551,13 +6550,13 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.00 sec</v>
+        <v>0.65 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:09.871Z</v>
       </c>
       <c r="F308" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="309">
@@ -6571,13 +6570,13 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:10.691Z</v>
       </c>
       <c r="F309" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="310">
@@ -6591,13 +6590,13 @@
         <v>PASS</v>
       </c>
       <c r="D310" t="str">
-        <v>0.00 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:11.444Z</v>
       </c>
       <c r="F310" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="311">
@@ -6611,13 +6610,13 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:12.309Z</v>
       </c>
       <c r="F311" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="312">
@@ -6631,13 +6630,13 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:13.208Z</v>
       </c>
       <c r="F312" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="313">
@@ -6651,13 +6650,13 @@
         <v>PASS</v>
       </c>
       <c r="D313" t="str">
-        <v>0.00 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:13.970Z</v>
       </c>
       <c r="F313" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="314">
@@ -6671,13 +6670,13 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:14.840Z</v>
       </c>
       <c r="F314" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="315">
@@ -6691,13 +6690,13 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:15.787Z</v>
       </c>
       <c r="F315" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="316">
@@ -6711,13 +6710,13 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:16.607Z</v>
       </c>
       <c r="F316" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="317">
@@ -6731,13 +6730,13 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:17.418Z</v>
       </c>
       <c r="F317" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="318">
@@ -6751,13 +6750,13 @@
         <v>PASS</v>
       </c>
       <c r="D318" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:18.221Z</v>
       </c>
       <c r="F318" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="319">
@@ -6771,13 +6770,13 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:19.138Z</v>
       </c>
       <c r="F319" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="320">
@@ -6791,13 +6790,13 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:19.987Z</v>
       </c>
       <c r="F320" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="321">
@@ -6811,13 +6810,13 @@
         <v>PASS</v>
       </c>
       <c r="D321" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:20.939Z</v>
       </c>
       <c r="F321" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="322">
@@ -6831,13 +6830,13 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:21.757Z</v>
       </c>
       <c r="F322" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="323">
@@ -6851,13 +6850,13 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:22.553Z</v>
       </c>
       <c r="F323" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="324">
@@ -6871,13 +6870,13 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>0.00 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:23.579Z</v>
       </c>
       <c r="F324" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="325">
@@ -6891,13 +6890,13 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:24.472Z</v>
       </c>
       <c r="F325" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="326">
@@ -6911,13 +6910,13 @@
         <v>PASS</v>
       </c>
       <c r="D326" t="str">
-        <v>0.00 sec</v>
+        <v>0.56 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:25.037Z</v>
       </c>
       <c r="F326" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="327">
@@ -6931,13 +6930,13 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.00 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:25.774Z</v>
       </c>
       <c r="F327" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="328">
@@ -6951,13 +6950,13 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:26.642Z</v>
       </c>
       <c r="F328" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="329">
@@ -6971,13 +6970,13 @@
         <v>PASS</v>
       </c>
       <c r="D329" t="str">
-        <v>0.00 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:27.670Z</v>
       </c>
       <c r="F329" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="330">
@@ -6991,13 +6990,13 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:28.458Z</v>
       </c>
       <c r="F330" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="331">
@@ -7011,13 +7010,13 @@
         <v>PASS</v>
       </c>
       <c r="D331" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:29.335Z</v>
       </c>
       <c r="F331" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="332">
@@ -7031,13 +7030,13 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>0.00 sec</v>
+        <v>0.68 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:30.013Z</v>
       </c>
       <c r="F332" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="333">
@@ -7051,13 +7050,13 @@
         <v>PASS</v>
       </c>
       <c r="D333" t="str">
-        <v>0.00 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:30.903Z</v>
       </c>
       <c r="F333" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="334">
@@ -7071,13 +7070,13 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:31.747Z</v>
       </c>
       <c r="F334" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="335">
@@ -7091,13 +7090,13 @@
         <v>PASS</v>
       </c>
       <c r="D335" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:32.557Z</v>
       </c>
       <c r="F335" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="336">
@@ -7111,13 +7110,13 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>0.00 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:33.318Z</v>
       </c>
       <c r="F336" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="337">
@@ -7131,13 +7130,13 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>0.00 sec</v>
+        <v>3.63 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:36.954Z</v>
       </c>
       <c r="F337" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="338">
@@ -7151,13 +7150,13 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>0.00 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:37.790Z</v>
       </c>
       <c r="F338" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="339">
@@ -7171,13 +7170,13 @@
         <v>PASS</v>
       </c>
       <c r="D339" t="str">
-        <v>0.00 sec</v>
+        <v>2.94 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:40.733Z</v>
       </c>
       <c r="F339" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="340">
@@ -7191,13 +7190,13 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:41.602Z</v>
       </c>
       <c r="F340" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="341">
@@ -7211,13 +7210,13 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.00 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:42.364Z</v>
       </c>
       <c r="F341" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="342">
@@ -7231,13 +7230,13 @@
         <v>PASS</v>
       </c>
       <c r="D342" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:43.133Z</v>
       </c>
       <c r="F342" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="343">
@@ -7251,13 +7250,13 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:44.058Z</v>
       </c>
       <c r="F343" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="344">
@@ -7271,13 +7270,13 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:44.871Z</v>
       </c>
       <c r="F344" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="345">
@@ -7291,13 +7290,13 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>0.00 sec</v>
+        <v>0.73 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:45.606Z</v>
       </c>
       <c r="F345" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="346">
@@ -7311,13 +7310,13 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.00 sec</v>
+        <v>0.64 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:46.245Z</v>
       </c>
       <c r="F346" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="347">
@@ -7331,13 +7330,13 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:47.038Z</v>
       </c>
       <c r="F347" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="348">
@@ -7351,13 +7350,13 @@
         <v>PASS</v>
       </c>
       <c r="D348" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:47.904Z</v>
       </c>
       <c r="F348" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="349">
@@ -7371,13 +7370,13 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:48.674Z</v>
       </c>
       <c r="F349" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="350">
@@ -7391,13 +7390,13 @@
         <v>PASS</v>
       </c>
       <c r="D350" t="str">
-        <v>0.00 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:49.488Z</v>
       </c>
       <c r="F350" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="351">
@@ -7411,13 +7410,13 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>0.00 sec</v>
+        <v>3.10 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:52.590Z</v>
       </c>
       <c r="F351" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="352">
@@ -7431,13 +7430,13 @@
         <v>PASS</v>
       </c>
       <c r="D352" t="str">
-        <v>0.00 sec</v>
+        <v>0.68 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:53.268Z</v>
       </c>
       <c r="F352" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="353">
@@ -7451,13 +7450,13 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.00 sec</v>
+        <v>0.66 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:53.928Z</v>
       </c>
       <c r="F353" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="354">
@@ -7471,13 +7470,13 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.00 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:54.647Z</v>
       </c>
       <c r="F354" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="355">
@@ -7491,13 +7490,13 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>0.00 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:55.675Z</v>
       </c>
       <c r="F355" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="356">
@@ -7511,13 +7510,13 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:56.529Z</v>
       </c>
       <c r="F356" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="357">
@@ -7531,13 +7530,13 @@
         <v>PASS</v>
       </c>
       <c r="D357" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:57.488Z</v>
       </c>
       <c r="F357" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="358">
@@ -7551,13 +7550,13 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:58.337Z</v>
       </c>
       <c r="F358" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="359">
@@ -7571,13 +7570,13 @@
         <v>PASS</v>
       </c>
       <c r="D359" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:48:59.119Z</v>
       </c>
       <c r="F359" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="360">
@@ -7591,13 +7590,13 @@
         <v>PASS</v>
       </c>
       <c r="D360" t="str">
-        <v>0.00 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:00.159Z</v>
       </c>
       <c r="F360" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="361">
@@ -7611,13 +7610,13 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>0.00 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:01.122Z</v>
       </c>
       <c r="F361" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="362">
@@ -7631,13 +7630,13 @@
         <v>PASS</v>
       </c>
       <c r="D362" t="str">
-        <v>0.00 sec</v>
+        <v>0.65 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:01.774Z</v>
       </c>
       <c r="F362" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="363">
@@ -7651,13 +7650,13 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:02.725Z</v>
       </c>
       <c r="F363" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="364">
@@ -7671,13 +7670,13 @@
         <v>PASS</v>
       </c>
       <c r="D364" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:03.550Z</v>
       </c>
       <c r="F364" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="365">
@@ -7691,13 +7690,13 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:04.368Z</v>
       </c>
       <c r="F365" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="366">
@@ -7711,13 +7710,13 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:05.156Z</v>
       </c>
       <c r="F366" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="367">
@@ -7731,13 +7730,13 @@
         <v>PASS</v>
       </c>
       <c r="D367" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:06.103Z</v>
       </c>
       <c r="F367" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="368">
@@ -7751,13 +7750,13 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>0.00 sec</v>
+        <v>0.64 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:06.738Z</v>
       </c>
       <c r="F368" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="369">
@@ -7771,13 +7770,13 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>0.00 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:07.690Z</v>
       </c>
       <c r="F369" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="370">
@@ -7791,13 +7790,13 @@
         <v>PASS</v>
       </c>
       <c r="D370" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:08.539Z</v>
       </c>
       <c r="F370" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="371">
@@ -7811,13 +7810,13 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:09.325Z</v>
       </c>
       <c r="F371" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="372">
@@ -7831,13 +7830,13 @@
         <v>PASS</v>
       </c>
       <c r="D372" t="str">
-        <v>0.00 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:10.123Z</v>
       </c>
       <c r="F372" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="373">
@@ -7851,13 +7850,13 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>0.00 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:10.983Z</v>
       </c>
       <c r="F373" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="374">
@@ -7871,13 +7870,13 @@
         <v>PASS</v>
       </c>
       <c r="D374" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:11.749Z</v>
       </c>
       <c r="F374" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="375">
@@ -7891,13 +7890,13 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:12.673Z</v>
       </c>
       <c r="F375" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="376">
@@ -7911,13 +7910,13 @@
         <v>PASS</v>
       </c>
       <c r="D376" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:13.501Z</v>
       </c>
       <c r="F376" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="377">
@@ -7931,13 +7930,13 @@
         <v>PASS</v>
       </c>
       <c r="D377" t="str">
-        <v>0.00 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:14.294Z</v>
       </c>
       <c r="F377" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="378">
@@ -7951,13 +7950,13 @@
         <v>PASS</v>
       </c>
       <c r="D378" t="str">
-        <v>0.00 sec</v>
+        <v>0.59 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:14.889Z</v>
       </c>
       <c r="F378" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="379">
@@ -7971,13 +7970,13 @@
         <v>PASS</v>
       </c>
       <c r="D379" t="str">
-        <v>0.00 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:15.654Z</v>
       </c>
       <c r="F379" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="380">
@@ -7991,13 +7990,13 @@
         <v>PASS</v>
       </c>
       <c r="D380" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:16.483Z</v>
       </c>
       <c r="F380" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="381">
@@ -8011,13 +8010,13 @@
         <v>PASS</v>
       </c>
       <c r="D381" t="str">
-        <v>0.00 sec</v>
+        <v>0.73 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:17.218Z</v>
       </c>
       <c r="F381" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="382">
@@ -8031,13 +8030,13 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:18.087Z</v>
       </c>
       <c r="F382" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="383">
@@ -8051,13 +8050,13 @@
         <v>PASS</v>
       </c>
       <c r="D383" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:18.907Z</v>
       </c>
       <c r="F383" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="384">
@@ -8071,13 +8070,13 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>0.00 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:19.917Z</v>
       </c>
       <c r="F384" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="385">
@@ -8091,13 +8090,13 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:20.833Z</v>
       </c>
       <c r="F385" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="386">
@@ -8111,13 +8110,13 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>0.00 sec</v>
+        <v>0.57 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:21.405Z</v>
       </c>
       <c r="F386" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="387">
@@ -8131,13 +8130,13 @@
         <v>PASS</v>
       </c>
       <c r="D387" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:22.334Z</v>
       </c>
       <c r="F387" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="388">
@@ -8151,13 +8150,13 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.00 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:23.206Z</v>
       </c>
       <c r="F388" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="389">
@@ -8171,13 +8170,13 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.00 sec</v>
+        <v>0.57 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:23.774Z</v>
       </c>
       <c r="F389" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="390">
@@ -8191,13 +8190,13 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>0.00 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:24.777Z</v>
       </c>
       <c r="F390" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="391">
@@ -8211,13 +8210,13 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.00 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:25.694Z</v>
       </c>
       <c r="F391" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="392">
@@ -8231,13 +8230,13 @@
         <v>PASS</v>
       </c>
       <c r="D392" t="str">
-        <v>0.00 sec</v>
+        <v>0.56 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:26.257Z</v>
       </c>
       <c r="F392" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="393">
@@ -8251,13 +8250,13 @@
         <v>PASS</v>
       </c>
       <c r="D393" t="str">
-        <v>0.00 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:27.194Z</v>
       </c>
       <c r="F393" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="394">
@@ -8271,13 +8270,13 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>0.00 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:28.040Z</v>
       </c>
       <c r="F394" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="395">
@@ -8291,13 +8290,13 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>0.00 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:28.824Z</v>
       </c>
       <c r="F395" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="396">
@@ -8311,13 +8310,13 @@
         <v>PASS</v>
       </c>
       <c r="D396" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:29.651Z</v>
       </c>
       <c r="F396" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="397">
@@ -8331,13 +8330,13 @@
         <v>PASS</v>
       </c>
       <c r="D397" t="str">
-        <v>0.00 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:30.585Z</v>
       </c>
       <c r="F397" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="398">
@@ -8351,13 +8350,13 @@
         <v>PASS</v>
       </c>
       <c r="D398" t="str">
-        <v>0.00 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:31.420Z</v>
       </c>
       <c r="F398" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="399">
@@ -8371,13 +8370,13 @@
         <v>PASS</v>
       </c>
       <c r="D399" t="str">
-        <v>0.00 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:32.317Z</v>
       </c>
       <c r="F399" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="400">
@@ -8391,13 +8390,13 @@
         <v>PASS</v>
       </c>
       <c r="D400" t="str">
-        <v>0.00 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:33.200Z</v>
       </c>
       <c r="F400" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="401">
@@ -8411,13 +8410,13 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>0.00 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-31T11:18:33.061Z</v>
+        <v>2026-08-01T10:49:34.017Z</v>
       </c>
       <c r="F401" t="str">
-        <v>Success</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium Report.xlsx
+++ b/reports/Selenium Report.xlsx
@@ -427,16 +427,16 @@
         <v>Valid citizen demo login</v>
       </c>
       <c r="C2" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>1.49 sec</v>
+        <v>2.02 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-01T10:43:40.603Z</v>
+        <v>2026-07-31T11:23:05.559Z</v>
       </c>
       <c r="F2" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="3">
@@ -447,16 +447,16 @@
         <v>Valid volunteer demo login</v>
       </c>
       <c r="C3" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>0.83 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-01T10:43:41.433Z</v>
+        <v>2026-07-31T11:23:07.122Z</v>
       </c>
       <c r="F3" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="4">
@@ -467,16 +467,16 @@
         <v>Valid admin demo login</v>
       </c>
       <c r="C4" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>0.75 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-01T10:43:42.183Z</v>
+        <v>2026-07-31T11:23:08.651Z</v>
       </c>
       <c r="F4" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="5">
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>3.71 sec</v>
+        <v>3.83 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-01T10:43:45.889Z</v>
+        <v>2026-07-31T11:23:12.484Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>3.56 sec</v>
+        <v>3.89 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-01T10:43:49.444Z</v>
+        <v>2026-07-31T11:23:16.374Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>3.52 sec</v>
+        <v>3.73 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-01T10:43:52.968Z</v>
+        <v>2026-07-31T11:23:20.105Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,13 +550,13 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>1.43 sec</v>
+        <v>1.81 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-01T10:43:54.400Z</v>
+        <v>2026-07-31T11:23:21.918Z</v>
       </c>
       <c r="F8" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="9">
@@ -570,10 +570,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>3.52 sec</v>
+        <v>3.87 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-01T10:43:57.922Z</v>
+        <v>2026-07-31T11:23:25.783Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -590,10 +590,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>3.85 sec</v>
+        <v>3.87 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-01T10:44:01.774Z</v>
+        <v>2026-07-31T11:23:29.655Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -610,13 +610,13 @@
         <v>PASS</v>
       </c>
       <c r="D11" t="str">
-        <v>0.78 sec</v>
+        <v>1.37 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-01T10:44:02.558Z</v>
+        <v>2026-07-31T11:23:31.026Z</v>
       </c>
       <c r="F11" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="12">
@@ -630,13 +630,13 @@
         <v>PASS</v>
       </c>
       <c r="D12" t="str">
-        <v>0.75 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-01T10:44:03.312Z</v>
+        <v>2026-07-31T11:23:32.337Z</v>
       </c>
       <c r="F12" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>PASS</v>
       </c>
       <c r="D13" t="str">
-        <v>0.81 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-01T10:44:04.127Z</v>
+        <v>2026-07-31T11:23:33.813Z</v>
       </c>
       <c r="F13" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="14">
@@ -670,13 +670,13 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>0.55 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-01T10:44:04.679Z</v>
+        <v>2026-07-31T11:23:35.240Z</v>
       </c>
       <c r="F14" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="15">
@@ -690,13 +690,13 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>0.92 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-01T10:44:05.601Z</v>
+        <v>2026-07-31T11:23:36.759Z</v>
       </c>
       <c r="F15" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="16">
@@ -710,13 +710,13 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>0.99 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-01T10:44:06.595Z</v>
+        <v>2026-07-31T11:23:38.208Z</v>
       </c>
       <c r="F16" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="17">
@@ -730,13 +730,13 @@
         <v>PASS</v>
       </c>
       <c r="D17" t="str">
-        <v>0.78 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-01T10:44:07.373Z</v>
+        <v>2026-07-31T11:23:39.557Z</v>
       </c>
       <c r="F17" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="18">
@@ -750,13 +750,13 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>0.72 sec</v>
+        <v>1.30 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-01T10:44:08.095Z</v>
+        <v>2026-07-31T11:23:40.861Z</v>
       </c>
       <c r="F18" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="19">
@@ -770,13 +770,13 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>0.78 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-01T10:44:08.876Z</v>
+        <v>2026-07-31T11:23:42.308Z</v>
       </c>
       <c r="F19" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="20">
@@ -790,13 +790,13 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>0.58 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-01T10:44:09.452Z</v>
+        <v>2026-07-31T11:23:43.673Z</v>
       </c>
       <c r="F20" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="21">
@@ -810,13 +810,13 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>0.90 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-01T10:44:10.349Z</v>
+        <v>2026-07-31T11:23:45.155Z</v>
       </c>
       <c r="F21" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="22">
@@ -830,13 +830,13 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>0.97 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-01T10:44:11.321Z</v>
+        <v>2026-07-31T11:23:46.322Z</v>
       </c>
       <c r="F22" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="23">
@@ -850,13 +850,13 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>0.51 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-01T10:44:11.829Z</v>
+        <v>2026-07-31T11:23:47.656Z</v>
       </c>
       <c r="F23" t="str">
-        <v>Email address does not exist.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="24">
@@ -870,13 +870,13 @@
         <v>PASS</v>
       </c>
       <c r="D24" t="str">
-        <v>0.83 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-01T10:44:12.655Z</v>
+        <v>2026-07-31T11:23:48.982Z</v>
       </c>
       <c r="F24" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="25">
@@ -890,13 +890,13 @@
         <v>PASS</v>
       </c>
       <c r="D25" t="str">
-        <v>0.91 sec</v>
+        <v>1.59 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-01T10:44:13.569Z</v>
+        <v>2026-07-31T11:23:50.572Z</v>
       </c>
       <c r="F25" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="26">
@@ -910,13 +910,13 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.81 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-01T10:44:14.382Z</v>
+        <v>2026-07-31T11:23:52.013Z</v>
       </c>
       <c r="F26" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="27">
@@ -930,13 +930,13 @@
         <v>PASS</v>
       </c>
       <c r="D27" t="str">
-        <v>0.90 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-01T10:44:15.284Z</v>
+        <v>2026-07-31T11:23:53.575Z</v>
       </c>
       <c r="F27" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="28">
@@ -950,13 +950,13 @@
         <v>PASS</v>
       </c>
       <c r="D28" t="str">
-        <v>0.56 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-01T10:44:15.845Z</v>
+        <v>2026-07-31T11:23:54.922Z</v>
       </c>
       <c r="F28" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="29">
@@ -970,13 +970,13 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.78 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-01T10:44:16.627Z</v>
+        <v>2026-07-31T11:23:56.272Z</v>
       </c>
       <c r="F29" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="30">
@@ -990,13 +990,13 @@
         <v>PASS</v>
       </c>
       <c r="D30" t="str">
-        <v>0.81 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-01T10:44:17.438Z</v>
+        <v>2026-07-31T11:23:57.581Z</v>
       </c>
       <c r="F30" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="31">
@@ -1010,13 +1010,13 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>0.89 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-01T10:44:18.328Z</v>
+        <v>2026-07-31T11:23:59.067Z</v>
       </c>
       <c r="F31" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="32">
@@ -1030,13 +1030,13 @@
         <v>PASS</v>
       </c>
       <c r="D32" t="str">
-        <v>0.61 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-01T10:44:18.943Z</v>
+        <v>2026-07-31T11:24:00.343Z</v>
       </c>
       <c r="F32" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="33">
@@ -1050,13 +1050,13 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>0.94 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-01T10:44:19.884Z</v>
+        <v>2026-07-31T11:24:01.868Z</v>
       </c>
       <c r="F33" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="34">
@@ -1070,13 +1070,13 @@
         <v>PASS</v>
       </c>
       <c r="D34" t="str">
-        <v>0.98 sec</v>
+        <v>1.27 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-01T10:44:20.868Z</v>
+        <v>2026-07-31T11:24:03.141Z</v>
       </c>
       <c r="F34" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="35">
@@ -1090,13 +1090,13 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.78 sec</v>
+        <v>1.39 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-01T10:44:21.649Z</v>
+        <v>2026-07-31T11:24:04.530Z</v>
       </c>
       <c r="F35" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="36">
@@ -1110,13 +1110,13 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.77 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-01T10:44:22.415Z</v>
+        <v>2026-07-31T11:24:05.839Z</v>
       </c>
       <c r="F36" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="37">
@@ -1130,13 +1130,13 @@
         <v>PASS</v>
       </c>
       <c r="D37" t="str">
-        <v>0.72 sec</v>
+        <v>1.57 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-01T10:44:23.134Z</v>
+        <v>2026-07-31T11:24:07.411Z</v>
       </c>
       <c r="F37" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="38">
@@ -1150,13 +1150,13 @@
         <v>PASS</v>
       </c>
       <c r="D38" t="str">
-        <v>0.78 sec</v>
+        <v>1.38 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-01T10:44:23.910Z</v>
+        <v>2026-07-31T11:24:08.790Z</v>
       </c>
       <c r="F38" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="39">
@@ -1170,13 +1170,13 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>0.94 sec</v>
+        <v>1.42 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-01T10:44:24.846Z</v>
+        <v>2026-07-31T11:24:10.208Z</v>
       </c>
       <c r="F39" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="40">
@@ -1190,13 +1190,13 @@
         <v>PASS</v>
       </c>
       <c r="D40" t="str">
-        <v>0.76 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-01T10:44:25.602Z</v>
+        <v>2026-07-31T11:24:11.655Z</v>
       </c>
       <c r="F40" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="41">
@@ -1210,13 +1210,13 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>0.56 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-01T10:44:26.165Z</v>
+        <v>2026-07-31T11:24:12.989Z</v>
       </c>
       <c r="F41" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="42">
@@ -1230,13 +1230,13 @@
         <v>PASS</v>
       </c>
       <c r="D42" t="str">
-        <v>0.75 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-01T10:44:26.915Z</v>
+        <v>2026-07-31T11:24:14.303Z</v>
       </c>
       <c r="F42" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="43">
@@ -1250,13 +1250,13 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.65 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-01T10:44:27.567Z</v>
+        <v>2026-07-31T11:24:15.755Z</v>
       </c>
       <c r="F43" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="44">
@@ -1270,13 +1270,13 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.58 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-01T10:44:28.145Z</v>
+        <v>2026-07-31T11:24:17.098Z</v>
       </c>
       <c r="F44" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="45">
@@ -1290,13 +1290,13 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.94 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-01T10:44:29.089Z</v>
+        <v>2026-07-31T11:24:18.590Z</v>
       </c>
       <c r="F45" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="46">
@@ -1310,13 +1310,13 @@
         <v>PASS</v>
       </c>
       <c r="D46" t="str">
-        <v>0.79 sec</v>
+        <v>1.37 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-01T10:44:29.880Z</v>
+        <v>2026-07-31T11:24:19.959Z</v>
       </c>
       <c r="F46" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="47">
@@ -1330,13 +1330,13 @@
         <v>PASS</v>
       </c>
       <c r="D47" t="str">
-        <v>1.03 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-01T10:44:30.912Z</v>
+        <v>2026-07-31T11:24:21.305Z</v>
       </c>
       <c r="F47" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="48">
@@ -1350,13 +1350,13 @@
         <v>PASS</v>
       </c>
       <c r="D48" t="str">
-        <v>0.75 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-01T10:44:31.666Z</v>
+        <v>2026-07-31T11:24:22.640Z</v>
       </c>
       <c r="F48" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="49">
@@ -1370,13 +1370,13 @@
         <v>PASS</v>
       </c>
       <c r="D49" t="str">
-        <v>0.95 sec</v>
+        <v>1.42 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-01T10:44:32.612Z</v>
+        <v>2026-07-31T11:24:24.057Z</v>
       </c>
       <c r="F49" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="50">
@@ -1390,13 +1390,13 @@
         <v>PASS</v>
       </c>
       <c r="D50" t="str">
-        <v>0.80 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-01T10:44:33.409Z</v>
+        <v>2026-07-31T11:24:25.540Z</v>
       </c>
       <c r="F50" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="51">
@@ -1410,13 +1410,13 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>0.72 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-01T10:44:34.127Z</v>
+        <v>2026-07-31T11:24:27.105Z</v>
       </c>
       <c r="F51" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="52">
@@ -1430,13 +1430,13 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>0.80 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-01T10:44:34.931Z</v>
+        <v>2026-07-31T11:24:28.440Z</v>
       </c>
       <c r="F52" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="53">
@@ -1450,13 +1450,13 @@
         <v>PASS</v>
       </c>
       <c r="D53" t="str">
-        <v>0.81 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-01T10:44:35.746Z</v>
+        <v>2026-07-31T11:24:29.789Z</v>
       </c>
       <c r="F53" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="54">
@@ -1470,13 +1470,13 @@
         <v>PASS</v>
       </c>
       <c r="D54" t="str">
-        <v>0.74 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-01T10:44:36.483Z</v>
+        <v>2026-07-31T11:24:31.121Z</v>
       </c>
       <c r="F54" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="55">
@@ -1490,13 +1490,13 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.84 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-01T10:44:37.322Z</v>
+        <v>2026-07-31T11:24:32.588Z</v>
       </c>
       <c r="F55" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="56">
@@ -1510,13 +1510,13 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.81 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-01T10:44:38.129Z</v>
+        <v>2026-07-31T11:24:33.772Z</v>
       </c>
       <c r="F56" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="57">
@@ -1530,13 +1530,13 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>1.01 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-01T10:44:39.144Z</v>
+        <v>2026-07-31T11:24:35.336Z</v>
       </c>
       <c r="F57" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="58">
@@ -1550,13 +1550,13 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>0.82 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-01T10:44:39.968Z</v>
+        <v>2026-07-31T11:24:36.788Z</v>
       </c>
       <c r="F58" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="59">
@@ -1570,13 +1570,13 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.95 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-01T10:44:40.916Z</v>
+        <v>2026-07-31T11:24:38.138Z</v>
       </c>
       <c r="F59" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="60">
@@ -1590,13 +1590,13 @@
         <v>PASS</v>
       </c>
       <c r="D60" t="str">
-        <v>1.01 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-01T10:44:41.925Z</v>
+        <v>2026-07-31T11:24:39.465Z</v>
       </c>
       <c r="F60" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="61">
@@ -1610,13 +1610,13 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>0.91 sec</v>
+        <v>1.57 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-01T10:44:42.831Z</v>
+        <v>2026-07-31T11:24:41.040Z</v>
       </c>
       <c r="F61" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="62">
@@ -1630,13 +1630,13 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>0.76 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-01T10:44:43.594Z</v>
+        <v>2026-07-31T11:24:42.482Z</v>
       </c>
       <c r="F62" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="63">
@@ -1650,13 +1650,13 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>0.68 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-01T10:44:44.278Z</v>
+        <v>2026-07-31T11:24:43.999Z</v>
       </c>
       <c r="F63" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="64">
@@ -1670,13 +1670,13 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>0.82 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-01T10:44:45.100Z</v>
+        <v>2026-07-31T11:24:45.453Z</v>
       </c>
       <c r="F64" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="65">
@@ -1690,13 +1690,13 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.97 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-01T10:44:46.073Z</v>
+        <v>2026-07-31T11:24:46.788Z</v>
       </c>
       <c r="F65" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="66">
@@ -1710,13 +1710,13 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>0.50 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-01T10:44:46.570Z</v>
+        <v>2026-07-31T11:24:48.110Z</v>
       </c>
       <c r="F66" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="67">
@@ -1730,13 +1730,13 @@
         <v>PASS</v>
       </c>
       <c r="D67" t="str">
-        <v>0.90 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-01T10:44:47.467Z</v>
+        <v>2026-07-31T11:24:49.673Z</v>
       </c>
       <c r="F67" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="68">
@@ -1750,13 +1750,13 @@
         <v>PASS</v>
       </c>
       <c r="D68" t="str">
-        <v>0.58 sec</v>
+        <v>1.30 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-01T10:44:48.045Z</v>
+        <v>2026-07-31T11:24:50.973Z</v>
       </c>
       <c r="F68" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="69">
@@ -1770,13 +1770,13 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>0.99 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-01T10:44:49.033Z</v>
+        <v>2026-07-31T11:24:52.499Z</v>
       </c>
       <c r="F69" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="70">
@@ -1790,13 +1790,13 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>0.71 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-01T10:44:49.742Z</v>
+        <v>2026-07-31T11:24:53.937Z</v>
       </c>
       <c r="F70" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="71">
@@ -1810,13 +1810,13 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>0.82 sec</v>
+        <v>1.37 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-01T10:44:50.561Z</v>
+        <v>2026-07-31T11:24:55.307Z</v>
       </c>
       <c r="F71" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="72">
@@ -1830,13 +1830,13 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>0.67 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-01T10:44:51.228Z</v>
+        <v>2026-07-31T11:24:56.620Z</v>
       </c>
       <c r="F72" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="73">
@@ -1850,13 +1850,13 @@
         <v>PASS</v>
       </c>
       <c r="D73" t="str">
-        <v>0.97 sec</v>
+        <v>1.42 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-01T10:44:52.198Z</v>
+        <v>2026-07-31T11:24:58.038Z</v>
       </c>
       <c r="F73" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="74">
@@ -1870,13 +1870,13 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.91 sec</v>
+        <v>1.37 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-01T10:44:53.106Z</v>
+        <v>2026-07-31T11:24:59.409Z</v>
       </c>
       <c r="F74" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="75">
@@ -1890,13 +1890,13 @@
         <v>PASS</v>
       </c>
       <c r="D75" t="str">
-        <v>0.70 sec</v>
+        <v>1.58 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-01T10:44:53.811Z</v>
+        <v>2026-07-31T11:25:00.987Z</v>
       </c>
       <c r="F75" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="76">
@@ -1910,13 +1910,13 @@
         <v>PASS</v>
       </c>
       <c r="D76" t="str">
-        <v>0.83 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-01T10:44:54.644Z</v>
+        <v>2026-07-31T11:25:02.337Z</v>
       </c>
       <c r="F76" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="77">
@@ -1930,13 +1930,13 @@
         <v>PASS</v>
       </c>
       <c r="D77" t="str">
-        <v>0.81 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-01T10:44:55.457Z</v>
+        <v>2026-07-31T11:25:03.673Z</v>
       </c>
       <c r="F77" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="78">
@@ -1950,13 +1950,13 @@
         <v>PASS</v>
       </c>
       <c r="D78" t="str">
-        <v>0.80 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-01T10:44:56.258Z</v>
+        <v>2026-07-31T11:25:05.014Z</v>
       </c>
       <c r="F78" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="79">
@@ -1970,13 +1970,13 @@
         <v>PASS</v>
       </c>
       <c r="D79" t="str">
-        <v>0.96 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-01T10:44:57.218Z</v>
+        <v>2026-07-31T11:25:06.471Z</v>
       </c>
       <c r="F79" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="80">
@@ -1990,13 +1990,13 @@
         <v>PASS</v>
       </c>
       <c r="D80" t="str">
-        <v>0.92 sec</v>
+        <v>1.37 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-01T10:44:58.135Z</v>
+        <v>2026-07-31T11:25:07.838Z</v>
       </c>
       <c r="F80" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="81">
@@ -2010,13 +2010,13 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>0.78 sec</v>
+        <v>1.58 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-01T10:44:58.914Z</v>
+        <v>2026-07-31T11:25:09.423Z</v>
       </c>
       <c r="F81" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="82">
@@ -2030,13 +2030,13 @@
         <v>PASS</v>
       </c>
       <c r="D82" t="str">
-        <v>1.03 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-01T10:44:59.941Z</v>
+        <v>2026-07-31T11:25:10.902Z</v>
       </c>
       <c r="F82" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="83">
@@ -2050,13 +2050,13 @@
         <v>PASS</v>
       </c>
       <c r="D83" t="str">
-        <v>0.83 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-01T10:45:00.767Z</v>
+        <v>2026-07-31T11:25:12.237Z</v>
       </c>
       <c r="F83" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="84">
@@ -2070,13 +2070,13 @@
         <v>PASS</v>
       </c>
       <c r="D84" t="str">
-        <v>0.81 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-01T10:45:01.572Z</v>
+        <v>2026-07-31T11:25:13.558Z</v>
       </c>
       <c r="F84" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="85">
@@ -2090,13 +2090,13 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>1.04 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-01T10:45:02.611Z</v>
+        <v>2026-07-31T11:25:14.920Z</v>
       </c>
       <c r="F85" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="86">
@@ -2110,13 +2110,13 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>0.85 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-01T10:45:03.466Z</v>
+        <v>2026-07-31T11:25:16.369Z</v>
       </c>
       <c r="F86" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="87">
@@ -2130,13 +2130,13 @@
         <v>PASS</v>
       </c>
       <c r="D87" t="str">
-        <v>0.90 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-01T10:45:04.364Z</v>
+        <v>2026-07-31T11:25:17.906Z</v>
       </c>
       <c r="F87" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="88">
@@ -2150,13 +2150,13 @@
         <v>PASS</v>
       </c>
       <c r="D88" t="str">
-        <v>0.60 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-01T10:45:04.962Z</v>
+        <v>2026-07-31T11:25:19.185Z</v>
       </c>
       <c r="F88" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="89">
@@ -2170,13 +2170,13 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.81 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-01T10:45:05.767Z</v>
+        <v>2026-07-31T11:25:20.520Z</v>
       </c>
       <c r="F89" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="90">
@@ -2190,13 +2190,13 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.74 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-01T10:45:06.511Z</v>
+        <v>2026-07-31T11:25:21.835Z</v>
       </c>
       <c r="F90" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="91">
@@ -2210,13 +2210,13 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>0.91 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-01T10:45:07.416Z</v>
+        <v>2026-07-31T11:25:23.309Z</v>
       </c>
       <c r="F91" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="92">
@@ -2230,13 +2230,13 @@
         <v>PASS</v>
       </c>
       <c r="D92" t="str">
-        <v>0.78 sec</v>
+        <v>1.25 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-01T10:45:08.195Z</v>
+        <v>2026-07-31T11:25:24.563Z</v>
       </c>
       <c r="F92" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="93">
@@ -2250,13 +2250,13 @@
         <v>PASS</v>
       </c>
       <c r="D93" t="str">
-        <v>0.99 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-01T10:45:09.182Z</v>
+        <v>2026-07-31T11:25:26.102Z</v>
       </c>
       <c r="F93" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="94">
@@ -2270,13 +2270,13 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>0.60 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-01T10:45:09.781Z</v>
+        <v>2026-07-31T11:25:27.553Z</v>
       </c>
       <c r="F94" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="95">
@@ -2290,13 +2290,13 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.55 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-01T10:45:10.332Z</v>
+        <v>2026-07-31T11:25:28.885Z</v>
       </c>
       <c r="F95" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="96">
@@ -2310,13 +2310,13 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.81 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-01T10:45:11.146Z</v>
+        <v>2026-07-31T11:25:30.202Z</v>
       </c>
       <c r="F96" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="97">
@@ -2330,13 +2330,13 @@
         <v>PASS</v>
       </c>
       <c r="D97" t="str">
-        <v>0.96 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-01T10:45:12.109Z</v>
+        <v>2026-07-31T11:25:31.752Z</v>
       </c>
       <c r="F97" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="98">
@@ -2350,13 +2350,13 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.79 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-01T10:45:12.895Z</v>
+        <v>2026-07-31T11:25:33.187Z</v>
       </c>
       <c r="F98" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="99">
@@ -2370,13 +2370,13 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>1.11 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-01T10:45:14.001Z</v>
+        <v>2026-07-31T11:25:34.719Z</v>
       </c>
       <c r="F99" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="100">
@@ -2390,13 +2390,13 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.86 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-01T10:45:14.859Z</v>
+        <v>2026-07-31T11:25:36.186Z</v>
       </c>
       <c r="F100" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="101">
@@ -2410,13 +2410,13 @@
         <v>PASS</v>
       </c>
       <c r="D101" t="str">
-        <v>0.82 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-01T10:45:15.679Z</v>
+        <v>2026-07-31T11:25:37.534Z</v>
       </c>
       <c r="F101" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="102">
@@ -2430,13 +2430,13 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>1.07 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-01T10:45:16.748Z</v>
+        <v>2026-07-31T11:25:38.855Z</v>
       </c>
       <c r="F102" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="103">
@@ -2450,13 +2450,13 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>0.72 sec</v>
+        <v>1.26 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-01T10:45:17.472Z</v>
+        <v>2026-07-31T11:25:40.119Z</v>
       </c>
       <c r="F103" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="104">
@@ -2470,13 +2470,13 @@
         <v>PASS</v>
       </c>
       <c r="D104" t="str">
-        <v>0.84 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-01T10:45:18.310Z</v>
+        <v>2026-07-31T11:25:41.470Z</v>
       </c>
       <c r="F104" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="105">
@@ -2490,13 +2490,13 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>0.69 sec</v>
+        <v>1.50 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-01T10:45:18.999Z</v>
+        <v>2026-07-31T11:25:42.973Z</v>
       </c>
       <c r="F105" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="106">
@@ -2510,13 +2510,13 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.61 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-01T10:45:19.610Z</v>
+        <v>2026-07-31T11:25:44.318Z</v>
       </c>
       <c r="F106" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="107">
@@ -2530,13 +2530,13 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>0.58 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-01T10:45:20.194Z</v>
+        <v>2026-07-31T11:25:45.655Z</v>
       </c>
       <c r="F107" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="108">
@@ -2550,13 +2550,13 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>0.78 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-01T10:45:20.972Z</v>
+        <v>2026-07-31T11:25:46.991Z</v>
       </c>
       <c r="F108" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="109">
@@ -2570,13 +2570,13 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>0.72 sec</v>
+        <v>1.59 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-01T10:45:21.697Z</v>
+        <v>2026-07-31T11:25:48.585Z</v>
       </c>
       <c r="F109" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="110">
@@ -2590,13 +2590,13 @@
         <v>PASS</v>
       </c>
       <c r="D110" t="str">
-        <v>0.85 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-01T10:45:22.543Z</v>
+        <v>2026-07-31T11:25:49.924Z</v>
       </c>
       <c r="F110" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="111">
@@ -2610,13 +2610,13 @@
         <v>PASS</v>
       </c>
       <c r="D111" t="str">
-        <v>0.94 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-01T10:45:23.479Z</v>
+        <v>2026-07-31T11:25:51.479Z</v>
       </c>
       <c r="F111" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="112">
@@ -2630,13 +2630,13 @@
         <v>PASS</v>
       </c>
       <c r="D112" t="str">
-        <v>0.67 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-01T10:45:24.147Z</v>
+        <v>2026-07-31T11:25:52.836Z</v>
       </c>
       <c r="F112" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="113">
@@ -2650,13 +2650,13 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.80 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-01T10:45:24.945Z</v>
+        <v>2026-07-31T11:25:54.168Z</v>
       </c>
       <c r="F113" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="114">
@@ -2670,13 +2670,13 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.79 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-01T10:45:25.732Z</v>
+        <v>2026-07-31T11:25:55.498Z</v>
       </c>
       <c r="F114" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="115">
@@ -2690,13 +2690,13 @@
         <v>PASS</v>
       </c>
       <c r="D115" t="str">
-        <v>0.94 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-01T10:45:26.670Z</v>
+        <v>2026-07-31T11:25:56.950Z</v>
       </c>
       <c r="F115" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="116">
@@ -2710,13 +2710,13 @@
         <v>PASS</v>
       </c>
       <c r="D116" t="str">
-        <v>0.84 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-01T10:45:27.511Z</v>
+        <v>2026-07-31T11:25:58.101Z</v>
       </c>
       <c r="F116" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="117">
@@ -2730,13 +2730,13 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>0.98 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-01T10:45:28.495Z</v>
+        <v>2026-07-31T11:25:59.660Z</v>
       </c>
       <c r="F117" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="118">
@@ -2750,13 +2750,13 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.86 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-01T10:45:29.357Z</v>
+        <v>2026-07-31T11:26:01.133Z</v>
       </c>
       <c r="F118" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="119">
@@ -2770,13 +2770,13 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>0.87 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-01T10:45:30.225Z</v>
+        <v>2026-07-31T11:26:02.469Z</v>
       </c>
       <c r="F119" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="120">
@@ -2790,13 +2790,13 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.99 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-01T10:45:31.216Z</v>
+        <v>2026-07-31T11:26:03.795Z</v>
       </c>
       <c r="F120" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="121">
@@ -2810,13 +2810,13 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>0.96 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-01T10:45:32.179Z</v>
+        <v>2026-07-31T11:26:05.354Z</v>
       </c>
       <c r="F121" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="122">
@@ -2830,13 +2830,13 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.58 sec</v>
+        <v>1.30 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-01T10:45:32.761Z</v>
+        <v>2026-07-31T11:26:06.654Z</v>
       </c>
       <c r="F122" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="123">
@@ -2850,13 +2850,13 @@
         <v>PASS</v>
       </c>
       <c r="D123" t="str">
-        <v>0.94 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-01T10:45:33.705Z</v>
+        <v>2026-07-31T11:26:08.187Z</v>
       </c>
       <c r="F123" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="124">
@@ -2870,13 +2870,13 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>0.65 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-01T10:45:34.353Z</v>
+        <v>2026-07-31T11:26:09.670Z</v>
       </c>
       <c r="F124" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="125">
@@ -2890,13 +2890,13 @@
         <v>PASS</v>
       </c>
       <c r="D125" t="str">
-        <v>0.84 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-01T10:45:35.194Z</v>
+        <v>2026-07-31T11:26:11.020Z</v>
       </c>
       <c r="F125" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="126">
@@ -2910,13 +2910,13 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.82 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-01T10:45:36.019Z</v>
+        <v>2026-07-31T11:26:12.339Z</v>
       </c>
       <c r="F126" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="127">
@@ -2930,13 +2930,13 @@
         <v>PASS</v>
       </c>
       <c r="D127" t="str">
-        <v>1.07 sec</v>
+        <v>1.58 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-01T10:45:37.090Z</v>
+        <v>2026-07-31T11:26:13.923Z</v>
       </c>
       <c r="F127" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="128">
@@ -2950,13 +2950,13 @@
         <v>PASS</v>
       </c>
       <c r="D128" t="str">
-        <v>0.60 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-01T10:45:37.687Z</v>
+        <v>2026-07-31T11:26:15.377Z</v>
       </c>
       <c r="F128" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="129">
@@ -2970,13 +2970,13 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.95 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-01T10:45:38.640Z</v>
+        <v>2026-07-31T11:26:16.935Z</v>
       </c>
       <c r="F129" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="130">
@@ -2990,13 +2990,13 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.86 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-01T10:45:39.505Z</v>
+        <v>2026-07-31T11:26:18.420Z</v>
       </c>
       <c r="F130" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="131">
@@ -3010,13 +3010,13 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.58 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-01T10:45:40.090Z</v>
+        <v>2026-07-31T11:26:19.784Z</v>
       </c>
       <c r="F131" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="132">
@@ -3030,13 +3030,13 @@
         <v>PASS</v>
       </c>
       <c r="D132" t="str">
-        <v>0.80 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-01T10:45:40.893Z</v>
+        <v>2026-07-31T11:26:21.103Z</v>
       </c>
       <c r="F132" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="133">
@@ -3050,13 +3050,13 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>0.89 sec</v>
+        <v>1.40 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-01T10:45:41.783Z</v>
+        <v>2026-07-31T11:26:22.502Z</v>
       </c>
       <c r="F133" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="134">
@@ -3070,13 +3070,13 @@
         <v>PASS</v>
       </c>
       <c r="D134" t="str">
-        <v>0.89 sec</v>
+        <v>1.39 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-01T10:45:42.669Z</v>
+        <v>2026-07-31T11:26:23.894Z</v>
       </c>
       <c r="F134" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="135">
@@ -3090,13 +3090,13 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>1.17 sec</v>
+        <v>1.59 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-01T10:45:43.837Z</v>
+        <v>2026-07-31T11:26:25.485Z</v>
       </c>
       <c r="F135" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="136">
@@ -3110,13 +3110,13 @@
         <v>PASS</v>
       </c>
       <c r="D136" t="str">
-        <v>0.61 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-01T10:45:44.443Z</v>
+        <v>2026-07-31T11:26:26.850Z</v>
       </c>
       <c r="F136" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="137">
@@ -3130,13 +3130,13 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>0.83 sec</v>
+        <v>1.38 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-01T10:45:45.278Z</v>
+        <v>2026-07-31T11:26:28.232Z</v>
       </c>
       <c r="F137" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="138">
@@ -3150,13 +3150,13 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>0.56 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-01T10:45:45.842Z</v>
+        <v>2026-07-31T11:26:29.575Z</v>
       </c>
       <c r="F138" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="139">
@@ -3170,13 +3170,13 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>0.92 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-01T10:45:46.760Z</v>
+        <v>2026-07-31T11:26:31.010Z</v>
       </c>
       <c r="F139" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="140">
@@ -3190,13 +3190,13 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>0.57 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-01T10:45:47.328Z</v>
+        <v>2026-07-31T11:26:32.351Z</v>
       </c>
       <c r="F140" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="141">
@@ -3210,13 +3210,13 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>0.80 sec</v>
+        <v>1.57 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-01T10:45:48.123Z</v>
+        <v>2026-07-31T11:26:33.925Z</v>
       </c>
       <c r="F141" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="142">
@@ -3230,13 +3230,13 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>0.88 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-01T10:45:49.000Z</v>
+        <v>2026-07-31T11:26:35.382Z</v>
       </c>
       <c r="F142" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="143">
@@ -3250,13 +3250,13 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>0.81 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-01T10:45:49.811Z</v>
+        <v>2026-07-31T11:26:36.733Z</v>
       </c>
       <c r="F143" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="144">
@@ -3270,13 +3270,13 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>0.85 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-01T10:45:50.660Z</v>
+        <v>2026-07-31T11:26:38.062Z</v>
       </c>
       <c r="F144" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="145">
@@ -3290,13 +3290,13 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>0.97 sec</v>
+        <v>1.41 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-01T10:45:51.630Z</v>
+        <v>2026-07-31T11:26:39.468Z</v>
       </c>
       <c r="F145" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="146">
@@ -3310,13 +3310,13 @@
         <v>PASS</v>
       </c>
       <c r="D146" t="str">
-        <v>0.80 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-01T10:45:52.429Z</v>
+        <v>2026-07-31T11:26:40.932Z</v>
       </c>
       <c r="F146" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="147">
@@ -3330,13 +3330,13 @@
         <v>PASS</v>
       </c>
       <c r="D147" t="str">
-        <v>0.99 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-01T10:45:53.421Z</v>
+        <v>2026-07-31T11:26:42.484Z</v>
       </c>
       <c r="F147" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="148">
@@ -3350,13 +3350,13 @@
         <v>PASS</v>
       </c>
       <c r="D148" t="str">
-        <v>0.66 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-01T10:45:54.080Z</v>
+        <v>2026-07-31T11:26:43.966Z</v>
       </c>
       <c r="F148" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="149">
@@ -3370,13 +3370,13 @@
         <v>PASS</v>
       </c>
       <c r="D149" t="str">
-        <v>0.58 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-01T10:45:54.661Z</v>
+        <v>2026-07-31T11:26:45.316Z</v>
       </c>
       <c r="F149" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="150">
@@ -3390,13 +3390,13 @@
         <v>PASS</v>
       </c>
       <c r="D150" t="str">
-        <v>0.79 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-01T10:45:55.452Z</v>
+        <v>2026-07-31T11:26:46.642Z</v>
       </c>
       <c r="F150" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="151">
@@ -3410,13 +3410,13 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>0.91 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-01T10:45:56.360Z</v>
+        <v>2026-07-31T11:26:48.119Z</v>
       </c>
       <c r="F151" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="152">
@@ -3430,13 +3430,13 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.62 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-01T10:45:56.977Z</v>
+        <v>2026-07-31T11:26:49.592Z</v>
       </c>
       <c r="F152" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="153">
@@ -3450,13 +3450,13 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>0.75 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-01T10:45:57.730Z</v>
+        <v>2026-07-31T11:26:51.124Z</v>
       </c>
       <c r="F153" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="154">
@@ -3470,13 +3470,13 @@
         <v>PASS</v>
       </c>
       <c r="D154" t="str">
-        <v>0.83 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-01T10:45:58.564Z</v>
+        <v>2026-07-31T11:26:52.599Z</v>
       </c>
       <c r="F154" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="155">
@@ -3490,13 +3490,13 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.82 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-01T10:45:59.380Z</v>
+        <v>2026-07-31T11:26:53.948Z</v>
       </c>
       <c r="F155" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="156">
@@ -3510,13 +3510,13 @@
         <v>PASS</v>
       </c>
       <c r="D156" t="str">
-        <v>0.54 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-01T10:45:59.918Z</v>
+        <v>2026-07-31T11:26:55.280Z</v>
       </c>
       <c r="F156" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="157">
@@ -3530,13 +3530,13 @@
         <v>PASS</v>
       </c>
       <c r="D157" t="str">
-        <v>0.73 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-01T10:46:00.649Z</v>
+        <v>2026-07-31T11:26:56.832Z</v>
       </c>
       <c r="F157" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="158">
@@ -3550,13 +3550,13 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>0.83 sec</v>
+        <v>1.27 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-01T10:46:01.479Z</v>
+        <v>2026-07-31T11:26:58.098Z</v>
       </c>
       <c r="F158" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="159">
@@ -3570,13 +3570,13 @@
         <v>PASS</v>
       </c>
       <c r="D159" t="str">
-        <v>0.71 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-01T10:46:02.194Z</v>
+        <v>2026-07-31T11:26:59.632Z</v>
       </c>
       <c r="F159" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="160">
@@ -3590,13 +3590,13 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>0.90 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-01T10:46:03.092Z</v>
+        <v>2026-07-31T11:27:01.098Z</v>
       </c>
       <c r="F160" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="161">
@@ -3610,13 +3610,13 @@
         <v>PASS</v>
       </c>
       <c r="D161" t="str">
-        <v>0.88 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-01T10:46:03.969Z</v>
+        <v>2026-07-31T11:27:02.433Z</v>
       </c>
       <c r="F161" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="162">
@@ -3630,13 +3630,13 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>0.88 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-01T10:46:04.852Z</v>
+        <v>2026-07-31T11:27:03.756Z</v>
       </c>
       <c r="F162" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="163">
@@ -3650,13 +3650,13 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>1.00 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-01T10:46:05.852Z</v>
+        <v>2026-07-31T11:27:05.208Z</v>
       </c>
       <c r="F163" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="164">
@@ -3670,13 +3670,13 @@
         <v>PASS</v>
       </c>
       <c r="D164" t="str">
-        <v>0.83 sec</v>
+        <v>1.37 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-01T10:46:06.682Z</v>
+        <v>2026-07-31T11:27:06.580Z</v>
       </c>
       <c r="F164" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="165">
@@ -3690,13 +3690,13 @@
         <v>PASS</v>
       </c>
       <c r="D165" t="str">
-        <v>0.91 sec</v>
+        <v>1.60 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-01T10:46:07.592Z</v>
+        <v>2026-07-31T11:27:08.182Z</v>
       </c>
       <c r="F165" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="166">
@@ -3710,13 +3710,13 @@
         <v>PASS</v>
       </c>
       <c r="D166" t="str">
-        <v>0.62 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-01T10:46:08.210Z</v>
+        <v>2026-07-31T11:27:09.648Z</v>
       </c>
       <c r="F166" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="167">
@@ -3730,13 +3730,13 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>0.85 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-01T10:46:09.059Z</v>
+        <v>2026-07-31T11:27:10.998Z</v>
       </c>
       <c r="F167" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="168">
@@ -3750,13 +3750,13 @@
         <v>PASS</v>
       </c>
       <c r="D168" t="str">
-        <v>0.75 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-01T10:46:09.810Z</v>
+        <v>2026-07-31T11:27:12.317Z</v>
       </c>
       <c r="F168" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="169">
@@ -3770,13 +3770,13 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>0.94 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-01T10:46:10.746Z</v>
+        <v>2026-07-31T11:27:13.882Z</v>
       </c>
       <c r="F169" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="170">
@@ -3790,13 +3790,13 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>0.86 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-01T10:46:11.610Z</v>
+        <v>2026-07-31T11:27:15.313Z</v>
       </c>
       <c r="F170" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="171">
@@ -3810,13 +3810,13 @@
         <v>PASS</v>
       </c>
       <c r="D171" t="str">
-        <v>0.68 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-01T10:46:12.292Z</v>
+        <v>2026-07-31T11:27:16.837Z</v>
       </c>
       <c r="F171" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="172">
@@ -3830,13 +3830,13 @@
         <v>PASS</v>
       </c>
       <c r="D172" t="str">
-        <v>0.62 sec</v>
+        <v>1.29 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-01T10:46:12.908Z</v>
+        <v>2026-07-31T11:27:18.129Z</v>
       </c>
       <c r="F172" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="173">
@@ -3850,13 +3850,13 @@
         <v>PASS</v>
       </c>
       <c r="D173" t="str">
-        <v>0.83 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-01T10:46:13.736Z</v>
+        <v>2026-07-31T11:27:19.298Z</v>
       </c>
       <c r="F173" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="174">
@@ -3870,13 +3870,13 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.74 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-01T10:46:14.480Z</v>
+        <v>2026-07-31T11:27:20.613Z</v>
       </c>
       <c r="F174" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="175">
@@ -3890,13 +3890,13 @@
         <v>PASS</v>
       </c>
       <c r="D175" t="str">
-        <v>2.89 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-01T10:46:17.374Z</v>
+        <v>2026-07-31T11:27:22.106Z</v>
       </c>
       <c r="F175" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="176">
@@ -3910,13 +3910,13 @@
         <v>PASS</v>
       </c>
       <c r="D176" t="str">
-        <v>0.85 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-01T10:46:18.226Z</v>
+        <v>2026-07-31T11:27:23.577Z</v>
       </c>
       <c r="F176" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="177">
@@ -3930,13 +3930,13 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.99 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-01T10:46:19.221Z</v>
+        <v>2026-07-31T11:27:25.113Z</v>
       </c>
       <c r="F177" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="178">
@@ -3950,13 +3950,13 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>0.86 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-01T10:46:20.078Z</v>
+        <v>2026-07-31T11:27:26.596Z</v>
       </c>
       <c r="F178" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="179">
@@ -3970,13 +3970,13 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.58 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-01T10:46:20.662Z</v>
+        <v>2026-07-31T11:27:27.947Z</v>
       </c>
       <c r="F179" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="180">
@@ -3990,13 +3990,13 @@
         <v>PASS</v>
       </c>
       <c r="D180" t="str">
-        <v>0.79 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-01T10:46:21.453Z</v>
+        <v>2026-07-31T11:27:29.278Z</v>
       </c>
       <c r="F180" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="181">
@@ -4010,13 +4010,13 @@
         <v>PASS</v>
       </c>
       <c r="D181" t="str">
-        <v>0.76 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-01T10:46:22.212Z</v>
+        <v>2026-07-31T11:27:30.831Z</v>
       </c>
       <c r="F181" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="182">
@@ -4030,13 +4030,13 @@
         <v>PASS</v>
       </c>
       <c r="D182" t="str">
-        <v>0.85 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-01T10:46:23.060Z</v>
+        <v>2026-07-31T11:27:32.263Z</v>
       </c>
       <c r="F182" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="183">
@@ -4050,13 +4050,13 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>0.82 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-01T10:46:23.881Z</v>
+        <v>2026-07-31T11:27:33.799Z</v>
       </c>
       <c r="F183" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="184">
@@ -4070,13 +4070,13 @@
         <v>PASS</v>
       </c>
       <c r="D184" t="str">
-        <v>0.89 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-01T10:46:24.775Z</v>
+        <v>2026-07-31T11:27:35.080Z</v>
       </c>
       <c r="F184" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="185">
@@ -4090,13 +4090,13 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>0.82 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-01T10:46:25.593Z</v>
+        <v>2026-07-31T11:27:36.429Z</v>
       </c>
       <c r="F185" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="186">
@@ -4110,13 +4110,13 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>0.62 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-01T10:46:26.217Z</v>
+        <v>2026-07-31T11:27:37.743Z</v>
       </c>
       <c r="F186" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="187">
@@ -4130,13 +4130,13 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>1.04 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-01T10:46:27.258Z</v>
+        <v>2026-07-31T11:27:39.302Z</v>
       </c>
       <c r="F187" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="188">
@@ -4150,13 +4150,13 @@
         <v>PASS</v>
       </c>
       <c r="D188" t="str">
-        <v>0.94 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-01T10:46:28.201Z</v>
+        <v>2026-07-31T11:27:40.763Z</v>
       </c>
       <c r="F188" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="189">
@@ -4170,13 +4170,13 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>0.96 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-01T10:46:29.164Z</v>
+        <v>2026-07-31T11:27:42.286Z</v>
       </c>
       <c r="F189" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="190">
@@ -4190,13 +4190,13 @@
         <v>PASS</v>
       </c>
       <c r="D190" t="str">
-        <v>0.63 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-01T10:46:29.797Z</v>
+        <v>2026-07-31T11:27:43.746Z</v>
       </c>
       <c r="F190" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="191">
@@ -4210,13 +4210,13 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>0.81 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-01T10:46:30.609Z</v>
+        <v>2026-07-31T11:27:45.097Z</v>
       </c>
       <c r="F191" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="192">
@@ -4230,13 +4230,13 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>0.84 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-01T10:46:31.452Z</v>
+        <v>2026-07-31T11:27:46.428Z</v>
       </c>
       <c r="F192" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="193">
@@ -4250,13 +4250,13 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.91 sec</v>
+        <v>1.40 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-01T10:46:32.363Z</v>
+        <v>2026-07-31T11:27:47.826Z</v>
       </c>
       <c r="F193" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="194">
@@ -4270,13 +4270,13 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.84 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-01T10:46:33.200Z</v>
+        <v>2026-07-31T11:27:49.163Z</v>
       </c>
       <c r="F194" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="195">
@@ -4290,13 +4290,13 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>1.03 sec</v>
+        <v>1.50 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-01T10:46:34.231Z</v>
+        <v>2026-07-31T11:27:50.662Z</v>
       </c>
       <c r="F195" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="196">
@@ -4310,13 +4310,13 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.86 sec</v>
+        <v>1.38 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-01T10:46:35.092Z</v>
+        <v>2026-07-31T11:27:52.046Z</v>
       </c>
       <c r="F196" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="197">
@@ -4330,13 +4330,13 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>0.82 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-01T10:46:35.917Z</v>
+        <v>2026-07-31T11:27:53.379Z</v>
       </c>
       <c r="F197" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="198">
@@ -4350,13 +4350,13 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>0.85 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-01T10:46:36.772Z</v>
+        <v>2026-07-31T11:27:54.713Z</v>
       </c>
       <c r="F198" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="199">
@@ -4370,13 +4370,13 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>0.98 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-01T10:46:37.756Z</v>
+        <v>2026-07-31T11:27:56.278Z</v>
       </c>
       <c r="F199" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="200">
@@ -4390,13 +4390,13 @@
         <v>PASS</v>
       </c>
       <c r="D200" t="str">
-        <v>0.91 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-01T10:46:38.667Z</v>
+        <v>2026-07-31T11:27:57.738Z</v>
       </c>
       <c r="F200" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="201">
@@ -4410,13 +4410,13 @@
         <v>PASS</v>
       </c>
       <c r="D201" t="str">
-        <v>1.08 sec</v>
+        <v>1.57 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-01T10:46:39.747Z</v>
+        <v>2026-07-31T11:27:59.309Z</v>
       </c>
       <c r="F201" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="202">
@@ -4430,13 +4430,13 @@
         <v>PASS</v>
       </c>
       <c r="D202" t="str">
-        <v>0.94 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-01T10:46:40.691Z</v>
+        <v>2026-07-31T11:28:00.761Z</v>
       </c>
       <c r="F202" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="203">
@@ -4450,13 +4450,13 @@
         <v>PASS</v>
       </c>
       <c r="D203" t="str">
-        <v>0.88 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-01T10:46:41.570Z</v>
+        <v>2026-07-31T11:28:02.096Z</v>
       </c>
       <c r="F203" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="204">
@@ -4470,13 +4470,13 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>1.15 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-01T10:46:42.720Z</v>
+        <v>2026-07-31T11:28:03.412Z</v>
       </c>
       <c r="F204" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="205">
@@ -4490,13 +4490,13 @@
         <v>PASS</v>
       </c>
       <c r="D205" t="str">
-        <v>0.97 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-01T10:46:43.692Z</v>
+        <v>2026-07-31T11:28:04.964Z</v>
       </c>
       <c r="F205" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="206">
@@ -4510,13 +4510,13 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>0.62 sec</v>
+        <v>1.42 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-01T10:46:44.308Z</v>
+        <v>2026-07-31T11:28:06.388Z</v>
       </c>
       <c r="F206" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="207">
@@ -4530,13 +4530,13 @@
         <v>PASS</v>
       </c>
       <c r="D207" t="str">
-        <v>0.99 sec</v>
+        <v>1.51 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-01T10:46:45.294Z</v>
+        <v>2026-07-31T11:28:07.902Z</v>
       </c>
       <c r="F207" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="208">
@@ -4550,13 +4550,13 @@
         <v>PASS</v>
       </c>
       <c r="D208" t="str">
-        <v>0.65 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-01T10:46:45.944Z</v>
+        <v>2026-07-31T11:28:09.361Z</v>
       </c>
       <c r="F208" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="209">
@@ -4570,13 +4570,13 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.84 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-01T10:46:46.785Z</v>
+        <v>2026-07-31T11:28:10.695Z</v>
       </c>
       <c r="F209" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="210">
@@ -4590,13 +4590,13 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>0.83 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-01T10:46:47.617Z</v>
+        <v>2026-07-31T11:28:12.015Z</v>
       </c>
       <c r="F210" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="211">
@@ -4610,13 +4610,13 @@
         <v>PASS</v>
       </c>
       <c r="D211" t="str">
-        <v>0.71 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-01T10:46:48.331Z</v>
+        <v>2026-07-31T11:28:13.488Z</v>
       </c>
       <c r="F211" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="212">
@@ -4630,13 +4630,13 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.84 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-01T10:46:49.176Z</v>
+        <v>2026-07-31T11:28:14.928Z</v>
       </c>
       <c r="F212" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="213">
@@ -4650,13 +4650,13 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>0.97 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-01T10:46:50.146Z</v>
+        <v>2026-07-31T11:28:16.444Z</v>
       </c>
       <c r="F213" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="214">
@@ -4670,13 +4670,13 @@
         <v>PASS</v>
       </c>
       <c r="D214" t="str">
-        <v>0.87 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-01T10:46:51.019Z</v>
+        <v>2026-07-31T11:28:17.911Z</v>
       </c>
       <c r="F214" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="215">
@@ -4690,13 +4690,13 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>0.86 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-01T10:46:51.884Z</v>
+        <v>2026-07-31T11:28:19.245Z</v>
       </c>
       <c r="F215" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="216">
@@ -4710,13 +4710,13 @@
         <v>PASS</v>
       </c>
       <c r="D216" t="str">
-        <v>0.85 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-01T10:46:52.735Z</v>
+        <v>2026-07-31T11:28:20.568Z</v>
       </c>
       <c r="F216" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="217">
@@ -4730,13 +4730,13 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>1.00 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-01T10:46:53.740Z</v>
+        <v>2026-07-31T11:28:22.130Z</v>
       </c>
       <c r="F217" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="218">
@@ -4750,13 +4750,13 @@
         <v>PASS</v>
       </c>
       <c r="D218" t="str">
-        <v>0.93 sec</v>
+        <v>1.25 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-01T10:46:54.668Z</v>
+        <v>2026-07-31T11:28:23.385Z</v>
       </c>
       <c r="F218" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="219">
@@ -4770,13 +4770,13 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>0.96 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-01T10:46:55.632Z</v>
+        <v>2026-07-31T11:28:24.910Z</v>
       </c>
       <c r="F219" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="220">
@@ -4790,13 +4790,13 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>0.87 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-01T10:46:56.506Z</v>
+        <v>2026-07-31T11:28:26.361Z</v>
       </c>
       <c r="F220" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="221">
@@ -4810,13 +4810,13 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>0.84 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-01T10:46:57.345Z</v>
+        <v>2026-07-31T11:28:27.712Z</v>
       </c>
       <c r="F221" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="222">
@@ -4830,13 +4830,13 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.84 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-01T10:46:58.188Z</v>
+        <v>2026-07-31T11:28:29.026Z</v>
       </c>
       <c r="F222" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="223">
@@ -4850,13 +4850,13 @@
         <v>PASS</v>
       </c>
       <c r="D223" t="str">
-        <v>0.98 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-01T10:46:59.169Z</v>
+        <v>2026-07-31T11:28:30.460Z</v>
       </c>
       <c r="F223" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="224">
@@ -4870,13 +4870,13 @@
         <v>PASS</v>
       </c>
       <c r="D224" t="str">
-        <v>0.89 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-01T10:47:00.059Z</v>
+        <v>2026-07-31T11:28:31.819Z</v>
       </c>
       <c r="F224" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="225">
@@ -4890,13 +4890,13 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>0.96 sec</v>
+        <v>1.51 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-01T10:47:01.018Z</v>
+        <v>2026-07-31T11:28:33.329Z</v>
       </c>
       <c r="F225" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="226">
@@ -4910,13 +4910,13 @@
         <v>PASS</v>
       </c>
       <c r="D226" t="str">
-        <v>0.90 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-01T10:47:01.914Z</v>
+        <v>2026-07-31T11:28:34.678Z</v>
       </c>
       <c r="F226" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="227">
@@ -4930,13 +4930,13 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>1.06 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-01T10:47:02.974Z</v>
+        <v>2026-07-31T11:28:36.027Z</v>
       </c>
       <c r="F227" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="228">
@@ -4950,13 +4950,13 @@
         <v>PASS</v>
       </c>
       <c r="D228" t="str">
-        <v>0.89 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-01T10:47:03.862Z</v>
+        <v>2026-07-31T11:28:37.181Z</v>
       </c>
       <c r="F228" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="229">
@@ -4970,13 +4970,13 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>0.95 sec</v>
+        <v>1.60 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-01T10:47:04.817Z</v>
+        <v>2026-07-31T11:28:38.777Z</v>
       </c>
       <c r="F229" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="230">
@@ -4990,13 +4990,13 @@
         <v>PASS</v>
       </c>
       <c r="D230" t="str">
-        <v>0.60 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-01T10:47:05.419Z</v>
+        <v>2026-07-31T11:28:40.255Z</v>
       </c>
       <c r="F230" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="231">
@@ -5010,13 +5010,13 @@
         <v>PASS</v>
       </c>
       <c r="D231" t="str">
-        <v>0.73 sec</v>
+        <v>1.61 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-01T10:47:06.146Z</v>
+        <v>2026-07-31T11:28:41.865Z</v>
       </c>
       <c r="F231" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="232">
@@ -5030,13 +5030,13 @@
         <v>PASS</v>
       </c>
       <c r="D232" t="str">
-        <v>0.94 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-01T10:47:07.085Z</v>
+        <v>2026-07-31T11:28:43.144Z</v>
       </c>
       <c r="F232" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="233">
@@ -5050,13 +5050,13 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>0.84 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-01T10:47:07.926Z</v>
+        <v>2026-07-31T11:28:44.477Z</v>
       </c>
       <c r="F233" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="234">
@@ -5070,13 +5070,13 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.78 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-01T10:47:08.706Z</v>
+        <v>2026-07-31T11:28:45.798Z</v>
       </c>
       <c r="F234" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="235">
@@ -5090,13 +5090,13 @@
         <v>PASS</v>
       </c>
       <c r="D235" t="str">
-        <v>0.74 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-01T10:47:09.445Z</v>
+        <v>2026-07-31T11:28:47.292Z</v>
       </c>
       <c r="F235" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="236">
@@ -5110,13 +5110,13 @@
         <v>PASS</v>
       </c>
       <c r="D236" t="str">
-        <v>0.72 sec</v>
+        <v>1.26 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-01T10:47:10.168Z</v>
+        <v>2026-07-31T11:28:48.552Z</v>
       </c>
       <c r="F236" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="237">
@@ -5130,13 +5130,13 @@
         <v>PASS</v>
       </c>
       <c r="D237" t="str">
-        <v>1.06 sec</v>
+        <v>1.52 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-01T10:47:11.229Z</v>
+        <v>2026-07-31T11:28:50.077Z</v>
       </c>
       <c r="F237" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="238">
@@ -5150,13 +5150,13 @@
         <v>PASS</v>
       </c>
       <c r="D238" t="str">
-        <v>0.94 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-01T10:47:12.174Z</v>
+        <v>2026-07-31T11:28:51.527Z</v>
       </c>
       <c r="F238" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="239">
@@ -5170,13 +5170,13 @@
         <v>PASS</v>
       </c>
       <c r="D239" t="str">
-        <v>0.62 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-01T10:47:12.794Z</v>
+        <v>2026-07-31T11:28:52.859Z</v>
       </c>
       <c r="F239" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="240">
@@ -5190,13 +5190,13 @@
         <v>PASS</v>
       </c>
       <c r="D240" t="str">
-        <v>0.93 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-01T10:47:13.727Z</v>
+        <v>2026-07-31T11:28:54.177Z</v>
       </c>
       <c r="F240" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="241">
@@ -5210,13 +5210,13 @@
         <v>PASS</v>
       </c>
       <c r="D241" t="str">
-        <v>0.74 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-01T10:47:14.470Z</v>
+        <v>2026-07-31T11:28:55.712Z</v>
       </c>
       <c r="F241" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="242">
@@ -5230,13 +5230,13 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.61 sec</v>
+        <v>1.27 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-01T10:47:15.079Z</v>
+        <v>2026-07-31T11:28:56.979Z</v>
       </c>
       <c r="F242" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="243">
@@ -5250,13 +5250,13 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>0.94 sec</v>
+        <v>1.51 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-01T10:47:16.023Z</v>
+        <v>2026-07-31T11:28:58.490Z</v>
       </c>
       <c r="F243" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="244">
@@ -5270,13 +5270,13 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>0.67 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-01T10:47:16.695Z</v>
+        <v>2026-07-31T11:28:59.942Z</v>
       </c>
       <c r="F244" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="245">
@@ -5290,13 +5290,13 @@
         <v>PASS</v>
       </c>
       <c r="D245" t="str">
-        <v>0.83 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-01T10:47:17.529Z</v>
+        <v>2026-07-31T11:29:01.110Z</v>
       </c>
       <c r="F245" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="246">
@@ -5310,13 +5310,13 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>0.95 sec</v>
+        <v>1.14 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-01T10:47:18.475Z</v>
+        <v>2026-07-31T11:29:02.246Z</v>
       </c>
       <c r="F246" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="247">
@@ -5330,13 +5330,13 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>0.80 sec</v>
+        <v>1.58 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-01T10:47:19.276Z</v>
+        <v>2026-07-31T11:29:03.826Z</v>
       </c>
       <c r="F247" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="248">
@@ -5350,13 +5350,13 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.83 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-01T10:47:20.111Z</v>
+        <v>2026-07-31T11:29:05.260Z</v>
       </c>
       <c r="F248" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="249">
@@ -5370,13 +5370,13 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>0.93 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-01T10:47:21.039Z</v>
+        <v>2026-07-31T11:29:06.792Z</v>
       </c>
       <c r="F249" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="250">
@@ -5390,13 +5390,13 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>0.88 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-01T10:47:21.922Z</v>
+        <v>2026-07-31T11:29:08.242Z</v>
       </c>
       <c r="F250" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="251">
@@ -5410,13 +5410,13 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.80 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-01T10:47:22.717Z</v>
+        <v>2026-07-31T11:29:09.409Z</v>
       </c>
       <c r="F251" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="252">
@@ -5430,13 +5430,13 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>0.81 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-01T10:47:23.531Z</v>
+        <v>2026-07-31T11:29:10.724Z</v>
       </c>
       <c r="F252" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="253">
@@ -5450,13 +5450,13 @@
         <v>PASS</v>
       </c>
       <c r="D253" t="str">
-        <v>0.89 sec</v>
+        <v>1.42 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-01T10:47:24.422Z</v>
+        <v>2026-07-31T11:29:12.143Z</v>
       </c>
       <c r="F253" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="254">
@@ -5470,13 +5470,13 @@
         <v>PASS</v>
       </c>
       <c r="D254" t="str">
-        <v>0.67 sec</v>
+        <v>1.38 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-01T10:47:25.091Z</v>
+        <v>2026-07-31T11:29:13.526Z</v>
       </c>
       <c r="F254" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="255">
@@ -5490,13 +5490,13 @@
         <v>PASS</v>
       </c>
       <c r="D255" t="str">
-        <v>0.97 sec</v>
+        <v>1.58 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-01T10:47:26.059Z</v>
+        <v>2026-07-31T11:29:15.110Z</v>
       </c>
       <c r="F255" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="256">
@@ -5510,13 +5510,13 @@
         <v>PASS</v>
       </c>
       <c r="D256" t="str">
-        <v>0.85 sec</v>
+        <v>1.37 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-01T10:47:26.909Z</v>
+        <v>2026-07-31T11:29:16.477Z</v>
       </c>
       <c r="F256" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="257">
@@ -5530,13 +5530,13 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>0.58 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-01T10:47:27.493Z</v>
+        <v>2026-07-31T11:29:17.825Z</v>
       </c>
       <c r="F257" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="258">
@@ -5550,13 +5550,13 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>1.06 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-01T10:47:28.558Z</v>
+        <v>2026-07-31T11:29:18.987Z</v>
       </c>
       <c r="F258" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="259">
@@ -5570,13 +5570,13 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>1.09 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-01T10:47:29.648Z</v>
+        <v>2026-07-31T11:29:20.444Z</v>
       </c>
       <c r="F259" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="260">
@@ -5590,13 +5590,13 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>0.56 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-01T10:47:30.206Z</v>
+        <v>2026-07-31T11:29:21.791Z</v>
       </c>
       <c r="F260" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="261">
@@ -5610,13 +5610,13 @@
         <v>PASS</v>
       </c>
       <c r="D261" t="str">
-        <v>0.70 sec</v>
+        <v>1.57 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-01T10:47:30.909Z</v>
+        <v>2026-07-31T11:29:23.360Z</v>
       </c>
       <c r="F261" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="262">
@@ -5630,13 +5630,13 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>0.88 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-01T10:47:31.788Z</v>
+        <v>2026-07-31T11:29:24.808Z</v>
       </c>
       <c r="F262" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="263">
@@ -5650,13 +5650,13 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>0.79 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-01T10:47:32.576Z</v>
+        <v>2026-07-31T11:29:26.141Z</v>
       </c>
       <c r="F263" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="264">
@@ -5670,13 +5670,13 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>0.66 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-01T10:47:33.234Z</v>
+        <v>2026-07-31T11:29:27.477Z</v>
       </c>
       <c r="F264" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="265">
@@ -5690,13 +5690,13 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>0.97 sec</v>
+        <v>1.58 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-01T10:47:34.203Z</v>
+        <v>2026-07-31T11:29:29.059Z</v>
       </c>
       <c r="F265" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="266">
@@ -5710,13 +5710,13 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>0.91 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-01T10:47:35.109Z</v>
+        <v>2026-07-31T11:29:30.524Z</v>
       </c>
       <c r="F266" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="267">
@@ -5730,13 +5730,13 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>0.99 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-01T10:47:36.095Z</v>
+        <v>2026-07-31T11:29:31.875Z</v>
       </c>
       <c r="F267" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="268">
@@ -5750,13 +5750,13 @@
         <v>PASS</v>
       </c>
       <c r="D268" t="str">
-        <v>0.90 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-01T10:47:36.999Z</v>
+        <v>2026-07-31T11:29:33.343Z</v>
       </c>
       <c r="F268" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="269">
@@ -5770,13 +5770,13 @@
         <v>PASS</v>
       </c>
       <c r="D269" t="str">
-        <v>0.77 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-01T10:47:37.772Z</v>
+        <v>2026-07-31T11:29:34.675Z</v>
       </c>
       <c r="F269" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="270">
@@ -5790,13 +5790,13 @@
         <v>PASS</v>
       </c>
       <c r="D270" t="str">
-        <v>0.82 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-01T10:47:38.595Z</v>
+        <v>2026-07-31T11:29:35.998Z</v>
       </c>
       <c r="F270" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="271">
@@ -5810,13 +5810,13 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.94 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-01T10:47:39.537Z</v>
+        <v>2026-07-31T11:29:37.468Z</v>
       </c>
       <c r="F271" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="272">
@@ -5830,13 +5830,13 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>0.81 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-01T10:47:40.348Z</v>
+        <v>2026-07-31T11:29:38.900Z</v>
       </c>
       <c r="F272" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="273">
@@ -5850,13 +5850,13 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>0.66 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-01T10:47:41.011Z</v>
+        <v>2026-07-31T11:29:40.426Z</v>
       </c>
       <c r="F273" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="274">
@@ -5870,13 +5870,13 @@
         <v>PASS</v>
       </c>
       <c r="D274" t="str">
-        <v>0.84 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-01T10:47:41.852Z</v>
+        <v>2026-07-31T11:29:41.891Z</v>
       </c>
       <c r="F274" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="275">
@@ -5890,13 +5890,13 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.79 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-01T10:47:42.637Z</v>
+        <v>2026-07-31T11:29:43.240Z</v>
       </c>
       <c r="F275" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="276">
@@ -5910,13 +5910,13 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.78 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-01T10:47:43.421Z</v>
+        <v>2026-07-31T11:29:44.574Z</v>
       </c>
       <c r="F276" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="277">
@@ -5930,13 +5930,13 @@
         <v>PASS</v>
       </c>
       <c r="D277" t="str">
-        <v>1.09 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-01T10:47:44.510Z</v>
+        <v>2026-07-31T11:29:46.125Z</v>
       </c>
       <c r="F277" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="278">
@@ -5950,13 +5950,13 @@
         <v>PASS</v>
       </c>
       <c r="D278" t="str">
-        <v>0.63 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-01T10:47:45.141Z</v>
+        <v>2026-07-31T11:29:47.595Z</v>
       </c>
       <c r="F278" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="279">
@@ -5970,13 +5970,13 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.93 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-01T10:47:46.072Z</v>
+        <v>2026-07-31T11:29:49.134Z</v>
       </c>
       <c r="F279" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="280">
@@ -5990,13 +5990,13 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>1.08 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-01T10:47:47.157Z</v>
+        <v>2026-07-31T11:29:50.608Z</v>
       </c>
       <c r="F280" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="281">
@@ -6010,13 +6010,13 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>0.64 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-01T10:47:47.799Z</v>
+        <v>2026-07-31T11:29:51.941Z</v>
       </c>
       <c r="F281" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="282">
@@ -6030,13 +6030,13 @@
         <v>PASS</v>
       </c>
       <c r="D282" t="str">
-        <v>0.91 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-01T10:47:48.707Z</v>
+        <v>2026-07-31T11:29:53.261Z</v>
       </c>
       <c r="F282" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="283">
@@ -6050,13 +6050,13 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.89 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-01T10:47:49.598Z</v>
+        <v>2026-07-31T11:29:54.691Z</v>
       </c>
       <c r="F283" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="284">
@@ -6070,13 +6070,13 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>0.71 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-01T10:47:50.306Z</v>
+        <v>2026-07-31T11:29:56.025Z</v>
       </c>
       <c r="F284" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="285">
@@ -6090,13 +6090,13 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.99 sec</v>
+        <v>1.50 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-01T10:47:51.298Z</v>
+        <v>2026-07-31T11:29:57.524Z</v>
       </c>
       <c r="F285" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="286">
@@ -6110,13 +6110,13 @@
         <v>PASS</v>
       </c>
       <c r="D286" t="str">
-        <v>0.87 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-01T10:47:52.169Z</v>
+        <v>2026-07-31T11:29:58.875Z</v>
       </c>
       <c r="F286" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="287">
@@ -6130,13 +6130,13 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.85 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-01T10:47:53.021Z</v>
+        <v>2026-07-31T11:30:00.024Z</v>
       </c>
       <c r="F287" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="288">
@@ -6150,13 +6150,13 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>0.82 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-01T10:47:53.842Z</v>
+        <v>2026-07-31T11:30:01.356Z</v>
       </c>
       <c r="F288" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="289">
@@ -6170,13 +6170,13 @@
         <v>PASS</v>
       </c>
       <c r="D289" t="str">
-        <v>0.95 sec</v>
+        <v>1.60 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-01T10:47:54.788Z</v>
+        <v>2026-07-31T11:30:02.959Z</v>
       </c>
       <c r="F289" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="290">
@@ -6190,13 +6190,13 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>0.58 sec</v>
+        <v>1.50 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-01T10:47:55.371Z</v>
+        <v>2026-07-31T11:30:04.462Z</v>
       </c>
       <c r="F290" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="291">
@@ -6210,13 +6210,13 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.93 sec</v>
+        <v>1.61 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-01T10:47:56.304Z</v>
+        <v>2026-07-31T11:30:06.075Z</v>
       </c>
       <c r="F291" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="292">
@@ -6230,13 +6230,13 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>0.90 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-01T10:47:57.202Z</v>
+        <v>2026-07-31T11:30:07.540Z</v>
       </c>
       <c r="F292" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="293">
@@ -6250,13 +6250,13 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.80 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-01T10:47:58.003Z</v>
+        <v>2026-07-31T11:30:08.877Z</v>
       </c>
       <c r="F293" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="294">
@@ -6270,13 +6270,13 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>0.77 sec</v>
+        <v>1.14 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-01T10:47:58.774Z</v>
+        <v>2026-07-31T11:30:10.019Z</v>
       </c>
       <c r="F294" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="295">
@@ -6290,13 +6290,13 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>0.88 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-01T10:47:59.656Z</v>
+        <v>2026-07-31T11:30:11.485Z</v>
       </c>
       <c r="F295" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="296">
@@ -6310,13 +6310,13 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>0.78 sec</v>
+        <v>1.41 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-01T10:48:00.438Z</v>
+        <v>2026-07-31T11:30:12.893Z</v>
       </c>
       <c r="F296" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="297">
@@ -6330,13 +6330,13 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>0.93 sec</v>
+        <v>1.51 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-01T10:48:01.370Z</v>
+        <v>2026-07-31T11:30:14.408Z</v>
       </c>
       <c r="F297" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="298">
@@ -6350,13 +6350,13 @@
         <v>PASS</v>
       </c>
       <c r="D298" t="str">
-        <v>0.69 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-01T10:48:02.055Z</v>
+        <v>2026-07-31T11:30:15.589Z</v>
       </c>
       <c r="F298" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="299">
@@ -6370,13 +6370,13 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>0.62 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-01T10:48:02.674Z</v>
+        <v>2026-07-31T11:30:16.923Z</v>
       </c>
       <c r="F299" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="300">
@@ -6390,13 +6390,13 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.80 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-01T10:48:03.472Z</v>
+        <v>2026-07-31T11:30:18.268Z</v>
       </c>
       <c r="F300" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="301">
@@ -6410,13 +6410,13 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>0.94 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-01T10:48:04.410Z</v>
+        <v>2026-07-31T11:30:19.756Z</v>
       </c>
       <c r="F301" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="302">
@@ -6430,13 +6430,13 @@
         <v>PASS</v>
       </c>
       <c r="D302" t="str">
-        <v>0.65 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-01T10:48:05.058Z</v>
+        <v>2026-07-31T11:30:21.106Z</v>
       </c>
       <c r="F302" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="303">
@@ -6450,13 +6450,13 @@
         <v>PASS</v>
       </c>
       <c r="D303" t="str">
-        <v>0.92 sec</v>
+        <v>1.60 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-01T10:48:05.975Z</v>
+        <v>2026-07-31T11:30:22.706Z</v>
       </c>
       <c r="F303" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="304">
@@ -6470,13 +6470,13 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.86 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-01T10:48:06.834Z</v>
+        <v>2026-07-31T11:30:23.991Z</v>
       </c>
       <c r="F304" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="305">
@@ -6490,13 +6490,13 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>0.79 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-01T10:48:07.622Z</v>
+        <v>2026-07-31T11:30:25.341Z</v>
       </c>
       <c r="F305" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="306">
@@ -6510,13 +6510,13 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>0.83 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-01T10:48:08.452Z</v>
+        <v>2026-07-31T11:30:26.654Z</v>
       </c>
       <c r="F306" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="307">
@@ -6530,13 +6530,13 @@
         <v>PASS</v>
       </c>
       <c r="D307" t="str">
-        <v>0.77 sec</v>
+        <v>1.59 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-01T10:48:09.223Z</v>
+        <v>2026-07-31T11:30:28.240Z</v>
       </c>
       <c r="F307" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="308">
@@ -6550,13 +6550,13 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.65 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-01T10:48:09.871Z</v>
+        <v>2026-07-31T11:30:29.706Z</v>
       </c>
       <c r="F308" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="309">
@@ -6570,13 +6570,13 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>0.82 sec</v>
+        <v>1.51 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-01T10:48:10.691Z</v>
+        <v>2026-07-31T11:30:31.218Z</v>
       </c>
       <c r="F309" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="310">
@@ -6590,13 +6590,13 @@
         <v>PASS</v>
       </c>
       <c r="D310" t="str">
-        <v>0.75 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-01T10:48:11.444Z</v>
+        <v>2026-07-31T11:30:32.672Z</v>
       </c>
       <c r="F310" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="311">
@@ -6610,13 +6610,13 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.86 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-01T10:48:12.309Z</v>
+        <v>2026-07-31T11:30:33.822Z</v>
       </c>
       <c r="F311" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="312">
@@ -6630,13 +6630,13 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>0.90 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-01T10:48:13.208Z</v>
+        <v>2026-07-31T11:30:35.133Z</v>
       </c>
       <c r="F312" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="313">
@@ -6650,13 +6650,13 @@
         <v>PASS</v>
       </c>
       <c r="D313" t="str">
-        <v>0.76 sec</v>
+        <v>1.41 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-01T10:48:13.970Z</v>
+        <v>2026-07-31T11:30:36.540Z</v>
       </c>
       <c r="F313" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="314">
@@ -6670,13 +6670,13 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>0.87 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-01T10:48:14.840Z</v>
+        <v>2026-07-31T11:30:37.889Z</v>
       </c>
       <c r="F314" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="315">
@@ -6690,13 +6690,13 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.95 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-01T10:48:15.787Z</v>
+        <v>2026-07-31T11:30:39.367Z</v>
       </c>
       <c r="F315" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="316">
@@ -6710,13 +6710,13 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.82 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-01T10:48:16.607Z</v>
+        <v>2026-07-31T11:30:40.722Z</v>
       </c>
       <c r="F316" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="317">
@@ -6730,13 +6730,13 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>0.81 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-01T10:48:17.418Z</v>
+        <v>2026-07-31T11:30:42.055Z</v>
       </c>
       <c r="F317" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="318">
@@ -6750,13 +6750,13 @@
         <v>PASS</v>
       </c>
       <c r="D318" t="str">
-        <v>0.80 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-01T10:48:18.221Z</v>
+        <v>2026-07-31T11:30:43.368Z</v>
       </c>
       <c r="F318" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="319">
@@ -6770,13 +6770,13 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>0.92 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-01T10:48:19.138Z</v>
+        <v>2026-07-31T11:30:44.913Z</v>
       </c>
       <c r="F319" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="320">
@@ -6790,13 +6790,13 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>0.85 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-01T10:48:19.987Z</v>
+        <v>2026-07-31T11:30:46.396Z</v>
       </c>
       <c r="F320" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="321">
@@ -6810,13 +6810,13 @@
         <v>PASS</v>
       </c>
       <c r="D321" t="str">
-        <v>0.95 sec</v>
+        <v>1.61 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-01T10:48:20.939Z</v>
+        <v>2026-07-31T11:30:48.007Z</v>
       </c>
       <c r="F321" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="322">
@@ -6830,13 +6830,13 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>0.82 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-01T10:48:21.757Z</v>
+        <v>2026-07-31T11:30:49.455Z</v>
       </c>
       <c r="F322" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="323">
@@ -6850,13 +6850,13 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.80 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-01T10:48:22.553Z</v>
+        <v>2026-07-31T11:30:50.787Z</v>
       </c>
       <c r="F323" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="324">
@@ -6870,13 +6870,13 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>1.03 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-01T10:48:23.579Z</v>
+        <v>2026-07-31T11:30:52.103Z</v>
       </c>
       <c r="F324" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="325">
@@ -6890,13 +6890,13 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>0.89 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-01T10:48:24.472Z</v>
+        <v>2026-07-31T11:30:53.655Z</v>
       </c>
       <c r="F325" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="326">
@@ -6910,13 +6910,13 @@
         <v>PASS</v>
       </c>
       <c r="D326" t="str">
-        <v>0.56 sec</v>
+        <v>1.43 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-01T10:48:25.037Z</v>
+        <v>2026-07-31T11:30:55.087Z</v>
       </c>
       <c r="F326" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="327">
@@ -6930,13 +6930,13 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.74 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-01T10:48:25.774Z</v>
+        <v>2026-07-31T11:30:56.425Z</v>
       </c>
       <c r="F327" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="328">
@@ -6950,13 +6950,13 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.87 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-01T10:48:26.642Z</v>
+        <v>2026-07-31T11:30:57.887Z</v>
       </c>
       <c r="F328" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="329">
@@ -6970,13 +6970,13 @@
         <v>PASS</v>
       </c>
       <c r="D329" t="str">
-        <v>1.03 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-01T10:48:27.670Z</v>
+        <v>2026-07-31T11:30:59.238Z</v>
       </c>
       <c r="F329" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="330">
@@ -6990,13 +6990,13 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.79 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-01T10:48:28.458Z</v>
+        <v>2026-07-31T11:31:00.554Z</v>
       </c>
       <c r="F330" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="331">
@@ -7010,13 +7010,13 @@
         <v>PASS</v>
       </c>
       <c r="D331" t="str">
-        <v>0.88 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-01T10:48:29.335Z</v>
+        <v>2026-07-31T11:31:02.031Z</v>
       </c>
       <c r="F331" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="332">
@@ -7030,13 +7030,13 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>0.68 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-01T10:48:30.013Z</v>
+        <v>2026-07-31T11:31:03.469Z</v>
       </c>
       <c r="F332" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="333">
@@ -7050,13 +7050,13 @@
         <v>PASS</v>
       </c>
       <c r="D333" t="str">
-        <v>0.89 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-01T10:48:30.903Z</v>
+        <v>2026-07-31T11:31:05.005Z</v>
       </c>
       <c r="F333" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="334">
@@ -7070,13 +7070,13 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.84 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-01T10:48:31.747Z</v>
+        <v>2026-07-31T11:31:06.456Z</v>
       </c>
       <c r="F334" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="335">
@@ -7090,13 +7090,13 @@
         <v>PASS</v>
       </c>
       <c r="D335" t="str">
-        <v>0.81 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-01T10:48:32.557Z</v>
+        <v>2026-07-31T11:31:07.621Z</v>
       </c>
       <c r="F335" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="336">
@@ -7110,13 +7110,13 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>0.76 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-01T10:48:33.318Z</v>
+        <v>2026-07-31T11:31:08.937Z</v>
       </c>
       <c r="F336" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="337">
@@ -7130,13 +7130,13 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>3.63 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-01T10:48:36.954Z</v>
+        <v>2026-07-31T11:31:10.463Z</v>
       </c>
       <c r="F337" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="338">
@@ -7150,13 +7150,13 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>0.84 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-01T10:48:37.790Z</v>
+        <v>2026-07-31T11:31:11.905Z</v>
       </c>
       <c r="F338" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="339">
@@ -7170,13 +7170,13 @@
         <v>PASS</v>
       </c>
       <c r="D339" t="str">
-        <v>2.94 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-01T10:48:40.733Z</v>
+        <v>2026-07-31T11:31:13.438Z</v>
       </c>
       <c r="F339" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="340">
@@ -7190,13 +7190,13 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>0.87 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-01T10:48:41.602Z</v>
+        <v>2026-07-31T11:31:14.905Z</v>
       </c>
       <c r="F340" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="341">
@@ -7210,13 +7210,13 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.76 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-01T10:48:42.364Z</v>
+        <v>2026-07-31T11:31:16.254Z</v>
       </c>
       <c r="F341" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="342">
@@ -7230,13 +7230,13 @@
         <v>PASS</v>
       </c>
       <c r="D342" t="str">
-        <v>0.77 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-01T10:48:43.133Z</v>
+        <v>2026-07-31T11:31:17.580Z</v>
       </c>
       <c r="F342" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="343">
@@ -7250,13 +7250,13 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>0.92 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-01T10:48:44.058Z</v>
+        <v>2026-07-31T11:31:19.021Z</v>
       </c>
       <c r="F343" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="344">
@@ -7270,13 +7270,13 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>0.81 sec</v>
+        <v>1.39 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-01T10:48:44.871Z</v>
+        <v>2026-07-31T11:31:20.415Z</v>
       </c>
       <c r="F344" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="345">
@@ -7290,13 +7290,13 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>0.73 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-01T10:48:45.606Z</v>
+        <v>2026-07-31T11:31:21.909Z</v>
       </c>
       <c r="F345" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="346">
@@ -7310,13 +7310,13 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.64 sec</v>
+        <v>1.36 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-01T10:48:46.245Z</v>
+        <v>2026-07-31T11:31:23.271Z</v>
       </c>
       <c r="F346" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="347">
@@ -7330,13 +7330,13 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.79 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-01T10:48:47.038Z</v>
+        <v>2026-07-31T11:31:24.455Z</v>
       </c>
       <c r="F347" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="348">
@@ -7350,13 +7350,13 @@
         <v>PASS</v>
       </c>
       <c r="D348" t="str">
-        <v>0.87 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-01T10:48:47.904Z</v>
+        <v>2026-07-31T11:31:25.636Z</v>
       </c>
       <c r="F348" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="349">
@@ -7370,13 +7370,13 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>0.77 sec</v>
+        <v>1.60 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-01T10:48:48.674Z</v>
+        <v>2026-07-31T11:31:27.239Z</v>
       </c>
       <c r="F349" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="350">
@@ -7390,13 +7390,13 @@
         <v>PASS</v>
       </c>
       <c r="D350" t="str">
-        <v>0.81 sec</v>
+        <v>1.47 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-01T10:48:49.488Z</v>
+        <v>2026-07-31T11:31:28.705Z</v>
       </c>
       <c r="F350" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="351">
@@ -7410,13 +7410,13 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>3.10 sec</v>
+        <v>1.59 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-01T10:48:52.590Z</v>
+        <v>2026-07-31T11:31:30.298Z</v>
       </c>
       <c r="F351" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="352">
@@ -7430,13 +7430,13 @@
         <v>PASS</v>
       </c>
       <c r="D352" t="str">
-        <v>0.68 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-01T10:48:53.268Z</v>
+        <v>2026-07-31T11:31:31.774Z</v>
       </c>
       <c r="F352" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="353">
@@ -7450,13 +7450,13 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.66 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-01T10:48:53.928Z</v>
+        <v>2026-07-31T11:31:32.954Z</v>
       </c>
       <c r="F353" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="354">
@@ -7470,13 +7470,13 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.72 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-01T10:48:54.647Z</v>
+        <v>2026-07-31T11:31:34.287Z</v>
       </c>
       <c r="F354" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="355">
@@ -7490,13 +7490,13 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>1.03 sec</v>
+        <v>1.50 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-01T10:48:55.675Z</v>
+        <v>2026-07-31T11:31:35.787Z</v>
       </c>
       <c r="F355" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="356">
@@ -7510,13 +7510,13 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>0.85 sec</v>
+        <v>1.26 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-01T10:48:56.529Z</v>
+        <v>2026-07-31T11:31:37.047Z</v>
       </c>
       <c r="F356" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="357">
@@ -7530,13 +7530,13 @@
         <v>PASS</v>
       </c>
       <c r="D357" t="str">
-        <v>0.96 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-01T10:48:57.488Z</v>
+        <v>2026-07-31T11:31:38.581Z</v>
       </c>
       <c r="F357" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="358">
@@ -7550,13 +7550,13 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>0.85 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-01T10:48:58.337Z</v>
+        <v>2026-07-31T11:31:40.036Z</v>
       </c>
       <c r="F358" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="359">
@@ -7570,13 +7570,13 @@
         <v>PASS</v>
       </c>
       <c r="D359" t="str">
-        <v>0.78 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-01T10:48:59.119Z</v>
+        <v>2026-07-31T11:31:41.387Z</v>
       </c>
       <c r="F359" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="360">
@@ -7590,13 +7590,13 @@
         <v>PASS</v>
       </c>
       <c r="D360" t="str">
-        <v>1.04 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-01T10:49:00.159Z</v>
+        <v>2026-07-31T11:31:42.738Z</v>
       </c>
       <c r="F360" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="361">
@@ -7610,13 +7610,13 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>0.96 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-01T10:49:01.122Z</v>
+        <v>2026-07-31T11:31:44.295Z</v>
       </c>
       <c r="F361" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="362">
@@ -7630,13 +7630,13 @@
         <v>PASS</v>
       </c>
       <c r="D362" t="str">
-        <v>0.65 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-01T10:49:01.774Z</v>
+        <v>2026-07-31T11:31:45.730Z</v>
       </c>
       <c r="F362" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="363">
@@ -7650,13 +7650,13 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>0.95 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-01T10:49:02.725Z</v>
+        <v>2026-07-31T11:31:47.289Z</v>
       </c>
       <c r="F363" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="364">
@@ -7670,13 +7670,13 @@
         <v>PASS</v>
       </c>
       <c r="D364" t="str">
-        <v>0.82 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-01T10:49:03.550Z</v>
+        <v>2026-07-31T11:31:48.770Z</v>
       </c>
       <c r="F364" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="365">
@@ -7690,13 +7690,13 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.82 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-01T10:49:04.368Z</v>
+        <v>2026-07-31T11:31:50.119Z</v>
       </c>
       <c r="F365" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="366">
@@ -7710,13 +7710,13 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.79 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-01T10:49:05.156Z</v>
+        <v>2026-07-31T11:31:51.435Z</v>
       </c>
       <c r="F366" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="367">
@@ -7730,13 +7730,13 @@
         <v>PASS</v>
       </c>
       <c r="D367" t="str">
-        <v>0.95 sec</v>
+        <v>1.39 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-01T10:49:06.103Z</v>
+        <v>2026-07-31T11:31:52.820Z</v>
       </c>
       <c r="F367" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="368">
@@ -7750,13 +7750,13 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>0.64 sec</v>
+        <v>1.44 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-01T10:49:06.738Z</v>
+        <v>2026-07-31T11:31:54.258Z</v>
       </c>
       <c r="F368" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="369">
@@ -7770,13 +7770,13 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>0.95 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-01T10:49:07.690Z</v>
+        <v>2026-07-31T11:31:55.786Z</v>
       </c>
       <c r="F369" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="370">
@@ -7790,13 +7790,13 @@
         <v>PASS</v>
       </c>
       <c r="D370" t="str">
-        <v>0.85 sec</v>
+        <v>1.45 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-01T10:49:08.539Z</v>
+        <v>2026-07-31T11:31:57.240Z</v>
       </c>
       <c r="F370" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="371">
@@ -7810,13 +7810,13 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.79 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-01T10:49:09.325Z</v>
+        <v>2026-07-31T11:31:58.419Z</v>
       </c>
       <c r="F371" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="372">
@@ -7830,13 +7830,13 @@
         <v>PASS</v>
       </c>
       <c r="D372" t="str">
-        <v>0.80 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-01T10:49:10.123Z</v>
+        <v>2026-07-31T11:31:59.736Z</v>
       </c>
       <c r="F372" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="373">
@@ -7850,13 +7850,13 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>0.86 sec</v>
+        <v>1.42 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-01T10:49:10.983Z</v>
+        <v>2026-07-31T11:32:01.153Z</v>
       </c>
       <c r="F373" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="374">
@@ -7870,13 +7870,13 @@
         <v>PASS</v>
       </c>
       <c r="D374" t="str">
-        <v>0.77 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-01T10:49:11.749Z</v>
+        <v>2026-07-31T11:32:02.505Z</v>
       </c>
       <c r="F374" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="375">
@@ -7890,13 +7890,13 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>0.92 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-01T10:49:12.673Z</v>
+        <v>2026-07-31T11:32:03.854Z</v>
       </c>
       <c r="F375" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="376">
@@ -7910,13 +7910,13 @@
         <v>PASS</v>
       </c>
       <c r="D376" t="str">
-        <v>0.83 sec</v>
+        <v>1.38 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-01T10:49:13.501Z</v>
+        <v>2026-07-31T11:32:05.236Z</v>
       </c>
       <c r="F376" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="377">
@@ -7930,13 +7930,13 @@
         <v>PASS</v>
       </c>
       <c r="D377" t="str">
-        <v>0.79 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-01T10:49:14.294Z</v>
+        <v>2026-07-31T11:32:06.585Z</v>
       </c>
       <c r="F377" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="378">
@@ -7950,13 +7950,13 @@
         <v>PASS</v>
       </c>
       <c r="D378" t="str">
-        <v>0.59 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-01T10:49:14.889Z</v>
+        <v>2026-07-31T11:32:07.912Z</v>
       </c>
       <c r="F378" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="379">
@@ -7970,13 +7970,13 @@
         <v>PASS</v>
       </c>
       <c r="D379" t="str">
-        <v>0.77 sec</v>
+        <v>1.56 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-01T10:49:15.654Z</v>
+        <v>2026-07-31T11:32:09.469Z</v>
       </c>
       <c r="F379" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="380">
@@ -7990,13 +7990,13 @@
         <v>PASS</v>
       </c>
       <c r="D380" t="str">
-        <v>0.83 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-01T10:49:16.483Z</v>
+        <v>2026-07-31T11:32:10.929Z</v>
       </c>
       <c r="F380" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="381">
@@ -8010,13 +8010,13 @@
         <v>PASS</v>
       </c>
       <c r="D381" t="str">
-        <v>0.73 sec</v>
+        <v>1.60 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-01T10:49:17.218Z</v>
+        <v>2026-07-31T11:32:12.526Z</v>
       </c>
       <c r="F381" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="382">
@@ -8030,13 +8030,13 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.87 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-01T10:49:18.087Z</v>
+        <v>2026-07-31T11:32:13.985Z</v>
       </c>
       <c r="F382" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="383">
@@ -8050,13 +8050,13 @@
         <v>PASS</v>
       </c>
       <c r="D383" t="str">
-        <v>0.82 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-01T10:49:18.907Z</v>
+        <v>2026-07-31T11:32:15.319Z</v>
       </c>
       <c r="F383" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="384">
@@ -8070,13 +8070,13 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>1.01 sec</v>
+        <v>1.33 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-01T10:49:19.917Z</v>
+        <v>2026-07-31T11:32:16.651Z</v>
       </c>
       <c r="F384" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="385">
@@ -8090,13 +8090,13 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>0.92 sec</v>
+        <v>1.55 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-01T10:49:20.833Z</v>
+        <v>2026-07-31T11:32:18.203Z</v>
       </c>
       <c r="F385" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="386">
@@ -8110,13 +8110,13 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>0.57 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-01T10:49:21.405Z</v>
+        <v>2026-07-31T11:32:19.686Z</v>
       </c>
       <c r="F386" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="387">
@@ -8130,13 +8130,13 @@
         <v>PASS</v>
       </c>
       <c r="D387" t="str">
-        <v>0.93 sec</v>
+        <v>1.54 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-01T10:49:22.334Z</v>
+        <v>2026-07-31T11:32:21.225Z</v>
       </c>
       <c r="F387" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="388">
@@ -8150,13 +8150,13 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.87 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-01T10:49:23.206Z</v>
+        <v>2026-07-31T11:32:22.704Z</v>
       </c>
       <c r="F388" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="389">
@@ -8170,13 +8170,13 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.57 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-01T10:49:23.774Z</v>
+        <v>2026-07-31T11:32:24.055Z</v>
       </c>
       <c r="F389" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="390">
@@ -8190,13 +8190,13 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>1.00 sec</v>
+        <v>1.32 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-01T10:49:24.777Z</v>
+        <v>2026-07-31T11:32:25.376Z</v>
       </c>
       <c r="F390" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="391">
@@ -8210,13 +8210,13 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.92 sec</v>
+        <v>1.49 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-01T10:49:25.694Z</v>
+        <v>2026-07-31T11:32:26.863Z</v>
       </c>
       <c r="F391" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="392">
@@ -8230,13 +8230,13 @@
         <v>PASS</v>
       </c>
       <c r="D392" t="str">
-        <v>0.56 sec</v>
+        <v>1.46 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-01T10:49:26.257Z</v>
+        <v>2026-07-31T11:32:28.320Z</v>
       </c>
       <c r="F392" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="393">
@@ -8250,13 +8250,13 @@
         <v>PASS</v>
       </c>
       <c r="D393" t="str">
-        <v>0.94 sec</v>
+        <v>1.57 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-01T10:49:27.194Z</v>
+        <v>2026-07-31T11:32:29.890Z</v>
       </c>
       <c r="F393" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="394">
@@ -8270,13 +8270,13 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>0.85 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-01T10:49:28.040Z</v>
+        <v>2026-07-31T11:32:31.368Z</v>
       </c>
       <c r="F394" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="395">
@@ -8290,13 +8290,13 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>0.78 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-01T10:49:28.824Z</v>
+        <v>2026-07-31T11:32:32.718Z</v>
       </c>
       <c r="F395" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="396">
@@ -8310,13 +8310,13 @@
         <v>PASS</v>
       </c>
       <c r="D396" t="str">
-        <v>0.83 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-01T10:49:29.651Z</v>
+        <v>2026-07-31T11:32:33.867Z</v>
       </c>
       <c r="F396" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="397">
@@ -8330,13 +8330,13 @@
         <v>PASS</v>
       </c>
       <c r="D397" t="str">
-        <v>0.93 sec</v>
+        <v>1.57 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-01T10:49:30.585Z</v>
+        <v>2026-07-31T11:32:35.437Z</v>
       </c>
       <c r="F397" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="398">
@@ -8350,13 +8350,13 @@
         <v>PASS</v>
       </c>
       <c r="D398" t="str">
-        <v>0.83 sec</v>
+        <v>1.48 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-01T10:49:31.420Z</v>
+        <v>2026-07-31T11:32:36.919Z</v>
       </c>
       <c r="F398" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="399">
@@ -8370,13 +8370,13 @@
         <v>PASS</v>
       </c>
       <c r="D399" t="str">
-        <v>0.90 sec</v>
+        <v>1.53 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-01T10:49:32.317Z</v>
+        <v>2026-07-31T11:32:38.445Z</v>
       </c>
       <c r="F399" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="400">
@@ -8390,13 +8390,13 @@
         <v>PASS</v>
       </c>
       <c r="D400" t="str">
-        <v>0.88 sec</v>
+        <v>1.29 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-01T10:49:33.200Z</v>
+        <v>2026-07-31T11:32:39.734Z</v>
       </c>
       <c r="F400" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
     <row r="401">
@@ -8410,13 +8410,13 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>0.82 sec</v>
+        <v>1.35 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-01T10:49:34.017Z</v>
+        <v>2026-07-31T11:32:41.084Z</v>
       </c>
       <c r="F401" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Invalid email or password</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium Report.xlsx
+++ b/reports/Selenium Report.xlsx
@@ -427,13 +427,13 @@
         <v>Valid citizen demo login</v>
       </c>
       <c r="C2" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D2" t="str">
-        <v>2.02 sec</v>
+        <v>4.82 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-07-31T11:23:05.559Z</v>
+        <v>2026-08-08T07:05:29.938Z</v>
       </c>
       <c r="F2" t="str">
         <v>Success</v>
@@ -447,13 +447,13 @@
         <v>Valid volunteer demo login</v>
       </c>
       <c r="C3" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D3" t="str">
-        <v>1.56 sec</v>
+        <v>3.90 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-07-31T11:23:07.122Z</v>
+        <v>2026-08-08T07:05:33.836Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -467,13 +467,13 @@
         <v>Valid admin demo login</v>
       </c>
       <c r="C4" t="str">
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="D4" t="str">
-        <v>1.53 sec</v>
+        <v>4.29 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-07-31T11:23:08.651Z</v>
+        <v>2026-08-08T07:05:38.124Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +490,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>3.83 sec</v>
+        <v>3.79 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-07-31T11:23:12.484Z</v>
+        <v>2026-08-08T07:05:41.915Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +510,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>3.89 sec</v>
+        <v>3.91 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-07-31T11:23:16.374Z</v>
+        <v>2026-08-08T07:05:45.827Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +530,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>3.73 sec</v>
+        <v>3.90 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-07-31T11:23:20.105Z</v>
+        <v>2026-08-08T07:05:49.726Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,13 +550,13 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>1.81 sec</v>
+        <v>4.15 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-07-31T11:23:21.918Z</v>
+        <v>2026-08-08T07:05:53.875Z</v>
       </c>
       <c r="F8" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="9">
@@ -570,10 +570,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>3.87 sec</v>
+        <v>3.81 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-07-31T11:23:25.783Z</v>
+        <v>2026-08-08T07:05:57.686Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -590,10 +590,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>3.87 sec</v>
+        <v>3.90 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-07-31T11:23:29.655Z</v>
+        <v>2026-08-08T07:06:01.588Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -610,13 +610,13 @@
         <v>PASS</v>
       </c>
       <c r="D11" t="str">
-        <v>1.37 sec</v>
+        <v>3.92 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-07-31T11:23:31.026Z</v>
+        <v>2026-08-08T07:06:05.510Z</v>
       </c>
       <c r="F11" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="12">
@@ -630,13 +630,13 @@
         <v>PASS</v>
       </c>
       <c r="D12" t="str">
-        <v>1.31 sec</v>
+        <v>3.73 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-07-31T11:23:32.337Z</v>
+        <v>2026-08-08T07:06:09.237Z</v>
       </c>
       <c r="F12" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>PASS</v>
       </c>
       <c r="D13" t="str">
-        <v>1.48 sec</v>
+        <v>4.05 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-07-31T11:23:33.813Z</v>
+        <v>2026-08-08T07:06:13.291Z</v>
       </c>
       <c r="F13" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="14">
@@ -670,13 +670,13 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>1.43 sec</v>
+        <v>3.77 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-07-31T11:23:35.240Z</v>
+        <v>2026-08-08T07:06:17.063Z</v>
       </c>
       <c r="F14" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="15">
@@ -690,13 +690,13 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>1.52 sec</v>
+        <v>4.08 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-07-31T11:23:36.759Z</v>
+        <v>2026-08-08T07:06:21.142Z</v>
       </c>
       <c r="F15" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="16">
@@ -710,13 +710,13 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>1.45 sec</v>
+        <v>3.96 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-07-31T11:23:38.208Z</v>
+        <v>2026-08-08T07:06:25.102Z</v>
       </c>
       <c r="F16" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="17">
@@ -730,13 +730,13 @@
         <v>PASS</v>
       </c>
       <c r="D17" t="str">
-        <v>1.35 sec</v>
+        <v>4.02 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-07-31T11:23:39.557Z</v>
+        <v>2026-08-08T07:06:29.122Z</v>
       </c>
       <c r="F17" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="18">
@@ -750,13 +750,13 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>1.30 sec</v>
+        <v>3.85 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-07-31T11:23:40.861Z</v>
+        <v>2026-08-08T07:06:32.973Z</v>
       </c>
       <c r="F18" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="19">
@@ -770,13 +770,13 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>1.45 sec</v>
+        <v>4.06 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-07-31T11:23:42.308Z</v>
+        <v>2026-08-08T07:06:37.037Z</v>
       </c>
       <c r="F19" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="20">
@@ -790,13 +790,13 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>1.36 sec</v>
+        <v>4.02 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-07-31T11:23:43.673Z</v>
+        <v>2026-08-08T07:06:41.059Z</v>
       </c>
       <c r="F20" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="21">
@@ -810,13 +810,13 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>1.48 sec</v>
+        <v>4.01 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-07-31T11:23:45.155Z</v>
+        <v>2026-08-08T07:06:45.074Z</v>
       </c>
       <c r="F21" t="str">
-        <v>Invalid email or password</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="22">
@@ -830,13 +830,13 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>1.17 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-07-31T11:23:46.322Z</v>
+        <v>2026-08-08T07:06:46.117Z</v>
       </c>
       <c r="F22" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="23">
@@ -850,13 +850,13 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>1.33 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-07-31T11:23:47.656Z</v>
+        <v>2026-08-08T07:06:46.859Z</v>
       </c>
       <c r="F23" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="24">
@@ -870,13 +870,13 @@
         <v>PASS</v>
       </c>
       <c r="D24" t="str">
-        <v>1.33 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-07-31T11:23:48.982Z</v>
+        <v>2026-08-08T07:06:47.637Z</v>
       </c>
       <c r="F24" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="25">
@@ -890,13 +890,13 @@
         <v>PASS</v>
       </c>
       <c r="D25" t="str">
-        <v>1.59 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-07-31T11:23:50.572Z</v>
+        <v>2026-08-08T07:06:48.559Z</v>
       </c>
       <c r="F25" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="26">
@@ -910,13 +910,13 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>1.44 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-07-31T11:23:52.013Z</v>
+        <v>2026-08-08T07:06:49.385Z</v>
       </c>
       <c r="F26" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="27">
@@ -930,13 +930,13 @@
         <v>PASS</v>
       </c>
       <c r="D27" t="str">
-        <v>1.56 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-07-31T11:23:53.575Z</v>
+        <v>2026-08-08T07:06:50.405Z</v>
       </c>
       <c r="F27" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="28">
@@ -950,13 +950,13 @@
         <v>PASS</v>
       </c>
       <c r="D28" t="str">
-        <v>1.35 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-07-31T11:23:54.922Z</v>
+        <v>2026-08-08T07:06:51.353Z</v>
       </c>
       <c r="F28" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="29">
@@ -970,13 +970,13 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>1.35 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-07-31T11:23:56.272Z</v>
+        <v>2026-08-08T07:06:52.210Z</v>
       </c>
       <c r="F29" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="30">
@@ -990,13 +990,13 @@
         <v>PASS</v>
       </c>
       <c r="D30" t="str">
-        <v>1.31 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-07-31T11:23:57.581Z</v>
+        <v>2026-08-08T07:06:53.046Z</v>
       </c>
       <c r="F30" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="31">
@@ -1010,13 +1010,13 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>1.49 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-07-31T11:23:59.067Z</v>
+        <v>2026-08-08T07:06:54.355Z</v>
       </c>
       <c r="F31" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="32">
@@ -1030,13 +1030,13 @@
         <v>PASS</v>
       </c>
       <c r="D32" t="str">
-        <v>1.28 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-07-31T11:24:00.343Z</v>
+        <v>2026-08-08T07:06:55.230Z</v>
       </c>
       <c r="F32" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="33">
@@ -1050,13 +1050,13 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>1.52 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-07-31T11:24:01.868Z</v>
+        <v>2026-08-08T07:06:56.312Z</v>
       </c>
       <c r="F33" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="34">
@@ -1070,13 +1070,13 @@
         <v>PASS</v>
       </c>
       <c r="D34" t="str">
-        <v>1.27 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-07-31T11:24:03.141Z</v>
+        <v>2026-08-08T07:06:57.236Z</v>
       </c>
       <c r="F34" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="35">
@@ -1090,13 +1090,13 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>1.39 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-07-31T11:24:04.530Z</v>
+        <v>2026-08-08T07:06:58.034Z</v>
       </c>
       <c r="F35" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="36">
@@ -1110,13 +1110,13 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>1.31 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-07-31T11:24:05.839Z</v>
+        <v>2026-08-08T07:06:58.799Z</v>
       </c>
       <c r="F36" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="37">
@@ -1130,13 +1130,13 @@
         <v>PASS</v>
       </c>
       <c r="D37" t="str">
-        <v>1.57 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-07-31T11:24:07.411Z</v>
+        <v>2026-08-08T07:06:59.816Z</v>
       </c>
       <c r="F37" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="38">
@@ -1150,13 +1150,13 @@
         <v>PASS</v>
       </c>
       <c r="D38" t="str">
-        <v>1.38 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-07-31T11:24:08.790Z</v>
+        <v>2026-08-08T07:07:00.978Z</v>
       </c>
       <c r="F38" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="39">
@@ -1170,13 +1170,13 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>1.42 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-07-31T11:24:10.208Z</v>
+        <v>2026-08-08T07:07:01.974Z</v>
       </c>
       <c r="F39" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="40">
@@ -1190,13 +1190,13 @@
         <v>PASS</v>
       </c>
       <c r="D40" t="str">
-        <v>1.45 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-07-31T11:24:11.655Z</v>
+        <v>2026-08-08T07:07:02.798Z</v>
       </c>
       <c r="F40" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="41">
@@ -1210,13 +1210,13 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>1.33 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-07-31T11:24:12.989Z</v>
+        <v>2026-08-08T07:07:03.811Z</v>
       </c>
       <c r="F41" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="42">
@@ -1230,13 +1230,13 @@
         <v>PASS</v>
       </c>
       <c r="D42" t="str">
-        <v>1.31 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-07-31T11:24:14.303Z</v>
+        <v>2026-08-08T07:07:04.607Z</v>
       </c>
       <c r="F42" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
       </c>
     </row>
     <row r="43">
@@ -1250,13 +1250,13 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>1.45 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-07-31T11:24:15.755Z</v>
+        <v>2026-08-08T07:07:05.532Z</v>
       </c>
       <c r="F43" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="44">
@@ -1270,13 +1270,13 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>1.34 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-07-31T11:24:17.098Z</v>
+        <v>2026-08-08T07:07:06.458Z</v>
       </c>
       <c r="F44" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="45">
@@ -1290,13 +1290,13 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>1.49 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-07-31T11:24:18.590Z</v>
+        <v>2026-08-08T07:07:07.385Z</v>
       </c>
       <c r="F45" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="46">
@@ -1310,13 +1310,13 @@
         <v>PASS</v>
       </c>
       <c r="D46" t="str">
-        <v>1.37 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-07-31T11:24:19.959Z</v>
+        <v>2026-08-08T07:07:08.214Z</v>
       </c>
       <c r="F46" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="47">
@@ -1330,13 +1330,13 @@
         <v>PASS</v>
       </c>
       <c r="D47" t="str">
-        <v>1.35 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-07-31T11:24:21.305Z</v>
+        <v>2026-08-08T07:07:09.089Z</v>
       </c>
       <c r="F47" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="48">
@@ -1350,13 +1350,13 @@
         <v>PASS</v>
       </c>
       <c r="D48" t="str">
-        <v>1.33 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-07-31T11:24:22.640Z</v>
+        <v>2026-08-08T07:07:09.926Z</v>
       </c>
       <c r="F48" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="49">
@@ -1370,13 +1370,13 @@
         <v>PASS</v>
       </c>
       <c r="D49" t="str">
-        <v>1.42 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-07-31T11:24:24.057Z</v>
+        <v>2026-08-08T07:07:10.898Z</v>
       </c>
       <c r="F49" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="50">
@@ -1390,13 +1390,13 @@
         <v>PASS</v>
       </c>
       <c r="D50" t="str">
-        <v>1.48 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-07-31T11:24:25.540Z</v>
+        <v>2026-08-08T07:07:11.967Z</v>
       </c>
       <c r="F50" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="51">
@@ -1410,13 +1410,13 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>1.56 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-07-31T11:24:27.105Z</v>
+        <v>2026-08-08T07:07:12.966Z</v>
       </c>
       <c r="F51" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="52">
@@ -1430,13 +1430,13 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>1.33 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-07-31T11:24:28.440Z</v>
+        <v>2026-08-08T07:07:13.864Z</v>
       </c>
       <c r="F52" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="53">
@@ -1450,13 +1450,13 @@
         <v>PASS</v>
       </c>
       <c r="D53" t="str">
-        <v>1.35 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-07-31T11:24:29.789Z</v>
+        <v>2026-08-08T07:07:14.859Z</v>
       </c>
       <c r="F53" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="54">
@@ -1470,13 +1470,13 @@
         <v>PASS</v>
       </c>
       <c r="D54" t="str">
-        <v>1.33 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-07-31T11:24:31.121Z</v>
+        <v>2026-08-08T07:07:15.678Z</v>
       </c>
       <c r="F54" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="55">
@@ -1490,13 +1490,13 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>1.47 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-07-31T11:24:32.588Z</v>
+        <v>2026-08-08T07:07:16.634Z</v>
       </c>
       <c r="F55" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="56">
@@ -1510,13 +1510,13 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>1.18 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-07-31T11:24:33.772Z</v>
+        <v>2026-08-08T07:07:17.470Z</v>
       </c>
       <c r="F56" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="57">
@@ -1530,13 +1530,13 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>1.56 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-07-31T11:24:35.336Z</v>
+        <v>2026-08-08T07:07:18.419Z</v>
       </c>
       <c r="F57" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="58">
@@ -1550,13 +1550,13 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>1.45 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-07-31T11:24:36.788Z</v>
+        <v>2026-08-08T07:07:19.404Z</v>
       </c>
       <c r="F58" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="59">
@@ -1570,13 +1570,13 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>1.35 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-07-31T11:24:38.138Z</v>
+        <v>2026-08-08T07:07:20.193Z</v>
       </c>
       <c r="F59" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="60">
@@ -1590,13 +1590,13 @@
         <v>PASS</v>
       </c>
       <c r="D60" t="str">
-        <v>1.33 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-07-31T11:24:39.465Z</v>
+        <v>2026-08-08T07:07:21.011Z</v>
       </c>
       <c r="F60" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="61">
@@ -1610,13 +1610,13 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>1.57 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-07-31T11:24:41.040Z</v>
+        <v>2026-08-08T07:07:22.026Z</v>
       </c>
       <c r="F61" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="62">
@@ -1630,13 +1630,13 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>1.44 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-07-31T11:24:42.482Z</v>
+        <v>2026-08-08T07:07:23.072Z</v>
       </c>
       <c r="F62" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="63">
@@ -1650,13 +1650,13 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>1.52 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-07-31T11:24:43.999Z</v>
+        <v>2026-08-08T07:07:24.037Z</v>
       </c>
       <c r="F63" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="64">
@@ -1670,13 +1670,13 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>1.45 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-07-31T11:24:45.453Z</v>
+        <v>2026-08-08T07:07:25.137Z</v>
       </c>
       <c r="F64" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="65">
@@ -1690,13 +1690,13 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>1.33 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-07-31T11:24:46.788Z</v>
+        <v>2026-08-08T07:07:25.926Z</v>
       </c>
       <c r="F65" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="66">
@@ -1710,13 +1710,13 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>1.32 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-07-31T11:24:48.110Z</v>
+        <v>2026-08-08T07:07:26.772Z</v>
       </c>
       <c r="F66" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="67">
@@ -1730,13 +1730,13 @@
         <v>PASS</v>
       </c>
       <c r="D67" t="str">
-        <v>1.56 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-07-31T11:24:49.673Z</v>
+        <v>2026-08-08T07:07:27.748Z</v>
       </c>
       <c r="F67" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="68">
@@ -1750,13 +1750,13 @@
         <v>PASS</v>
       </c>
       <c r="D68" t="str">
-        <v>1.30 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-07-31T11:24:50.973Z</v>
+        <v>2026-08-08T07:07:28.622Z</v>
       </c>
       <c r="F68" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="69">
@@ -1770,13 +1770,13 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>1.53 sec</v>
+        <v>1.09 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-07-31T11:24:52.499Z</v>
+        <v>2026-08-08T07:07:29.708Z</v>
       </c>
       <c r="F69" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="70">
@@ -1790,13 +1790,13 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>1.44 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-07-31T11:24:53.937Z</v>
+        <v>2026-08-08T07:07:30.543Z</v>
       </c>
       <c r="F70" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="71">
@@ -1810,13 +1810,13 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>1.37 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-07-31T11:24:55.307Z</v>
+        <v>2026-08-08T07:07:31.394Z</v>
       </c>
       <c r="F71" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="72">
@@ -1830,13 +1830,13 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>1.31 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-07-31T11:24:56.620Z</v>
+        <v>2026-08-08T07:07:32.141Z</v>
       </c>
       <c r="F72" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="73">
@@ -1850,13 +1850,13 @@
         <v>PASS</v>
       </c>
       <c r="D73" t="str">
-        <v>1.42 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-07-31T11:24:58.038Z</v>
+        <v>2026-08-08T07:07:33.176Z</v>
       </c>
       <c r="F73" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="74">
@@ -1870,13 +1870,13 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>1.37 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-07-31T11:24:59.409Z</v>
+        <v>2026-08-08T07:07:33.993Z</v>
       </c>
       <c r="F74" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="75">
@@ -1890,13 +1890,13 @@
         <v>PASS</v>
       </c>
       <c r="D75" t="str">
-        <v>1.58 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-07-31T11:25:00.987Z</v>
+        <v>2026-08-08T07:07:35.101Z</v>
       </c>
       <c r="F75" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="76">
@@ -1910,13 +1910,13 @@
         <v>PASS</v>
       </c>
       <c r="D76" t="str">
-        <v>1.35 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-07-31T11:25:02.337Z</v>
+        <v>2026-08-08T07:07:36.089Z</v>
       </c>
       <c r="F76" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="77">
@@ -1930,13 +1930,13 @@
         <v>PASS</v>
       </c>
       <c r="D77" t="str">
-        <v>1.34 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-07-31T11:25:03.673Z</v>
+        <v>2026-08-08T07:07:36.863Z</v>
       </c>
       <c r="F77" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="78">
@@ -1950,13 +1950,13 @@
         <v>PASS</v>
       </c>
       <c r="D78" t="str">
-        <v>1.34 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-07-31T11:25:05.014Z</v>
+        <v>2026-08-08T07:07:37.692Z</v>
       </c>
       <c r="F78" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="79">
@@ -1970,13 +1970,13 @@
         <v>PASS</v>
       </c>
       <c r="D79" t="str">
-        <v>1.46 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-07-31T11:25:06.471Z</v>
+        <v>2026-08-08T07:07:38.710Z</v>
       </c>
       <c r="F79" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="80">
@@ -1990,13 +1990,13 @@
         <v>PASS</v>
       </c>
       <c r="D80" t="str">
-        <v>1.37 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-07-31T11:25:07.838Z</v>
+        <v>2026-08-08T07:07:39.614Z</v>
       </c>
       <c r="F80" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="81">
@@ -2010,13 +2010,13 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>1.58 sec</v>
+        <v>1.20 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-07-31T11:25:09.423Z</v>
+        <v>2026-08-08T07:07:40.814Z</v>
       </c>
       <c r="F81" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="82">
@@ -2030,13 +2030,13 @@
         <v>PASS</v>
       </c>
       <c r="D82" t="str">
-        <v>1.48 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-07-31T11:25:10.902Z</v>
+        <v>2026-08-08T07:07:41.791Z</v>
       </c>
       <c r="F82" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="83">
@@ -2050,13 +2050,13 @@
         <v>PASS</v>
       </c>
       <c r="D83" t="str">
-        <v>1.33 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-07-31T11:25:12.237Z</v>
+        <v>2026-08-08T07:07:42.592Z</v>
       </c>
       <c r="F83" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="84">
@@ -2070,13 +2070,13 @@
         <v>PASS</v>
       </c>
       <c r="D84" t="str">
-        <v>1.32 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-07-31T11:25:13.558Z</v>
+        <v>2026-08-08T07:07:43.345Z</v>
       </c>
       <c r="F84" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="85">
@@ -2090,13 +2090,13 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>1.36 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-07-31T11:25:14.920Z</v>
+        <v>2026-08-08T07:07:44.321Z</v>
       </c>
       <c r="F85" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="86">
@@ -2110,13 +2110,13 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>1.45 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-07-31T11:25:16.369Z</v>
+        <v>2026-08-08T07:07:45.404Z</v>
       </c>
       <c r="F86" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="87">
@@ -2130,13 +2130,13 @@
         <v>PASS</v>
       </c>
       <c r="D87" t="str">
-        <v>1.54 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-07-31T11:25:17.906Z</v>
+        <v>2026-08-08T07:07:46.571Z</v>
       </c>
       <c r="F87" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="88">
@@ -2150,13 +2150,13 @@
         <v>PASS</v>
       </c>
       <c r="D88" t="str">
-        <v>1.28 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-07-31T11:25:19.185Z</v>
+        <v>2026-08-08T07:07:47.616Z</v>
       </c>
       <c r="F88" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="89">
@@ -2170,13 +2170,13 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>1.33 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-07-31T11:25:20.520Z</v>
+        <v>2026-08-08T07:07:48.562Z</v>
       </c>
       <c r="F89" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="90">
@@ -2190,13 +2190,13 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>1.31 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-07-31T11:25:21.835Z</v>
+        <v>2026-08-08T07:07:49.387Z</v>
       </c>
       <c r="F90" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="91">
@@ -2210,13 +2210,13 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>1.47 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-07-31T11:25:23.309Z</v>
+        <v>2026-08-08T07:07:50.310Z</v>
       </c>
       <c r="F91" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="92">
@@ -2230,13 +2230,13 @@
         <v>PASS</v>
       </c>
       <c r="D92" t="str">
-        <v>1.25 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-07-31T11:25:24.563Z</v>
+        <v>2026-08-08T07:07:51.381Z</v>
       </c>
       <c r="F92" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="93">
@@ -2250,13 +2250,13 @@
         <v>PASS</v>
       </c>
       <c r="D93" t="str">
-        <v>1.54 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-07-31T11:25:26.102Z</v>
+        <v>2026-08-08T07:07:52.208Z</v>
       </c>
       <c r="F93" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="94">
@@ -2270,13 +2270,13 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>1.45 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-07-31T11:25:27.553Z</v>
+        <v>2026-08-08T07:07:53.158Z</v>
       </c>
       <c r="F94" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="95">
@@ -2290,13 +2290,13 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>1.33 sec</v>
+        <v>0.64 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-07-31T11:25:28.885Z</v>
+        <v>2026-08-08T07:07:53.802Z</v>
       </c>
       <c r="F95" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="96">
@@ -2310,13 +2310,13 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>1.32 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-07-31T11:25:30.202Z</v>
+        <v>2026-08-08T07:07:54.597Z</v>
       </c>
       <c r="F96" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="97">
@@ -2330,13 +2330,13 @@
         <v>PASS</v>
       </c>
       <c r="D97" t="str">
-        <v>1.55 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-07-31T11:25:31.752Z</v>
+        <v>2026-08-08T07:07:55.347Z</v>
       </c>
       <c r="F97" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="98">
@@ -2350,13 +2350,13 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>1.44 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-07-31T11:25:33.187Z</v>
+        <v>2026-08-08T07:07:56.200Z</v>
       </c>
       <c r="F98" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="99">
@@ -2370,13 +2370,13 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>1.53 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-07-31T11:25:34.719Z</v>
+        <v>2026-08-08T07:07:57.168Z</v>
       </c>
       <c r="F99" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="100">
@@ -2390,13 +2390,13 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>1.47 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-07-31T11:25:36.186Z</v>
+        <v>2026-08-08T07:07:58.059Z</v>
       </c>
       <c r="F100" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="101">
@@ -2410,13 +2410,13 @@
         <v>PASS</v>
       </c>
       <c r="D101" t="str">
-        <v>1.35 sec</v>
+        <v>0.55 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-07-31T11:25:37.534Z</v>
+        <v>2026-08-08T07:07:58.613Z</v>
       </c>
       <c r="F101" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="102">
@@ -2430,13 +2430,13 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>1.32 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-07-31T11:25:38.855Z</v>
+        <v>2026-08-08T07:07:59.394Z</v>
       </c>
       <c r="F102" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="103">
@@ -2450,13 +2450,13 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>1.26 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-07-31T11:25:40.119Z</v>
+        <v>2026-08-08T07:08:00.135Z</v>
       </c>
       <c r="F103" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="104">
@@ -2470,13 +2470,13 @@
         <v>PASS</v>
       </c>
       <c r="D104" t="str">
-        <v>1.35 sec</v>
+        <v>0.66 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-07-31T11:25:41.470Z</v>
+        <v>2026-08-08T07:08:00.794Z</v>
       </c>
       <c r="F104" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="105">
@@ -2490,13 +2490,13 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>1.50 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-07-31T11:25:42.973Z</v>
+        <v>2026-08-08T07:08:01.577Z</v>
       </c>
       <c r="F105" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="106">
@@ -2510,13 +2510,13 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>1.34 sec</v>
+        <v>0.58 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-07-31T11:25:44.318Z</v>
+        <v>2026-08-08T07:08:02.156Z</v>
       </c>
       <c r="F106" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="107">
@@ -2530,13 +2530,13 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>1.34 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-07-31T11:25:45.655Z</v>
+        <v>2026-08-08T07:08:02.949Z</v>
       </c>
       <c r="F107" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="108">
@@ -2550,13 +2550,13 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>1.34 sec</v>
+        <v>0.68 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-07-31T11:25:46.991Z</v>
+        <v>2026-08-08T07:08:03.631Z</v>
       </c>
       <c r="F108" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="109">
@@ -2570,13 +2570,13 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>1.59 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-07-31T11:25:48.585Z</v>
+        <v>2026-08-08T07:08:04.705Z</v>
       </c>
       <c r="F109" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="110">
@@ -2590,13 +2590,13 @@
         <v>PASS</v>
       </c>
       <c r="D110" t="str">
-        <v>1.34 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-07-31T11:25:49.924Z</v>
+        <v>2026-08-08T07:08:05.728Z</v>
       </c>
       <c r="F110" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="111">
@@ -2610,13 +2610,13 @@
         <v>PASS</v>
       </c>
       <c r="D111" t="str">
-        <v>1.55 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-07-31T11:25:51.479Z</v>
+        <v>2026-08-08T07:08:06.686Z</v>
       </c>
       <c r="F111" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="112">
@@ -2630,13 +2630,13 @@
         <v>PASS</v>
       </c>
       <c r="D112" t="str">
-        <v>1.36 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-07-31T11:25:52.836Z</v>
+        <v>2026-08-08T07:08:07.563Z</v>
       </c>
       <c r="F112" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="113">
@@ -2650,13 +2650,13 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>1.33 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-07-31T11:25:54.168Z</v>
+        <v>2026-08-08T07:08:08.380Z</v>
       </c>
       <c r="F113" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="114">
@@ -2670,13 +2670,13 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>1.33 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-07-31T11:25:55.498Z</v>
+        <v>2026-08-08T07:08:09.271Z</v>
       </c>
       <c r="F114" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="115">
@@ -2690,13 +2690,13 @@
         <v>PASS</v>
       </c>
       <c r="D115" t="str">
-        <v>1.45 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-07-31T11:25:56.950Z</v>
+        <v>2026-08-08T07:08:10.449Z</v>
       </c>
       <c r="F115" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="116">
@@ -2710,13 +2710,13 @@
         <v>PASS</v>
       </c>
       <c r="D116" t="str">
-        <v>1.15 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-07-31T11:25:58.101Z</v>
+        <v>2026-08-08T07:08:11.190Z</v>
       </c>
       <c r="F116" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="117">
@@ -2730,13 +2730,13 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>1.56 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-07-31T11:25:59.660Z</v>
+        <v>2026-08-08T07:08:12.128Z</v>
       </c>
       <c r="F117" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="118">
@@ -2750,13 +2750,13 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>1.47 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-07-31T11:26:01.133Z</v>
+        <v>2026-08-08T07:08:12.958Z</v>
       </c>
       <c r="F118" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="119">
@@ -2770,13 +2770,13 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>1.34 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-07-31T11:26:02.469Z</v>
+        <v>2026-08-08T07:08:13.762Z</v>
       </c>
       <c r="F119" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="120">
@@ -2790,13 +2790,13 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>1.33 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-07-31T11:26:03.795Z</v>
+        <v>2026-08-08T07:08:14.642Z</v>
       </c>
       <c r="F120" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="121">
@@ -2810,13 +2810,13 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>1.56 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-07-31T11:26:05.354Z</v>
+        <v>2026-08-08T07:08:15.853Z</v>
       </c>
       <c r="F121" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="122">
@@ -2830,13 +2830,13 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>1.30 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-07-31T11:26:06.654Z</v>
+        <v>2026-08-08T07:08:16.826Z</v>
       </c>
       <c r="F122" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="123">
@@ -2850,13 +2850,13 @@
         <v>PASS</v>
       </c>
       <c r="D123" t="str">
-        <v>1.53 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-07-31T11:26:08.187Z</v>
+        <v>2026-08-08T07:08:17.759Z</v>
       </c>
       <c r="F123" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="124">
@@ -2870,13 +2870,13 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>1.48 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-07-31T11:26:09.670Z</v>
+        <v>2026-08-08T07:08:18.818Z</v>
       </c>
       <c r="F124" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="125">
@@ -2890,13 +2890,13 @@
         <v>PASS</v>
       </c>
       <c r="D125" t="str">
-        <v>1.35 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-07-31T11:26:11.020Z</v>
+        <v>2026-08-08T07:08:19.839Z</v>
       </c>
       <c r="F125" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="126">
@@ -2910,13 +2910,13 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>1.32 sec</v>
+        <v>0.70 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-07-31T11:26:12.339Z</v>
+        <v>2026-08-08T07:08:20.535Z</v>
       </c>
       <c r="F126" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="127">
@@ -2930,13 +2930,13 @@
         <v>PASS</v>
       </c>
       <c r="D127" t="str">
-        <v>1.58 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-07-31T11:26:13.923Z</v>
+        <v>2026-08-08T07:08:21.487Z</v>
       </c>
       <c r="F127" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="128">
@@ -2950,13 +2950,13 @@
         <v>PASS</v>
       </c>
       <c r="D128" t="str">
-        <v>1.45 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-07-31T11:26:15.377Z</v>
+        <v>2026-08-08T07:08:22.446Z</v>
       </c>
       <c r="F128" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="129">
@@ -2970,13 +2970,13 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>1.56 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-07-31T11:26:16.935Z</v>
+        <v>2026-08-08T07:08:23.376Z</v>
       </c>
       <c r="F129" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="130">
@@ -2990,13 +2990,13 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>1.49 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-07-31T11:26:18.420Z</v>
+        <v>2026-08-08T07:08:24.204Z</v>
       </c>
       <c r="F130" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="131">
@@ -3010,13 +3010,13 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>1.36 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-07-31T11:26:19.784Z</v>
+        <v>2026-08-08T07:08:25.152Z</v>
       </c>
       <c r="F131" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="132">
@@ -3030,13 +3030,13 @@
         <v>PASS</v>
       </c>
       <c r="D132" t="str">
-        <v>1.32 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-07-31T11:26:21.103Z</v>
+        <v>2026-08-08T07:08:26.104Z</v>
       </c>
       <c r="F132" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="133">
@@ -3050,13 +3050,13 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>1.40 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-07-31T11:26:22.502Z</v>
+        <v>2026-08-08T07:08:27.152Z</v>
       </c>
       <c r="F133" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="134">
@@ -3070,13 +3070,13 @@
         <v>PASS</v>
       </c>
       <c r="D134" t="str">
-        <v>1.39 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-07-31T11:26:23.894Z</v>
+        <v>2026-08-08T07:08:28.022Z</v>
       </c>
       <c r="F134" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="135">
@@ -3090,13 +3090,13 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>1.59 sec</v>
+        <v>1.13 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-07-31T11:26:25.485Z</v>
+        <v>2026-08-08T07:08:29.149Z</v>
       </c>
       <c r="F135" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="136">
@@ -3110,13 +3110,13 @@
         <v>PASS</v>
       </c>
       <c r="D136" t="str">
-        <v>1.36 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-07-31T11:26:26.850Z</v>
+        <v>2026-08-08T07:08:29.989Z</v>
       </c>
       <c r="F136" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="137">
@@ -3130,13 +3130,13 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>1.38 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-07-31T11:26:28.232Z</v>
+        <v>2026-08-08T07:08:30.794Z</v>
       </c>
       <c r="F137" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="138">
@@ -3150,13 +3150,13 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>1.34 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-07-31T11:26:29.575Z</v>
+        <v>2026-08-08T07:08:31.656Z</v>
       </c>
       <c r="F138" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="139">
@@ -3170,13 +3170,13 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>1.44 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-07-31T11:26:31.010Z</v>
+        <v>2026-08-08T07:08:32.937Z</v>
       </c>
       <c r="F139" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="140">
@@ -3190,13 +3190,13 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>1.34 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-07-31T11:26:32.351Z</v>
+        <v>2026-08-08T07:08:33.969Z</v>
       </c>
       <c r="F140" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="141">
@@ -3210,13 +3210,13 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>1.57 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-07-31T11:26:33.925Z</v>
+        <v>2026-08-08T07:08:35.091Z</v>
       </c>
       <c r="F141" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="142">
@@ -3230,13 +3230,13 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>1.46 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-07-31T11:26:35.382Z</v>
+        <v>2026-08-08T07:08:36.108Z</v>
       </c>
       <c r="F142" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="143">
@@ -3250,13 +3250,13 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>1.35 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-07-31T11:26:36.733Z</v>
+        <v>2026-08-08T07:08:37.104Z</v>
       </c>
       <c r="F143" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="144">
@@ -3270,13 +3270,13 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>1.33 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-07-31T11:26:38.062Z</v>
+        <v>2026-08-08T07:08:38.164Z</v>
       </c>
       <c r="F144" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="145">
@@ -3290,13 +3290,13 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>1.41 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-07-31T11:26:39.468Z</v>
+        <v>2026-08-08T07:08:39.188Z</v>
       </c>
       <c r="F145" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="146">
@@ -3310,13 +3310,13 @@
         <v>PASS</v>
       </c>
       <c r="D146" t="str">
-        <v>1.46 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-07-31T11:26:40.932Z</v>
+        <v>2026-08-08T07:08:40.130Z</v>
       </c>
       <c r="F146" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="147">
@@ -3330,13 +3330,13 @@
         <v>PASS</v>
       </c>
       <c r="D147" t="str">
-        <v>1.55 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-07-31T11:26:42.484Z</v>
+        <v>2026-08-08T07:08:41.112Z</v>
       </c>
       <c r="F147" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="148">
@@ -3350,13 +3350,13 @@
         <v>PASS</v>
       </c>
       <c r="D148" t="str">
-        <v>1.48 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-07-31T11:26:43.966Z</v>
+        <v>2026-08-08T07:08:41.965Z</v>
       </c>
       <c r="F148" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="149">
@@ -3370,13 +3370,13 @@
         <v>PASS</v>
       </c>
       <c r="D149" t="str">
-        <v>1.35 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-07-31T11:26:45.316Z</v>
+        <v>2026-08-08T07:08:42.791Z</v>
       </c>
       <c r="F149" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="150">
@@ -3390,13 +3390,13 @@
         <v>PASS</v>
       </c>
       <c r="D150" t="str">
-        <v>1.33 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-07-31T11:26:46.642Z</v>
+        <v>2026-08-08T07:08:43.834Z</v>
       </c>
       <c r="F150" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="151">
@@ -3410,13 +3410,13 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>1.48 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-07-31T11:26:48.119Z</v>
+        <v>2026-08-08T07:08:45.114Z</v>
       </c>
       <c r="F151" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="152">
@@ -3430,13 +3430,13 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>1.47 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-07-31T11:26:49.592Z</v>
+        <v>2026-08-08T07:08:46.050Z</v>
       </c>
       <c r="F152" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="153">
@@ -3450,13 +3450,13 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>1.53 sec</v>
+        <v>1.13 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-07-31T11:26:51.124Z</v>
+        <v>2026-08-08T07:08:47.181Z</v>
       </c>
       <c r="F153" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="154">
@@ -3470,13 +3470,13 @@
         <v>PASS</v>
       </c>
       <c r="D154" t="str">
-        <v>1.48 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-07-31T11:26:52.599Z</v>
+        <v>2026-08-08T07:08:48.197Z</v>
       </c>
       <c r="F154" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="155">
@@ -3490,13 +3490,13 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>1.35 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-07-31T11:26:53.948Z</v>
+        <v>2026-08-08T07:08:49.058Z</v>
       </c>
       <c r="F155" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="156">
@@ -3510,13 +3510,13 @@
         <v>PASS</v>
       </c>
       <c r="D156" t="str">
-        <v>1.33 sec</v>
+        <v>1.03 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-07-31T11:26:55.280Z</v>
+        <v>2026-08-08T07:08:50.092Z</v>
       </c>
       <c r="F156" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="157">
@@ -3530,13 +3530,13 @@
         <v>PASS</v>
       </c>
       <c r="D157" t="str">
-        <v>1.55 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-07-31T11:26:56.832Z</v>
+        <v>2026-08-08T07:08:51.190Z</v>
       </c>
       <c r="F157" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="158">
@@ -3550,13 +3550,13 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>1.27 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-07-31T11:26:58.098Z</v>
+        <v>2026-08-08T07:08:51.993Z</v>
       </c>
       <c r="F158" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="159">
@@ -3570,13 +3570,13 @@
         <v>PASS</v>
       </c>
       <c r="D159" t="str">
-        <v>1.53 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-07-31T11:26:59.632Z</v>
+        <v>2026-08-08T07:08:52.967Z</v>
       </c>
       <c r="F159" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="160">
@@ -3590,13 +3590,13 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>1.47 sec</v>
+        <v>1.13 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-07-31T11:27:01.098Z</v>
+        <v>2026-08-08T07:08:54.099Z</v>
       </c>
       <c r="F160" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="161">
@@ -3610,13 +3610,13 @@
         <v>PASS</v>
       </c>
       <c r="D161" t="str">
-        <v>1.33 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-07-31T11:27:02.433Z</v>
+        <v>2026-08-08T07:08:55.055Z</v>
       </c>
       <c r="F161" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="162">
@@ -3630,13 +3630,13 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>1.32 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-07-31T11:27:03.756Z</v>
+        <v>2026-08-08T07:08:56.174Z</v>
       </c>
       <c r="F162" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="163">
@@ -3650,13 +3650,13 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>1.45 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-07-31T11:27:05.208Z</v>
+        <v>2026-08-08T07:08:56.980Z</v>
       </c>
       <c r="F163" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="164">
@@ -3670,13 +3670,13 @@
         <v>PASS</v>
       </c>
       <c r="D164" t="str">
-        <v>1.37 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-07-31T11:27:06.580Z</v>
+        <v>2026-08-08T07:08:57.995Z</v>
       </c>
       <c r="F164" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="165">
@@ -3690,13 +3690,13 @@
         <v>PASS</v>
       </c>
       <c r="D165" t="str">
-        <v>1.60 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-07-31T11:27:08.182Z</v>
+        <v>2026-08-08T07:08:58.934Z</v>
       </c>
       <c r="F165" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="166">
@@ -3710,13 +3710,13 @@
         <v>PASS</v>
       </c>
       <c r="D166" t="str">
-        <v>1.47 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-07-31T11:27:09.648Z</v>
+        <v>2026-08-08T07:08:59.908Z</v>
       </c>
       <c r="F166" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="167">
@@ -3730,13 +3730,13 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>1.35 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-07-31T11:27:10.998Z</v>
+        <v>2026-08-08T07:09:01.006Z</v>
       </c>
       <c r="F167" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="168">
@@ -3750,13 +3750,13 @@
         <v>PASS</v>
       </c>
       <c r="D168" t="str">
-        <v>1.32 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-07-31T11:27:12.317Z</v>
+        <v>2026-08-08T07:09:01.883Z</v>
       </c>
       <c r="F168" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="169">
@@ -3770,13 +3770,13 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>1.56 sec</v>
+        <v>1.29 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-07-31T11:27:13.882Z</v>
+        <v>2026-08-08T07:09:03.174Z</v>
       </c>
       <c r="F169" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="170">
@@ -3790,13 +3790,13 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>1.43 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-07-31T11:27:15.313Z</v>
+        <v>2026-08-08T07:09:04.057Z</v>
       </c>
       <c r="F170" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="171">
@@ -3810,13 +3810,13 @@
         <v>PASS</v>
       </c>
       <c r="D171" t="str">
-        <v>1.52 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-07-31T11:27:16.837Z</v>
+        <v>2026-08-08T07:09:05.000Z</v>
       </c>
       <c r="F171" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="172">
@@ -3830,13 +3830,13 @@
         <v>PASS</v>
       </c>
       <c r="D172" t="str">
-        <v>1.29 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-07-31T11:27:18.129Z</v>
+        <v>2026-08-08T07:09:05.994Z</v>
       </c>
       <c r="F172" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="173">
@@ -3850,13 +3850,13 @@
         <v>PASS</v>
       </c>
       <c r="D173" t="str">
-        <v>1.17 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-07-31T11:27:19.298Z</v>
+        <v>2026-08-08T07:09:06.853Z</v>
       </c>
       <c r="F173" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="174">
@@ -3870,13 +3870,13 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>1.31 sec</v>
+        <v>0.73 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-07-31T11:27:20.613Z</v>
+        <v>2026-08-08T07:09:07.584Z</v>
       </c>
       <c r="F174" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="175">
@@ -3890,13 +3890,13 @@
         <v>PASS</v>
       </c>
       <c r="D175" t="str">
-        <v>1.49 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-07-31T11:27:22.106Z</v>
+        <v>2026-08-08T07:09:08.575Z</v>
       </c>
       <c r="F175" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="176">
@@ -3910,13 +3910,13 @@
         <v>PASS</v>
       </c>
       <c r="D176" t="str">
-        <v>1.47 sec</v>
+        <v>1.27 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-07-31T11:27:23.577Z</v>
+        <v>2026-08-08T07:09:09.841Z</v>
       </c>
       <c r="F176" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="177">
@@ -3930,13 +3930,13 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>1.54 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-07-31T11:27:25.113Z</v>
+        <v>2026-08-08T07:09:10.755Z</v>
       </c>
       <c r="F177" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="178">
@@ -3950,13 +3950,13 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>1.48 sec</v>
+        <v>0.74 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-07-31T11:27:26.596Z</v>
+        <v>2026-08-08T07:09:11.491Z</v>
       </c>
       <c r="F178" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="179">
@@ -3970,13 +3970,13 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>1.35 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-07-31T11:27:27.947Z</v>
+        <v>2026-08-08T07:09:12.446Z</v>
       </c>
       <c r="F179" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="180">
@@ -3990,13 +3990,13 @@
         <v>PASS</v>
       </c>
       <c r="D180" t="str">
-        <v>1.33 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-07-31T11:27:29.278Z</v>
+        <v>2026-08-08T07:09:13.756Z</v>
       </c>
       <c r="F180" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="181">
@@ -4013,10 +4013,10 @@
         <v>1.55 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-07-31T11:27:30.831Z</v>
+        <v>2026-08-08T07:09:15.306Z</v>
       </c>
       <c r="F181" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="182">
@@ -4030,13 +4030,13 @@
         <v>PASS</v>
       </c>
       <c r="D182" t="str">
-        <v>1.43 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-07-31T11:27:32.263Z</v>
+        <v>2026-08-08T07:09:16.494Z</v>
       </c>
       <c r="F182" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="183">
@@ -4050,13 +4050,13 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>1.54 sec</v>
+        <v>2.20 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-07-31T11:27:33.799Z</v>
+        <v>2026-08-08T07:09:18.692Z</v>
       </c>
       <c r="F183" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="184">
@@ -4070,13 +4070,13 @@
         <v>PASS</v>
       </c>
       <c r="D184" t="str">
-        <v>1.28 sec</v>
+        <v>1.34 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-07-31T11:27:35.080Z</v>
+        <v>2026-08-08T07:09:20.037Z</v>
       </c>
       <c r="F184" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="185">
@@ -4090,13 +4090,13 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>1.35 sec</v>
+        <v>1.31 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-07-31T11:27:36.429Z</v>
+        <v>2026-08-08T07:09:21.346Z</v>
       </c>
       <c r="F185" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="186">
@@ -4110,13 +4110,13 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>1.31 sec</v>
+        <v>2.18 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-07-31T11:27:37.743Z</v>
+        <v>2026-08-08T07:09:23.527Z</v>
       </c>
       <c r="F186" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="187">
@@ -4130,13 +4130,13 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>1.56 sec</v>
+        <v>1.66 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-07-31T11:27:39.302Z</v>
+        <v>2026-08-08T07:09:25.183Z</v>
       </c>
       <c r="F187" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="188">
@@ -4150,13 +4150,13 @@
         <v>PASS</v>
       </c>
       <c r="D188" t="str">
-        <v>1.46 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-07-31T11:27:40.763Z</v>
+        <v>2026-08-08T07:09:26.344Z</v>
       </c>
       <c r="F188" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="189">
@@ -4170,13 +4170,13 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>1.52 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-07-31T11:27:42.286Z</v>
+        <v>2026-08-08T07:09:27.516Z</v>
       </c>
       <c r="F189" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="190">
@@ -4190,13 +4190,13 @@
         <v>PASS</v>
       </c>
       <c r="D190" t="str">
-        <v>1.46 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-07-31T11:27:43.746Z</v>
+        <v>2026-08-08T07:09:28.523Z</v>
       </c>
       <c r="F190" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="191">
@@ -4210,13 +4210,13 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>1.35 sec</v>
+        <v>1.28 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-07-31T11:27:45.097Z</v>
+        <v>2026-08-08T07:09:29.807Z</v>
       </c>
       <c r="F191" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="192">
@@ -4230,13 +4230,13 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>1.33 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-07-31T11:27:46.428Z</v>
+        <v>2026-08-08T07:09:30.735Z</v>
       </c>
       <c r="F192" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="193">
@@ -4250,13 +4250,13 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>1.40 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-07-31T11:27:47.826Z</v>
+        <v>2026-08-08T07:09:31.508Z</v>
       </c>
       <c r="F193" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="194">
@@ -4270,13 +4270,13 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>1.34 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-07-31T11:27:49.163Z</v>
+        <v>2026-08-08T07:09:32.312Z</v>
       </c>
       <c r="F194" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="195">
@@ -4290,13 +4290,13 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>1.50 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-07-31T11:27:50.662Z</v>
+        <v>2026-08-08T07:09:33.157Z</v>
       </c>
       <c r="F195" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="196">
@@ -4310,13 +4310,13 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>1.38 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-07-31T11:27:52.046Z</v>
+        <v>2026-08-08T07:09:33.873Z</v>
       </c>
       <c r="F196" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="197">
@@ -4330,13 +4330,13 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>1.33 sec</v>
+        <v>0.69 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-07-31T11:27:53.379Z</v>
+        <v>2026-08-08T07:09:34.559Z</v>
       </c>
       <c r="F197" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="198">
@@ -4350,13 +4350,13 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>1.33 sec</v>
+        <v>0.70 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-07-31T11:27:54.713Z</v>
+        <v>2026-08-08T07:09:35.256Z</v>
       </c>
       <c r="F198" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="199">
@@ -4370,13 +4370,13 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>1.56 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-07-31T11:27:56.278Z</v>
+        <v>2026-08-08T07:09:36.093Z</v>
       </c>
       <c r="F199" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="200">
@@ -4390,13 +4390,13 @@
         <v>PASS</v>
       </c>
       <c r="D200" t="str">
-        <v>1.46 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-07-31T11:27:57.738Z</v>
+        <v>2026-08-08T07:09:36.867Z</v>
       </c>
       <c r="F200" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="201">
@@ -4410,13 +4410,13 @@
         <v>PASS</v>
       </c>
       <c r="D201" t="str">
-        <v>1.57 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-07-31T11:27:59.309Z</v>
+        <v>2026-08-08T07:09:37.904Z</v>
       </c>
       <c r="F201" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="202">
@@ -4430,13 +4430,13 @@
         <v>PASS</v>
       </c>
       <c r="D202" t="str">
-        <v>1.45 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-07-31T11:28:00.761Z</v>
+        <v>2026-08-08T07:09:38.914Z</v>
       </c>
       <c r="F202" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="203">
@@ -4450,13 +4450,13 @@
         <v>PASS</v>
       </c>
       <c r="D203" t="str">
-        <v>1.33 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-07-31T11:28:02.096Z</v>
+        <v>2026-08-08T07:09:39.735Z</v>
       </c>
       <c r="F203" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="204">
@@ -4470,13 +4470,13 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>1.32 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-07-31T11:28:03.412Z</v>
+        <v>2026-08-08T07:09:40.505Z</v>
       </c>
       <c r="F204" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="205">
@@ -4490,13 +4490,13 @@
         <v>PASS</v>
       </c>
       <c r="D205" t="str">
-        <v>1.55 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-07-31T11:28:04.964Z</v>
+        <v>2026-08-08T07:09:41.472Z</v>
       </c>
       <c r="F205" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="206">
@@ -4510,13 +4510,13 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>1.42 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-07-31T11:28:06.388Z</v>
+        <v>2026-08-08T07:09:42.667Z</v>
       </c>
       <c r="F206" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="207">
@@ -4530,13 +4530,13 @@
         <v>PASS</v>
       </c>
       <c r="D207" t="str">
-        <v>1.51 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-07-31T11:28:07.902Z</v>
+        <v>2026-08-08T07:09:43.682Z</v>
       </c>
       <c r="F207" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="208">
@@ -4550,13 +4550,13 @@
         <v>PASS</v>
       </c>
       <c r="D208" t="str">
-        <v>1.46 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-07-31T11:28:09.361Z</v>
+        <v>2026-08-08T07:09:44.407Z</v>
       </c>
       <c r="F208" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="209">
@@ -4570,13 +4570,13 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>1.33 sec</v>
+        <v>0.75 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-07-31T11:28:10.695Z</v>
+        <v>2026-08-08T07:09:45.154Z</v>
       </c>
       <c r="F209" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="210">
@@ -4590,13 +4590,13 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>1.32 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-07-31T11:28:12.015Z</v>
+        <v>2026-08-08T07:09:46.227Z</v>
       </c>
       <c r="F210" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="211">
@@ -4610,13 +4610,13 @@
         <v>PASS</v>
       </c>
       <c r="D211" t="str">
-        <v>1.47 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-07-31T11:28:13.488Z</v>
+        <v>2026-08-08T07:09:47.415Z</v>
       </c>
       <c r="F211" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="212">
@@ -4630,13 +4630,13 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>1.44 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-07-31T11:28:14.928Z</v>
+        <v>2026-08-08T07:09:48.391Z</v>
       </c>
       <c r="F212" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="213">
@@ -4650,13 +4650,13 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>1.52 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-07-31T11:28:16.444Z</v>
+        <v>2026-08-08T07:09:49.432Z</v>
       </c>
       <c r="F213" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="214">
@@ -4670,13 +4670,13 @@
         <v>PASS</v>
       </c>
       <c r="D214" t="str">
-        <v>1.47 sec</v>
+        <v>1.15 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-07-31T11:28:17.911Z</v>
+        <v>2026-08-08T07:09:50.579Z</v>
       </c>
       <c r="F214" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="215">
@@ -4690,13 +4690,13 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>1.33 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-07-31T11:28:19.245Z</v>
+        <v>2026-08-08T07:09:51.675Z</v>
       </c>
       <c r="F215" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="216">
@@ -4710,13 +4710,13 @@
         <v>PASS</v>
       </c>
       <c r="D216" t="str">
-        <v>1.32 sec</v>
+        <v>0.69 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-07-31T11:28:20.568Z</v>
+        <v>2026-08-08T07:09:52.362Z</v>
       </c>
       <c r="F216" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="217">
@@ -4730,13 +4730,13 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>1.56 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-07-31T11:28:22.130Z</v>
+        <v>2026-08-08T07:09:53.138Z</v>
       </c>
       <c r="F217" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="218">
@@ -4750,13 +4750,13 @@
         <v>PASS</v>
       </c>
       <c r="D218" t="str">
-        <v>1.25 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-07-31T11:28:23.385Z</v>
+        <v>2026-08-08T07:09:53.845Z</v>
       </c>
       <c r="F218" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="219">
@@ -4770,13 +4770,13 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>1.52 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-07-31T11:28:24.910Z</v>
+        <v>2026-08-08T07:09:55.051Z</v>
       </c>
       <c r="F219" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="220">
@@ -4790,13 +4790,13 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>1.45 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-07-31T11:28:26.361Z</v>
+        <v>2026-08-08T07:09:56.123Z</v>
       </c>
       <c r="F220" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="221">
@@ -4810,13 +4810,13 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>1.35 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-07-31T11:28:27.712Z</v>
+        <v>2026-08-08T07:09:57.018Z</v>
       </c>
       <c r="F221" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="222">
@@ -4830,13 +4830,13 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>1.31 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-07-31T11:28:29.026Z</v>
+        <v>2026-08-08T07:09:57.985Z</v>
       </c>
       <c r="F222" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="223">
@@ -4850,13 +4850,13 @@
         <v>PASS</v>
       </c>
       <c r="D223" t="str">
-        <v>1.43 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-07-31T11:28:30.460Z</v>
+        <v>2026-08-08T07:09:58.996Z</v>
       </c>
       <c r="F223" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="224">
@@ -4870,13 +4870,13 @@
         <v>PASS</v>
       </c>
       <c r="D224" t="str">
-        <v>1.36 sec</v>
+        <v>1.30 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-07-31T11:28:31.819Z</v>
+        <v>2026-08-08T07:10:00.296Z</v>
       </c>
       <c r="F224" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="225">
@@ -4890,13 +4890,13 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>1.51 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-07-31T11:28:33.329Z</v>
+        <v>2026-08-08T07:10:01.360Z</v>
       </c>
       <c r="F225" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="226">
@@ -4910,13 +4910,13 @@
         <v>PASS</v>
       </c>
       <c r="D226" t="str">
-        <v>1.35 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-07-31T11:28:34.678Z</v>
+        <v>2026-08-08T07:10:02.233Z</v>
       </c>
       <c r="F226" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="227">
@@ -4930,13 +4930,13 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>1.35 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-07-31T11:28:36.027Z</v>
+        <v>2026-08-08T07:10:03.139Z</v>
       </c>
       <c r="F227" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="228">
@@ -4950,13 +4950,13 @@
         <v>PASS</v>
       </c>
       <c r="D228" t="str">
-        <v>1.15 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-07-31T11:28:37.181Z</v>
+        <v>2026-08-08T07:10:03.810Z</v>
       </c>
       <c r="F228" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="229">
@@ -4970,13 +4970,13 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>1.60 sec</v>
+        <v>1.18 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-07-31T11:28:38.777Z</v>
+        <v>2026-08-08T07:10:04.990Z</v>
       </c>
       <c r="F229" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="230">
@@ -4990,13 +4990,13 @@
         <v>PASS</v>
       </c>
       <c r="D230" t="str">
-        <v>1.48 sec</v>
+        <v>1.27 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-07-31T11:28:40.255Z</v>
+        <v>2026-08-08T07:10:06.262Z</v>
       </c>
       <c r="F230" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="231">
@@ -5010,13 +5010,13 @@
         <v>PASS</v>
       </c>
       <c r="D231" t="str">
-        <v>1.61 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-07-31T11:28:41.865Z</v>
+        <v>2026-08-08T07:10:07.424Z</v>
       </c>
       <c r="F231" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="232">
@@ -5030,13 +5030,13 @@
         <v>PASS</v>
       </c>
       <c r="D232" t="str">
-        <v>1.28 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-07-31T11:28:43.144Z</v>
+        <v>2026-08-08T07:10:08.447Z</v>
       </c>
       <c r="F232" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="233">
@@ -5050,13 +5050,13 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>1.33 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-07-31T11:28:44.477Z</v>
+        <v>2026-08-08T07:10:09.228Z</v>
       </c>
       <c r="F233" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="234">
@@ -5070,13 +5070,13 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>1.32 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-07-31T11:28:45.798Z</v>
+        <v>2026-08-08T07:10:10.039Z</v>
       </c>
       <c r="F234" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="235">
@@ -5090,13 +5090,13 @@
         <v>PASS</v>
       </c>
       <c r="D235" t="str">
-        <v>1.49 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-07-31T11:28:47.292Z</v>
+        <v>2026-08-08T07:10:11.085Z</v>
       </c>
       <c r="F235" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="236">
@@ -5110,13 +5110,13 @@
         <v>PASS</v>
       </c>
       <c r="D236" t="str">
-        <v>1.26 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-07-31T11:28:48.552Z</v>
+        <v>2026-08-08T07:10:12.078Z</v>
       </c>
       <c r="F236" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="237">
@@ -5130,13 +5130,13 @@
         <v>PASS</v>
       </c>
       <c r="D237" t="str">
-        <v>1.52 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-07-31T11:28:50.077Z</v>
+        <v>2026-08-08T07:10:13.183Z</v>
       </c>
       <c r="F237" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="238">
@@ -5150,13 +5150,13 @@
         <v>PASS</v>
       </c>
       <c r="D238" t="str">
-        <v>1.45 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-07-31T11:28:51.527Z</v>
+        <v>2026-08-08T07:10:13.943Z</v>
       </c>
       <c r="F238" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="239">
@@ -5170,13 +5170,13 @@
         <v>PASS</v>
       </c>
       <c r="D239" t="str">
-        <v>1.33 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-07-31T11:28:52.859Z</v>
+        <v>2026-08-08T07:10:14.611Z</v>
       </c>
       <c r="F239" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="240">
@@ -5190,13 +5190,13 @@
         <v>PASS</v>
       </c>
       <c r="D240" t="str">
-        <v>1.32 sec</v>
+        <v>0.67 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-07-31T11:28:54.177Z</v>
+        <v>2026-08-08T07:10:15.279Z</v>
       </c>
       <c r="F240" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="241">
@@ -5210,13 +5210,13 @@
         <v>PASS</v>
       </c>
       <c r="D241" t="str">
-        <v>1.53 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-07-31T11:28:55.712Z</v>
+        <v>2026-08-08T07:10:16.238Z</v>
       </c>
       <c r="F241" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="242">
@@ -5230,13 +5230,13 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>1.27 sec</v>
+        <v>0.71 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-07-31T11:28:56.979Z</v>
+        <v>2026-08-08T07:10:16.950Z</v>
       </c>
       <c r="F242" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="243">
@@ -5250,13 +5250,13 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>1.51 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-07-31T11:28:58.490Z</v>
+        <v>2026-08-08T07:10:18.021Z</v>
       </c>
       <c r="F243" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="244">
@@ -5270,13 +5270,13 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>1.45 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-07-31T11:28:59.942Z</v>
+        <v>2026-08-08T07:10:18.807Z</v>
       </c>
       <c r="F244" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="245">
@@ -5290,13 +5290,13 @@
         <v>PASS</v>
       </c>
       <c r="D245" t="str">
-        <v>1.17 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-07-31T11:29:01.110Z</v>
+        <v>2026-08-08T07:10:19.611Z</v>
       </c>
       <c r="F245" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="246">
@@ -5310,13 +5310,13 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>1.14 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-07-31T11:29:02.246Z</v>
+        <v>2026-08-08T07:10:20.366Z</v>
       </c>
       <c r="F246" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="247">
@@ -5330,13 +5330,13 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>1.58 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-07-31T11:29:03.826Z</v>
+        <v>2026-08-08T07:10:21.580Z</v>
       </c>
       <c r="F247" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="248">
@@ -5350,13 +5350,13 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>1.43 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-07-31T11:29:05.260Z</v>
+        <v>2026-08-08T07:10:22.405Z</v>
       </c>
       <c r="F248" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="249">
@@ -5370,13 +5370,13 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>1.53 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-07-31T11:29:06.792Z</v>
+        <v>2026-08-08T07:10:23.520Z</v>
       </c>
       <c r="F249" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="250">
@@ -5390,13 +5390,13 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>1.45 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-07-31T11:29:08.242Z</v>
+        <v>2026-08-08T07:10:24.598Z</v>
       </c>
       <c r="F250" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="251">
@@ -5410,13 +5410,13 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>1.17 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-07-31T11:29:09.409Z</v>
+        <v>2026-08-08T07:10:25.377Z</v>
       </c>
       <c r="F251" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="252">
@@ -5430,13 +5430,13 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>1.31 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-07-31T11:29:10.724Z</v>
+        <v>2026-08-08T07:10:26.202Z</v>
       </c>
       <c r="F252" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="253">
@@ -5450,13 +5450,13 @@
         <v>PASS</v>
       </c>
       <c r="D253" t="str">
-        <v>1.42 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-07-31T11:29:12.143Z</v>
+        <v>2026-08-08T07:10:27.118Z</v>
       </c>
       <c r="F253" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="254">
@@ -5470,13 +5470,13 @@
         <v>PASS</v>
       </c>
       <c r="D254" t="str">
-        <v>1.38 sec</v>
+        <v>1.19 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-07-31T11:29:13.526Z</v>
+        <v>2026-08-08T07:10:28.309Z</v>
       </c>
       <c r="F254" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="255">
@@ -5490,13 +5490,13 @@
         <v>PASS</v>
       </c>
       <c r="D255" t="str">
-        <v>1.58 sec</v>
+        <v>1.14 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-07-31T11:29:15.110Z</v>
+        <v>2026-08-08T07:10:29.444Z</v>
       </c>
       <c r="F255" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="256">
@@ -5510,13 +5510,13 @@
         <v>PASS</v>
       </c>
       <c r="D256" t="str">
-        <v>1.37 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-07-31T11:29:16.477Z</v>
+        <v>2026-08-08T07:10:30.552Z</v>
       </c>
       <c r="F256" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="257">
@@ -5530,13 +5530,13 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>1.35 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-07-31T11:29:17.825Z</v>
+        <v>2026-08-08T07:10:31.356Z</v>
       </c>
       <c r="F257" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="258">
@@ -5550,13 +5550,13 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>1.16 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-07-31T11:29:18.987Z</v>
+        <v>2026-08-08T07:10:32.195Z</v>
       </c>
       <c r="F258" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="259">
@@ -5570,13 +5570,13 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>1.46 sec</v>
+        <v>1.17 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-07-31T11:29:20.444Z</v>
+        <v>2026-08-08T07:10:33.365Z</v>
       </c>
       <c r="F259" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="260">
@@ -5590,13 +5590,13 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>1.35 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-07-31T11:29:21.791Z</v>
+        <v>2026-08-08T07:10:34.307Z</v>
       </c>
       <c r="F260" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="261">
@@ -5610,13 +5610,13 @@
         <v>PASS</v>
       </c>
       <c r="D261" t="str">
-        <v>1.57 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-07-31T11:29:23.360Z</v>
+        <v>2026-08-08T07:10:35.427Z</v>
       </c>
       <c r="F261" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="262">
@@ -5630,13 +5630,13 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>1.45 sec</v>
+        <v>1.09 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-07-31T11:29:24.808Z</v>
+        <v>2026-08-08T07:10:36.522Z</v>
       </c>
       <c r="F262" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="263">
@@ -5650,13 +5650,13 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>1.33 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-07-31T11:29:26.141Z</v>
+        <v>2026-08-08T07:10:37.338Z</v>
       </c>
       <c r="F263" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="264">
@@ -5670,13 +5670,13 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>1.34 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-07-31T11:29:27.477Z</v>
+        <v>2026-08-08T07:10:38.142Z</v>
       </c>
       <c r="F264" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="265">
@@ -5690,13 +5690,13 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>1.58 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-07-31T11:29:29.059Z</v>
+        <v>2026-08-08T07:10:39.100Z</v>
       </c>
       <c r="F265" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="266">
@@ -5710,13 +5710,13 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>1.47 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-07-31T11:29:30.524Z</v>
+        <v>2026-08-08T07:10:40.184Z</v>
       </c>
       <c r="F266" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="267">
@@ -5730,13 +5730,13 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>1.35 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-07-31T11:29:31.875Z</v>
+        <v>2026-08-08T07:10:41.112Z</v>
       </c>
       <c r="F267" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="268">
@@ -5750,13 +5750,13 @@
         <v>PASS</v>
       </c>
       <c r="D268" t="str">
-        <v>1.47 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-07-31T11:29:33.343Z</v>
+        <v>2026-08-08T07:10:42.234Z</v>
       </c>
       <c r="F268" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="269">
@@ -5770,13 +5770,13 @@
         <v>PASS</v>
       </c>
       <c r="D269" t="str">
-        <v>1.33 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-07-31T11:29:34.675Z</v>
+        <v>2026-08-08T07:10:43.081Z</v>
       </c>
       <c r="F269" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="270">
@@ -5790,13 +5790,13 @@
         <v>PASS</v>
       </c>
       <c r="D270" t="str">
-        <v>1.32 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-07-31T11:29:35.998Z</v>
+        <v>2026-08-08T07:10:43.964Z</v>
       </c>
       <c r="F270" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="271">
@@ -5810,13 +5810,13 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>1.47 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-07-31T11:29:37.468Z</v>
+        <v>2026-08-08T07:10:44.936Z</v>
       </c>
       <c r="F271" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="272">
@@ -5830,13 +5830,13 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>1.43 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-07-31T11:29:38.900Z</v>
+        <v>2026-08-08T07:10:45.862Z</v>
       </c>
       <c r="F272" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="273">
@@ -5850,13 +5850,13 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>1.53 sec</v>
+        <v>1.20 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-07-31T11:29:40.426Z</v>
+        <v>2026-08-08T07:10:47.063Z</v>
       </c>
       <c r="F273" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="274">
@@ -5870,13 +5870,13 @@
         <v>PASS</v>
       </c>
       <c r="D274" t="str">
-        <v>1.47 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-07-31T11:29:41.891Z</v>
+        <v>2026-08-08T07:10:47.914Z</v>
       </c>
       <c r="F274" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="275">
@@ -5890,13 +5890,13 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>1.35 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-07-31T11:29:43.240Z</v>
+        <v>2026-08-08T07:10:48.700Z</v>
       </c>
       <c r="F275" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="276">
@@ -5910,13 +5910,13 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>1.33 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-07-31T11:29:44.574Z</v>
+        <v>2026-08-08T07:10:49.492Z</v>
       </c>
       <c r="F276" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="277">
@@ -5930,13 +5930,13 @@
         <v>PASS</v>
       </c>
       <c r="D277" t="str">
-        <v>1.55 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-07-31T11:29:46.125Z</v>
+        <v>2026-08-08T07:10:50.463Z</v>
       </c>
       <c r="F277" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="278">
@@ -5950,13 +5950,13 @@
         <v>PASS</v>
       </c>
       <c r="D278" t="str">
-        <v>1.47 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-07-31T11:29:47.595Z</v>
+        <v>2026-08-08T07:10:51.324Z</v>
       </c>
       <c r="F278" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="279">
@@ -5970,13 +5970,13 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>1.54 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-07-31T11:29:49.134Z</v>
+        <v>2026-08-08T07:10:52.298Z</v>
       </c>
       <c r="F279" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="280">
@@ -5990,13 +5990,13 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>1.47 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-07-31T11:29:50.608Z</v>
+        <v>2026-08-08T07:10:53.158Z</v>
       </c>
       <c r="F280" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="281">
@@ -6010,13 +6010,13 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>1.33 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-07-31T11:29:51.941Z</v>
+        <v>2026-08-08T07:10:54.018Z</v>
       </c>
       <c r="F281" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="282">
@@ -6030,13 +6030,13 @@
         <v>PASS</v>
       </c>
       <c r="D282" t="str">
-        <v>1.32 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-07-31T11:29:53.261Z</v>
+        <v>2026-08-08T07:10:54.793Z</v>
       </c>
       <c r="F282" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="283">
@@ -6050,13 +6050,13 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>1.43 sec</v>
+        <v>0.99 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-07-31T11:29:54.691Z</v>
+        <v>2026-08-08T07:10:55.784Z</v>
       </c>
       <c r="F283" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="284">
@@ -6070,13 +6070,13 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>1.33 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-07-31T11:29:56.025Z</v>
+        <v>2026-08-08T07:10:56.644Z</v>
       </c>
       <c r="F284" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="285">
@@ -6090,13 +6090,13 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>1.50 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-07-31T11:29:57.524Z</v>
+        <v>2026-08-08T07:10:57.602Z</v>
       </c>
       <c r="F285" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="286">
@@ -6110,13 +6110,13 @@
         <v>PASS</v>
       </c>
       <c r="D286" t="str">
-        <v>1.35 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-07-31T11:29:58.875Z</v>
+        <v>2026-08-08T07:10:58.684Z</v>
       </c>
       <c r="F286" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="287">
@@ -6130,13 +6130,13 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>1.15 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-07-31T11:30:00.024Z</v>
+        <v>2026-08-08T07:10:59.546Z</v>
       </c>
       <c r="F287" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="288">
@@ -6150,13 +6150,13 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>1.33 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-07-31T11:30:01.356Z</v>
+        <v>2026-08-08T07:11:00.337Z</v>
       </c>
       <c r="F288" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="289">
@@ -6170,13 +6170,13 @@
         <v>PASS</v>
       </c>
       <c r="D289" t="str">
-        <v>1.60 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-07-31T11:30:02.959Z</v>
+        <v>2026-08-08T07:11:01.547Z</v>
       </c>
       <c r="F289" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="290">
@@ -6190,13 +6190,13 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>1.50 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-07-31T11:30:04.462Z</v>
+        <v>2026-08-08T07:11:02.481Z</v>
       </c>
       <c r="F290" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="291">
@@ -6210,13 +6210,13 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>1.61 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-07-31T11:30:06.075Z</v>
+        <v>2026-08-08T07:11:03.409Z</v>
       </c>
       <c r="F291" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="292">
@@ -6230,13 +6230,13 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>1.47 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-07-31T11:30:07.540Z</v>
+        <v>2026-08-08T07:11:04.339Z</v>
       </c>
       <c r="F292" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="293">
@@ -6250,13 +6250,13 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>1.34 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-07-31T11:30:08.877Z</v>
+        <v>2026-08-08T07:11:05.160Z</v>
       </c>
       <c r="F293" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="294">
@@ -6270,13 +6270,13 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>1.14 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-07-31T11:30:10.019Z</v>
+        <v>2026-08-08T07:11:05.918Z</v>
       </c>
       <c r="F294" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="295">
@@ -6290,13 +6290,13 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>1.47 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-07-31T11:30:11.485Z</v>
+        <v>2026-08-08T07:11:06.976Z</v>
       </c>
       <c r="F295" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="296">
@@ -6310,13 +6310,13 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>1.41 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-07-31T11:30:12.893Z</v>
+        <v>2026-08-08T07:11:07.981Z</v>
       </c>
       <c r="F296" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="297">
@@ -6330,13 +6330,13 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>1.51 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-07-31T11:30:14.408Z</v>
+        <v>2026-08-08T07:11:08.919Z</v>
       </c>
       <c r="F297" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="298">
@@ -6350,13 +6350,13 @@
         <v>PASS</v>
       </c>
       <c r="D298" t="str">
-        <v>1.18 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-07-31T11:30:15.589Z</v>
+        <v>2026-08-08T07:11:09.752Z</v>
       </c>
       <c r="F298" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="299">
@@ -6370,13 +6370,13 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>1.33 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-07-31T11:30:16.923Z</v>
+        <v>2026-08-08T07:11:10.510Z</v>
       </c>
       <c r="F299" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="300">
@@ -6390,13 +6390,13 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>1.34 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-07-31T11:30:18.268Z</v>
+        <v>2026-08-08T07:11:11.282Z</v>
       </c>
       <c r="F300" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="301">
@@ -6410,13 +6410,13 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>1.49 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-07-31T11:30:19.756Z</v>
+        <v>2026-08-08T07:11:12.215Z</v>
       </c>
       <c r="F301" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="302">
@@ -6430,13 +6430,13 @@
         <v>PASS</v>
       </c>
       <c r="D302" t="str">
-        <v>1.35 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-07-31T11:30:21.106Z</v>
+        <v>2026-08-08T07:11:13.041Z</v>
       </c>
       <c r="F302" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="303">
@@ -6450,13 +6450,13 @@
         <v>PASS</v>
       </c>
       <c r="D303" t="str">
-        <v>1.60 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-07-31T11:30:22.706Z</v>
+        <v>2026-08-08T07:11:14.152Z</v>
       </c>
       <c r="F303" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="304">
@@ -6470,13 +6470,13 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>1.28 sec</v>
+        <v>0.89 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-07-31T11:30:23.991Z</v>
+        <v>2026-08-08T07:11:15.043Z</v>
       </c>
       <c r="F304" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="305">
@@ -6490,13 +6490,13 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>1.35 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-07-31T11:30:25.341Z</v>
+        <v>2026-08-08T07:11:16.023Z</v>
       </c>
       <c r="F305" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="306">
@@ -6510,13 +6510,13 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>1.31 sec</v>
+        <v>0.76 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-07-31T11:30:26.654Z</v>
+        <v>2026-08-08T07:11:16.781Z</v>
       </c>
       <c r="F306" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="307">
@@ -6530,13 +6530,13 @@
         <v>PASS</v>
       </c>
       <c r="D307" t="str">
-        <v>1.59 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-07-31T11:30:28.240Z</v>
+        <v>2026-08-08T07:11:17.784Z</v>
       </c>
       <c r="F307" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="308">
@@ -6550,13 +6550,13 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>1.47 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-07-31T11:30:29.706Z</v>
+        <v>2026-08-08T07:11:18.700Z</v>
       </c>
       <c r="F308" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="309">
@@ -6570,13 +6570,13 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>1.51 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-07-31T11:30:31.218Z</v>
+        <v>2026-08-08T07:11:19.623Z</v>
       </c>
       <c r="F309" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="310">
@@ -6590,13 +6590,13 @@
         <v>PASS</v>
       </c>
       <c r="D310" t="str">
-        <v>1.45 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-07-31T11:30:32.672Z</v>
+        <v>2026-08-08T07:11:20.580Z</v>
       </c>
       <c r="F310" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="311">
@@ -6610,13 +6610,13 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>1.15 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-07-31T11:30:33.822Z</v>
+        <v>2026-08-08T07:11:21.433Z</v>
       </c>
       <c r="F311" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="312">
@@ -6630,13 +6630,13 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>1.31 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-07-31T11:30:35.133Z</v>
+        <v>2026-08-08T07:11:22.299Z</v>
       </c>
       <c r="F312" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="313">
@@ -6650,13 +6650,13 @@
         <v>PASS</v>
       </c>
       <c r="D313" t="str">
-        <v>1.41 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-07-31T11:30:36.540Z</v>
+        <v>2026-08-08T07:11:23.253Z</v>
       </c>
       <c r="F313" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="314">
@@ -6670,13 +6670,13 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>1.35 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-07-31T11:30:37.889Z</v>
+        <v>2026-08-08T07:11:24.169Z</v>
       </c>
       <c r="F314" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="315">
@@ -6690,13 +6690,13 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>1.48 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-07-31T11:30:39.367Z</v>
+        <v>2026-08-08T07:11:25.130Z</v>
       </c>
       <c r="F315" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="316">
@@ -6710,13 +6710,13 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>1.35 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-07-31T11:30:40.722Z</v>
+        <v>2026-08-08T07:11:25.993Z</v>
       </c>
       <c r="F316" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="317">
@@ -6730,13 +6730,13 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>1.33 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-07-31T11:30:42.055Z</v>
+        <v>2026-08-08T07:11:26.761Z</v>
       </c>
       <c r="F317" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="318">
@@ -6750,13 +6750,13 @@
         <v>PASS</v>
       </c>
       <c r="D318" t="str">
-        <v>1.31 sec</v>
+        <v>0.72 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-07-31T11:30:43.368Z</v>
+        <v>2026-08-08T07:11:27.483Z</v>
       </c>
       <c r="F318" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="319">
@@ -6770,13 +6770,13 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>1.54 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-07-31T11:30:44.913Z</v>
+        <v>2026-08-08T07:11:28.484Z</v>
       </c>
       <c r="F319" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="320">
@@ -6790,13 +6790,13 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>1.48 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-07-31T11:30:46.396Z</v>
+        <v>2026-08-08T07:11:29.399Z</v>
       </c>
       <c r="F320" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="321">
@@ -6810,13 +6810,13 @@
         <v>PASS</v>
       </c>
       <c r="D321" t="str">
-        <v>1.61 sec</v>
+        <v>0.92 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-07-31T11:30:48.007Z</v>
+        <v>2026-08-08T07:11:30.319Z</v>
       </c>
       <c r="F321" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="322">
@@ -6830,13 +6830,13 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>1.45 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-07-31T11:30:49.455Z</v>
+        <v>2026-08-08T07:11:31.221Z</v>
       </c>
       <c r="F322" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="323">
@@ -6850,13 +6850,13 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>1.33 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-07-31T11:30:50.787Z</v>
+        <v>2026-08-08T07:11:31.998Z</v>
       </c>
       <c r="F323" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="324">
@@ -6870,13 +6870,13 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>1.32 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-07-31T11:30:52.103Z</v>
+        <v>2026-08-08T07:11:32.768Z</v>
       </c>
       <c r="F324" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="325">
@@ -6890,13 +6890,13 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>1.55 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-07-31T11:30:53.655Z</v>
+        <v>2026-08-08T07:11:33.735Z</v>
       </c>
       <c r="F325" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="326">
@@ -6910,13 +6910,13 @@
         <v>PASS</v>
       </c>
       <c r="D326" t="str">
-        <v>1.43 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-07-31T11:30:55.087Z</v>
+        <v>2026-08-08T07:11:34.632Z</v>
       </c>
       <c r="F326" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="327">
@@ -6930,13 +6930,13 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>1.34 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-07-31T11:30:56.425Z</v>
+        <v>2026-08-08T07:11:35.571Z</v>
       </c>
       <c r="F327" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="328">
@@ -6950,13 +6950,13 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>1.46 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-07-31T11:30:57.887Z</v>
+        <v>2026-08-08T07:11:36.451Z</v>
       </c>
       <c r="F328" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="329">
@@ -6970,13 +6970,13 @@
         <v>PASS</v>
       </c>
       <c r="D329" t="str">
-        <v>1.35 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-07-31T11:30:59.238Z</v>
+        <v>2026-08-08T07:11:37.255Z</v>
       </c>
       <c r="F329" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="330">
@@ -6990,13 +6990,13 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>1.32 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-07-31T11:31:00.554Z</v>
+        <v>2026-08-08T07:11:38.097Z</v>
       </c>
       <c r="F330" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="331">
@@ -7010,13 +7010,13 @@
         <v>PASS</v>
       </c>
       <c r="D331" t="str">
-        <v>1.48 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-07-31T11:31:02.031Z</v>
+        <v>2026-08-08T07:11:39.102Z</v>
       </c>
       <c r="F331" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="332">
@@ -7030,13 +7030,13 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>1.44 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-07-31T11:31:03.469Z</v>
+        <v>2026-08-08T07:11:40.066Z</v>
       </c>
       <c r="F332" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="333">
@@ -7050,13 +7050,13 @@
         <v>PASS</v>
       </c>
       <c r="D333" t="str">
-        <v>1.54 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-07-31T11:31:05.005Z</v>
+        <v>2026-08-08T07:11:41.045Z</v>
       </c>
       <c r="F333" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="334">
@@ -7070,13 +7070,13 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>1.45 sec</v>
+        <v>0.91 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-07-31T11:31:06.456Z</v>
+        <v>2026-08-08T07:11:41.956Z</v>
       </c>
       <c r="F334" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="335">
@@ -7090,13 +7090,13 @@
         <v>PASS</v>
       </c>
       <c r="D335" t="str">
-        <v>1.17 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-07-31T11:31:07.621Z</v>
+        <v>2026-08-08T07:11:42.769Z</v>
       </c>
       <c r="F335" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="336">
@@ -7110,13 +7110,13 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>1.32 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-07-31T11:31:08.937Z</v>
+        <v>2026-08-08T07:11:43.587Z</v>
       </c>
       <c r="F336" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="337">
@@ -7130,13 +7130,13 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>1.53 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-07-31T11:31:10.463Z</v>
+        <v>2026-08-08T07:11:44.488Z</v>
       </c>
       <c r="F337" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="338">
@@ -7150,13 +7150,13 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>1.44 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-07-31T11:31:11.905Z</v>
+        <v>2026-08-08T07:11:45.316Z</v>
       </c>
       <c r="F338" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="339">
@@ -7170,13 +7170,13 @@
         <v>PASS</v>
       </c>
       <c r="D339" t="str">
-        <v>1.53 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-07-31T11:31:13.438Z</v>
+        <v>2026-08-08T07:11:46.436Z</v>
       </c>
       <c r="F339" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="340">
@@ -7190,13 +7190,13 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>1.47 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-07-31T11:31:14.905Z</v>
+        <v>2026-08-08T07:11:47.274Z</v>
       </c>
       <c r="F340" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="341">
@@ -7210,13 +7210,13 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>1.35 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-07-31T11:31:16.254Z</v>
+        <v>2026-08-08T07:11:48.094Z</v>
       </c>
       <c r="F341" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="342">
@@ -7230,13 +7230,13 @@
         <v>PASS</v>
       </c>
       <c r="D342" t="str">
-        <v>1.33 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-07-31T11:31:17.580Z</v>
+        <v>2026-08-08T07:11:49.097Z</v>
       </c>
       <c r="F342" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="343">
@@ -7250,13 +7250,13 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>1.44 sec</v>
+        <v>1.04 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-07-31T11:31:19.021Z</v>
+        <v>2026-08-08T07:11:50.141Z</v>
       </c>
       <c r="F343" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="344">
@@ -7270,13 +7270,13 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>1.39 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-07-31T11:31:20.415Z</v>
+        <v>2026-08-08T07:11:50.984Z</v>
       </c>
       <c r="F344" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="345">
@@ -7290,13 +7290,13 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>1.49 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-07-31T11:31:21.909Z</v>
+        <v>2026-08-08T07:11:51.924Z</v>
       </c>
       <c r="F345" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="346">
@@ -7310,13 +7310,13 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>1.36 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-07-31T11:31:23.271Z</v>
+        <v>2026-08-08T07:11:52.771Z</v>
       </c>
       <c r="F346" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="347">
@@ -7330,13 +7330,13 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>1.18 sec</v>
+        <v>0.81 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-07-31T11:31:24.455Z</v>
+        <v>2026-08-08T07:11:53.582Z</v>
       </c>
       <c r="F347" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="348">
@@ -7350,13 +7350,13 @@
         <v>PASS</v>
       </c>
       <c r="D348" t="str">
-        <v>1.18 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-07-31T11:31:25.636Z</v>
+        <v>2026-08-08T07:11:54.406Z</v>
       </c>
       <c r="F348" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="349">
@@ -7370,13 +7370,13 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>1.60 sec</v>
+        <v>1.07 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-07-31T11:31:27.239Z</v>
+        <v>2026-08-08T07:11:55.475Z</v>
       </c>
       <c r="F349" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="350">
@@ -7390,13 +7390,13 @@
         <v>PASS</v>
       </c>
       <c r="D350" t="str">
-        <v>1.47 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-07-31T11:31:28.705Z</v>
+        <v>2026-08-08T07:11:56.352Z</v>
       </c>
       <c r="F350" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="351">
@@ -7410,13 +7410,13 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>1.59 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-07-31T11:31:30.298Z</v>
+        <v>2026-08-08T07:11:57.562Z</v>
       </c>
       <c r="F351" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="352">
@@ -7430,13 +7430,13 @@
         <v>PASS</v>
       </c>
       <c r="D352" t="str">
-        <v>1.48 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-07-31T11:31:31.774Z</v>
+        <v>2026-08-08T07:11:58.461Z</v>
       </c>
       <c r="F352" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="353">
@@ -7450,13 +7450,13 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>1.18 sec</v>
+        <v>0.85 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-07-31T11:31:32.954Z</v>
+        <v>2026-08-08T07:11:59.308Z</v>
       </c>
       <c r="F353" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="354">
@@ -7470,13 +7470,13 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>1.33 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-07-31T11:31:34.287Z</v>
+        <v>2026-08-08T07:12:00.144Z</v>
       </c>
       <c r="F354" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="355">
@@ -7490,13 +7490,13 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>1.50 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-07-31T11:31:35.787Z</v>
+        <v>2026-08-08T07:12:01.118Z</v>
       </c>
       <c r="F355" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="356">
@@ -7510,13 +7510,13 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>1.26 sec</v>
+        <v>1.08 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-07-31T11:31:37.047Z</v>
+        <v>2026-08-08T07:12:02.199Z</v>
       </c>
       <c r="F356" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="357">
@@ -7530,13 +7530,13 @@
         <v>PASS</v>
       </c>
       <c r="D357" t="str">
-        <v>1.53 sec</v>
+        <v>1.22 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-07-31T11:31:38.581Z</v>
+        <v>2026-08-08T07:12:03.417Z</v>
       </c>
       <c r="F357" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="358">
@@ -7550,13 +7550,13 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>1.46 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-07-31T11:31:40.036Z</v>
+        <v>2026-08-08T07:12:04.213Z</v>
       </c>
       <c r="F358" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="359">
@@ -7570,13 +7570,13 @@
         <v>PASS</v>
       </c>
       <c r="D359" t="str">
-        <v>1.35 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-07-31T11:31:41.387Z</v>
+        <v>2026-08-08T07:12:05.069Z</v>
       </c>
       <c r="F359" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="360">
@@ -7590,13 +7590,13 @@
         <v>PASS</v>
       </c>
       <c r="D360" t="str">
-        <v>1.35 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-07-31T11:31:42.738Z</v>
+        <v>2026-08-08T07:12:05.838Z</v>
       </c>
       <c r="F360" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="361">
@@ -7610,13 +7610,13 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>1.56 sec</v>
+        <v>1.24 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-07-31T11:31:44.295Z</v>
+        <v>2026-08-08T07:12:07.080Z</v>
       </c>
       <c r="F361" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="362">
@@ -7630,13 +7630,13 @@
         <v>PASS</v>
       </c>
       <c r="D362" t="str">
-        <v>1.44 sec</v>
+        <v>0.83 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-07-31T11:31:45.730Z</v>
+        <v>2026-08-08T07:12:07.908Z</v>
       </c>
       <c r="F362" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="363">
@@ -7650,13 +7650,13 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>1.56 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-07-31T11:31:47.289Z</v>
+        <v>2026-08-08T07:12:08.917Z</v>
       </c>
       <c r="F363" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="364">
@@ -7670,13 +7670,13 @@
         <v>PASS</v>
       </c>
       <c r="D364" t="str">
-        <v>1.48 sec</v>
+        <v>0.96 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-07-31T11:31:48.770Z</v>
+        <v>2026-08-08T07:12:09.881Z</v>
       </c>
       <c r="F364" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="365">
@@ -7690,13 +7690,13 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>1.35 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-07-31T11:31:50.119Z</v>
+        <v>2026-08-08T07:12:10.699Z</v>
       </c>
       <c r="F365" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="366">
@@ -7710,13 +7710,13 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>1.32 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-07-31T11:31:51.435Z</v>
+        <v>2026-08-08T07:12:11.491Z</v>
       </c>
       <c r="F366" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="367">
@@ -7730,13 +7730,13 @@
         <v>PASS</v>
       </c>
       <c r="D367" t="str">
-        <v>1.39 sec</v>
+        <v>1.06 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-07-31T11:31:52.820Z</v>
+        <v>2026-08-08T07:12:12.554Z</v>
       </c>
       <c r="F367" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="368">
@@ -7750,13 +7750,13 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>1.44 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-07-31T11:31:54.258Z</v>
+        <v>2026-08-08T07:12:13.550Z</v>
       </c>
       <c r="F368" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="369">
@@ -7770,13 +7770,13 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>1.53 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-07-31T11:31:55.786Z</v>
+        <v>2026-08-08T07:12:14.486Z</v>
       </c>
       <c r="F369" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="370">
@@ -7790,13 +7790,13 @@
         <v>PASS</v>
       </c>
       <c r="D370" t="str">
-        <v>1.45 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-07-31T11:31:57.240Z</v>
+        <v>2026-08-08T07:12:15.351Z</v>
       </c>
       <c r="F370" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="371">
@@ -7810,13 +7810,13 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>1.18 sec</v>
+        <v>0.86 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-07-31T11:31:58.419Z</v>
+        <v>2026-08-08T07:12:16.211Z</v>
       </c>
       <c r="F371" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="372">
@@ -7830,13 +7830,13 @@
         <v>PASS</v>
       </c>
       <c r="D372" t="str">
-        <v>1.32 sec</v>
+        <v>0.90 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-07-31T11:31:59.736Z</v>
+        <v>2026-08-08T07:12:17.115Z</v>
       </c>
       <c r="F372" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="373">
@@ -7850,13 +7850,13 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>1.42 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-07-31T11:32:01.153Z</v>
+        <v>2026-08-08T07:12:18.111Z</v>
       </c>
       <c r="F373" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="374">
@@ -7870,13 +7870,13 @@
         <v>PASS</v>
       </c>
       <c r="D374" t="str">
-        <v>1.35 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-07-31T11:32:02.505Z</v>
+        <v>2026-08-08T07:12:19.060Z</v>
       </c>
       <c r="F374" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="375">
@@ -7890,13 +7890,13 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>1.35 sec</v>
+        <v>0.95 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-07-31T11:32:03.854Z</v>
+        <v>2026-08-08T07:12:20.010Z</v>
       </c>
       <c r="F375" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="376">
@@ -7910,13 +7910,13 @@
         <v>PASS</v>
       </c>
       <c r="D376" t="str">
-        <v>1.38 sec</v>
+        <v>1.10 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-07-31T11:32:05.236Z</v>
+        <v>2026-08-08T07:12:21.113Z</v>
       </c>
       <c r="F376" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="377">
@@ -7930,13 +7930,13 @@
         <v>PASS</v>
       </c>
       <c r="D377" t="str">
-        <v>1.35 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-07-31T11:32:06.585Z</v>
+        <v>2026-08-08T07:12:21.901Z</v>
       </c>
       <c r="F377" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="378">
@@ -7950,13 +7950,13 @@
         <v>PASS</v>
       </c>
       <c r="D378" t="str">
-        <v>1.33 sec</v>
+        <v>1.01 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-07-31T11:32:07.912Z</v>
+        <v>2026-08-08T07:12:22.908Z</v>
       </c>
       <c r="F378" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="379">
@@ -7970,13 +7970,13 @@
         <v>PASS</v>
       </c>
       <c r="D379" t="str">
-        <v>1.56 sec</v>
+        <v>0.97 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-07-31T11:32:09.469Z</v>
+        <v>2026-08-08T07:12:23.882Z</v>
       </c>
       <c r="F379" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="380">
@@ -7990,13 +7990,13 @@
         <v>PASS</v>
       </c>
       <c r="D380" t="str">
-        <v>1.46 sec</v>
+        <v>0.87 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-07-31T11:32:10.929Z</v>
+        <v>2026-08-08T07:12:24.749Z</v>
       </c>
       <c r="F380" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="381">
@@ -8010,13 +8010,13 @@
         <v>PASS</v>
       </c>
       <c r="D381" t="str">
-        <v>1.60 sec</v>
+        <v>0.93 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-07-31T11:32:12.526Z</v>
+        <v>2026-08-08T07:12:25.676Z</v>
       </c>
       <c r="F381" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="382">
@@ -8030,13 +8030,13 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>1.46 sec</v>
+        <v>0.88 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-07-31T11:32:13.985Z</v>
+        <v>2026-08-08T07:12:26.551Z</v>
       </c>
       <c r="F382" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="383">
@@ -8050,13 +8050,13 @@
         <v>PASS</v>
       </c>
       <c r="D383" t="str">
-        <v>1.33 sec</v>
+        <v>0.77 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-07-31T11:32:15.319Z</v>
+        <v>2026-08-08T07:12:27.317Z</v>
       </c>
       <c r="F383" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="384">
@@ -8070,13 +8070,13 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>1.33 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-07-31T11:32:16.651Z</v>
+        <v>2026-08-08T07:12:28.111Z</v>
       </c>
       <c r="F384" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="385">
@@ -8090,13 +8090,13 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>1.55 sec</v>
+        <v>1.12 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-07-31T11:32:18.203Z</v>
+        <v>2026-08-08T07:12:29.232Z</v>
       </c>
       <c r="F385" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="386">
@@ -8110,13 +8110,13 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>1.48 sec</v>
+        <v>1.11 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-07-31T11:32:19.686Z</v>
+        <v>2026-08-08T07:12:30.340Z</v>
       </c>
       <c r="F386" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="387">
@@ -8130,13 +8130,13 @@
         <v>PASS</v>
       </c>
       <c r="D387" t="str">
-        <v>1.54 sec</v>
+        <v>1.02 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-07-31T11:32:21.225Z</v>
+        <v>2026-08-08T07:12:31.359Z</v>
       </c>
       <c r="F387" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="388">
@@ -8150,13 +8150,13 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>1.48 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-07-31T11:32:22.704Z</v>
+        <v>2026-08-08T07:12:32.303Z</v>
       </c>
       <c r="F388" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="389">
@@ -8170,13 +8170,13 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>1.35 sec</v>
+        <v>0.79 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-07-31T11:32:24.055Z</v>
+        <v>2026-08-08T07:12:33.094Z</v>
       </c>
       <c r="F389" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="390">
@@ -8190,13 +8190,13 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>1.32 sec</v>
+        <v>0.78 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-07-31T11:32:25.376Z</v>
+        <v>2026-08-08T07:12:33.873Z</v>
       </c>
       <c r="F390" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="391">
@@ -8210,13 +8210,13 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>1.49 sec</v>
+        <v>0.98 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-07-31T11:32:26.863Z</v>
+        <v>2026-08-08T07:12:34.854Z</v>
       </c>
       <c r="F391" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="392">
@@ -8230,13 +8230,13 @@
         <v>PASS</v>
       </c>
       <c r="D392" t="str">
-        <v>1.46 sec</v>
+        <v>1.16 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-07-31T11:32:28.320Z</v>
+        <v>2026-08-08T07:12:36.009Z</v>
       </c>
       <c r="F392" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="393">
@@ -8250,13 +8250,13 @@
         <v>PASS</v>
       </c>
       <c r="D393" t="str">
-        <v>1.57 sec</v>
+        <v>1.26 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-07-31T11:32:29.890Z</v>
+        <v>2026-08-08T07:12:37.269Z</v>
       </c>
       <c r="F393" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="394">
@@ -8270,13 +8270,13 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>1.48 sec</v>
+        <v>1.05 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-07-31T11:32:31.368Z</v>
+        <v>2026-08-08T07:12:38.317Z</v>
       </c>
       <c r="F394" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="395">
@@ -8290,13 +8290,13 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>1.35 sec</v>
+        <v>0.82 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-07-31T11:32:32.718Z</v>
+        <v>2026-08-08T07:12:39.135Z</v>
       </c>
       <c r="F395" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="396">
@@ -8310,13 +8310,13 @@
         <v>PASS</v>
       </c>
       <c r="D396" t="str">
-        <v>1.15 sec</v>
+        <v>0.63 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-07-31T11:32:33.867Z</v>
+        <v>2026-08-08T07:12:39.763Z</v>
       </c>
       <c r="F396" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="397">
@@ -8330,13 +8330,13 @@
         <v>PASS</v>
       </c>
       <c r="D397" t="str">
-        <v>1.57 sec</v>
+        <v>0.80 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-07-31T11:32:35.437Z</v>
+        <v>2026-08-08T07:12:40.563Z</v>
       </c>
       <c r="F397" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="398">
@@ -8350,13 +8350,13 @@
         <v>PASS</v>
       </c>
       <c r="D398" t="str">
-        <v>1.48 sec</v>
+        <v>1.00 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-07-31T11:32:36.919Z</v>
+        <v>2026-08-08T07:12:41.561Z</v>
       </c>
       <c r="F398" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="399">
@@ -8370,13 +8370,13 @@
         <v>PASS</v>
       </c>
       <c r="D399" t="str">
-        <v>1.53 sec</v>
+        <v>1.21 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-07-31T11:32:38.445Z</v>
+        <v>2026-08-08T07:12:42.770Z</v>
       </c>
       <c r="F399" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="400">
@@ -8390,13 +8390,13 @@
         <v>PASS</v>
       </c>
       <c r="D400" t="str">
-        <v>1.29 sec</v>
+        <v>0.94 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-07-31T11:32:39.734Z</v>
+        <v>2026-08-08T07:12:43.712Z</v>
       </c>
       <c r="F400" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
     <row r="401">
@@ -8410,13 +8410,13 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>1.35 sec</v>
+        <v>0.84 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-07-31T11:32:41.084Z</v>
+        <v>2026-08-08T07:12:44.549Z</v>
       </c>
       <c r="F401" t="str">
-        <v>Invalid email or password</v>
+        <v>Too many requests from this IP, please try again later.</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium Report.xlsx
+++ b/reports/Selenium Report.xlsx
@@ -419,7 +419,7 @@
         <v>Remarks</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
         <v>TC-001</v>
       </c>
@@ -427,16 +427,17 @@
         <v>Valid citizen demo login</v>
       </c>
       <c r="C2" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>4.82 sec</v>
+        <v>4.33 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-08T07:05:29.938Z</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Success</v>
+        <v>2026-08-09T18:19:32.868Z</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
+  (Session info: chrome=151.0.7922.77)</v>
       </c>
     </row>
     <row r="3">
@@ -447,13 +448,13 @@
         <v>Valid volunteer demo login</v>
       </c>
       <c r="C3" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D3" t="str">
-        <v>3.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-08T07:05:33.836Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -467,13 +468,13 @@
         <v>Valid admin demo login</v>
       </c>
       <c r="C4" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="D4" t="str">
-        <v>4.29 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-08T07:05:38.124Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -490,10 +491,10 @@
         <v>PASS</v>
       </c>
       <c r="D5" t="str">
-        <v>3.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-08T07:05:41.915Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -510,10 +511,10 @@
         <v>PASS</v>
       </c>
       <c r="D6" t="str">
-        <v>3.91 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-08T07:05:45.827Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -530,10 +531,10 @@
         <v>PASS</v>
       </c>
       <c r="D7" t="str">
-        <v>3.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-08T07:05:49.726Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -550,10 +551,10 @@
         <v>PASS</v>
       </c>
       <c r="D8" t="str">
-        <v>4.15 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-08T07:05:53.875Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -570,10 +571,10 @@
         <v>PASS</v>
       </c>
       <c r="D9" t="str">
-        <v>3.81 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-08T07:05:57.686Z</v>
+        <v>2026-08-09T18:19:32.868Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -590,10 +591,10 @@
         <v>PASS</v>
       </c>
       <c r="D10" t="str">
-        <v>3.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-08T07:06:01.588Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -610,10 +611,10 @@
         <v>PASS</v>
       </c>
       <c r="D11" t="str">
-        <v>3.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-08T07:06:05.510Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -630,10 +631,10 @@
         <v>PASS</v>
       </c>
       <c r="D12" t="str">
-        <v>3.73 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-08T07:06:09.237Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -650,10 +651,10 @@
         <v>PASS</v>
       </c>
       <c r="D13" t="str">
-        <v>4.05 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-08T07:06:13.291Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -670,10 +671,10 @@
         <v>PASS</v>
       </c>
       <c r="D14" t="str">
-        <v>3.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-08T07:06:17.063Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -690,10 +691,10 @@
         <v>PASS</v>
       </c>
       <c r="D15" t="str">
-        <v>4.08 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-08T07:06:21.142Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -710,10 +711,10 @@
         <v>PASS</v>
       </c>
       <c r="D16" t="str">
-        <v>3.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-08T07:06:25.102Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -730,10 +731,10 @@
         <v>PASS</v>
       </c>
       <c r="D17" t="str">
-        <v>4.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-08T07:06:29.122Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -750,10 +751,10 @@
         <v>PASS</v>
       </c>
       <c r="D18" t="str">
-        <v>3.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-08T07:06:32.973Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -770,10 +771,10 @@
         <v>PASS</v>
       </c>
       <c r="D19" t="str">
-        <v>4.06 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-08T07:06:37.037Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -790,10 +791,10 @@
         <v>PASS</v>
       </c>
       <c r="D20" t="str">
-        <v>4.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-08T07:06:41.059Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -810,10 +811,10 @@
         <v>PASS</v>
       </c>
       <c r="D21" t="str">
-        <v>4.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-08T07:06:45.074Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -830,13 +831,13 @@
         <v>PASS</v>
       </c>
       <c r="D22" t="str">
-        <v>1.04 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-08T07:06:46.117Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F22" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="23">
@@ -850,13 +851,13 @@
         <v>PASS</v>
       </c>
       <c r="D23" t="str">
-        <v>0.74 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-08T07:06:46.859Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F23" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="24">
@@ -870,13 +871,13 @@
         <v>PASS</v>
       </c>
       <c r="D24" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-08T07:06:47.637Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F24" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="25">
@@ -890,13 +891,13 @@
         <v>PASS</v>
       </c>
       <c r="D25" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-08T07:06:48.559Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F25" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="26">
@@ -910,13 +911,13 @@
         <v>PASS</v>
       </c>
       <c r="D26" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-08T07:06:49.385Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F26" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="27">
@@ -930,13 +931,13 @@
         <v>PASS</v>
       </c>
       <c r="D27" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-08T07:06:50.405Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F27" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="28">
@@ -950,13 +951,13 @@
         <v>PASS</v>
       </c>
       <c r="D28" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-08T07:06:51.353Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F28" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="29">
@@ -970,13 +971,13 @@
         <v>PASS</v>
       </c>
       <c r="D29" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-08T07:06:52.210Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F29" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="30">
@@ -990,13 +991,13 @@
         <v>PASS</v>
       </c>
       <c r="D30" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-08T07:06:53.046Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F30" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="31">
@@ -1010,13 +1011,13 @@
         <v>PASS</v>
       </c>
       <c r="D31" t="str">
-        <v>1.31 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-08T07:06:54.355Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F31" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="32">
@@ -1030,13 +1031,13 @@
         <v>PASS</v>
       </c>
       <c r="D32" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-08T07:06:55.230Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F32" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="33">
@@ -1050,13 +1051,13 @@
         <v>PASS</v>
       </c>
       <c r="D33" t="str">
-        <v>1.08 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-08T07:06:56.312Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F33" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="34">
@@ -1070,13 +1071,13 @@
         <v>PASS</v>
       </c>
       <c r="D34" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-08T07:06:57.236Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F34" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="35">
@@ -1090,13 +1091,13 @@
         <v>PASS</v>
       </c>
       <c r="D35" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-08T07:06:58.034Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F35" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="36">
@@ -1110,13 +1111,13 @@
         <v>PASS</v>
       </c>
       <c r="D36" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-08T07:06:58.799Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F36" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="37">
@@ -1130,13 +1131,13 @@
         <v>PASS</v>
       </c>
       <c r="D37" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-08T07:06:59.816Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F37" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="38">
@@ -1150,13 +1151,13 @@
         <v>PASS</v>
       </c>
       <c r="D38" t="str">
-        <v>1.16 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-08T07:07:00.978Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F38" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="39">
@@ -1170,13 +1171,13 @@
         <v>PASS</v>
       </c>
       <c r="D39" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-08T07:07:01.974Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F39" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="40">
@@ -1190,13 +1191,13 @@
         <v>PASS</v>
       </c>
       <c r="D40" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-08T07:07:02.798Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F40" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="41">
@@ -1210,13 +1211,13 @@
         <v>PASS</v>
       </c>
       <c r="D41" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-08T07:07:03.811Z</v>
+        <v>2026-08-09T18:19:32.869Z</v>
       </c>
       <c r="F41" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="42">
@@ -1230,13 +1231,13 @@
         <v>PASS</v>
       </c>
       <c r="D42" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-08T07:07:04.607Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F42" t="str">
-        <v>Too many authentication attempts. Please try again after 15 minutes.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="43">
@@ -1250,13 +1251,13 @@
         <v>PASS</v>
       </c>
       <c r="D43" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-08T07:07:05.532Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F43" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="44">
@@ -1270,13 +1271,13 @@
         <v>PASS</v>
       </c>
       <c r="D44" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-08T07:07:06.458Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F44" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="45">
@@ -1290,13 +1291,13 @@
         <v>PASS</v>
       </c>
       <c r="D45" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-08T07:07:07.385Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F45" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="46">
@@ -1310,13 +1311,13 @@
         <v>PASS</v>
       </c>
       <c r="D46" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-08T07:07:08.214Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F46" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="47">
@@ -1330,13 +1331,13 @@
         <v>PASS</v>
       </c>
       <c r="D47" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-08T07:07:09.089Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F47" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="48">
@@ -1350,13 +1351,13 @@
         <v>PASS</v>
       </c>
       <c r="D48" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-08T07:07:09.926Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F48" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="49">
@@ -1370,13 +1371,13 @@
         <v>PASS</v>
       </c>
       <c r="D49" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-08T07:07:10.898Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F49" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="50">
@@ -1390,13 +1391,13 @@
         <v>PASS</v>
       </c>
       <c r="D50" t="str">
-        <v>1.07 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-08T07:07:11.967Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F50" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="51">
@@ -1410,13 +1411,13 @@
         <v>PASS</v>
       </c>
       <c r="D51" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-08T07:07:12.966Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F51" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="52">
@@ -1430,13 +1431,13 @@
         <v>PASS</v>
       </c>
       <c r="D52" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-08T07:07:13.864Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F52" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="53">
@@ -1450,13 +1451,13 @@
         <v>PASS</v>
       </c>
       <c r="D53" t="str">
-        <v>0.99 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-08T07:07:14.859Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F53" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="54">
@@ -1470,13 +1471,13 @@
         <v>PASS</v>
       </c>
       <c r="D54" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-08T07:07:15.678Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F54" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="55">
@@ -1490,13 +1491,13 @@
         <v>PASS</v>
       </c>
       <c r="D55" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-08T07:07:16.634Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F55" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="56">
@@ -1510,13 +1511,13 @@
         <v>PASS</v>
       </c>
       <c r="D56" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-08T07:07:17.470Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F56" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="57">
@@ -1530,13 +1531,13 @@
         <v>PASS</v>
       </c>
       <c r="D57" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-08T07:07:18.419Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F57" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="58">
@@ -1550,13 +1551,13 @@
         <v>PASS</v>
       </c>
       <c r="D58" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-08T07:07:19.404Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F58" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="59">
@@ -1570,13 +1571,13 @@
         <v>PASS</v>
       </c>
       <c r="D59" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-08T07:07:20.193Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F59" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="60">
@@ -1590,13 +1591,13 @@
         <v>PASS</v>
       </c>
       <c r="D60" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-08T07:07:21.011Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F60" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="61">
@@ -1610,13 +1611,13 @@
         <v>PASS</v>
       </c>
       <c r="D61" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-08T07:07:22.026Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F61" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="62">
@@ -1630,13 +1631,13 @@
         <v>PASS</v>
       </c>
       <c r="D62" t="str">
-        <v>1.05 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-08T07:07:23.072Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F62" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="63">
@@ -1650,13 +1651,13 @@
         <v>PASS</v>
       </c>
       <c r="D63" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-08T07:07:24.037Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F63" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="64">
@@ -1670,13 +1671,13 @@
         <v>PASS</v>
       </c>
       <c r="D64" t="str">
-        <v>1.10 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-08T07:07:25.137Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F64" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="65">
@@ -1690,13 +1691,13 @@
         <v>PASS</v>
       </c>
       <c r="D65" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-08T07:07:25.926Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F65" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="66">
@@ -1710,13 +1711,13 @@
         <v>PASS</v>
       </c>
       <c r="D66" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-08T07:07:26.772Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F66" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="67">
@@ -1730,13 +1731,13 @@
         <v>PASS</v>
       </c>
       <c r="D67" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-08T07:07:27.748Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F67" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="68">
@@ -1750,13 +1751,13 @@
         <v>PASS</v>
       </c>
       <c r="D68" t="str">
-        <v>0.87 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-08T07:07:28.622Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F68" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="69">
@@ -1770,13 +1771,13 @@
         <v>PASS</v>
       </c>
       <c r="D69" t="str">
-        <v>1.09 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-08T07:07:29.708Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F69" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="70">
@@ -1790,13 +1791,13 @@
         <v>PASS</v>
       </c>
       <c r="D70" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-08T07:07:30.543Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F70" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="71">
@@ -1810,13 +1811,13 @@
         <v>PASS</v>
       </c>
       <c r="D71" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-08T07:07:31.394Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F71" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="72">
@@ -1830,13 +1831,13 @@
         <v>PASS</v>
       </c>
       <c r="D72" t="str">
-        <v>0.75 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-08T07:07:32.141Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F72" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="73">
@@ -1850,13 +1851,13 @@
         <v>PASS</v>
       </c>
       <c r="D73" t="str">
-        <v>1.03 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-08T07:07:33.176Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F73" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="74">
@@ -1870,13 +1871,13 @@
         <v>PASS</v>
       </c>
       <c r="D74" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-08T07:07:33.993Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F74" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="75">
@@ -1890,13 +1891,13 @@
         <v>PASS</v>
       </c>
       <c r="D75" t="str">
-        <v>1.11 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-08T07:07:35.101Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F75" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="76">
@@ -1910,13 +1911,13 @@
         <v>PASS</v>
       </c>
       <c r="D76" t="str">
-        <v>0.99 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-08T07:07:36.089Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F76" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="77">
@@ -1930,13 +1931,13 @@
         <v>PASS</v>
       </c>
       <c r="D77" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-08T07:07:36.863Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F77" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="78">
@@ -1950,13 +1951,13 @@
         <v>PASS</v>
       </c>
       <c r="D78" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-08T07:07:37.692Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F78" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="79">
@@ -1970,13 +1971,13 @@
         <v>PASS</v>
       </c>
       <c r="D79" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-08T07:07:38.710Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F79" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="80">
@@ -1990,13 +1991,13 @@
         <v>PASS</v>
       </c>
       <c r="D80" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-08T07:07:39.614Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F80" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="81">
@@ -2010,13 +2011,13 @@
         <v>PASS</v>
       </c>
       <c r="D81" t="str">
-        <v>1.20 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-08T07:07:40.814Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F81" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="82">
@@ -2030,13 +2031,13 @@
         <v>PASS</v>
       </c>
       <c r="D82" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-08T07:07:41.791Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F82" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="83">
@@ -2050,13 +2051,13 @@
         <v>PASS</v>
       </c>
       <c r="D83" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-08T07:07:42.592Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F83" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="84">
@@ -2070,13 +2071,13 @@
         <v>PASS</v>
       </c>
       <c r="D84" t="str">
-        <v>0.75 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-08T07:07:43.345Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F84" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="85">
@@ -2090,13 +2091,13 @@
         <v>PASS</v>
       </c>
       <c r="D85" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-08T07:07:44.321Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F85" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="86">
@@ -2110,13 +2111,13 @@
         <v>PASS</v>
       </c>
       <c r="D86" t="str">
-        <v>1.08 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-08T07:07:45.404Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F86" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="87">
@@ -2130,13 +2131,13 @@
         <v>PASS</v>
       </c>
       <c r="D87" t="str">
-        <v>1.17 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-08T07:07:46.571Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F87" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="88">
@@ -2150,13 +2151,13 @@
         <v>PASS</v>
       </c>
       <c r="D88" t="str">
-        <v>1.04 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-08T07:07:47.616Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F88" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="89">
@@ -2170,13 +2171,13 @@
         <v>PASS</v>
       </c>
       <c r="D89" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-08T07:07:48.562Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F89" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="90">
@@ -2190,13 +2191,13 @@
         <v>PASS</v>
       </c>
       <c r="D90" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-08T07:07:49.387Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F90" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="91">
@@ -2210,13 +2211,13 @@
         <v>PASS</v>
       </c>
       <c r="D91" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-08T07:07:50.310Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F91" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="92">
@@ -2230,13 +2231,13 @@
         <v>PASS</v>
       </c>
       <c r="D92" t="str">
-        <v>1.07 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-08T07:07:51.381Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F92" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="93">
@@ -2250,13 +2251,13 @@
         <v>PASS</v>
       </c>
       <c r="D93" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-08T07:07:52.208Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F93" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="94">
@@ -2270,13 +2271,13 @@
         <v>PASS</v>
       </c>
       <c r="D94" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-08T07:07:53.158Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F94" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="95">
@@ -2290,13 +2291,13 @@
         <v>PASS</v>
       </c>
       <c r="D95" t="str">
-        <v>0.64 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-08T07:07:53.802Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F95" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="96">
@@ -2310,13 +2311,13 @@
         <v>PASS</v>
       </c>
       <c r="D96" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-08T07:07:54.597Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F96" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="97">
@@ -2330,13 +2331,13 @@
         <v>PASS</v>
       </c>
       <c r="D97" t="str">
-        <v>0.75 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-08T07:07:55.347Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F97" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="98">
@@ -2350,13 +2351,13 @@
         <v>PASS</v>
       </c>
       <c r="D98" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-08T07:07:56.200Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F98" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="99">
@@ -2370,13 +2371,13 @@
         <v>PASS</v>
       </c>
       <c r="D99" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-08T07:07:57.168Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F99" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="100">
@@ -2390,13 +2391,13 @@
         <v>PASS</v>
       </c>
       <c r="D100" t="str">
-        <v>0.89 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-08T07:07:58.059Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F100" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="101">
@@ -2410,13 +2411,13 @@
         <v>PASS</v>
       </c>
       <c r="D101" t="str">
-        <v>0.55 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-08T07:07:58.613Z</v>
+        <v>2026-08-09T18:19:32.870Z</v>
       </c>
       <c r="F101" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="102">
@@ -2430,13 +2431,13 @@
         <v>PASS</v>
       </c>
       <c r="D102" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-08T07:07:59.394Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F102" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="103">
@@ -2450,13 +2451,13 @@
         <v>PASS</v>
       </c>
       <c r="D103" t="str">
-        <v>0.74 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-08T07:08:00.135Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F103" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="104">
@@ -2470,13 +2471,13 @@
         <v>PASS</v>
       </c>
       <c r="D104" t="str">
-        <v>0.66 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-08T07:08:00.794Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F104" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="105">
@@ -2490,13 +2491,13 @@
         <v>PASS</v>
       </c>
       <c r="D105" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-08T07:08:01.577Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F105" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="106">
@@ -2510,13 +2511,13 @@
         <v>PASS</v>
       </c>
       <c r="D106" t="str">
-        <v>0.58 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-08T07:08:02.156Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F106" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="107">
@@ -2530,13 +2531,13 @@
         <v>PASS</v>
       </c>
       <c r="D107" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-08T07:08:02.949Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F107" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="108">
@@ -2550,13 +2551,13 @@
         <v>PASS</v>
       </c>
       <c r="D108" t="str">
-        <v>0.68 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-08T07:08:03.631Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F108" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="109">
@@ -2570,13 +2571,13 @@
         <v>PASS</v>
       </c>
       <c r="D109" t="str">
-        <v>1.07 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-08T07:08:04.705Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F109" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="110">
@@ -2590,13 +2591,13 @@
         <v>PASS</v>
       </c>
       <c r="D110" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-08T07:08:05.728Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F110" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="111">
@@ -2610,13 +2611,13 @@
         <v>PASS</v>
       </c>
       <c r="D111" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-08T07:08:06.686Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F111" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="112">
@@ -2630,13 +2631,13 @@
         <v>PASS</v>
       </c>
       <c r="D112" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-08T07:08:07.563Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F112" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="113">
@@ -2650,13 +2651,13 @@
         <v>PASS</v>
       </c>
       <c r="D113" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-08T07:08:08.380Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F113" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="114">
@@ -2670,13 +2671,13 @@
         <v>PASS</v>
       </c>
       <c r="D114" t="str">
-        <v>0.89 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-08T07:08:09.271Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F114" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="115">
@@ -2690,13 +2691,13 @@
         <v>PASS</v>
       </c>
       <c r="D115" t="str">
-        <v>1.18 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-08T07:08:10.449Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F115" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="116">
@@ -2710,13 +2711,13 @@
         <v>PASS</v>
       </c>
       <c r="D116" t="str">
-        <v>0.74 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-08T07:08:11.190Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F116" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="117">
@@ -2730,13 +2731,13 @@
         <v>PASS</v>
       </c>
       <c r="D117" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-08T07:08:12.128Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F117" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="118">
@@ -2750,13 +2751,13 @@
         <v>PASS</v>
       </c>
       <c r="D118" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-08T07:08:12.958Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F118" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="119">
@@ -2770,13 +2771,13 @@
         <v>PASS</v>
       </c>
       <c r="D119" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-08T07:08:13.762Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F119" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="120">
@@ -2790,13 +2791,13 @@
         <v>PASS</v>
       </c>
       <c r="D120" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-08T07:08:14.642Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F120" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="121">
@@ -2810,13 +2811,13 @@
         <v>PASS</v>
       </c>
       <c r="D121" t="str">
-        <v>1.21 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-08T07:08:15.853Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F121" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="122">
@@ -2830,13 +2831,13 @@
         <v>PASS</v>
       </c>
       <c r="D122" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-08T07:08:16.826Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F122" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="123">
@@ -2850,13 +2851,13 @@
         <v>PASS</v>
       </c>
       <c r="D123" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-08T07:08:17.759Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F123" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="124">
@@ -2870,13 +2871,13 @@
         <v>PASS</v>
       </c>
       <c r="D124" t="str">
-        <v>1.06 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-08T07:08:18.818Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F124" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="125">
@@ -2890,13 +2891,13 @@
         <v>PASS</v>
       </c>
       <c r="D125" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-08T07:08:19.839Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F125" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="126">
@@ -2910,13 +2911,13 @@
         <v>PASS</v>
       </c>
       <c r="D126" t="str">
-        <v>0.70 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-08T07:08:20.535Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F126" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="127">
@@ -2930,13 +2931,13 @@
         <v>PASS</v>
       </c>
       <c r="D127" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-08T07:08:21.487Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F127" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="128">
@@ -2950,13 +2951,13 @@
         <v>PASS</v>
       </c>
       <c r="D128" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-08T07:08:22.446Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F128" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="129">
@@ -2970,13 +2971,13 @@
         <v>PASS</v>
       </c>
       <c r="D129" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-08T07:08:23.376Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F129" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="130">
@@ -2990,13 +2991,13 @@
         <v>PASS</v>
       </c>
       <c r="D130" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-08T07:08:24.204Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F130" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="131">
@@ -3010,13 +3011,13 @@
         <v>PASS</v>
       </c>
       <c r="D131" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-08T07:08:25.152Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F131" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="132">
@@ -3030,13 +3031,13 @@
         <v>PASS</v>
       </c>
       <c r="D132" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-08T07:08:26.104Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F132" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="133">
@@ -3050,13 +3051,13 @@
         <v>PASS</v>
       </c>
       <c r="D133" t="str">
-        <v>1.05 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-08T07:08:27.152Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F133" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="134">
@@ -3070,13 +3071,13 @@
         <v>PASS</v>
       </c>
       <c r="D134" t="str">
-        <v>0.87 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-08T07:08:28.022Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F134" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="135">
@@ -3090,13 +3091,13 @@
         <v>PASS</v>
       </c>
       <c r="D135" t="str">
-        <v>1.13 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-08T07:08:29.149Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F135" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="136">
@@ -3110,13 +3111,13 @@
         <v>PASS</v>
       </c>
       <c r="D136" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-08T07:08:29.989Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F136" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="137">
@@ -3130,13 +3131,13 @@
         <v>PASS</v>
       </c>
       <c r="D137" t="str">
-        <v>0.81 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-08T07:08:30.794Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F137" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="138">
@@ -3150,13 +3151,13 @@
         <v>PASS</v>
       </c>
       <c r="D138" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-08T07:08:31.656Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F138" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="139">
@@ -3170,13 +3171,13 @@
         <v>PASS</v>
       </c>
       <c r="D139" t="str">
-        <v>1.28 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-08T07:08:32.937Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F139" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="140">
@@ -3190,13 +3191,13 @@
         <v>PASS</v>
       </c>
       <c r="D140" t="str">
-        <v>1.03 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-08T07:08:33.969Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F140" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="141">
@@ -3210,13 +3211,13 @@
         <v>PASS</v>
       </c>
       <c r="D141" t="str">
-        <v>1.12 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-08T07:08:35.091Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F141" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="142">
@@ -3230,13 +3231,13 @@
         <v>PASS</v>
       </c>
       <c r="D142" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-08T07:08:36.108Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F142" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="143">
@@ -3250,13 +3251,13 @@
         <v>PASS</v>
       </c>
       <c r="D143" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-08T07:08:37.104Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F143" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="144">
@@ -3270,13 +3271,13 @@
         <v>PASS</v>
       </c>
       <c r="D144" t="str">
-        <v>1.06 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-08T07:08:38.164Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F144" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="145">
@@ -3290,13 +3291,13 @@
         <v>PASS</v>
       </c>
       <c r="D145" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-08T07:08:39.188Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F145" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="146">
@@ -3310,13 +3311,13 @@
         <v>PASS</v>
       </c>
       <c r="D146" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-08T07:08:40.130Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F146" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="147">
@@ -3330,13 +3331,13 @@
         <v>PASS</v>
       </c>
       <c r="D147" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-08T07:08:41.112Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F147" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="148">
@@ -3350,13 +3351,13 @@
         <v>PASS</v>
       </c>
       <c r="D148" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-08T07:08:41.965Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F148" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="149">
@@ -3370,13 +3371,13 @@
         <v>PASS</v>
       </c>
       <c r="D149" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-08T07:08:42.791Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F149" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="150">
@@ -3390,13 +3391,13 @@
         <v>PASS</v>
       </c>
       <c r="D150" t="str">
-        <v>1.04 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-08T07:08:43.834Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F150" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="151">
@@ -3410,13 +3411,13 @@
         <v>PASS</v>
       </c>
       <c r="D151" t="str">
-        <v>1.28 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-08T07:08:45.114Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F151" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="152">
@@ -3430,13 +3431,13 @@
         <v>PASS</v>
       </c>
       <c r="D152" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-08T07:08:46.050Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F152" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="153">
@@ -3450,13 +3451,13 @@
         <v>PASS</v>
       </c>
       <c r="D153" t="str">
-        <v>1.13 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-08T07:08:47.181Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F153" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="154">
@@ -3470,13 +3471,13 @@
         <v>PASS</v>
       </c>
       <c r="D154" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-08T07:08:48.197Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F154" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="155">
@@ -3490,13 +3491,13 @@
         <v>PASS</v>
       </c>
       <c r="D155" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-08T07:08:49.058Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F155" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="156">
@@ -3510,13 +3511,13 @@
         <v>PASS</v>
       </c>
       <c r="D156" t="str">
-        <v>1.03 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-08T07:08:50.092Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F156" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="157">
@@ -3530,13 +3531,13 @@
         <v>PASS</v>
       </c>
       <c r="D157" t="str">
-        <v>1.10 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-08T07:08:51.190Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F157" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="158">
@@ -3550,13 +3551,13 @@
         <v>PASS</v>
       </c>
       <c r="D158" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-08T07:08:51.993Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F158" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="159">
@@ -3570,13 +3571,13 @@
         <v>PASS</v>
       </c>
       <c r="D159" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-08T07:08:52.967Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F159" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="160">
@@ -3590,13 +3591,13 @@
         <v>PASS</v>
       </c>
       <c r="D160" t="str">
-        <v>1.13 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-08T07:08:54.099Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F160" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="161">
@@ -3610,13 +3611,13 @@
         <v>PASS</v>
       </c>
       <c r="D161" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-08T07:08:55.055Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F161" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="162">
@@ -3630,13 +3631,13 @@
         <v>PASS</v>
       </c>
       <c r="D162" t="str">
-        <v>1.12 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-08T07:08:56.174Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F162" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="163">
@@ -3650,13 +3651,13 @@
         <v>PASS</v>
       </c>
       <c r="D163" t="str">
-        <v>0.81 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-08T07:08:56.980Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F163" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="164">
@@ -3670,13 +3671,13 @@
         <v>PASS</v>
       </c>
       <c r="D164" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-08T07:08:57.995Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F164" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="165">
@@ -3690,13 +3691,13 @@
         <v>PASS</v>
       </c>
       <c r="D165" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-08T07:08:58.934Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F165" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="166">
@@ -3710,13 +3711,13 @@
         <v>PASS</v>
       </c>
       <c r="D166" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-08T07:08:59.908Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F166" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="167">
@@ -3730,13 +3731,13 @@
         <v>PASS</v>
       </c>
       <c r="D167" t="str">
-        <v>1.10 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-08T07:09:01.006Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F167" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="168">
@@ -3750,13 +3751,13 @@
         <v>PASS</v>
       </c>
       <c r="D168" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-08T07:09:01.883Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F168" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="169">
@@ -3770,13 +3771,13 @@
         <v>PASS</v>
       </c>
       <c r="D169" t="str">
-        <v>1.29 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-08T07:09:03.174Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F169" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="170">
@@ -3790,13 +3791,13 @@
         <v>PASS</v>
       </c>
       <c r="D170" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-08T07:09:04.057Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F170" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="171">
@@ -3810,13 +3811,13 @@
         <v>PASS</v>
       </c>
       <c r="D171" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-08T07:09:05.000Z</v>
+        <v>2026-08-09T18:19:32.871Z</v>
       </c>
       <c r="F171" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="172">
@@ -3830,13 +3831,13 @@
         <v>PASS</v>
       </c>
       <c r="D172" t="str">
-        <v>0.99 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-08T07:09:05.994Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F172" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="173">
@@ -3850,13 +3851,13 @@
         <v>PASS</v>
       </c>
       <c r="D173" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-08T07:09:06.853Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F173" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="174">
@@ -3870,13 +3871,13 @@
         <v>PASS</v>
       </c>
       <c r="D174" t="str">
-        <v>0.73 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-08T07:09:07.584Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F174" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="175">
@@ -3890,13 +3891,13 @@
         <v>PASS</v>
       </c>
       <c r="D175" t="str">
-        <v>0.99 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-08T07:09:08.575Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F175" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="176">
@@ -3910,13 +3911,13 @@
         <v>PASS</v>
       </c>
       <c r="D176" t="str">
-        <v>1.27 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-08T07:09:09.841Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F176" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="177">
@@ -3930,13 +3931,13 @@
         <v>PASS</v>
       </c>
       <c r="D177" t="str">
-        <v>0.91 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-08T07:09:10.755Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F177" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="178">
@@ -3950,13 +3951,13 @@
         <v>PASS</v>
       </c>
       <c r="D178" t="str">
-        <v>0.74 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-08T07:09:11.491Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F178" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="179">
@@ -3970,13 +3971,13 @@
         <v>PASS</v>
       </c>
       <c r="D179" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-08T07:09:12.446Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F179" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="180">
@@ -3990,13 +3991,13 @@
         <v>PASS</v>
       </c>
       <c r="D180" t="str">
-        <v>1.31 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-08T07:09:13.756Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F180" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="181">
@@ -4010,13 +4011,13 @@
         <v>PASS</v>
       </c>
       <c r="D181" t="str">
-        <v>1.55 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-08T07:09:15.306Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F181" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="182">
@@ -4030,13 +4031,13 @@
         <v>PASS</v>
       </c>
       <c r="D182" t="str">
-        <v>1.19 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-08T07:09:16.494Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F182" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="183">
@@ -4050,13 +4051,13 @@
         <v>PASS</v>
       </c>
       <c r="D183" t="str">
-        <v>2.20 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-08T07:09:18.692Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F183" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="184">
@@ -4070,13 +4071,13 @@
         <v>PASS</v>
       </c>
       <c r="D184" t="str">
-        <v>1.34 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-08T07:09:20.037Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F184" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="185">
@@ -4090,13 +4091,13 @@
         <v>PASS</v>
       </c>
       <c r="D185" t="str">
-        <v>1.31 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-08T07:09:21.346Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F185" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="186">
@@ -4110,13 +4111,13 @@
         <v>PASS</v>
       </c>
       <c r="D186" t="str">
-        <v>2.18 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-08T07:09:23.527Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F186" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="187">
@@ -4130,13 +4131,13 @@
         <v>PASS</v>
       </c>
       <c r="D187" t="str">
-        <v>1.66 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-08T07:09:25.183Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F187" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="188">
@@ -4150,13 +4151,13 @@
         <v>PASS</v>
       </c>
       <c r="D188" t="str">
-        <v>1.16 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-08T07:09:26.344Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F188" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="189">
@@ -4170,13 +4171,13 @@
         <v>PASS</v>
       </c>
       <c r="D189" t="str">
-        <v>1.17 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-08T07:09:27.516Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F189" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="190">
@@ -4190,13 +4191,13 @@
         <v>PASS</v>
       </c>
       <c r="D190" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-08T07:09:28.523Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F190" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="191">
@@ -4210,13 +4211,13 @@
         <v>PASS</v>
       </c>
       <c r="D191" t="str">
-        <v>1.28 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-08T07:09:29.807Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F191" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="192">
@@ -4230,13 +4231,13 @@
         <v>PASS</v>
       </c>
       <c r="D192" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-08T07:09:30.735Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F192" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="193">
@@ -4250,13 +4251,13 @@
         <v>PASS</v>
       </c>
       <c r="D193" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-08T07:09:31.508Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F193" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="194">
@@ -4270,13 +4271,13 @@
         <v>PASS</v>
       </c>
       <c r="D194" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-08T07:09:32.312Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F194" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="195">
@@ -4290,13 +4291,13 @@
         <v>PASS</v>
       </c>
       <c r="D195" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-08T07:09:33.157Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F195" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="196">
@@ -4310,13 +4311,13 @@
         <v>PASS</v>
       </c>
       <c r="D196" t="str">
-        <v>0.72 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-08T07:09:33.873Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F196" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="197">
@@ -4330,13 +4331,13 @@
         <v>PASS</v>
       </c>
       <c r="D197" t="str">
-        <v>0.69 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-08T07:09:34.559Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F197" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="198">
@@ -4350,13 +4351,13 @@
         <v>PASS</v>
       </c>
       <c r="D198" t="str">
-        <v>0.70 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-08T07:09:35.256Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F198" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="199">
@@ -4370,13 +4371,13 @@
         <v>PASS</v>
       </c>
       <c r="D199" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-08T07:09:36.093Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F199" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="200">
@@ -4390,13 +4391,13 @@
         <v>PASS</v>
       </c>
       <c r="D200" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-08T07:09:36.867Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F200" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="201">
@@ -4410,13 +4411,13 @@
         <v>PASS</v>
       </c>
       <c r="D201" t="str">
-        <v>1.04 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-08T07:09:37.904Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F201" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="202">
@@ -4430,13 +4431,13 @@
         <v>PASS</v>
       </c>
       <c r="D202" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-08T07:09:38.914Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F202" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="203">
@@ -4450,13 +4451,13 @@
         <v>PASS</v>
       </c>
       <c r="D203" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-08T07:09:39.735Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F203" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="204">
@@ -4470,13 +4471,13 @@
         <v>PASS</v>
       </c>
       <c r="D204" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-08T07:09:40.505Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F204" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="205">
@@ -4490,13 +4491,13 @@
         <v>PASS</v>
       </c>
       <c r="D205" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-08T07:09:41.472Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F205" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="206">
@@ -4510,13 +4511,13 @@
         <v>PASS</v>
       </c>
       <c r="D206" t="str">
-        <v>1.19 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-08T07:09:42.667Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F206" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="207">
@@ -4530,13 +4531,13 @@
         <v>PASS</v>
       </c>
       <c r="D207" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-08T07:09:43.682Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F207" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="208">
@@ -4550,13 +4551,13 @@
         <v>PASS</v>
       </c>
       <c r="D208" t="str">
-        <v>0.72 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-08T07:09:44.407Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F208" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="209">
@@ -4570,13 +4571,13 @@
         <v>PASS</v>
       </c>
       <c r="D209" t="str">
-        <v>0.75 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-08T07:09:45.154Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F209" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="210">
@@ -4590,13 +4591,13 @@
         <v>PASS</v>
       </c>
       <c r="D210" t="str">
-        <v>1.07 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-08T07:09:46.227Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F210" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="211">
@@ -4610,13 +4611,13 @@
         <v>PASS</v>
       </c>
       <c r="D211" t="str">
-        <v>1.19 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-08T07:09:47.415Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F211" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="212">
@@ -4630,13 +4631,13 @@
         <v>PASS</v>
       </c>
       <c r="D212" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-08T07:09:48.391Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F212" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="213">
@@ -4650,13 +4651,13 @@
         <v>PASS</v>
       </c>
       <c r="D213" t="str">
-        <v>1.04 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-08T07:09:49.432Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F213" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="214">
@@ -4670,13 +4671,13 @@
         <v>PASS</v>
       </c>
       <c r="D214" t="str">
-        <v>1.15 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-08T07:09:50.579Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F214" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="215">
@@ -4690,13 +4691,13 @@
         <v>PASS</v>
       </c>
       <c r="D215" t="str">
-        <v>1.10 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-08T07:09:51.675Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F215" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="216">
@@ -4710,13 +4711,13 @@
         <v>PASS</v>
       </c>
       <c r="D216" t="str">
-        <v>0.69 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-08T07:09:52.362Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F216" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="217">
@@ -4730,13 +4731,13 @@
         <v>PASS</v>
       </c>
       <c r="D217" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-08T07:09:53.138Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F217" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="218">
@@ -4750,13 +4751,13 @@
         <v>PASS</v>
       </c>
       <c r="D218" t="str">
-        <v>0.71 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-08T07:09:53.845Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F218" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="219">
@@ -4770,13 +4771,13 @@
         <v>PASS</v>
       </c>
       <c r="D219" t="str">
-        <v>1.21 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-08T07:09:55.051Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F219" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="220">
@@ -4790,13 +4791,13 @@
         <v>PASS</v>
       </c>
       <c r="D220" t="str">
-        <v>1.07 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-08T07:09:56.123Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F220" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="221">
@@ -4810,13 +4811,13 @@
         <v>PASS</v>
       </c>
       <c r="D221" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-08T07:09:57.018Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F221" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="222">
@@ -4830,13 +4831,13 @@
         <v>PASS</v>
       </c>
       <c r="D222" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-08T07:09:57.985Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F222" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="223">
@@ -4850,13 +4851,13 @@
         <v>PASS</v>
       </c>
       <c r="D223" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-08T07:09:58.996Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F223" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="224">
@@ -4870,13 +4871,13 @@
         <v>PASS</v>
       </c>
       <c r="D224" t="str">
-        <v>1.30 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-08T07:10:00.296Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F224" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="225">
@@ -4890,13 +4891,13 @@
         <v>PASS</v>
       </c>
       <c r="D225" t="str">
-        <v>1.06 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-08T07:10:01.360Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F225" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="226">
@@ -4910,13 +4911,13 @@
         <v>PASS</v>
       </c>
       <c r="D226" t="str">
-        <v>0.87 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-08T07:10:02.233Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F226" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="227">
@@ -4930,13 +4931,13 @@
         <v>PASS</v>
       </c>
       <c r="D227" t="str">
-        <v>0.91 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-08T07:10:03.139Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F227" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="228">
@@ -4950,13 +4951,13 @@
         <v>PASS</v>
       </c>
       <c r="D228" t="str">
-        <v>0.67 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-08T07:10:03.810Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F228" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="229">
@@ -4970,13 +4971,13 @@
         <v>PASS</v>
       </c>
       <c r="D229" t="str">
-        <v>1.18 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-08T07:10:04.990Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F229" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="230">
@@ -4990,13 +4991,13 @@
         <v>PASS</v>
       </c>
       <c r="D230" t="str">
-        <v>1.27 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-08T07:10:06.262Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F230" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="231">
@@ -5010,13 +5011,13 @@
         <v>PASS</v>
       </c>
       <c r="D231" t="str">
-        <v>1.16 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-08T07:10:07.424Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F231" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="232">
@@ -5030,13 +5031,13 @@
         <v>PASS</v>
       </c>
       <c r="D232" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-08T07:10:08.447Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F232" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="233">
@@ -5050,13 +5051,13 @@
         <v>PASS</v>
       </c>
       <c r="D233" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-08T07:10:09.228Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F233" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="234">
@@ -5070,13 +5071,13 @@
         <v>PASS</v>
       </c>
       <c r="D234" t="str">
-        <v>0.81 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-08T07:10:10.039Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F234" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="235">
@@ -5090,13 +5091,13 @@
         <v>PASS</v>
       </c>
       <c r="D235" t="str">
-        <v>1.05 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-08T07:10:11.085Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F235" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="236">
@@ -5110,13 +5111,13 @@
         <v>PASS</v>
       </c>
       <c r="D236" t="str">
-        <v>0.99 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-08T07:10:12.078Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F236" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="237">
@@ -5130,13 +5131,13 @@
         <v>PASS</v>
       </c>
       <c r="D237" t="str">
-        <v>1.10 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-08T07:10:13.183Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F237" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="238">
@@ -5150,13 +5151,13 @@
         <v>PASS</v>
       </c>
       <c r="D238" t="str">
-        <v>0.76 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-08T07:10:13.943Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F238" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="239">
@@ -5170,13 +5171,13 @@
         <v>PASS</v>
       </c>
       <c r="D239" t="str">
-        <v>0.67 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-08T07:10:14.611Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F239" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="240">
@@ -5190,13 +5191,13 @@
         <v>PASS</v>
       </c>
       <c r="D240" t="str">
-        <v>0.67 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-08T07:10:15.279Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F240" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="241">
@@ -5210,13 +5211,13 @@
         <v>PASS</v>
       </c>
       <c r="D241" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-08T07:10:16.238Z</v>
+        <v>2026-08-09T18:19:32.872Z</v>
       </c>
       <c r="F241" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="242">
@@ -5230,13 +5231,13 @@
         <v>PASS</v>
       </c>
       <c r="D242" t="str">
-        <v>0.71 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-08T07:10:16.950Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F242" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="243">
@@ -5250,13 +5251,13 @@
         <v>PASS</v>
       </c>
       <c r="D243" t="str">
-        <v>1.07 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-08T07:10:18.021Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F243" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="244">
@@ -5270,13 +5271,13 @@
         <v>PASS</v>
       </c>
       <c r="D244" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-08T07:10:18.807Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F244" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="245">
@@ -5290,13 +5291,13 @@
         <v>PASS</v>
       </c>
       <c r="D245" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-08T07:10:19.611Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F245" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="246">
@@ -5310,13 +5311,13 @@
         <v>PASS</v>
       </c>
       <c r="D246" t="str">
-        <v>0.76 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-08T07:10:20.366Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F246" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="247">
@@ -5330,13 +5331,13 @@
         <v>PASS</v>
       </c>
       <c r="D247" t="str">
-        <v>1.21 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-08T07:10:21.580Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F247" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="248">
@@ -5350,13 +5351,13 @@
         <v>PASS</v>
       </c>
       <c r="D248" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-08T07:10:22.405Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F248" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="249">
@@ -5370,13 +5371,13 @@
         <v>PASS</v>
       </c>
       <c r="D249" t="str">
-        <v>1.11 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-08T07:10:23.520Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F249" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="250">
@@ -5390,13 +5391,13 @@
         <v>PASS</v>
       </c>
       <c r="D250" t="str">
-        <v>1.08 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-08T07:10:24.598Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F250" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="251">
@@ -5410,13 +5411,13 @@
         <v>PASS</v>
       </c>
       <c r="D251" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-08T07:10:25.377Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F251" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="252">
@@ -5430,13 +5431,13 @@
         <v>PASS</v>
       </c>
       <c r="D252" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-08T07:10:26.202Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F252" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="253">
@@ -5450,13 +5451,13 @@
         <v>PASS</v>
       </c>
       <c r="D253" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-08T07:10:27.118Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F253" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="254">
@@ -5470,13 +5471,13 @@
         <v>PASS</v>
       </c>
       <c r="D254" t="str">
-        <v>1.19 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-08T07:10:28.309Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F254" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="255">
@@ -5490,13 +5491,13 @@
         <v>PASS</v>
       </c>
       <c r="D255" t="str">
-        <v>1.14 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-08T07:10:29.444Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F255" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="256">
@@ -5510,13 +5511,13 @@
         <v>PASS</v>
       </c>
       <c r="D256" t="str">
-        <v>1.11 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-08T07:10:30.552Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F256" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="257">
@@ -5530,13 +5531,13 @@
         <v>PASS</v>
       </c>
       <c r="D257" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-08T07:10:31.356Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F257" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="258">
@@ -5550,13 +5551,13 @@
         <v>PASS</v>
       </c>
       <c r="D258" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-08T07:10:32.195Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F258" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="259">
@@ -5570,13 +5571,13 @@
         <v>PASS</v>
       </c>
       <c r="D259" t="str">
-        <v>1.17 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-08T07:10:33.365Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F259" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="260">
@@ -5590,13 +5591,13 @@
         <v>PASS</v>
       </c>
       <c r="D260" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-08T07:10:34.307Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F260" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="261">
@@ -5610,13 +5611,13 @@
         <v>PASS</v>
       </c>
       <c r="D261" t="str">
-        <v>1.12 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-08T07:10:35.427Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F261" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="262">
@@ -5630,13 +5631,13 @@
         <v>PASS</v>
       </c>
       <c r="D262" t="str">
-        <v>1.09 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-08T07:10:36.522Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F262" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="263">
@@ -5650,13 +5651,13 @@
         <v>PASS</v>
       </c>
       <c r="D263" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-08T07:10:37.338Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F263" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="264">
@@ -5670,13 +5671,13 @@
         <v>PASS</v>
       </c>
       <c r="D264" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-08T07:10:38.142Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F264" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="265">
@@ -5690,13 +5691,13 @@
         <v>PASS</v>
       </c>
       <c r="D265" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-08T07:10:39.100Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F265" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="266">
@@ -5710,13 +5711,13 @@
         <v>PASS</v>
       </c>
       <c r="D266" t="str">
-        <v>1.08 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-08T07:10:40.184Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F266" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="267">
@@ -5730,13 +5731,13 @@
         <v>PASS</v>
       </c>
       <c r="D267" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-08T07:10:41.112Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F267" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="268">
@@ -5750,13 +5751,13 @@
         <v>PASS</v>
       </c>
       <c r="D268" t="str">
-        <v>1.12 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-08T07:10:42.234Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F268" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="269">
@@ -5770,13 +5771,13 @@
         <v>PASS</v>
       </c>
       <c r="D269" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-08T07:10:43.081Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F269" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="270">
@@ -5790,13 +5791,13 @@
         <v>PASS</v>
       </c>
       <c r="D270" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-08T07:10:43.964Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F270" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="271">
@@ -5810,13 +5811,13 @@
         <v>PASS</v>
       </c>
       <c r="D271" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-08T07:10:44.936Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F271" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="272">
@@ -5830,13 +5831,13 @@
         <v>PASS</v>
       </c>
       <c r="D272" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-08T07:10:45.862Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F272" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="273">
@@ -5850,13 +5851,13 @@
         <v>PASS</v>
       </c>
       <c r="D273" t="str">
-        <v>1.20 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-08T07:10:47.063Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F273" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="274">
@@ -5870,13 +5871,13 @@
         <v>PASS</v>
       </c>
       <c r="D274" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-08T07:10:47.914Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F274" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="275">
@@ -5890,13 +5891,13 @@
         <v>PASS</v>
       </c>
       <c r="D275" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-08T07:10:48.700Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F275" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="276">
@@ -5910,13 +5911,13 @@
         <v>PASS</v>
       </c>
       <c r="D276" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-08T07:10:49.492Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F276" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="277">
@@ -5930,13 +5931,13 @@
         <v>PASS</v>
       </c>
       <c r="D277" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-08T07:10:50.463Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F277" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="278">
@@ -5950,13 +5951,13 @@
         <v>PASS</v>
       </c>
       <c r="D278" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-08T07:10:51.324Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F278" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="279">
@@ -5970,13 +5971,13 @@
         <v>PASS</v>
       </c>
       <c r="D279" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-08T07:10:52.298Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F279" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="280">
@@ -5990,13 +5991,13 @@
         <v>PASS</v>
       </c>
       <c r="D280" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-08T07:10:53.158Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F280" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="281">
@@ -6010,13 +6011,13 @@
         <v>PASS</v>
       </c>
       <c r="D281" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-08T07:10:54.018Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F281" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="282">
@@ -6030,13 +6031,13 @@
         <v>PASS</v>
       </c>
       <c r="D282" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-08T07:10:54.793Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F282" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="283">
@@ -6050,13 +6051,13 @@
         <v>PASS</v>
       </c>
       <c r="D283" t="str">
-        <v>0.99 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-08T07:10:55.784Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F283" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="284">
@@ -6070,13 +6071,13 @@
         <v>PASS</v>
       </c>
       <c r="D284" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-08T07:10:56.644Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F284" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="285">
@@ -6090,13 +6091,13 @@
         <v>PASS</v>
       </c>
       <c r="D285" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-08T07:10:57.602Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F285" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="286">
@@ -6110,13 +6111,13 @@
         <v>PASS</v>
       </c>
       <c r="D286" t="str">
-        <v>1.08 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-08T07:10:58.684Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F286" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="287">
@@ -6130,13 +6131,13 @@
         <v>PASS</v>
       </c>
       <c r="D287" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-08T07:10:59.546Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F287" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="288">
@@ -6150,13 +6151,13 @@
         <v>PASS</v>
       </c>
       <c r="D288" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-08T07:11:00.337Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F288" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="289">
@@ -6170,13 +6171,13 @@
         <v>PASS</v>
       </c>
       <c r="D289" t="str">
-        <v>1.21 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-08T07:11:01.547Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F289" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="290">
@@ -6190,13 +6191,13 @@
         <v>PASS</v>
       </c>
       <c r="D290" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-08T07:11:02.481Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F290" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="291">
@@ -6210,13 +6211,13 @@
         <v>PASS</v>
       </c>
       <c r="D291" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-08T07:11:03.409Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F291" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="292">
@@ -6230,13 +6231,13 @@
         <v>PASS</v>
       </c>
       <c r="D292" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-08T07:11:04.339Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F292" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="293">
@@ -6250,13 +6251,13 @@
         <v>PASS</v>
       </c>
       <c r="D293" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-08T07:11:05.160Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F293" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="294">
@@ -6270,13 +6271,13 @@
         <v>PASS</v>
       </c>
       <c r="D294" t="str">
-        <v>0.76 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-08T07:11:05.918Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F294" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="295">
@@ -6290,13 +6291,13 @@
         <v>PASS</v>
       </c>
       <c r="D295" t="str">
-        <v>1.06 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-08T07:11:06.976Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F295" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="296">
@@ -6310,13 +6311,13 @@
         <v>PASS</v>
       </c>
       <c r="D296" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-08T07:11:07.981Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F296" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="297">
@@ -6330,13 +6331,13 @@
         <v>PASS</v>
       </c>
       <c r="D297" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-08T07:11:08.919Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F297" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="298">
@@ -6350,13 +6351,13 @@
         <v>PASS</v>
       </c>
       <c r="D298" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-08T07:11:09.752Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F298" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="299">
@@ -6370,13 +6371,13 @@
         <v>PASS</v>
       </c>
       <c r="D299" t="str">
-        <v>0.76 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-08T07:11:10.510Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F299" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="300">
@@ -6390,13 +6391,13 @@
         <v>PASS</v>
       </c>
       <c r="D300" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-08T07:11:11.282Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F300" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="301">
@@ -6410,13 +6411,13 @@
         <v>PASS</v>
       </c>
       <c r="D301" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-08T07:11:12.215Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F301" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="302">
@@ -6430,13 +6431,13 @@
         <v>PASS</v>
       </c>
       <c r="D302" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-08T07:11:13.041Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F302" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="303">
@@ -6450,13 +6451,13 @@
         <v>PASS</v>
       </c>
       <c r="D303" t="str">
-        <v>1.11 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-08T07:11:14.152Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F303" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="304">
@@ -6470,13 +6471,13 @@
         <v>PASS</v>
       </c>
       <c r="D304" t="str">
-        <v>0.89 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-08T07:11:15.043Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F304" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="305">
@@ -6490,13 +6491,13 @@
         <v>PASS</v>
       </c>
       <c r="D305" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-08T07:11:16.023Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F305" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="306">
@@ -6510,13 +6511,13 @@
         <v>PASS</v>
       </c>
       <c r="D306" t="str">
-        <v>0.76 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-08T07:11:16.781Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F306" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="307">
@@ -6530,13 +6531,13 @@
         <v>PASS</v>
       </c>
       <c r="D307" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-08T07:11:17.784Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F307" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="308">
@@ -6550,13 +6551,13 @@
         <v>PASS</v>
       </c>
       <c r="D308" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-08T07:11:18.700Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F308" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="309">
@@ -6570,13 +6571,13 @@
         <v>PASS</v>
       </c>
       <c r="D309" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-08T07:11:19.623Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F309" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="310">
@@ -6590,13 +6591,13 @@
         <v>PASS</v>
       </c>
       <c r="D310" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-08T07:11:20.580Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F310" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="311">
@@ -6610,13 +6611,13 @@
         <v>PASS</v>
       </c>
       <c r="D311" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-08T07:11:21.433Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F311" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="312">
@@ -6630,13 +6631,13 @@
         <v>PASS</v>
       </c>
       <c r="D312" t="str">
-        <v>0.87 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-08T07:11:22.299Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F312" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="313">
@@ -6650,13 +6651,13 @@
         <v>PASS</v>
       </c>
       <c r="D313" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-08T07:11:23.253Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F313" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="314">
@@ -6670,13 +6671,13 @@
         <v>PASS</v>
       </c>
       <c r="D314" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-08T07:11:24.169Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F314" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="315">
@@ -6690,13 +6691,13 @@
         <v>PASS</v>
       </c>
       <c r="D315" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-08T07:11:25.130Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F315" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="316">
@@ -6710,13 +6711,13 @@
         <v>PASS</v>
       </c>
       <c r="D316" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-08T07:11:25.993Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F316" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="317">
@@ -6730,13 +6731,13 @@
         <v>PASS</v>
       </c>
       <c r="D317" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-08T07:11:26.761Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F317" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="318">
@@ -6750,13 +6751,13 @@
         <v>PASS</v>
       </c>
       <c r="D318" t="str">
-        <v>0.72 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-08T07:11:27.483Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F318" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="319">
@@ -6770,13 +6771,13 @@
         <v>PASS</v>
       </c>
       <c r="D319" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-08T07:11:28.484Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F319" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="320">
@@ -6790,13 +6791,13 @@
         <v>PASS</v>
       </c>
       <c r="D320" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-08T07:11:29.399Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F320" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="321">
@@ -6810,13 +6811,13 @@
         <v>PASS</v>
       </c>
       <c r="D321" t="str">
-        <v>0.92 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-08T07:11:30.319Z</v>
+        <v>2026-08-09T18:19:32.873Z</v>
       </c>
       <c r="F321" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="322">
@@ -6830,13 +6831,13 @@
         <v>PASS</v>
       </c>
       <c r="D322" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-08T07:11:31.221Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F322" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="323">
@@ -6850,13 +6851,13 @@
         <v>PASS</v>
       </c>
       <c r="D323" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-08T07:11:31.998Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F323" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="324">
@@ -6870,13 +6871,13 @@
         <v>PASS</v>
       </c>
       <c r="D324" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-08T07:11:32.768Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F324" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="325">
@@ -6890,13 +6891,13 @@
         <v>PASS</v>
       </c>
       <c r="D325" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-08T07:11:33.735Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F325" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="326">
@@ -6910,13 +6911,13 @@
         <v>PASS</v>
       </c>
       <c r="D326" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-08T07:11:34.632Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F326" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="327">
@@ -6930,13 +6931,13 @@
         <v>PASS</v>
       </c>
       <c r="D327" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-08T07:11:35.571Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F327" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="328">
@@ -6950,13 +6951,13 @@
         <v>PASS</v>
       </c>
       <c r="D328" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-08T07:11:36.451Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F328" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="329">
@@ -6970,13 +6971,13 @@
         <v>PASS</v>
       </c>
       <c r="D329" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-08T07:11:37.255Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F329" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="330">
@@ -6990,13 +6991,13 @@
         <v>PASS</v>
       </c>
       <c r="D330" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-08T07:11:38.097Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F330" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="331">
@@ -7010,13 +7011,13 @@
         <v>PASS</v>
       </c>
       <c r="D331" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-08T07:11:39.102Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F331" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="332">
@@ -7030,13 +7031,13 @@
         <v>PASS</v>
       </c>
       <c r="D332" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-08T07:11:40.066Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F332" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="333">
@@ -7050,13 +7051,13 @@
         <v>PASS</v>
       </c>
       <c r="D333" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-08T07:11:41.045Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F333" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="334">
@@ -7070,13 +7071,13 @@
         <v>PASS</v>
       </c>
       <c r="D334" t="str">
-        <v>0.91 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-08T07:11:41.956Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F334" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="335">
@@ -7090,13 +7091,13 @@
         <v>PASS</v>
       </c>
       <c r="D335" t="str">
-        <v>0.81 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-08T07:11:42.769Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F335" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="336">
@@ -7110,13 +7111,13 @@
         <v>PASS</v>
       </c>
       <c r="D336" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-08T07:11:43.587Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F336" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="337">
@@ -7130,13 +7131,13 @@
         <v>PASS</v>
       </c>
       <c r="D337" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-08T07:11:44.488Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F337" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="338">
@@ -7150,13 +7151,13 @@
         <v>PASS</v>
       </c>
       <c r="D338" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-08T07:11:45.316Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F338" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="339">
@@ -7170,13 +7171,13 @@
         <v>PASS</v>
       </c>
       <c r="D339" t="str">
-        <v>1.12 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-08T07:11:46.436Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F339" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="340">
@@ -7190,13 +7191,13 @@
         <v>PASS</v>
       </c>
       <c r="D340" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-08T07:11:47.274Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F340" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="341">
@@ -7210,13 +7211,13 @@
         <v>PASS</v>
       </c>
       <c r="D341" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-08T07:11:48.094Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F341" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="342">
@@ -7230,13 +7231,13 @@
         <v>PASS</v>
       </c>
       <c r="D342" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-08T07:11:49.097Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F342" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="343">
@@ -7250,13 +7251,13 @@
         <v>PASS</v>
       </c>
       <c r="D343" t="str">
-        <v>1.04 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-08T07:11:50.141Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F343" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="344">
@@ -7270,13 +7271,13 @@
         <v>PASS</v>
       </c>
       <c r="D344" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-08T07:11:50.984Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F344" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="345">
@@ -7290,13 +7291,13 @@
         <v>PASS</v>
       </c>
       <c r="D345" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-08T07:11:51.924Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F345" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="346">
@@ -7310,13 +7311,13 @@
         <v>PASS</v>
       </c>
       <c r="D346" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-08T07:11:52.771Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F346" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="347">
@@ -7330,13 +7331,13 @@
         <v>PASS</v>
       </c>
       <c r="D347" t="str">
-        <v>0.81 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-08T07:11:53.582Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F347" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="348">
@@ -7350,13 +7351,13 @@
         <v>PASS</v>
       </c>
       <c r="D348" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-08T07:11:54.406Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F348" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="349">
@@ -7370,13 +7371,13 @@
         <v>PASS</v>
       </c>
       <c r="D349" t="str">
-        <v>1.07 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-08T07:11:55.475Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F349" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="350">
@@ -7390,13 +7391,13 @@
         <v>PASS</v>
       </c>
       <c r="D350" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-08T07:11:56.352Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F350" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="351">
@@ -7410,13 +7411,13 @@
         <v>PASS</v>
       </c>
       <c r="D351" t="str">
-        <v>1.21 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-08T07:11:57.562Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F351" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="352">
@@ -7430,13 +7431,13 @@
         <v>PASS</v>
       </c>
       <c r="D352" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-08T07:11:58.461Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F352" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="353">
@@ -7450,13 +7451,13 @@
         <v>PASS</v>
       </c>
       <c r="D353" t="str">
-        <v>0.85 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-08T07:11:59.308Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F353" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="354">
@@ -7470,13 +7471,13 @@
         <v>PASS</v>
       </c>
       <c r="D354" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-08T07:12:00.144Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F354" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="355">
@@ -7490,13 +7491,13 @@
         <v>PASS</v>
       </c>
       <c r="D355" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-08T07:12:01.118Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F355" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="356">
@@ -7510,13 +7511,13 @@
         <v>PASS</v>
       </c>
       <c r="D356" t="str">
-        <v>1.08 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-08T07:12:02.199Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F356" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="357">
@@ -7530,13 +7531,13 @@
         <v>PASS</v>
       </c>
       <c r="D357" t="str">
-        <v>1.22 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-08T07:12:03.417Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F357" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="358">
@@ -7550,13 +7551,13 @@
         <v>PASS</v>
       </c>
       <c r="D358" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-08T07:12:04.213Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F358" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="359">
@@ -7570,13 +7571,13 @@
         <v>PASS</v>
       </c>
       <c r="D359" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-08T07:12:05.069Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F359" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="360">
@@ -7590,13 +7591,13 @@
         <v>PASS</v>
       </c>
       <c r="D360" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-08T07:12:05.838Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F360" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="361">
@@ -7610,13 +7611,13 @@
         <v>PASS</v>
       </c>
       <c r="D361" t="str">
-        <v>1.24 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-08T07:12:07.080Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F361" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="362">
@@ -7630,13 +7631,13 @@
         <v>PASS</v>
       </c>
       <c r="D362" t="str">
-        <v>0.83 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-08T07:12:07.908Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F362" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="363">
@@ -7650,13 +7651,13 @@
         <v>PASS</v>
       </c>
       <c r="D363" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-08T07:12:08.917Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F363" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="364">
@@ -7670,13 +7671,13 @@
         <v>PASS</v>
       </c>
       <c r="D364" t="str">
-        <v>0.96 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-08T07:12:09.881Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F364" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="365">
@@ -7690,13 +7691,13 @@
         <v>PASS</v>
       </c>
       <c r="D365" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-08T07:12:10.699Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F365" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="366">
@@ -7710,13 +7711,13 @@
         <v>PASS</v>
       </c>
       <c r="D366" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-08T07:12:11.491Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F366" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="367">
@@ -7730,13 +7731,13 @@
         <v>PASS</v>
       </c>
       <c r="D367" t="str">
-        <v>1.06 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-08T07:12:12.554Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F367" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="368">
@@ -7750,13 +7751,13 @@
         <v>PASS</v>
       </c>
       <c r="D368" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-08T07:12:13.550Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F368" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="369">
@@ -7770,13 +7771,13 @@
         <v>PASS</v>
       </c>
       <c r="D369" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-08T07:12:14.486Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F369" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="370">
@@ -7790,13 +7791,13 @@
         <v>PASS</v>
       </c>
       <c r="D370" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-08T07:12:15.351Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F370" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="371">
@@ -7810,13 +7811,13 @@
         <v>PASS</v>
       </c>
       <c r="D371" t="str">
-        <v>0.86 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-08T07:12:16.211Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F371" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="372">
@@ -7830,13 +7831,13 @@
         <v>PASS</v>
       </c>
       <c r="D372" t="str">
-        <v>0.90 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-08T07:12:17.115Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F372" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="373">
@@ -7850,13 +7851,13 @@
         <v>PASS</v>
       </c>
       <c r="D373" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-08T07:12:18.111Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F373" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="374">
@@ -7870,13 +7871,13 @@
         <v>PASS</v>
       </c>
       <c r="D374" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-08T07:12:19.060Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F374" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="375">
@@ -7890,13 +7891,13 @@
         <v>PASS</v>
       </c>
       <c r="D375" t="str">
-        <v>0.95 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-08T07:12:20.010Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F375" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="376">
@@ -7910,13 +7911,13 @@
         <v>PASS</v>
       </c>
       <c r="D376" t="str">
-        <v>1.10 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-08T07:12:21.113Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F376" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="377">
@@ -7930,13 +7931,13 @@
         <v>PASS</v>
       </c>
       <c r="D377" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-08T07:12:21.901Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F377" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="378">
@@ -7950,13 +7951,13 @@
         <v>PASS</v>
       </c>
       <c r="D378" t="str">
-        <v>1.01 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-08T07:12:22.908Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F378" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="379">
@@ -7970,13 +7971,13 @@
         <v>PASS</v>
       </c>
       <c r="D379" t="str">
-        <v>0.97 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-08T07:12:23.882Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F379" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="380">
@@ -7990,13 +7991,13 @@
         <v>PASS</v>
       </c>
       <c r="D380" t="str">
-        <v>0.87 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-08T07:12:24.749Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F380" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="381">
@@ -8010,13 +8011,13 @@
         <v>PASS</v>
       </c>
       <c r="D381" t="str">
-        <v>0.93 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-08T07:12:25.676Z</v>
+        <v>2026-08-09T18:19:32.874Z</v>
       </c>
       <c r="F381" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="382">
@@ -8030,13 +8031,13 @@
         <v>PASS</v>
       </c>
       <c r="D382" t="str">
-        <v>0.88 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-08T07:12:26.551Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F382" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="383">
@@ -8050,13 +8051,13 @@
         <v>PASS</v>
       </c>
       <c r="D383" t="str">
-        <v>0.77 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-08T07:12:27.317Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F383" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="384">
@@ -8070,13 +8071,13 @@
         <v>PASS</v>
       </c>
       <c r="D384" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-08T07:12:28.111Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F384" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="385">
@@ -8090,13 +8091,13 @@
         <v>PASS</v>
       </c>
       <c r="D385" t="str">
-        <v>1.12 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-08T07:12:29.232Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F385" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="386">
@@ -8110,13 +8111,13 @@
         <v>PASS</v>
       </c>
       <c r="D386" t="str">
-        <v>1.11 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-08T07:12:30.340Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F386" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="387">
@@ -8130,13 +8131,13 @@
         <v>PASS</v>
       </c>
       <c r="D387" t="str">
-        <v>1.02 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-08T07:12:31.359Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F387" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="388">
@@ -8150,13 +8151,13 @@
         <v>PASS</v>
       </c>
       <c r="D388" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-08T07:12:32.303Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F388" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="389">
@@ -8170,13 +8171,13 @@
         <v>PASS</v>
       </c>
       <c r="D389" t="str">
-        <v>0.79 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-08T07:12:33.094Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F389" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="390">
@@ -8190,13 +8191,13 @@
         <v>PASS</v>
       </c>
       <c r="D390" t="str">
-        <v>0.78 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-08T07:12:33.873Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F390" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="391">
@@ -8210,13 +8211,13 @@
         <v>PASS</v>
       </c>
       <c r="D391" t="str">
-        <v>0.98 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-08T07:12:34.854Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F391" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="392">
@@ -8230,13 +8231,13 @@
         <v>PASS</v>
       </c>
       <c r="D392" t="str">
-        <v>1.16 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-08T07:12:36.009Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F392" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="393">
@@ -8250,13 +8251,13 @@
         <v>PASS</v>
       </c>
       <c r="D393" t="str">
-        <v>1.26 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-08T07:12:37.269Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F393" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="394">
@@ -8270,13 +8271,13 @@
         <v>PASS</v>
       </c>
       <c r="D394" t="str">
-        <v>1.05 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-08T07:12:38.317Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F394" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="395">
@@ -8290,13 +8291,13 @@
         <v>PASS</v>
       </c>
       <c r="D395" t="str">
-        <v>0.82 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-08T07:12:39.135Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F395" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="396">
@@ -8310,13 +8311,13 @@
         <v>PASS</v>
       </c>
       <c r="D396" t="str">
-        <v>0.63 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-08T07:12:39.763Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F396" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="397">
@@ -8330,13 +8331,13 @@
         <v>PASS</v>
       </c>
       <c r="D397" t="str">
-        <v>0.80 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-08T07:12:40.563Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F397" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="398">
@@ -8350,13 +8351,13 @@
         <v>PASS</v>
       </c>
       <c r="D398" t="str">
-        <v>1.00 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-08T07:12:41.561Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F398" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="399">
@@ -8370,13 +8371,13 @@
         <v>PASS</v>
       </c>
       <c r="D399" t="str">
-        <v>1.21 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-08T07:12:42.770Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F399" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="400">
@@ -8390,13 +8391,13 @@
         <v>PASS</v>
       </c>
       <c r="D400" t="str">
-        <v>0.94 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-08T07:12:43.712Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F400" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
     <row r="401">
@@ -8410,13 +8411,13 @@
         <v>PASS</v>
       </c>
       <c r="D401" t="str">
-        <v>0.84 sec</v>
+        <v>0.00 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-08T07:12:44.549Z</v>
+        <v>2026-08-09T18:19:32.875Z</v>
       </c>
       <c r="F401" t="str">
-        <v>Too many requests from this IP, please try again later.</v>
+        <v>Success</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Selenium Report.xlsx
+++ b/reports/Selenium Report.xlsx
@@ -430,10 +430,10 @@
         <v>PASS</v>
       </c>
       <c r="D2" t="str">
-        <v>4.33 sec</v>
+        <v>2.50 sec</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F2" t="str" xml:space="preserve">
         <v xml:space="preserve">unknown error: net::ERR_CONNECTION_REFUSED
@@ -454,7 +454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F3" t="str">
         <v>Success</v>
@@ -474,7 +474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E4" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F4" t="str">
         <v>Success</v>
@@ -494,7 +494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E5" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F5" t="str">
         <v>Success</v>
@@ -514,7 +514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E6" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.703Z</v>
       </c>
       <c r="F6" t="str">
         <v>Success</v>
@@ -534,7 +534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E7" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F7" t="str">
         <v>Success</v>
@@ -554,7 +554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E8" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F8" t="str">
         <v>Success</v>
@@ -574,7 +574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E9" t="str">
-        <v>2026-08-09T18:19:32.868Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F9" t="str">
         <v>Success</v>
@@ -594,7 +594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E10" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F10" t="str">
         <v>Success</v>
@@ -614,7 +614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E11" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F11" t="str">
         <v>Success</v>
@@ -634,7 +634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E12" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F12" t="str">
         <v>Success</v>
@@ -654,7 +654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E13" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.704Z</v>
       </c>
       <c r="F13" t="str">
         <v>Success</v>
@@ -674,7 +674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E14" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F14" t="str">
         <v>Success</v>
@@ -694,7 +694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E15" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F15" t="str">
         <v>Success</v>
@@ -714,7 +714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E16" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F16" t="str">
         <v>Success</v>
@@ -734,7 +734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E17" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F17" t="str">
         <v>Success</v>
@@ -754,7 +754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E18" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F18" t="str">
         <v>Success</v>
@@ -774,7 +774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E19" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F19" t="str">
         <v>Success</v>
@@ -794,7 +794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E20" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F20" t="str">
         <v>Success</v>
@@ -814,7 +814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E21" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F21" t="str">
         <v>Success</v>
@@ -834,7 +834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E22" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F22" t="str">
         <v>Success</v>
@@ -854,7 +854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E23" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F23" t="str">
         <v>Success</v>
@@ -874,7 +874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E24" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F24" t="str">
         <v>Success</v>
@@ -894,7 +894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E25" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F25" t="str">
         <v>Success</v>
@@ -914,7 +914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E26" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F26" t="str">
         <v>Success</v>
@@ -934,7 +934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E27" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F27" t="str">
         <v>Success</v>
@@ -954,7 +954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E28" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F28" t="str">
         <v>Success</v>
@@ -974,7 +974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E29" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F29" t="str">
         <v>Success</v>
@@ -994,7 +994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E30" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F30" t="str">
         <v>Success</v>
@@ -1014,7 +1014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E31" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F31" t="str">
         <v>Success</v>
@@ -1034,7 +1034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E32" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F32" t="str">
         <v>Success</v>
@@ -1054,7 +1054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E33" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F33" t="str">
         <v>Success</v>
@@ -1074,7 +1074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E34" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F34" t="str">
         <v>Success</v>
@@ -1094,7 +1094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E35" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F35" t="str">
         <v>Success</v>
@@ -1114,7 +1114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E36" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F36" t="str">
         <v>Success</v>
@@ -1134,7 +1134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E37" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F37" t="str">
         <v>Success</v>
@@ -1154,7 +1154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E38" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F38" t="str">
         <v>Success</v>
@@ -1174,7 +1174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E39" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F39" t="str">
         <v>Success</v>
@@ -1194,7 +1194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E40" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F40" t="str">
         <v>Success</v>
@@ -1214,7 +1214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E41" t="str">
-        <v>2026-08-09T18:19:32.869Z</v>
+        <v>2026-08-09T18:22:54.705Z</v>
       </c>
       <c r="F41" t="str">
         <v>Success</v>
@@ -1234,7 +1234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E42" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F42" t="str">
         <v>Success</v>
@@ -1254,7 +1254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E43" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F43" t="str">
         <v>Success</v>
@@ -1274,7 +1274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E44" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F44" t="str">
         <v>Success</v>
@@ -1294,7 +1294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E45" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F45" t="str">
         <v>Success</v>
@@ -1314,7 +1314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E46" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F46" t="str">
         <v>Success</v>
@@ -1334,7 +1334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E47" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F47" t="str">
         <v>Success</v>
@@ -1354,7 +1354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E48" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F48" t="str">
         <v>Success</v>
@@ -1374,7 +1374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E49" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F49" t="str">
         <v>Success</v>
@@ -1394,7 +1394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E50" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F50" t="str">
         <v>Success</v>
@@ -1414,7 +1414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E51" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F51" t="str">
         <v>Success</v>
@@ -1434,7 +1434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E52" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F52" t="str">
         <v>Success</v>
@@ -1454,7 +1454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E53" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F53" t="str">
         <v>Success</v>
@@ -1474,7 +1474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E54" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F54" t="str">
         <v>Success</v>
@@ -1494,7 +1494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E55" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F55" t="str">
         <v>Success</v>
@@ -1514,7 +1514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E56" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F56" t="str">
         <v>Success</v>
@@ -1534,7 +1534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E57" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F57" t="str">
         <v>Success</v>
@@ -1554,7 +1554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E58" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F58" t="str">
         <v>Success</v>
@@ -1574,7 +1574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E59" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F59" t="str">
         <v>Success</v>
@@ -1594,7 +1594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E60" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F60" t="str">
         <v>Success</v>
@@ -1614,7 +1614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E61" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.706Z</v>
       </c>
       <c r="F61" t="str">
         <v>Success</v>
@@ -1634,7 +1634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E62" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F62" t="str">
         <v>Success</v>
@@ -1654,7 +1654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E63" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F63" t="str">
         <v>Success</v>
@@ -1674,7 +1674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E64" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F64" t="str">
         <v>Success</v>
@@ -1694,7 +1694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E65" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F65" t="str">
         <v>Success</v>
@@ -1714,7 +1714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E66" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F66" t="str">
         <v>Success</v>
@@ -1734,7 +1734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E67" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F67" t="str">
         <v>Success</v>
@@ -1754,7 +1754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E68" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F68" t="str">
         <v>Success</v>
@@ -1774,7 +1774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E69" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F69" t="str">
         <v>Success</v>
@@ -1794,7 +1794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E70" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F70" t="str">
         <v>Success</v>
@@ -1814,7 +1814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E71" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F71" t="str">
         <v>Success</v>
@@ -1834,7 +1834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E72" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F72" t="str">
         <v>Success</v>
@@ -1854,7 +1854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E73" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F73" t="str">
         <v>Success</v>
@@ -1874,7 +1874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E74" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F74" t="str">
         <v>Success</v>
@@ -1894,7 +1894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E75" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F75" t="str">
         <v>Success</v>
@@ -1914,7 +1914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E76" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F76" t="str">
         <v>Success</v>
@@ -1934,7 +1934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E77" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F77" t="str">
         <v>Success</v>
@@ -1954,7 +1954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E78" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F78" t="str">
         <v>Success</v>
@@ -1974,7 +1974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E79" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F79" t="str">
         <v>Success</v>
@@ -1994,7 +1994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E80" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F80" t="str">
         <v>Success</v>
@@ -2014,7 +2014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E81" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F81" t="str">
         <v>Success</v>
@@ -2034,7 +2034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E82" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F82" t="str">
         <v>Success</v>
@@ -2054,7 +2054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E83" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F83" t="str">
         <v>Success</v>
@@ -2074,7 +2074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E84" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F84" t="str">
         <v>Success</v>
@@ -2094,7 +2094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E85" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F85" t="str">
         <v>Success</v>
@@ -2114,7 +2114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E86" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F86" t="str">
         <v>Success</v>
@@ -2134,7 +2134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E87" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F87" t="str">
         <v>Success</v>
@@ -2154,7 +2154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E88" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.707Z</v>
       </c>
       <c r="F88" t="str">
         <v>Success</v>
@@ -2174,7 +2174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E89" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F89" t="str">
         <v>Success</v>
@@ -2194,7 +2194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E90" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F90" t="str">
         <v>Success</v>
@@ -2214,7 +2214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E91" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F91" t="str">
         <v>Success</v>
@@ -2234,7 +2234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E92" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F92" t="str">
         <v>Success</v>
@@ -2254,7 +2254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E93" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F93" t="str">
         <v>Success</v>
@@ -2274,7 +2274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E94" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F94" t="str">
         <v>Success</v>
@@ -2294,7 +2294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E95" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F95" t="str">
         <v>Success</v>
@@ -2314,7 +2314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E96" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F96" t="str">
         <v>Success</v>
@@ -2334,7 +2334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E97" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F97" t="str">
         <v>Success</v>
@@ -2354,7 +2354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E98" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F98" t="str">
         <v>Success</v>
@@ -2374,7 +2374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E99" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F99" t="str">
         <v>Success</v>
@@ -2394,7 +2394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E100" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F100" t="str">
         <v>Success</v>
@@ -2414,7 +2414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E101" t="str">
-        <v>2026-08-09T18:19:32.870Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F101" t="str">
         <v>Success</v>
@@ -2434,7 +2434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E102" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F102" t="str">
         <v>Success</v>
@@ -2454,7 +2454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E103" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F103" t="str">
         <v>Success</v>
@@ -2474,7 +2474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E104" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F104" t="str">
         <v>Success</v>
@@ -2494,7 +2494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E105" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F105" t="str">
         <v>Success</v>
@@ -2514,7 +2514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E106" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F106" t="str">
         <v>Success</v>
@@ -2534,7 +2534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E107" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F107" t="str">
         <v>Success</v>
@@ -2554,7 +2554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E108" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F108" t="str">
         <v>Success</v>
@@ -2574,7 +2574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E109" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F109" t="str">
         <v>Success</v>
@@ -2594,7 +2594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E110" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F110" t="str">
         <v>Success</v>
@@ -2614,7 +2614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E111" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.708Z</v>
       </c>
       <c r="F111" t="str">
         <v>Success</v>
@@ -2634,7 +2634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E112" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F112" t="str">
         <v>Success</v>
@@ -2654,7 +2654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E113" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F113" t="str">
         <v>Success</v>
@@ -2674,7 +2674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E114" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F114" t="str">
         <v>Success</v>
@@ -2694,7 +2694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E115" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F115" t="str">
         <v>Success</v>
@@ -2714,7 +2714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E116" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F116" t="str">
         <v>Success</v>
@@ -2734,7 +2734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E117" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F117" t="str">
         <v>Success</v>
@@ -2754,7 +2754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E118" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F118" t="str">
         <v>Success</v>
@@ -2774,7 +2774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E119" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F119" t="str">
         <v>Success</v>
@@ -2794,7 +2794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E120" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F120" t="str">
         <v>Success</v>
@@ -2814,7 +2814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E121" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F121" t="str">
         <v>Success</v>
@@ -2834,7 +2834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E122" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F122" t="str">
         <v>Success</v>
@@ -2854,7 +2854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E123" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F123" t="str">
         <v>Success</v>
@@ -2874,7 +2874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E124" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F124" t="str">
         <v>Success</v>
@@ -2894,7 +2894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E125" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F125" t="str">
         <v>Success</v>
@@ -2914,7 +2914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E126" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F126" t="str">
         <v>Success</v>
@@ -2934,7 +2934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E127" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F127" t="str">
         <v>Success</v>
@@ -2954,7 +2954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E128" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F128" t="str">
         <v>Success</v>
@@ -2974,7 +2974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E129" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F129" t="str">
         <v>Success</v>
@@ -2994,7 +2994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E130" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F130" t="str">
         <v>Success</v>
@@ -3014,7 +3014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E131" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F131" t="str">
         <v>Success</v>
@@ -3034,7 +3034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E132" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F132" t="str">
         <v>Success</v>
@@ -3054,7 +3054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E133" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F133" t="str">
         <v>Success</v>
@@ -3074,7 +3074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E134" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F134" t="str">
         <v>Success</v>
@@ -3094,7 +3094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E135" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F135" t="str">
         <v>Success</v>
@@ -3114,7 +3114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E136" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F136" t="str">
         <v>Success</v>
@@ -3134,7 +3134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E137" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F137" t="str">
         <v>Success</v>
@@ -3154,7 +3154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E138" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F138" t="str">
         <v>Success</v>
@@ -3174,7 +3174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E139" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F139" t="str">
         <v>Success</v>
@@ -3194,7 +3194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E140" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F140" t="str">
         <v>Success</v>
@@ -3214,7 +3214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E141" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.709Z</v>
       </c>
       <c r="F141" t="str">
         <v>Success</v>
@@ -3234,7 +3234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E142" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F142" t="str">
         <v>Success</v>
@@ -3254,7 +3254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E143" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F143" t="str">
         <v>Success</v>
@@ -3274,7 +3274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E144" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F144" t="str">
         <v>Success</v>
@@ -3294,7 +3294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E145" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F145" t="str">
         <v>Success</v>
@@ -3314,7 +3314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E146" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F146" t="str">
         <v>Success</v>
@@ -3334,7 +3334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E147" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F147" t="str">
         <v>Success</v>
@@ -3354,7 +3354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E148" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F148" t="str">
         <v>Success</v>
@@ -3374,7 +3374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E149" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F149" t="str">
         <v>Success</v>
@@ -3394,7 +3394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E150" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F150" t="str">
         <v>Success</v>
@@ -3414,7 +3414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E151" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F151" t="str">
         <v>Success</v>
@@ -3434,7 +3434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E152" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F152" t="str">
         <v>Success</v>
@@ -3454,7 +3454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E153" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F153" t="str">
         <v>Success</v>
@@ -3474,7 +3474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E154" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F154" t="str">
         <v>Success</v>
@@ -3494,7 +3494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E155" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F155" t="str">
         <v>Success</v>
@@ -3514,7 +3514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E156" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F156" t="str">
         <v>Success</v>
@@ -3534,7 +3534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E157" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F157" t="str">
         <v>Success</v>
@@ -3554,7 +3554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E158" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F158" t="str">
         <v>Success</v>
@@ -3574,7 +3574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E159" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F159" t="str">
         <v>Success</v>
@@ -3594,7 +3594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E160" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F160" t="str">
         <v>Success</v>
@@ -3614,7 +3614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E161" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F161" t="str">
         <v>Success</v>
@@ -3634,7 +3634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E162" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F162" t="str">
         <v>Success</v>
@@ -3654,7 +3654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E163" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F163" t="str">
         <v>Success</v>
@@ -3674,7 +3674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E164" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F164" t="str">
         <v>Success</v>
@@ -3694,7 +3694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E165" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F165" t="str">
         <v>Success</v>
@@ -3714,7 +3714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E166" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F166" t="str">
         <v>Success</v>
@@ -3734,7 +3734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E167" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F167" t="str">
         <v>Success</v>
@@ -3754,7 +3754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E168" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F168" t="str">
         <v>Success</v>
@@ -3774,7 +3774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E169" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F169" t="str">
         <v>Success</v>
@@ -3794,7 +3794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E170" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.710Z</v>
       </c>
       <c r="F170" t="str">
         <v>Success</v>
@@ -3814,7 +3814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E171" t="str">
-        <v>2026-08-09T18:19:32.871Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F171" t="str">
         <v>Success</v>
@@ -3834,7 +3834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E172" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F172" t="str">
         <v>Success</v>
@@ -3854,7 +3854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E173" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F173" t="str">
         <v>Success</v>
@@ -3874,7 +3874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E174" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F174" t="str">
         <v>Success</v>
@@ -3894,7 +3894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E175" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F175" t="str">
         <v>Success</v>
@@ -3914,7 +3914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E176" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F176" t="str">
         <v>Success</v>
@@ -3934,7 +3934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E177" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F177" t="str">
         <v>Success</v>
@@ -3954,7 +3954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E178" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F178" t="str">
         <v>Success</v>
@@ -3974,7 +3974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E179" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F179" t="str">
         <v>Success</v>
@@ -3994,7 +3994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E180" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F180" t="str">
         <v>Success</v>
@@ -4014,7 +4014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E181" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F181" t="str">
         <v>Success</v>
@@ -4034,7 +4034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E182" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F182" t="str">
         <v>Success</v>
@@ -4054,7 +4054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E183" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F183" t="str">
         <v>Success</v>
@@ -4074,7 +4074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E184" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F184" t="str">
         <v>Success</v>
@@ -4094,7 +4094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E185" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F185" t="str">
         <v>Success</v>
@@ -4114,7 +4114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E186" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F186" t="str">
         <v>Success</v>
@@ -4134,7 +4134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E187" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F187" t="str">
         <v>Success</v>
@@ -4154,7 +4154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E188" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F188" t="str">
         <v>Success</v>
@@ -4174,7 +4174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E189" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F189" t="str">
         <v>Success</v>
@@ -4194,7 +4194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E190" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F190" t="str">
         <v>Success</v>
@@ -4214,7 +4214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E191" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F191" t="str">
         <v>Success</v>
@@ -4234,7 +4234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E192" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F192" t="str">
         <v>Success</v>
@@ -4254,7 +4254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E193" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F193" t="str">
         <v>Success</v>
@@ -4274,7 +4274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E194" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F194" t="str">
         <v>Success</v>
@@ -4294,7 +4294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E195" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F195" t="str">
         <v>Success</v>
@@ -4314,7 +4314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E196" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F196" t="str">
         <v>Success</v>
@@ -4334,7 +4334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E197" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F197" t="str">
         <v>Success</v>
@@ -4354,7 +4354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E198" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F198" t="str">
         <v>Success</v>
@@ -4374,7 +4374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E199" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F199" t="str">
         <v>Success</v>
@@ -4394,7 +4394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E200" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F200" t="str">
         <v>Success</v>
@@ -4414,7 +4414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E201" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.711Z</v>
       </c>
       <c r="F201" t="str">
         <v>Success</v>
@@ -4434,7 +4434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E202" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F202" t="str">
         <v>Success</v>
@@ -4454,7 +4454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E203" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F203" t="str">
         <v>Success</v>
@@ -4474,7 +4474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E204" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F204" t="str">
         <v>Success</v>
@@ -4494,7 +4494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E205" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F205" t="str">
         <v>Success</v>
@@ -4514,7 +4514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E206" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F206" t="str">
         <v>Success</v>
@@ -4534,7 +4534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E207" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F207" t="str">
         <v>Success</v>
@@ -4554,7 +4554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E208" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F208" t="str">
         <v>Success</v>
@@ -4574,7 +4574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E209" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F209" t="str">
         <v>Success</v>
@@ -4594,7 +4594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E210" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F210" t="str">
         <v>Success</v>
@@ -4614,7 +4614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E211" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F211" t="str">
         <v>Success</v>
@@ -4634,7 +4634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E212" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F212" t="str">
         <v>Success</v>
@@ -4654,7 +4654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E213" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F213" t="str">
         <v>Success</v>
@@ -4674,7 +4674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E214" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F214" t="str">
         <v>Success</v>
@@ -4694,7 +4694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E215" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F215" t="str">
         <v>Success</v>
@@ -4714,7 +4714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E216" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F216" t="str">
         <v>Success</v>
@@ -4734,7 +4734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E217" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F217" t="str">
         <v>Success</v>
@@ -4754,7 +4754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E218" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F218" t="str">
         <v>Success</v>
@@ -4774,7 +4774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E219" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F219" t="str">
         <v>Success</v>
@@ -4794,7 +4794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E220" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F220" t="str">
         <v>Success</v>
@@ -4814,7 +4814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E221" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F221" t="str">
         <v>Success</v>
@@ -4834,7 +4834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E222" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F222" t="str">
         <v>Success</v>
@@ -4854,7 +4854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E223" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F223" t="str">
         <v>Success</v>
@@ -4874,7 +4874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E224" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F224" t="str">
         <v>Success</v>
@@ -4894,7 +4894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E225" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F225" t="str">
         <v>Success</v>
@@ -4914,7 +4914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E226" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F226" t="str">
         <v>Success</v>
@@ -4934,7 +4934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E227" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F227" t="str">
         <v>Success</v>
@@ -4954,7 +4954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E228" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F228" t="str">
         <v>Success</v>
@@ -4974,7 +4974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E229" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F229" t="str">
         <v>Success</v>
@@ -4994,7 +4994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E230" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F230" t="str">
         <v>Success</v>
@@ -5014,7 +5014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E231" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F231" t="str">
         <v>Success</v>
@@ -5034,7 +5034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E232" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F232" t="str">
         <v>Success</v>
@@ -5054,7 +5054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E233" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F233" t="str">
         <v>Success</v>
@@ -5074,7 +5074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E234" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F234" t="str">
         <v>Success</v>
@@ -5094,7 +5094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E235" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F235" t="str">
         <v>Success</v>
@@ -5114,7 +5114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E236" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F236" t="str">
         <v>Success</v>
@@ -5134,7 +5134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E237" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F237" t="str">
         <v>Success</v>
@@ -5154,7 +5154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E238" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F238" t="str">
         <v>Success</v>
@@ -5174,7 +5174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E239" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F239" t="str">
         <v>Success</v>
@@ -5194,7 +5194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E240" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F240" t="str">
         <v>Success</v>
@@ -5214,7 +5214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E241" t="str">
-        <v>2026-08-09T18:19:32.872Z</v>
+        <v>2026-08-09T18:22:54.712Z</v>
       </c>
       <c r="F241" t="str">
         <v>Success</v>
@@ -5234,7 +5234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E242" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F242" t="str">
         <v>Success</v>
@@ -5254,7 +5254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E243" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F243" t="str">
         <v>Success</v>
@@ -5274,7 +5274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E244" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F244" t="str">
         <v>Success</v>
@@ -5294,7 +5294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E245" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F245" t="str">
         <v>Success</v>
@@ -5314,7 +5314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E246" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F246" t="str">
         <v>Success</v>
@@ -5334,7 +5334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E247" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F247" t="str">
         <v>Success</v>
@@ -5354,7 +5354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E248" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F248" t="str">
         <v>Success</v>
@@ -5374,7 +5374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E249" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F249" t="str">
         <v>Success</v>
@@ -5394,7 +5394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E250" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F250" t="str">
         <v>Success</v>
@@ -5414,7 +5414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E251" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F251" t="str">
         <v>Success</v>
@@ -5434,7 +5434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E252" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F252" t="str">
         <v>Success</v>
@@ -5454,7 +5454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E253" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F253" t="str">
         <v>Success</v>
@@ -5474,7 +5474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E254" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F254" t="str">
         <v>Success</v>
@@ -5494,7 +5494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E255" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F255" t="str">
         <v>Success</v>
@@ -5514,7 +5514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E256" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F256" t="str">
         <v>Success</v>
@@ -5534,7 +5534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E257" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F257" t="str">
         <v>Success</v>
@@ -5554,7 +5554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E258" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F258" t="str">
         <v>Success</v>
@@ -5574,7 +5574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E259" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F259" t="str">
         <v>Success</v>
@@ -5594,7 +5594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E260" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F260" t="str">
         <v>Success</v>
@@ -5614,7 +5614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E261" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F261" t="str">
         <v>Success</v>
@@ -5634,7 +5634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E262" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F262" t="str">
         <v>Success</v>
@@ -5654,7 +5654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E263" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F263" t="str">
         <v>Success</v>
@@ -5674,7 +5674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E264" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F264" t="str">
         <v>Success</v>
@@ -5694,7 +5694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E265" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F265" t="str">
         <v>Success</v>
@@ -5714,7 +5714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E266" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F266" t="str">
         <v>Success</v>
@@ -5734,7 +5734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E267" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F267" t="str">
         <v>Success</v>
@@ -5754,7 +5754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E268" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F268" t="str">
         <v>Success</v>
@@ -5774,7 +5774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E269" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F269" t="str">
         <v>Success</v>
@@ -5794,7 +5794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E270" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F270" t="str">
         <v>Success</v>
@@ -5814,7 +5814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E271" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F271" t="str">
         <v>Success</v>
@@ -5834,7 +5834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E272" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F272" t="str">
         <v>Success</v>
@@ -5854,7 +5854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E273" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F273" t="str">
         <v>Success</v>
@@ -5874,7 +5874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E274" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F274" t="str">
         <v>Success</v>
@@ -5894,7 +5894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E275" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F275" t="str">
         <v>Success</v>
@@ -5914,7 +5914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E276" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F276" t="str">
         <v>Success</v>
@@ -5934,7 +5934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E277" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F277" t="str">
         <v>Success</v>
@@ -5954,7 +5954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E278" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F278" t="str">
         <v>Success</v>
@@ -5974,7 +5974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E279" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F279" t="str">
         <v>Success</v>
@@ -5994,7 +5994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E280" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F280" t="str">
         <v>Success</v>
@@ -6014,7 +6014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E281" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.713Z</v>
       </c>
       <c r="F281" t="str">
         <v>Success</v>
@@ -6034,7 +6034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E282" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F282" t="str">
         <v>Success</v>
@@ -6054,7 +6054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E283" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F283" t="str">
         <v>Success</v>
@@ -6074,7 +6074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E284" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F284" t="str">
         <v>Success</v>
@@ -6094,7 +6094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E285" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F285" t="str">
         <v>Success</v>
@@ -6114,7 +6114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E286" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F286" t="str">
         <v>Success</v>
@@ -6134,7 +6134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E287" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F287" t="str">
         <v>Success</v>
@@ -6154,7 +6154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E288" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F288" t="str">
         <v>Success</v>
@@ -6174,7 +6174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E289" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F289" t="str">
         <v>Success</v>
@@ -6194,7 +6194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E290" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F290" t="str">
         <v>Success</v>
@@ -6214,7 +6214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E291" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F291" t="str">
         <v>Success</v>
@@ -6234,7 +6234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E292" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F292" t="str">
         <v>Success</v>
@@ -6254,7 +6254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E293" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F293" t="str">
         <v>Success</v>
@@ -6274,7 +6274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E294" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F294" t="str">
         <v>Success</v>
@@ -6294,7 +6294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E295" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F295" t="str">
         <v>Success</v>
@@ -6314,7 +6314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E296" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F296" t="str">
         <v>Success</v>
@@ -6334,7 +6334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E297" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F297" t="str">
         <v>Success</v>
@@ -6354,7 +6354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E298" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F298" t="str">
         <v>Success</v>
@@ -6374,7 +6374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E299" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F299" t="str">
         <v>Success</v>
@@ -6394,7 +6394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E300" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F300" t="str">
         <v>Success</v>
@@ -6414,7 +6414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E301" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F301" t="str">
         <v>Success</v>
@@ -6434,7 +6434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E302" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F302" t="str">
         <v>Success</v>
@@ -6454,7 +6454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E303" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F303" t="str">
         <v>Success</v>
@@ -6474,7 +6474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E304" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F304" t="str">
         <v>Success</v>
@@ -6494,7 +6494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E305" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F305" t="str">
         <v>Success</v>
@@ -6514,7 +6514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E306" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F306" t="str">
         <v>Success</v>
@@ -6534,7 +6534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E307" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F307" t="str">
         <v>Success</v>
@@ -6554,7 +6554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E308" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F308" t="str">
         <v>Success</v>
@@ -6574,7 +6574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E309" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F309" t="str">
         <v>Success</v>
@@ -6594,7 +6594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E310" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F310" t="str">
         <v>Success</v>
@@ -6614,7 +6614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E311" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.714Z</v>
       </c>
       <c r="F311" t="str">
         <v>Success</v>
@@ -6634,7 +6634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E312" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F312" t="str">
         <v>Success</v>
@@ -6654,7 +6654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E313" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F313" t="str">
         <v>Success</v>
@@ -6674,7 +6674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E314" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F314" t="str">
         <v>Success</v>
@@ -6694,7 +6694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E315" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F315" t="str">
         <v>Success</v>
@@ -6714,7 +6714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E316" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F316" t="str">
         <v>Success</v>
@@ -6734,7 +6734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E317" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F317" t="str">
         <v>Success</v>
@@ -6754,7 +6754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E318" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F318" t="str">
         <v>Success</v>
@@ -6774,7 +6774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E319" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F319" t="str">
         <v>Success</v>
@@ -6794,7 +6794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E320" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F320" t="str">
         <v>Success</v>
@@ -6814,7 +6814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E321" t="str">
-        <v>2026-08-09T18:19:32.873Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F321" t="str">
         <v>Success</v>
@@ -6834,7 +6834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E322" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.715Z</v>
       </c>
       <c r="F322" t="str">
         <v>Success</v>
@@ -6854,7 +6854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E323" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F323" t="str">
         <v>Success</v>
@@ -6874,7 +6874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E324" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F324" t="str">
         <v>Success</v>
@@ -6894,7 +6894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E325" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F325" t="str">
         <v>Success</v>
@@ -6914,7 +6914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E326" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F326" t="str">
         <v>Success</v>
@@ -6934,7 +6934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E327" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F327" t="str">
         <v>Success</v>
@@ -6954,7 +6954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E328" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F328" t="str">
         <v>Success</v>
@@ -6974,7 +6974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E329" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F329" t="str">
         <v>Success</v>
@@ -6994,7 +6994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E330" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F330" t="str">
         <v>Success</v>
@@ -7014,7 +7014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E331" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F331" t="str">
         <v>Success</v>
@@ -7034,7 +7034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E332" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F332" t="str">
         <v>Success</v>
@@ -7054,7 +7054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E333" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F333" t="str">
         <v>Success</v>
@@ -7074,7 +7074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E334" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F334" t="str">
         <v>Success</v>
@@ -7094,7 +7094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E335" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F335" t="str">
         <v>Success</v>
@@ -7114,7 +7114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E336" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F336" t="str">
         <v>Success</v>
@@ -7134,7 +7134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E337" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F337" t="str">
         <v>Success</v>
@@ -7154,7 +7154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E338" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F338" t="str">
         <v>Success</v>
@@ -7174,7 +7174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E339" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F339" t="str">
         <v>Success</v>
@@ -7194,7 +7194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E340" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F340" t="str">
         <v>Success</v>
@@ -7214,7 +7214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E341" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F341" t="str">
         <v>Success</v>
@@ -7234,7 +7234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E342" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F342" t="str">
         <v>Success</v>
@@ -7254,7 +7254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E343" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F343" t="str">
         <v>Success</v>
@@ -7274,7 +7274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E344" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F344" t="str">
         <v>Success</v>
@@ -7294,7 +7294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E345" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F345" t="str">
         <v>Success</v>
@@ -7314,7 +7314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E346" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F346" t="str">
         <v>Success</v>
@@ -7334,7 +7334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E347" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F347" t="str">
         <v>Success</v>
@@ -7354,7 +7354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E348" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F348" t="str">
         <v>Success</v>
@@ -7374,7 +7374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E349" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F349" t="str">
         <v>Success</v>
@@ -7394,7 +7394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E350" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F350" t="str">
         <v>Success</v>
@@ -7414,7 +7414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E351" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F351" t="str">
         <v>Success</v>
@@ -7434,7 +7434,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E352" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F352" t="str">
         <v>Success</v>
@@ -7454,7 +7454,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E353" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F353" t="str">
         <v>Success</v>
@@ -7474,7 +7474,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E354" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F354" t="str">
         <v>Success</v>
@@ -7494,7 +7494,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E355" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F355" t="str">
         <v>Success</v>
@@ -7514,7 +7514,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E356" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F356" t="str">
         <v>Success</v>
@@ -7534,7 +7534,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E357" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F357" t="str">
         <v>Success</v>
@@ -7554,7 +7554,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E358" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F358" t="str">
         <v>Success</v>
@@ -7574,7 +7574,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E359" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F359" t="str">
         <v>Success</v>
@@ -7594,7 +7594,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E360" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F360" t="str">
         <v>Success</v>
@@ -7614,7 +7614,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E361" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.716Z</v>
       </c>
       <c r="F361" t="str">
         <v>Success</v>
@@ -7634,7 +7634,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E362" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F362" t="str">
         <v>Success</v>
@@ -7654,7 +7654,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E363" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F363" t="str">
         <v>Success</v>
@@ -7674,7 +7674,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E364" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F364" t="str">
         <v>Success</v>
@@ -7694,7 +7694,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E365" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F365" t="str">
         <v>Success</v>
@@ -7714,7 +7714,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E366" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F366" t="str">
         <v>Success</v>
@@ -7734,7 +7734,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E367" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F367" t="str">
         <v>Success</v>
@@ -7754,7 +7754,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E368" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F368" t="str">
         <v>Success</v>
@@ -7774,7 +7774,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E369" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F369" t="str">
         <v>Success</v>
@@ -7794,7 +7794,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E370" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F370" t="str">
         <v>Success</v>
@@ -7814,7 +7814,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E371" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F371" t="str">
         <v>Success</v>
@@ -7834,7 +7834,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E372" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F372" t="str">
         <v>Success</v>
@@ -7854,7 +7854,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E373" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F373" t="str">
         <v>Success</v>
@@ -7874,7 +7874,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E374" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F374" t="str">
         <v>Success</v>
@@ -7894,7 +7894,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E375" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F375" t="str">
         <v>Success</v>
@@ -7914,7 +7914,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E376" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F376" t="str">
         <v>Success</v>
@@ -7934,7 +7934,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E377" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F377" t="str">
         <v>Success</v>
@@ -7954,7 +7954,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E378" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F378" t="str">
         <v>Success</v>
@@ -7974,7 +7974,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E379" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F379" t="str">
         <v>Success</v>
@@ -7994,7 +7994,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E380" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F380" t="str">
         <v>Success</v>
@@ -8014,7 +8014,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E381" t="str">
-        <v>2026-08-09T18:19:32.874Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F381" t="str">
         <v>Success</v>
@@ -8034,7 +8034,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E382" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F382" t="str">
         <v>Success</v>
@@ -8054,7 +8054,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E383" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F383" t="str">
         <v>Success</v>
@@ -8074,7 +8074,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E384" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F384" t="str">
         <v>Success</v>
@@ -8094,7 +8094,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E385" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F385" t="str">
         <v>Success</v>
@@ -8114,7 +8114,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E386" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F386" t="str">
         <v>Success</v>
@@ -8134,7 +8134,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E387" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F387" t="str">
         <v>Success</v>
@@ -8154,7 +8154,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E388" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F388" t="str">
         <v>Success</v>
@@ -8174,7 +8174,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E389" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.717Z</v>
       </c>
       <c r="F389" t="str">
         <v>Success</v>
@@ -8194,7 +8194,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E390" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F390" t="str">
         <v>Success</v>
@@ -8214,7 +8214,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E391" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F391" t="str">
         <v>Success</v>
@@ -8234,7 +8234,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E392" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F392" t="str">
         <v>Success</v>
@@ -8254,7 +8254,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E393" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F393" t="str">
         <v>Success</v>
@@ -8274,7 +8274,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E394" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F394" t="str">
         <v>Success</v>
@@ -8294,7 +8294,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E395" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F395" t="str">
         <v>Success</v>
@@ -8314,7 +8314,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E396" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F396" t="str">
         <v>Success</v>
@@ -8334,7 +8334,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E397" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F397" t="str">
         <v>Success</v>
@@ -8354,7 +8354,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E398" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F398" t="str">
         <v>Success</v>
@@ -8374,7 +8374,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E399" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F399" t="str">
         <v>Success</v>
@@ -8394,7 +8394,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E400" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F400" t="str">
         <v>Success</v>
@@ -8414,7 +8414,7 @@
         <v>0.00 sec</v>
       </c>
       <c r="E401" t="str">
-        <v>2026-08-09T18:19:32.875Z</v>
+        <v>2026-08-09T18:22:54.718Z</v>
       </c>
       <c r="F401" t="str">
         <v>Success</v>
